--- a/results/05_transient_transcription_output/203/203_196905_SF.JPG_stage_recalc_multi_day_tot_and_avgs.xlsx
+++ b/results/05_transient_transcription_output/203/203_196905_SF.JPG_stage_recalc_multi_day_tot_and_avgs.xlsx
@@ -125,7 +125,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -162,6 +162,30 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -778,73 +802,73 @@
         <v>186.2</v>
       </c>
       <c r="D4" s="10" t="n">
-        <v>28.8</v>
+        <v>28.2</v>
       </c>
       <c r="E4" s="10" t="n">
-        <v>19.8</v>
+        <v>20</v>
       </c>
       <c r="F4" s="10" t="n">
-        <v>24.3</v>
+        <v>24.1</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>87.8</v>
-      </c>
-      <c r="H4" s="8" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="H4" s="3" t="n">
         <v>18.2</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>1.7</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>9.9</v>
+        <v>2.9</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>20.2</v>
+        <v>2.2</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>20.1</v>
+        <v>26.1</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>83.40000000000001</v>
+        <v>23.4</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>99</v>
+        <v>9</v>
       </c>
       <c r="P4" s="3" t="n">
         <v>0.2</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>28.7</v>
+        <v>28.2</v>
       </c>
       <c r="R4" s="3" t="n">
         <v>24.1</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>0.8</v>
+        <v>27.1</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>168.9</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="U4" s="3" t="n">
         <v>12.2</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>25.2</v>
+        <v>25.8</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>22.8</v>
+        <v>2.8</v>
       </c>
       <c r="X4" s="3" t="n">
         <v>26.2</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>811.8</v>
+        <v>81.8</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>0.8</v>
+        <v>5.8</v>
       </c>
       <c r="AA4" s="3" t="inlineStr">
         <is>
@@ -860,7 +884,7 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>403.5</v>
+        <v>438.5</v>
       </c>
       <c r="D5" s="10" t="n">
         <v>32.6</v>
@@ -875,16 +899,16 @@
         <v>14.4</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>16.8</v>
+        <v>6.2</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>32.5</v>
+        <v>3.5</v>
       </c>
       <c r="J5" s="3" t="n">
         <v>5.5</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L5" s="3" t="n">
         <v>18.9</v>
@@ -893,10 +917,10 @@
         <v>18.8</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>28.6</v>
+        <v>21.6</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>99</v>
+        <v>9</v>
       </c>
       <c r="P5" s="3" t="n">
         <v>0.2</v>
@@ -911,22 +935,22 @@
         <v>27.8</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>156.6</v>
+        <v>56.6</v>
       </c>
       <c r="U5" s="3" t="n">
         <v>21.2</v>
       </c>
       <c r="V5" s="3" t="n">
-        <v>27.2</v>
+        <v>87.2</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="X5" s="8" t="n">
-        <v>27.8</v>
+        <v>24.6</v>
+      </c>
+      <c r="X5" s="3" t="n">
+        <v>2.8</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>77</v>
+        <v>2</v>
       </c>
       <c r="Z5" s="3" t="n">
         <v>8.199999999999999</v>
@@ -945,28 +969,28 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>422.3</v>
+        <v>22.3</v>
       </c>
       <c r="D6" s="10" t="n">
         <v>34.2</v>
       </c>
       <c r="E6" s="10" t="n">
-        <v>18.8</v>
+        <v>18.2</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>26.5</v>
-      </c>
-      <c r="G6" s="10" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="G6" s="3" t="n">
         <v>15.4</v>
       </c>
       <c r="H6" s="3" t="n">
         <v>17.2</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>11.6</v>
+        <v>4.6</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>7.2</v>
+        <v>0.7</v>
       </c>
       <c r="K6" s="3" t="n">
         <v>0</v>
@@ -974,14 +998,14 @@
       <c r="L6" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="M6" s="3" t="n">
-        <v>20</v>
+      <c r="M6" s="8" t="n">
+        <v>66</v>
       </c>
       <c r="N6" s="3" t="n">
         <v>23.3</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="P6" s="3" t="n">
         <v>0</v>
@@ -996,13 +1020,13 @@
         <v>28.6</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>55.2</v>
+        <v>51.8</v>
       </c>
       <c r="U6" s="3" t="n">
         <v>20.7</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>28.7</v>
+        <v>28.2</v>
       </c>
       <c r="W6" s="3" t="n">
         <v>23.7</v>
@@ -1014,7 +1038,7 @@
         <v>66.40000000000001</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>4.1</v>
+        <v>13.2</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
@@ -1030,16 +1054,16 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>4335.1</v>
+        <v>4778.5</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>34.7</v>
+        <v>24.7</v>
       </c>
       <c r="E7" s="10" t="n">
-        <v>19.3</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="G7" s="10" t="n">
         <v>15.4</v>
@@ -1048,10 +1072,10 @@
         <v>18.2</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>43.3</v>
+        <v>2.3</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>1.9</v>
+        <v>7.9</v>
       </c>
       <c r="K7" s="3" t="n">
         <v>0</v>
@@ -1060,16 +1084,16 @@
         <v>20.1</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>20.1</v>
+        <v>2.1</v>
       </c>
       <c r="N7" s="8" t="n">
         <v>35.1</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q7" s="3" t="n">
         <v>34.2</v>
@@ -1078,7 +1102,7 @@
         <v>25.5</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>27.1</v>
+        <v>22.1</v>
       </c>
       <c r="T7" s="3" t="n">
         <v>50.6</v>
@@ -1090,16 +1114,16 @@
         <v>29.5</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>24.4</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="X7" s="3" t="n">
-        <v>27.3</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="Y7" s="3" t="n">
         <v>66.2</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>13.8</v>
+        <v>438.5</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1115,28 +1139,28 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>299</v>
+        <v>299.6</v>
       </c>
       <c r="D8" s="10" t="n">
         <v>34.41</v>
       </c>
       <c r="E8" s="10" t="n">
-        <v>20.8</v>
+        <v>20.6</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>27.6</v>
-      </c>
-      <c r="G8" s="3" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="G8" s="10" t="n">
         <v>14</v>
       </c>
-      <c r="H8" s="8" t="n">
-        <v>119</v>
+      <c r="H8" s="3" t="n">
+        <v>19</v>
       </c>
       <c r="I8" s="3" t="n">
         <v>2</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>0.4</v>
+        <v>4</v>
       </c>
       <c r="K8" s="3" t="n">
         <v>30.9</v>
@@ -1154,28 +1178,28 @@
         <v>96.5</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="Q8" s="8" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="Q8" s="3" t="n">
         <v>21.4</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>21.2</v>
+        <v>2.2</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>25.1</v>
+        <v>23.1</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>98</v>
+        <v>28</v>
       </c>
       <c r="U8" s="3" t="n">
-        <v>10.4</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="V8" s="3" t="n">
-        <v>22.2</v>
+        <v>2.2</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>21.9</v>
+        <v>24.9</v>
       </c>
       <c r="X8" s="3" t="n">
         <v>26.1</v>
@@ -1184,7 +1208,7 @@
         <v>97.40000000000001</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>0.6</v>
+        <v>26.6</v>
       </c>
       <c r="AA8" s="3" t="inlineStr">
         <is>
@@ -1206,7 +1230,7 @@
         <v>164.8</v>
       </c>
       <c r="E9" s="10" t="n">
-        <v>96.90000000000001</v>
+        <v>96.8</v>
       </c>
       <c r="F9" s="10" t="n">
         <v>130.8</v>
@@ -1224,22 +1248,22 @@
         <v>27.5</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>30.9</v>
+        <v>3.9</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>100.2</v>
+        <v>16.2</v>
       </c>
       <c r="M9" s="3" t="n">
         <v>99.59999999999999</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>115.8</v>
+        <v>15.8</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>1894.5</v>
+        <v>494.5</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>11.2</v>
+        <v>1.2</v>
       </c>
       <c r="Q9" s="3" t="n">
         <v>149.6</v>
@@ -1251,7 +1275,7 @@
         <v>135.7</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>229.9</v>
+        <v>329.9</v>
       </c>
       <c r="U9" s="3" t="n">
         <v>81</v>
@@ -1268,7 +1292,13 @@
       <c r="Y9" s="3" t="n">
         <v>388.8</v>
       </c>
-      <c r="Z9" s="3" t="n"/>
+      <c r="Z9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">222424272
+777
+</t>
+        </is>
+      </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -1298,7 +1328,7 @@
         <v>13.6</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>17.9</v>
+        <v>12.9</v>
       </c>
       <c r="I10" s="3" t="n">
         <v>3.3</v>
@@ -1306,48 +1336,54 @@
       <c r="J10" s="3" t="n">
         <v>5.5</v>
       </c>
-      <c r="K10" s="3" t="n"/>
-      <c r="L10" s="3" t="n">
-        <v>20</v>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+2221
+</t>
+        </is>
+      </c>
+      <c r="L10" s="8" t="n">
+        <v>60</v>
       </c>
       <c r="M10" s="3" t="n">
         <v>19.9</v>
       </c>
-      <c r="N10" s="8" t="n">
+      <c r="N10" s="3" t="n">
         <v>23.2</v>
       </c>
       <c r="O10" s="3" t="n">
         <v>98.90000000000001</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>10.2</v>
+        <v>1.2</v>
       </c>
       <c r="Q10" s="3" t="n">
         <v>29.9</v>
       </c>
-      <c r="R10" s="8" t="n">
+      <c r="R10" s="3" t="n">
         <v>24.4</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>27.1</v>
+        <v>2.1</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>66</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="U10" s="3" t="n">
-        <v>16.2</v>
+        <v>1.2</v>
       </c>
       <c r="V10" s="3" t="n">
-        <v>26.6</v>
-      </c>
-      <c r="W10" s="8" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="W10" s="3" t="n">
         <v>23.4</v>
       </c>
       <c r="X10" s="3" t="n">
         <v>26.7</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>77.8</v>
+        <v>272.8</v>
       </c>
       <c r="Z10" s="3" t="n">
         <v>41.6</v>
@@ -1369,7 +1405,7 @@
         <v>265.6</v>
       </c>
       <c r="D11" s="10" t="n">
-        <v>30</v>
+        <v>30.1</v>
       </c>
       <c r="E11" s="10" t="n">
         <v>19.8</v>
@@ -1377,17 +1413,17 @@
       <c r="F11" s="10" t="n">
         <v>24.9</v>
       </c>
-      <c r="G11" s="10" t="n">
-        <v>10.3</v>
+      <c r="G11" s="3" t="n">
+        <v>1.3</v>
       </c>
       <c r="H11" s="3" t="n">
         <v>18.2</v>
       </c>
-      <c r="I11" s="8" t="n">
-        <v>86.59999999999999</v>
+      <c r="I11" s="3" t="n">
+        <v>1.6</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>82.8</v>
+        <v>2.8</v>
       </c>
       <c r="K11" s="3" t="n">
         <v>0</v>
@@ -1398,11 +1434,16 @@
       <c r="M11" s="3" t="n">
         <v>20.9</v>
       </c>
-      <c r="N11" s="8" t="n">
-        <v>124.5</v>
-      </c>
-      <c r="O11" s="3" t="n">
-        <v>92.3</v>
+      <c r="N11" s="3" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="O11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">897
+505
+1799
+</t>
+        </is>
       </c>
       <c r="P11" s="3" t="n">
         <v>0.6</v>
@@ -1410,32 +1451,36 @@
       <c r="Q11" s="8" t="n">
         <v>29.9</v>
       </c>
-      <c r="R11" s="8" t="n">
+      <c r="R11" s="3" t="n">
         <v>25.5</v>
       </c>
-      <c r="S11" s="8" t="n">
+      <c r="S11" s="3" t="n">
         <v>29.8</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>70.59999999999999</v>
-      </c>
-      <c r="U11" s="8" t="n">
+        <v>720.6</v>
+      </c>
+      <c r="U11" s="3" t="n">
         <v>12.4</v>
       </c>
-      <c r="V11" s="8" t="n">
-        <v>27.1</v>
-      </c>
-      <c r="W11" s="8" t="n">
+      <c r="V11" s="3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="W11" s="3" t="n">
         <v>24.9</v>
       </c>
       <c r="X11" s="3" t="n">
         <v>30.1</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>84</v>
-      </c>
-      <c r="Z11" s="3" t="n">
-        <v>8.300000000000001</v>
+        <v>24</v>
+      </c>
+      <c r="Z11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">244
+744
+</t>
+        </is>
       </c>
       <c r="AA11" s="3" t="inlineStr">
         <is>
@@ -1451,7 +1496,7 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>347.1</v>
+        <v>342.4</v>
       </c>
       <c r="D12" s="10" t="n">
         <v>31.8</v>
@@ -1471,11 +1516,11 @@
       <c r="I12" s="3" t="n">
         <v>2.7</v>
       </c>
-      <c r="J12" s="8" t="n">
-        <v>44.6</v>
+      <c r="J12" s="3" t="n">
+        <v>4.6</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="L12" s="3" t="n">
         <v>23.3</v>
@@ -1484,10 +1529,10 @@
         <v>23</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>27.9</v>
+        <v>2.9</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>97.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="P12" s="3" t="n">
         <v>0.5</v>
@@ -1505,22 +1550,22 @@
         <v>57.8</v>
       </c>
       <c r="U12" s="3" t="n">
-        <v>19.8</v>
+        <v>1.8</v>
       </c>
       <c r="V12" s="3" t="n">
-        <v>27.9</v>
-      </c>
-      <c r="W12" s="8" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="W12" s="3" t="n">
         <v>24.6</v>
       </c>
       <c r="X12" s="3" t="n">
         <v>28.8</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>76.7</v>
+        <v>7.7</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>5.7</v>
+        <v>57.2</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1536,7 +1581,7 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>1428.6</v>
+        <v>428.6</v>
       </c>
       <c r="D13" s="10" t="n">
         <v>32.8</v>
@@ -1557,13 +1602,13 @@
         <v>3.3</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="K13" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L13" s="8" t="n">
-        <v>22.1</v>
+      <c r="L13" s="3" t="n">
+        <v>2.1</v>
       </c>
       <c r="M13" s="3" t="n">
         <v>21.9</v>
@@ -1572,10 +1617,10 @@
         <v>26.1</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>98</v>
+        <v>9.5</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>10.4</v>
+        <v>26.4</v>
       </c>
       <c r="Q13" s="3" t="n">
         <v>32.6</v>
@@ -1592,8 +1637,8 @@
       <c r="U13" s="3" t="n">
         <v>23.3</v>
       </c>
-      <c r="V13" s="8" t="n">
-        <v>28</v>
+      <c r="V13" s="3" t="n">
+        <v>28.6</v>
       </c>
       <c r="W13" s="3" t="n">
         <v>24.8</v>
@@ -1602,10 +1647,10 @@
         <v>29.3</v>
       </c>
       <c r="Y13" s="3" t="n">
-        <v>77.59999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="Z13" s="3" t="n">
-        <v>8.699999999999999</v>
+        <v>23.1</v>
       </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
@@ -1636,34 +1681,34 @@
         <v>8.800000000000001</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>20.3</v>
+        <v>2.3</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>52.1</v>
+        <v>22.1</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>11.1</v>
+        <v>1.1</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>22.4</v>
+        <v>2.4</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>22.1</v>
+        <v>2.1</v>
       </c>
       <c r="N14" s="3" t="n">
         <v>26.4</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>97.3</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>10.7</v>
+        <v>0.7</v>
       </c>
       <c r="Q14" s="3" t="n">
-        <v>82.40000000000001</v>
+        <v>22.4</v>
       </c>
       <c r="R14" s="3" t="n">
         <v>21.1</v>
@@ -1678,10 +1723,10 @@
         <v>2.9</v>
       </c>
       <c r="V14" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="W14" s="3" t="n">
-        <v>21.6</v>
+        <v>26</v>
+      </c>
+      <c r="W14" s="8" t="n">
+        <v>41.6</v>
       </c>
       <c r="X14" s="3" t="n">
         <v>25.5</v>
@@ -1690,7 +1735,7 @@
         <v>96</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>8.5</v>
+        <v>2.5</v>
       </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
@@ -1706,7 +1751,7 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>359.6</v>
+        <v>5.6</v>
       </c>
       <c r="D15" s="10" t="n">
         <v>32.5</v>
@@ -1717,11 +1762,11 @@
       <c r="F15" s="10" t="n">
         <v>26.7</v>
       </c>
-      <c r="G15" s="10" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="H15" s="8" t="n">
-        <v>419.6</v>
+      <c r="G15" s="3" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="H15" s="3" t="n">
+        <v>19.6</v>
       </c>
       <c r="I15" s="3" t="n">
         <v>2.4</v>
@@ -1730,7 +1775,7 @@
         <v>3.9</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>25.9</v>
+        <v>25.7</v>
       </c>
       <c r="L15" s="3" t="n">
         <v>21.6</v>
@@ -1742,7 +1787,7 @@
         <v>25.8</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>180</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="P15" s="3" t="n">
         <v>0</v>
@@ -1754,7 +1799,7 @@
         <v>25.8</v>
       </c>
       <c r="S15" s="3" t="n">
-        <v>89.2</v>
+        <v>29.2</v>
       </c>
       <c r="T15" s="3" t="n">
         <v>61.7</v>
@@ -1766,7 +1811,7 @@
         <v>28.7</v>
       </c>
       <c r="W15" s="3" t="n">
-        <v>24.8</v>
+        <v>4.8</v>
       </c>
       <c r="X15" s="3" t="n">
         <v>28.8</v>
@@ -1775,7 +1820,7 @@
         <v>73.09999999999999</v>
       </c>
       <c r="Z15" s="3" t="n">
-        <v>0.9</v>
+        <v>20.9</v>
       </c>
       <c r="AA15" s="3" t="inlineStr">
         <is>
@@ -1797,16 +1842,16 @@
         <v>157.9</v>
       </c>
       <c r="E16" s="10" t="n">
-        <v>105.5</v>
+        <v>105.6</v>
       </c>
       <c r="F16" s="10" t="n">
         <v>131.7</v>
       </c>
-      <c r="G16" s="10" t="n">
+      <c r="G16" s="3" t="n">
         <v>52.4</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>99.2</v>
+        <v>929.2</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>11.5</v>
@@ -1814,19 +1859,37 @@
       <c r="J16" s="3" t="n">
         <v>19.4</v>
       </c>
-      <c r="K16" s="3" t="n"/>
-      <c r="L16" s="3" t="n"/>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">790691
+22
+5682
+</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="n">
+        <v>10.6</v>
+      </c>
       <c r="M16" s="3" t="n">
-        <v>109.5</v>
-      </c>
-      <c r="N16" s="3" t="n">
-        <v>130.7</v>
-      </c>
-      <c r="O16" s="3" t="n">
-        <v>490.1</v>
+        <v>19.5</v>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">791727
+14
+000
+</t>
+        </is>
+      </c>
+      <c r="O16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11722
+77218
+</t>
+        </is>
       </c>
       <c r="P16" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>2.2</v>
       </c>
       <c r="Q16" s="3" t="n">
         <v>148.7</v>
@@ -1838,24 +1901,42 @@
         <v>136.1</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>331.8</v>
+        <v>31.8</v>
       </c>
       <c r="U16" s="3" t="n">
         <v>76.59999999999999</v>
       </c>
-      <c r="V16" s="3" t="n">
-        <v>133.7</v>
-      </c>
-      <c r="W16" s="3" t="n">
-        <v>120.7</v>
-      </c>
-      <c r="X16" s="3" t="n">
-        <v>142.5</v>
-      </c>
-      <c r="Y16" s="3" t="n">
-        <v>407.4</v>
-      </c>
-      <c r="Z16" s="3" t="n"/>
+      <c r="V16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7277978
+7566
+</t>
+        </is>
+      </c>
+      <c r="W16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22414
+8711011466 7
+</t>
+        </is>
+      </c>
+      <c r="X16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">36595
+99781
+</t>
+        </is>
+      </c>
+      <c r="Y16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5555
+5721
+</t>
+        </is>
+      </c>
+      <c r="Z16" s="3" t="n">
+        <v>741.1</v>
+      </c>
       <c r="AA16" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -1870,22 +1951,22 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>318.2</v>
+        <v>38.2</v>
       </c>
       <c r="D17" s="10" t="n">
-        <v>31.5</v>
+        <v>31.6</v>
       </c>
       <c r="E17" s="10" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="F17" s="10" t="n">
-        <v>26.4</v>
+        <v>26.3</v>
       </c>
       <c r="G17" s="10" t="n">
         <v>10.5</v>
       </c>
-      <c r="H17" s="3" t="n">
-        <v>19.8</v>
+      <c r="H17" s="8" t="n">
+        <v>292.8</v>
       </c>
       <c r="I17" s="3" t="n">
         <v>2.3</v>
@@ -1896,20 +1977,20 @@
       <c r="K17" s="3" t="n">
         <v>36.8</v>
       </c>
-      <c r="L17" s="8" t="n">
-        <v>10.6</v>
+      <c r="L17" s="3" t="n">
+        <v>2.1</v>
       </c>
       <c r="M17" s="3" t="n">
         <v>21.9</v>
       </c>
-      <c r="N17" s="3" t="n">
-        <v>26.1</v>
+      <c r="N17" s="8" t="n">
+        <v>30.7</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>98</v>
-      </c>
-      <c r="P17" s="8" t="n">
-        <v>10.4</v>
+        <v>490.1</v>
+      </c>
+      <c r="P17" s="3" t="n">
+        <v>0.1</v>
       </c>
       <c r="Q17" s="3" t="n">
         <v>29.7</v>
@@ -1917,26 +1998,26 @@
       <c r="R17" s="3" t="n">
         <v>24.4</v>
       </c>
-      <c r="S17" s="8" t="n">
-        <v>72.2</v>
+      <c r="S17" s="3" t="n">
+        <v>2.2</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>66.40000000000001</v>
+        <v>6.4</v>
       </c>
       <c r="U17" s="3" t="n">
         <v>15.3</v>
       </c>
-      <c r="V17" s="3" t="n">
+      <c r="V17" s="8" t="n">
+        <v>33.7</v>
+      </c>
+      <c r="W17" s="8" t="n">
         <v>26.7</v>
       </c>
-      <c r="W17" s="3" t="n">
-        <v>94.09999999999999</v>
-      </c>
-      <c r="X17" s="3" t="n">
-        <v>28.5</v>
+      <c r="X17" s="8" t="n">
+        <v>42.5</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>81.5</v>
+        <v>47.6</v>
       </c>
       <c r="Z17" s="3" t="n">
         <v>6.9</v>
@@ -1958,16 +2039,16 @@
         <v>368</v>
       </c>
       <c r="D18" s="10" t="n">
-        <v>32.1</v>
+        <v>32.2</v>
       </c>
       <c r="E18" s="10" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>26.7</v>
-      </c>
-      <c r="G18" s="10" t="n">
-        <v>10.9</v>
+        <v>26.6</v>
+      </c>
+      <c r="G18" s="3" t="n">
+        <v>16.9</v>
       </c>
       <c r="H18" s="3" t="n">
         <v>20.4</v>
@@ -1976,20 +2057,30 @@
         <v>2.5</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="K18" s="3" t="n"/>
+        <v>4.3</v>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+222
+</t>
+        </is>
+      </c>
       <c r="L18" s="3" t="n">
-        <v>22.1</v>
+        <v>24.4</v>
       </c>
       <c r="M18" s="3" t="n">
         <v>21.1</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="O18" s="3" t="n">
-        <v>92.3</v>
+        <v>26.1</v>
+      </c>
+      <c r="O18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">27844
+171719
+</t>
+        </is>
       </c>
       <c r="P18" s="3" t="n">
         <v>0.6</v>
@@ -1997,32 +2088,40 @@
       <c r="Q18" s="3" t="n">
         <v>32.1</v>
       </c>
-      <c r="R18" s="8" t="n">
+      <c r="R18" s="3" t="n">
         <v>25.2</v>
       </c>
       <c r="S18" s="3" t="n">
-        <v>27.7</v>
+        <v>7.7</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>58</v>
-      </c>
-      <c r="U18" s="8" t="n">
+        <v>58.5</v>
+      </c>
+      <c r="U18" s="3" t="n">
         <v>20</v>
       </c>
       <c r="V18" s="3" t="n">
-        <v>28.5</v>
+        <v>26.7</v>
       </c>
       <c r="W18" s="3" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="X18" s="3" t="n">
-        <v>27.9</v>
-      </c>
-      <c r="Y18" s="3" t="n">
-        <v>71.7</v>
+        <v>4.1</v>
+      </c>
+      <c r="X18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7444
+1779 7
+</t>
+        </is>
+      </c>
+      <c r="Y18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09442
+77 7
+</t>
+        </is>
       </c>
       <c r="Z18" s="3" t="n">
-        <v>1.1</v>
+        <v>17.1</v>
       </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
@@ -2041,15 +2140,15 @@
         <v>265.6</v>
       </c>
       <c r="D19" s="10" t="n">
-        <v>30.4</v>
+        <v>30</v>
       </c>
       <c r="E19" s="10" t="n">
         <v>22.2</v>
       </c>
       <c r="F19" s="10" t="n">
-        <v>26.3</v>
-      </c>
-      <c r="G19" s="10" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="G19" s="3" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="H19" s="3" t="n">
@@ -2062,19 +2161,19 @@
         <v>2.8</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>10.4</v>
+        <v>1.4</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>21.4</v>
+        <v>2.3</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>26.3</v>
+        <v>24.8</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>97.59999999999999</v>
+        <v>297.3</v>
       </c>
       <c r="P19" s="3" t="n">
         <v>0.6</v>
@@ -2094,17 +2193,17 @@
       <c r="U19" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="V19" s="8" t="n">
-        <v>24.3</v>
+      <c r="V19" s="3" t="n">
+        <v>28.5</v>
       </c>
       <c r="W19" s="3" t="n">
-        <v>22.9</v>
+        <v>24.4</v>
       </c>
       <c r="X19" s="3" t="n">
-        <v>21.4</v>
+        <v>2.9</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>22</v>
+        <v>7218.7</v>
       </c>
       <c r="Z19" s="3" t="n">
         <v>3.3</v>
@@ -2129,7 +2228,7 @@
         <v>31.4</v>
       </c>
       <c r="E20" s="10" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="F20" s="10" t="n">
         <v>26.5</v>
@@ -2144,26 +2243,24 @@
         <v>2.5</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>14.5</v>
+        <v>4.5</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>11.2</v>
+        <v>1.2</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>22.3</v>
+        <v>21.6</v>
       </c>
       <c r="M20" s="3" t="n">
         <v>21.4</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>25.4</v>
+        <v>26.3</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>98</v>
-      </c>
-      <c r="P20" s="3" t="n">
-        <v>0.4</v>
-      </c>
+        <v>9.6</v>
+      </c>
+      <c r="P20" s="3" t="n"/>
       <c r="Q20" s="3" t="n">
         <v>30.7</v>
       </c>
@@ -2177,19 +2274,19 @@
         <v>62.3</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>16.6</v>
+        <v>1.6</v>
       </c>
       <c r="V20" s="3" t="n">
-        <v>27.3</v>
+        <v>24.3</v>
       </c>
       <c r="W20" s="3" t="n">
-        <v>23.8</v>
+        <v>2.9</v>
       </c>
       <c r="X20" s="3" t="n">
-        <v>27.2</v>
+        <v>27.1</v>
       </c>
       <c r="Y20" s="3" t="n">
-        <v>22</v>
+        <v>89</v>
       </c>
       <c r="Z20" s="3" t="n">
         <v>9.1</v>
@@ -2211,7 +2308,7 @@
         <v>340.8</v>
       </c>
       <c r="D21" s="10" t="n">
-        <v>30.7</v>
+        <v>30.6</v>
       </c>
       <c r="E21" s="10" t="n">
         <v>21.2</v>
@@ -2232,22 +2329,22 @@
         <v>3.4</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>21.6</v>
+        <v>2.6</v>
       </c>
       <c r="M21" s="3" t="n">
         <v>21.5</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>25.6</v>
+        <v>25.4</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>99</v>
+        <v>986</v>
       </c>
       <c r="P21" s="3" t="n">
-        <v>0.2</v>
+        <v>6.2</v>
       </c>
       <c r="Q21" s="3" t="n">
         <v>30.6</v>
@@ -2259,22 +2356,22 @@
         <v>31.2</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>71.2</v>
+        <v>4.2</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>12.6</v>
+        <v>1.6</v>
       </c>
       <c r="V21" s="3" t="n">
-        <v>27.8</v>
+        <v>2.3</v>
       </c>
       <c r="W21" s="3" t="n">
-        <v>24.6</v>
+        <v>23.8</v>
       </c>
       <c r="X21" s="3" t="n">
-        <v>28.9</v>
+        <v>7.2</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>772.3</v>
+        <v>75</v>
       </c>
       <c r="Z21" s="3" t="n">
         <v>8.4</v>
@@ -2293,22 +2390,22 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>399.3</v>
+        <v>395.3</v>
       </c>
       <c r="D22" s="10" t="n">
-        <v>32.9</v>
-      </c>
-      <c r="E22" s="10" t="n">
+        <v>-66.40000000000001</v>
+      </c>
+      <c r="E22" s="3" t="n">
         <v>21.1</v>
       </c>
       <c r="F22" s="10" t="n">
-        <v>27</v>
-      </c>
-      <c r="G22" s="10" t="n">
-        <v>11.8</v>
+        <v>-73</v>
+      </c>
+      <c r="G22" s="3" t="n">
+        <v>14.8</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>19.8</v>
+        <v>12.8</v>
       </c>
       <c r="I22" s="3" t="n">
         <v>2.5</v>
@@ -2317,22 +2414,25 @@
         <v>4.3</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" s="8" t="n">
-        <v>21.6</v>
+        <v>0.6</v>
+      </c>
+      <c r="L22" s="3" t="n">
+        <v>2.3</v>
       </c>
       <c r="M22" s="3" t="n">
         <v>21</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>24.7</v>
+        <v>25.6</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>92.5</v>
-      </c>
-      <c r="P22" s="3" t="n">
-        <v>0.4</v>
+        <v>99.59999999999999</v>
+      </c>
+      <c r="P22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">68 2
+</t>
+        </is>
       </c>
       <c r="Q22" s="3" t="n">
         <v>32.4</v>
@@ -2343,23 +2443,26 @@
       <c r="S22" s="3" t="n">
         <v>89.3</v>
       </c>
-      <c r="T22" s="3" t="n">
-        <v>60.5</v>
+      <c r="T22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">65 2
+</t>
+        </is>
       </c>
       <c r="U22" s="3" t="n">
         <v>19.2</v>
       </c>
       <c r="V22" s="3" t="n">
-        <v>26.5</v>
+        <v>27.8</v>
       </c>
       <c r="W22" s="3" t="n">
         <v>24.6</v>
       </c>
       <c r="X22" s="3" t="n">
-        <v>29.7</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="Y22" s="3" t="n">
-        <v>86</v>
+        <v>72.3</v>
       </c>
       <c r="Z22" s="3" t="n">
         <v>4.9</v>
@@ -2378,43 +2481,62 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>1739.6</v>
+        <v>739.6</v>
       </c>
       <c r="D23" s="10" t="n">
-        <v>157.5</v>
-      </c>
-      <c r="E23" s="10" t="n">
-        <v>107.2</v>
+        <v>57.8</v>
+      </c>
+      <c r="E23" s="17" t="n">
+        <v>7.2</v>
       </c>
       <c r="F23" s="10" t="n">
-        <v>132.4</v>
+        <v>32.5</v>
       </c>
       <c r="G23" s="3" t="n">
         <v>50.3</v>
       </c>
-      <c r="H23" s="3" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="I23" s="3" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="J23" s="3" t="n">
-        <v>19.3</v>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">41444444
+1
+8684
+</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">27955
+42
+12141
+</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">212
+1141089
+</t>
+        </is>
       </c>
       <c r="K23" s="3" t="n">
         <v>7.7</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>7.7</v>
+        <v>18.2</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>91.09999999999999</v>
-      </c>
-      <c r="O23" s="3" t="n">
-        <v>1489.4</v>
+        <v>24.7</v>
+      </c>
+      <c r="O23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">418686866
+50756012
+1441
+</t>
+        </is>
       </c>
       <c r="P23" s="3" t="n">
         <v>2.2</v>
@@ -2426,28 +2548,28 @@
         <v>128.1</v>
       </c>
       <c r="S23" s="3" t="n">
-        <v>1146.8</v>
+        <v>146.8</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>395.7</v>
+        <v>325.7</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>792.4</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="V23" s="3" t="n">
-        <v>134.4</v>
+        <v>86.5</v>
       </c>
       <c r="W23" s="3" t="n">
-        <v>120.3</v>
+        <v>24.6</v>
       </c>
       <c r="X23" s="3" t="n">
-        <v>1408.1</v>
+        <v>2.7</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>3940.4</v>
+        <v>860.6</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>8.699999999999999</v>
+        <v>3.7</v>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -2463,73 +2585,81 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>343.9</v>
+        <v>739.6</v>
       </c>
       <c r="D24" s="10" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="E24" s="10" t="n">
-        <v>21.4</v>
+        <v>11.6</v>
+      </c>
+      <c r="E24" s="17" t="n">
+        <v>7.2</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>26.5</v>
-      </c>
-      <c r="G24" s="10" t="n">
-        <v>10.1</v>
+        <v>32.5</v>
+      </c>
+      <c r="G24" s="3" t="n">
+        <v>50.3</v>
       </c>
       <c r="H24" s="8" t="n">
         <v>1.8</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>3.9</v>
+        <v>19.3</v>
       </c>
       <c r="K24" s="3" t="n">
         <v>19.3</v>
       </c>
-      <c r="L24" s="8" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="M24" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="N24" s="8" t="n">
-        <v>26.8</v>
+      <c r="L24" s="3" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="M24" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6169690911
+2929
+</t>
+        </is>
       </c>
       <c r="O24" s="3" t="n">
         <v>97.90000000000001</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="Q24" s="3" t="n">
-        <v>31.1</v>
-      </c>
-      <c r="R24" s="3" t="n">
-        <v>85.59999999999999</v>
-      </c>
-      <c r="S24" s="3" t="n">
-        <v>29.4</v>
+        <v>2.2</v>
+      </c>
+      <c r="Q24" s="8" t="n">
+        <v>55.7</v>
+      </c>
+      <c r="R24" s="8" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="S24" s="8" t="n">
+        <v>46.8</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>65.09999999999999</v>
+        <v>325.7</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="V24" s="3" t="n">
-        <v>26.9</v>
+        <v>79.40000000000001</v>
+      </c>
+      <c r="V24" s="8" t="n">
+        <v>34.4</v>
       </c>
       <c r="W24" s="3" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="X24" s="3" t="n">
-        <v>22.2</v>
+        <v>2.3</v>
+      </c>
+      <c r="X24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">74950
+448468
+</t>
+        </is>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>79.8</v>
+        <v>399</v>
       </c>
       <c r="Z24" s="3" t="n">
         <v>7.3</v>
@@ -2548,31 +2678,31 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>106.7</v>
+        <v>34.9</v>
       </c>
       <c r="D25" s="10" t="n">
-        <v>26.3</v>
+        <v>31.6</v>
       </c>
       <c r="E25" s="10" t="n">
-        <v>20.6</v>
+        <v>21.5</v>
       </c>
       <c r="F25" s="10" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="G25" s="10" t="n">
-        <v>5.7</v>
+        <v>26.4</v>
+      </c>
+      <c r="G25" s="3" t="n">
+        <v>1.1</v>
       </c>
       <c r="H25" s="3" t="n">
         <v>20.4</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>2.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>0.8</v>
+        <v>3.9</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>0.2</v>
+        <v>19.3</v>
       </c>
       <c r="L25" s="3" t="n">
         <v>21.6</v>
@@ -2580,41 +2710,41 @@
       <c r="M25" s="3" t="n">
         <v>21.4</v>
       </c>
-      <c r="N25" s="3" t="n">
-        <v>25.4</v>
+      <c r="N25" s="8" t="n">
+        <v>26.8</v>
       </c>
       <c r="O25" s="3" t="n">
         <v>97.90000000000001</v>
       </c>
       <c r="P25" s="3" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="Q25" s="3" t="n">
-        <v>26.2</v>
-      </c>
-      <c r="R25" s="8" t="n">
-        <v>146.1</v>
+        <v>31.1</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>156.1</v>
       </c>
       <c r="S25" s="3" t="n">
-        <v>28.7</v>
+        <v>29.4</v>
       </c>
       <c r="T25" s="3" t="n">
-        <v>84.40000000000001</v>
+        <v>6.1</v>
       </c>
       <c r="U25" s="3" t="n">
-        <v>5.3</v>
+        <v>15.9</v>
       </c>
       <c r="V25" s="3" t="n">
-        <v>244.1</v>
+        <v>26.9</v>
       </c>
       <c r="W25" s="3" t="n">
         <v>24.1</v>
       </c>
-      <c r="X25" s="3" t="n">
-        <v>26.8</v>
+      <c r="X25" s="8" t="n">
+        <v>40.8</v>
       </c>
       <c r="Y25" s="3" t="n">
-        <v>79.8</v>
+        <v>2.8</v>
       </c>
       <c r="Z25" s="3" t="n">
         <v>7.3</v>
@@ -2633,76 +2763,92 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>90</v>
+        <v>16.7</v>
       </c>
       <c r="D26" s="10" t="n">
-        <v>25.1</v>
+        <v>26.4</v>
       </c>
       <c r="E26" s="10" t="n">
-        <v>21</v>
+        <v>20.6</v>
       </c>
       <c r="F26" s="10" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="G26" s="3" t="n">
-        <v>14.1</v>
+        <v>23.5</v>
+      </c>
+      <c r="G26" s="10" t="n">
+        <v>5.7</v>
       </c>
       <c r="H26" s="3" t="n">
         <v>20.2</v>
       </c>
-      <c r="I26" s="3" t="n">
-        <v>0.5</v>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">215852
+147
+</t>
+        </is>
       </c>
       <c r="J26" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="K26" s="3" t="n">
-        <v>0.2</v>
+        <v>6.8</v>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+77
+</t>
+        </is>
       </c>
       <c r="L26" s="3" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="M26" s="3" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="N26" s="3" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="O26" s="3" t="n">
+        <v>97</v>
+      </c>
+      <c r="P26" s="3" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="Q26" s="3" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="S26" s="3" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="T26" s="3" t="n">
+        <v>84.40000000000001</v>
+      </c>
+      <c r="U26" s="3" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="V26" s="3" t="n">
         <v>24.4</v>
       </c>
-      <c r="M26" s="3" t="n">
-        <v>924</v>
-      </c>
-      <c r="N26" s="3" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="O26" s="3" t="n">
-        <v>1297</v>
-      </c>
-      <c r="P26" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" s="3" t="n">
-        <v>24.3</v>
-      </c>
-      <c r="R26" s="3" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="S26" s="3" t="n">
-        <v>28</v>
-      </c>
-      <c r="T26" s="3" t="n">
-        <v>92</v>
-      </c>
-      <c r="U26" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="V26" s="3" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="W26" s="3" t="n">
-        <v>22.8</v>
+      <c r="W26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7771717
+11811408 7
+</t>
+        </is>
       </c>
       <c r="X26" s="3" t="n">
-        <v>27.1</v>
+        <v>2.2</v>
       </c>
       <c r="Y26" s="3" t="n">
         <v>87.7</v>
       </c>
-      <c r="Z26" s="3" t="n">
-        <v>3.8</v>
+      <c r="Z26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">88
+893
+</t>
+        </is>
       </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
@@ -2718,76 +2864,68 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>322</v>
+        <v>90</v>
       </c>
       <c r="D27" s="10" t="n">
-        <v>30.5</v>
+        <v>25.2</v>
       </c>
       <c r="E27" s="10" t="n">
-        <v>20.6</v>
+        <v>21.1</v>
       </c>
       <c r="F27" s="10" t="n">
-        <v>25.5</v>
+        <v>23.1</v>
       </c>
       <c r="G27" s="10" t="n">
-        <v>9.9</v>
+        <v>4.1</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>19.2</v>
       </c>
-      <c r="I27" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J27" s="3" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="K27" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="I27" s="3" t="n"/>
+      <c r="J27" s="3" t="n"/>
+      <c r="K27" s="3" t="n"/>
       <c r="L27" s="3" t="n">
-        <v>24.4</v>
+        <v>21.4</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="N27" s="8" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="O27" s="3" t="n">
-        <v>100</v>
-      </c>
+        <v>2.4</v>
+      </c>
+      <c r="N27" s="3" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="O27" s="3" t="n"/>
       <c r="P27" s="3" t="n">
-        <v>10.4</v>
+        <v>8</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>28.8</v>
+        <v>4.3</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="S27" s="3" t="n">
-        <v>89</v>
+        <v>23.3</v>
+      </c>
+      <c r="S27" s="8" t="n">
+        <v>86</v>
       </c>
       <c r="T27" s="3" t="n">
-        <v>73.2</v>
+        <v>926</v>
       </c>
       <c r="U27" s="3" t="n">
-        <v>10.5</v>
+        <v>2.4</v>
       </c>
       <c r="V27" s="3" t="n">
-        <v>26.9</v>
+        <v>23.8</v>
       </c>
       <c r="W27" s="3" t="n">
         <v>22.8</v>
       </c>
       <c r="X27" s="3" t="n">
-        <v>29</v>
+        <v>26.8</v>
       </c>
       <c r="Y27" s="3" t="n">
         <v>91.8</v>
       </c>
       <c r="Z27" s="3" t="n">
-        <v>2.4</v>
+        <v>3.8</v>
       </c>
       <c r="AA27" s="3" t="inlineStr">
         <is>
@@ -2803,76 +2941,80 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>2990.7</v>
+        <v>322</v>
       </c>
       <c r="D28" s="10" t="n">
-        <v>31.8</v>
+        <v>30.4</v>
       </c>
       <c r="E28" s="10" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="F28" s="10" t="n">
-        <v>26.1</v>
+        <v>25.5</v>
       </c>
       <c r="G28" s="10" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="H28" s="3" t="n">
-        <v>19.1</v>
+        <v>9.9</v>
+      </c>
+      <c r="H28" s="8" t="n">
+        <v>29.1</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>1.9</v>
+        <v>6.9</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" s="8" t="n">
-        <v>20.9</v>
+        <v>2</v>
+      </c>
+      <c r="L28" s="3" t="n">
+        <v>20.7</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>20.6</v>
+        <v>26.5</v>
       </c>
       <c r="N28" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="O28" s="3" t="n">
-        <v>4.9</v>
+      <c r="O28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">280
+2923
+</t>
+        </is>
       </c>
       <c r="P28" s="3" t="n">
-        <v>0.8</v>
+        <v>16.4</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>31.2</v>
+        <v>28.8</v>
       </c>
       <c r="R28" s="3" t="n">
-        <v>24.8</v>
+        <v>24.9</v>
       </c>
       <c r="S28" s="3" t="n">
-        <v>27.2</v>
+        <v>29</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>60.2</v>
+        <v>73.2</v>
       </c>
       <c r="U28" s="3" t="n">
-        <v>18.1</v>
+        <v>1.5</v>
       </c>
       <c r="V28" s="3" t="n">
-        <v>28.6</v>
+        <v>26.9</v>
       </c>
       <c r="W28" s="3" t="n">
-        <v>24.4</v>
+        <v>2.8</v>
       </c>
       <c r="X28" s="3" t="n">
-        <v>28.4</v>
+        <v>27.1</v>
       </c>
       <c r="Y28" s="3" t="n">
         <v>81.8</v>
       </c>
       <c r="Z28" s="3" t="n">
-        <v>6.4</v>
+        <v>2.4</v>
       </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
@@ -2888,34 +3030,34 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>3468.1</v>
+        <v>290.7</v>
       </c>
       <c r="D29" s="10" t="n">
-        <v>31.5</v>
+        <v>31.7</v>
       </c>
       <c r="E29" s="10" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="F29" s="10" t="n">
-        <v>26</v>
+        <v>26.1</v>
       </c>
       <c r="G29" s="10" t="n">
-        <v>11</v>
-      </c>
-      <c r="H29" s="8" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="H29" s="3" t="n">
         <v>18.9</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>2.6</v>
+        <v>3.8</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>28.1</v>
+        <v>21.9</v>
       </c>
       <c r="M29" s="3" t="n">
         <v>20.6</v>
@@ -2923,41 +3065,45 @@
       <c r="N29" s="3" t="n">
         <v>24.1</v>
       </c>
-      <c r="O29" s="3" t="n">
-        <v>195.3</v>
+      <c r="O29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">280
+2923
+</t>
+        </is>
       </c>
       <c r="P29" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Q29" s="8" t="n">
-        <v>25.3</v>
+        <v>0.5</v>
+      </c>
+      <c r="Q29" s="3" t="n">
+        <v>31.2</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>23.6</v>
+        <v>24.8</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>28</v>
+        <v>27.2</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>27</v>
+        <v>60.2</v>
       </c>
       <c r="U29" s="3" t="n">
-        <v>14.2</v>
+        <v>18.1</v>
       </c>
       <c r="V29" s="3" t="n">
-        <v>22.4</v>
+        <v>28.6</v>
       </c>
       <c r="W29" s="3" t="n">
-        <v>24.6</v>
+        <v>24.4</v>
       </c>
       <c r="X29" s="3" t="n">
-        <v>36.1</v>
+        <v>29.1</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>72.59999999999999</v>
+        <v>724.6</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
@@ -2973,76 +3119,76 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>1056.2</v>
+        <v>846.2</v>
       </c>
       <c r="D30" s="10" t="n">
-        <v>145.2</v>
+        <v>145.3</v>
       </c>
       <c r="E30" s="10" t="n">
-        <v>103.2</v>
+        <v>104.2</v>
       </c>
       <c r="F30" s="10" t="n">
-        <v>124.2</v>
-      </c>
-      <c r="G30" s="10" t="n">
-        <v>42</v>
+        <v>124.6</v>
+      </c>
+      <c r="G30" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>119.2</v>
+        <v>12.2</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>111</v>
+        <v>2.6</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>38.8</v>
+        <v>8.4</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>106.5</v>
+        <v>21.1</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>1159.2</v>
+        <v>20.6</v>
       </c>
       <c r="N30" s="3" t="n">
         <v>23.9</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>487.6</v>
+        <v>95.3</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>2.8</v>
+        <v>1.1</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>1185.8</v>
+        <v>825.3</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>120.7</v>
+        <v>23.6</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>140.9</v>
+        <v>28</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>396.8</v>
+        <v>8</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>14.2</v>
+        <v>4.1</v>
       </c>
       <c r="V30" s="3" t="n">
-        <v>126.1</v>
+        <v>2.4</v>
       </c>
       <c r="W30" s="3" t="n">
-        <v>21.3</v>
+        <v>24.6</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>135.8</v>
+        <v>2.4</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>90.8</v>
+        <v>4.2</v>
       </c>
       <c r="Z30" s="3" t="n">
-        <v>2.5</v>
+        <v>1.3</v>
       </c>
       <c r="AA30" s="3" t="inlineStr">
         <is>
@@ -3058,76 +3204,76 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>211.2</v>
+        <v>15.2</v>
       </c>
       <c r="D31" s="10" t="n">
-        <v>29</v>
+        <v>29.1</v>
       </c>
       <c r="E31" s="10" t="n">
-        <v>20.6</v>
+        <v>20.8</v>
       </c>
       <c r="F31" s="10" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="G31" s="10" t="n">
-        <v>8.4</v>
+        <v>24.9</v>
+      </c>
+      <c r="G31" s="3" t="n">
+        <v>42</v>
       </c>
       <c r="H31" s="3" t="n">
         <v>96.59999999999999</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>7.1</v>
+        <v>1.6</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>2.2</v>
+        <v>0.4</v>
       </c>
       <c r="K31" s="3" t="n">
         <v>38.8</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>21.3</v>
+        <v>16.5</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>21</v>
+        <v>15.1</v>
       </c>
       <c r="N31" s="8" t="n">
         <v>23.9</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>97.5</v>
+        <v>487.6</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="Q31" s="3" t="n">
-        <v>27.2</v>
-      </c>
-      <c r="R31" s="3" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="S31" s="3" t="n">
-        <v>28.2</v>
+        <v>2.8</v>
+      </c>
+      <c r="Q31" s="8" t="n">
+        <v>35.8</v>
+      </c>
+      <c r="R31" s="8" t="n">
+        <v>280.7</v>
+      </c>
+      <c r="S31" s="8" t="n">
+        <v>40.9</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>79.40000000000001</v>
-      </c>
-      <c r="U31" s="3" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="V31" s="3" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="W31" s="8" t="n">
-        <v>15.9</v>
+        <v>396.8</v>
+      </c>
+      <c r="U31" s="8" t="n">
+        <v>81.5</v>
+      </c>
+      <c r="V31" s="8" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="W31" s="3" t="n">
+        <v>21.3</v>
       </c>
       <c r="X31" s="3" t="n">
-        <v>27.2</v>
+        <v>4.6</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>4.2</v>
+        <v>44.2</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>5.8</v>
+        <v>2.5</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -3143,76 +3289,74 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>384.7</v>
+        <v>211.2</v>
       </c>
       <c r="D32" s="10" t="n">
-        <v>31.1</v>
+        <v>29</v>
       </c>
       <c r="E32" s="10" t="n">
-        <v>19.3</v>
+        <v>20.6</v>
       </c>
       <c r="F32" s="10" t="n">
-        <v>25.2</v>
+        <v>24.8</v>
       </c>
       <c r="G32" s="10" t="n">
-        <v>11.8</v>
+        <v>8.4</v>
       </c>
       <c r="H32" s="3" t="n">
         <v>19.3</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="J32" s="8" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="K32" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" s="8" t="n">
-        <v>20.1</v>
+        <v>72.09999999999999</v>
+      </c>
+      <c r="J32" s="3" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="K32" s="3" t="n"/>
+      <c r="L32" s="3" t="n">
+        <v>41.3</v>
       </c>
       <c r="M32" s="3" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="N32" s="8" t="n">
+        <v>21</v>
+      </c>
+      <c r="N32" s="3" t="n">
         <v>24.8</v>
       </c>
       <c r="O32" s="3" t="n">
-        <v>100</v>
+        <v>9.5</v>
       </c>
       <c r="P32" s="3" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="Q32" s="3" t="n">
-        <v>31.1</v>
-      </c>
-      <c r="R32" s="8" t="n">
-        <v>24.9</v>
+        <v>7.2</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>24.1</v>
       </c>
       <c r="S32" s="3" t="n">
-        <v>22.5</v>
+        <v>28.2</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>61</v>
+        <v>22.9</v>
       </c>
       <c r="U32" s="3" t="n">
-        <v>17.5</v>
+        <v>8.1</v>
       </c>
       <c r="V32" s="3" t="n">
-        <v>97.40000000000001</v>
-      </c>
-      <c r="W32" s="3" t="n">
-        <v>23.2</v>
+        <v>25.2</v>
+      </c>
+      <c r="W32" s="8" t="n">
+        <v>15.9</v>
       </c>
       <c r="X32" s="3" t="n">
-        <v>27.2</v>
+        <v>2.2</v>
       </c>
       <c r="Y32" s="3" t="n">
-        <v>24.9</v>
+        <v>4.9</v>
       </c>
       <c r="Z32" s="3" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -3228,76 +3372,74 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>213.3</v>
+        <v>384.7</v>
       </c>
       <c r="D33" s="10" t="n">
-        <v>29.2</v>
+        <v>31.1</v>
       </c>
       <c r="E33" s="10" t="n">
-        <v>19.6</v>
+        <v>19.3</v>
       </c>
       <c r="F33" s="10" t="n">
-        <v>24.4</v>
+        <v>25.2</v>
       </c>
       <c r="G33" s="10" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="H33" s="8" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="H33" s="3" t="n">
         <v>18</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>8.300000000000001</v>
+        <v>1.4</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>51.6</v>
+        <v>4.4</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="L33" s="3" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="M33" s="8" t="n">
-        <v>21.4</v>
-      </c>
-      <c r="N33" s="8" t="n">
-        <v>23.5</v>
+        <v>20</v>
+      </c>
+      <c r="L33" s="8" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="M33" s="3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="N33" s="3" t="n">
+        <v>23.3</v>
       </c>
       <c r="O33" s="3" t="n">
-        <v>99</v>
+        <v>10</v>
       </c>
       <c r="P33" s="3" t="n">
-        <v>0.2</v>
+        <v>6</v>
       </c>
       <c r="Q33" s="3" t="n">
-        <v>28.9</v>
-      </c>
-      <c r="R33" s="8" t="n">
-        <v>84.59999999999999</v>
+        <v>31.1</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>24.9</v>
       </c>
       <c r="S33" s="3" t="n">
-        <v>982.1</v>
+        <v>2.5</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>70.90000000000001</v>
+        <v>61</v>
       </c>
       <c r="U33" s="3" t="n">
-        <v>11.5</v>
+        <v>17.5</v>
       </c>
       <c r="V33" s="3" t="n">
-        <v>25.6</v>
+        <v>2.4</v>
       </c>
       <c r="W33" s="3" t="n">
-        <v>23.8</v>
+        <v>23.2</v>
       </c>
       <c r="X33" s="3" t="n">
-        <v>28.3</v>
-      </c>
-      <c r="Y33" s="3" t="n">
-        <v>74.59999999999999</v>
-      </c>
+        <v>2.2</v>
+      </c>
+      <c r="Y33" s="3" t="n"/>
       <c r="Z33" s="3" t="n">
-        <v>9.300000000000001</v>
+        <v>5.2</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3313,76 +3455,72 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>311.6</v>
+        <v>213.3</v>
       </c>
       <c r="D34" s="10" t="n">
-        <v>31.9</v>
+        <v>29.2</v>
       </c>
       <c r="E34" s="10" t="n">
-        <v>21.5</v>
+        <v>19.6</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>26.7</v>
+        <v>24.4</v>
       </c>
       <c r="G34" s="10" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="H34" s="3" t="n">
         <v>18.8</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>8.300000000000001</v>
+        <v>2.3</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>3.5</v>
+        <v>1.1</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0.2</v>
+        <v>4.8</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>21.8</v>
+        <v>21.5</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="N34" s="8" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="N34" s="3" t="n">
         <v>25.4</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>1199</v>
+        <v>992.6</v>
       </c>
       <c r="P34" s="3" t="n">
         <v>0.2</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>20.5</v>
+        <v>28.9</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>25.8</v>
+        <v>4.6</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>30.2</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>69.40000000000001</v>
+        <v>2720.9</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>13.3</v>
+        <v>11.5</v>
       </c>
       <c r="V34" s="3" t="n">
-        <v>27.3</v>
-      </c>
-      <c r="W34" s="8" t="n">
-        <v>138248.4</v>
-      </c>
-      <c r="X34" s="3" t="n">
-        <v>29.7</v>
-      </c>
-      <c r="Y34" s="3" t="n">
-        <v>262.1</v>
-      </c>
+        <v>25.6</v>
+      </c>
+      <c r="W34" s="3" t="n">
+        <v>83.8</v>
+      </c>
+      <c r="X34" s="3" t="n"/>
+      <c r="Y34" s="3" t="n"/>
       <c r="Z34" s="3" t="n">
-        <v>4.5</v>
+        <v>2.3</v>
       </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
@@ -3398,76 +3536,88 @@
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>353.4</v>
+        <v>311.6</v>
       </c>
       <c r="D35" s="10" t="n">
-        <v>31</v>
+        <v>31.9</v>
       </c>
       <c r="E35" s="10" t="n">
-        <v>20.7</v>
+        <v>21.5</v>
       </c>
       <c r="F35" s="10" t="n">
-        <v>25.9</v>
-      </c>
-      <c r="G35" s="10" t="n">
-        <v>10.3</v>
+        <v>26.6</v>
+      </c>
+      <c r="G35" s="3" t="n">
+        <v>1.5</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="I35" s="3" t="n">
-        <v>12.4</v>
+        <v>2.2</v>
+      </c>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20
+9217
+</t>
+        </is>
       </c>
       <c r="J35" s="3" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="K35" s="3" t="n">
-        <v>10</v>
+        <v>6.2</v>
       </c>
       <c r="L35" s="3" t="n">
-        <v>21.6</v>
+        <v>21.8</v>
       </c>
       <c r="M35" s="3" t="n">
-        <v>21.3</v>
+        <v>21.7</v>
       </c>
       <c r="N35" s="3" t="n">
         <v>25.9</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>97.8</v>
+        <v>996</v>
       </c>
       <c r="P35" s="3" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="Q35" s="8" t="n">
-        <v>31.1</v>
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Q35" s="3" t="n">
+        <v>30.5</v>
       </c>
       <c r="R35" s="3" t="n">
-        <v>26.9</v>
+        <v>25.8</v>
       </c>
       <c r="S35" s="3" t="n">
-        <v>27.5</v>
+        <v>30.2</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>61.3</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="U35" s="3" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="V35" s="3" t="n">
-        <v>27.8</v>
-      </c>
-      <c r="W35" s="8" t="n">
-        <v>46.6</v>
-      </c>
-      <c r="X35" s="3" t="n">
-        <v>28.9</v>
-      </c>
-      <c r="Y35" s="3" t="n">
-        <v>82</v>
+        <v>13.3</v>
+      </c>
+      <c r="V35" s="8" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="W35" s="3" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="X35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">242461
+289
+</t>
+        </is>
+      </c>
+      <c r="Y35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">26282
+79794
+</t>
+        </is>
       </c>
       <c r="Z35" s="3" t="n">
-        <v>6.5</v>
+        <v>4.5</v>
       </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
@@ -3483,74 +3633,74 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>430.7</v>
+        <v>353.4</v>
       </c>
       <c r="D36" s="10" t="n">
-        <v>32.1</v>
+        <v>31</v>
       </c>
       <c r="E36" s="10" t="n">
-        <v>20.9</v>
+        <v>20.7</v>
       </c>
       <c r="F36" s="10" t="n">
-        <v>26.5</v>
+        <v>25.9</v>
       </c>
       <c r="G36" s="10" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="H36" s="3" t="n">
-        <v>19.8</v>
-      </c>
+        <v>10.3</v>
+      </c>
+      <c r="H36" s="3" t="n"/>
       <c r="I36" s="3" t="n">
-        <v>2.4</v>
+        <v>22.4</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>14.4</v>
+        <v>4</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>30.6</v>
-      </c>
-      <c r="L36" s="8" t="n">
-        <v>41</v>
+        <v>0</v>
+      </c>
+      <c r="L36" s="3" t="n">
+        <v>21.6</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>20.7</v>
+        <v>21.3</v>
       </c>
       <c r="N36" s="3" t="n">
         <v>25.1</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>972.5</v>
+        <v>97.2</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>10.6</v>
+        <v>0.7</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>32.1</v>
+        <v>31.1</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>26</v>
+        <v>24.9</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>29.7</v>
+        <v>27.5</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>62.2</v>
+        <v>6.3</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>18</v>
+        <v>17.4</v>
       </c>
       <c r="V36" s="3" t="n">
-        <v>28.7</v>
-      </c>
-      <c r="W36" s="8" t="n">
-        <v>24.6</v>
-      </c>
-      <c r="X36" s="3" t="n">
-        <v>28.3</v>
-      </c>
-      <c r="Y36" s="3" t="n">
-        <v>79.40000000000001</v>
-      </c>
+        <v>27.8</v>
+      </c>
+      <c r="W36" s="3" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="X36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">242461
+289
+</t>
+        </is>
+      </c>
+      <c r="Y36" s="3" t="n"/>
       <c r="Z36" s="3" t="n">
         <v>8.4</v>
       </c>
@@ -3568,76 +3718,70 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>1693.7</v>
+        <v>430.7</v>
       </c>
       <c r="D37" s="10" t="n">
-        <v>155.4</v>
+        <v>152.2</v>
       </c>
       <c r="E37" s="10" t="n">
-        <v>102</v>
+        <v>101.7</v>
       </c>
       <c r="F37" s="10" t="n">
-        <v>128.7</v>
-      </c>
-      <c r="G37" s="10" t="n">
-        <v>53.4</v>
-      </c>
+        <v>126.9</v>
+      </c>
+      <c r="G37" s="3" t="n"/>
       <c r="H37" s="3" t="n">
-        <v>96.5</v>
+        <v>13.8</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>10.1</v>
+        <v>2.4</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>0.4</v>
+        <v>4.4</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>35.6</v>
+        <v>30.6</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>106</v>
+        <v>21</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>1015.9</v>
+        <v>20.7</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>24.2</v>
+        <v>242.8</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>1192.7</v>
+        <v>9.5</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>1.7</v>
+        <v>0.6</v>
       </c>
       <c r="Q37" s="3" t="n">
-        <v>153.7</v>
+        <v>32.1</v>
       </c>
       <c r="R37" s="3" t="n">
-        <v>126.2</v>
+        <v>26</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>1143.1</v>
+        <v>29.7</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>324.8</v>
+        <v>62.2</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>77.7</v>
+        <v>18.4</v>
       </c>
       <c r="V37" s="3" t="n">
-        <v>136.8</v>
+        <v>28.7</v>
       </c>
       <c r="W37" s="3" t="n">
-        <v>121.6</v>
-      </c>
-      <c r="X37" s="3" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="Y37" s="3" t="n">
-        <v>72</v>
-      </c>
+        <v>26.6</v>
+      </c>
+      <c r="X37" s="3" t="n"/>
+      <c r="Y37" s="3" t="n"/>
       <c r="Z37" s="3" t="n">
-        <v>1.1</v>
+        <v>7909.7</v>
       </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
@@ -3653,77 +3797,83 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>338.7</v>
+        <v>693.7</v>
       </c>
       <c r="D38" s="10" t="n">
-        <v>31</v>
+        <v>30.4</v>
       </c>
       <c r="E38" s="10" t="n">
-        <v>20.4</v>
+        <v>20.3</v>
       </c>
       <c r="F38" s="10" t="n">
-        <v>25.7</v>
+        <v>28.7</v>
       </c>
       <c r="G38" s="10" t="n">
-        <v>10.6</v>
+        <v>53.4</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>19.3</v>
+        <v>96.5</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="J38" s="3" t="n">
-        <v>18.1</v>
+        <v>4</v>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">887 1
+18 74
+</t>
+        </is>
       </c>
       <c r="K38" s="3" t="n">
         <v>35.6</v>
       </c>
       <c r="L38" s="3" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="M38" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="N38" s="8" t="n">
-        <v>28.1</v>
-      </c>
-      <c r="O38" s="3" t="n">
-        <v>98.5</v>
+        <v>16</v>
+      </c>
+      <c r="M38" s="8" t="n">
+        <v>185.8</v>
+      </c>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">42477
+114111
+</t>
+        </is>
+      </c>
+      <c r="O38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24268701
+6888
+</t>
+        </is>
       </c>
       <c r="P38" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="Q38" s="3" t="n">
-        <v>20.7</v>
-      </c>
-      <c r="R38" s="3" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="S38" s="3" t="n">
-        <v>28.6</v>
+        <v>1.7</v>
+      </c>
+      <c r="Q38" s="8" t="n">
+        <v>53.7</v>
+      </c>
+      <c r="R38" s="8" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="S38" s="8" t="n">
+        <v>43.1</v>
       </c>
       <c r="T38" s="3" t="n">
-        <v>65</v>
+        <v>324.8</v>
       </c>
       <c r="U38" s="3" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="V38" s="3" t="n">
-        <v>87.40000000000001</v>
-      </c>
-      <c r="W38" s="3" t="n">
-        <v>24.3</v>
-      </c>
-      <c r="X38" s="3" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="Y38" s="3" t="n">
-        <v>98.2</v>
-      </c>
-      <c r="Z38" s="3" t="n">
-        <v>1.9</v>
-      </c>
+        <v>77.7</v>
+      </c>
+      <c r="V38" s="8" t="n">
+        <v>36.8</v>
+      </c>
+      <c r="W38" s="8" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="X38" s="3" t="n"/>
+      <c r="Y38" s="3" t="n"/>
+      <c r="Z38" s="3" t="n"/>
       <c r="AA38" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -3738,76 +3888,78 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>332.5</v>
-      </c>
-      <c r="D39" s="10" t="n">
-        <v>31.9</v>
-      </c>
-      <c r="E39" s="10" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="F39" s="10" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="G39" s="10" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="H39" s="8" t="n">
+        <v>38.7</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="E39" s="23" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="G39" s="3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H39" s="3" t="n">
         <v>19.3</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>1.7</v>
+        <v>20.6</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="K39" s="3" t="n">
-        <v>0.6</v>
-      </c>
+        <v>18.1</v>
+      </c>
+      <c r="K39" s="3" t="n"/>
       <c r="L39" s="3" t="n">
-        <v>28</v>
-      </c>
-      <c r="M39" s="8" t="n">
-        <v>20.9</v>
+        <v>21.2</v>
+      </c>
+      <c r="M39" s="3" t="n">
+        <v>21</v>
       </c>
       <c r="N39" s="8" t="n">
-        <v>14.8</v>
+        <v>24.1</v>
       </c>
       <c r="O39" s="3" t="n">
-        <v>99</v>
+        <v>492.7</v>
       </c>
       <c r="P39" s="3" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="Q39" s="3" t="n">
-        <v>71.90000000000001</v>
+        <v>36.7</v>
       </c>
       <c r="R39" s="3" t="n">
-        <v>86</v>
+        <v>25.2</v>
       </c>
       <c r="S39" s="3" t="n">
-        <v>89.8</v>
+        <v>28.6</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>63.2</v>
+        <v>65</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>17.3</v>
+        <v>15.5</v>
       </c>
       <c r="V39" s="3" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="W39" s="3" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="X39" s="3" t="n">
-        <v>27.6</v>
-      </c>
-      <c r="Y39" s="3" t="n">
-        <v>78.40000000000001</v>
+        <v>32.4</v>
+      </c>
+      <c r="W39" s="8" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="X39" s="8" t="n">
+        <v>88.5</v>
+      </c>
+      <c r="Y39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">177
+1
+</t>
+        </is>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>38.6</v>
+        <v>2.9</v>
       </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -3823,76 +3975,76 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>453.7</v>
+        <v>32.5</v>
       </c>
       <c r="D40" s="10" t="n">
-        <v>32.9</v>
+        <v>31.9</v>
       </c>
       <c r="E40" s="10" t="n">
-        <v>18.8</v>
+        <v>20.3</v>
       </c>
       <c r="F40" s="10" t="n">
-        <v>25.9</v>
+        <v>26</v>
       </c>
       <c r="G40" s="10" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="H40" s="8" t="n">
-        <v>18.2</v>
+        <v>11.7</v>
+      </c>
+      <c r="H40" s="3" t="n">
+        <v>19.3</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>12.7</v>
+        <v>21.7</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>19.8</v>
+        <v>21</v>
       </c>
       <c r="M40" s="3" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="N40" s="8" t="n">
-        <v>46.8</v>
+        <v>20.9</v>
+      </c>
+      <c r="N40" s="3" t="n">
+        <v>24.8</v>
       </c>
       <c r="O40" s="3" t="n">
-        <v>97.8</v>
+        <v>98.5</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="Q40" s="3" t="n">
-        <v>32.8</v>
+        <v>31.9</v>
       </c>
       <c r="R40" s="3" t="n">
         <v>26</v>
       </c>
-      <c r="S40" s="8" t="n">
-        <v>29.3</v>
+      <c r="S40" s="3" t="n">
+        <v>89.8</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>59.2</v>
-      </c>
-      <c r="U40" s="3" t="n">
-        <v>20.2</v>
+        <v>63.2</v>
+      </c>
+      <c r="U40" s="8" t="n">
+        <v>27.3</v>
       </c>
       <c r="V40" s="3" t="n">
-        <v>27.8</v>
+        <v>24.7</v>
       </c>
       <c r="W40" s="3" t="n">
-        <v>23.8</v>
+        <v>24.3</v>
       </c>
       <c r="X40" s="3" t="n">
-        <v>26.9</v>
+        <v>2.5</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>98.2</v>
+        <v>88.2</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>10.4</v>
+        <v>0.8</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3908,76 +4060,74 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>265.6</v>
-      </c>
-      <c r="D41" s="10" t="n">
-        <v>31.6</v>
-      </c>
-      <c r="E41" s="10" t="n">
+        <v>453.7</v>
+      </c>
+      <c r="D41" s="23" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="G41" s="3" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H41" s="3" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="I41" s="3" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="J41" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="K41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" s="3" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="M41" s="3" t="n">
         <v>19.6</v>
       </c>
-      <c r="F41" s="10" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="G41" s="10" t="n">
-        <v>12</v>
-      </c>
-      <c r="H41" s="8" t="n">
-        <v>18</v>
-      </c>
-      <c r="I41" s="3" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="J41" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="K41" s="3" t="n">
-        <v>43.4</v>
-      </c>
-      <c r="L41" s="3" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="M41" s="3" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="N41" s="8" t="n">
-        <v>28.6</v>
+      <c r="N41" s="3" t="n">
+        <v>4.6</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>99</v>
+        <v>97.8</v>
       </c>
       <c r="P41" s="3" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="Q41" s="3" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="R41" s="3" t="n">
-        <v>21.4</v>
+        <v>32.8</v>
+      </c>
+      <c r="R41" s="8" t="n">
+        <v>66</v>
       </c>
       <c r="S41" s="3" t="n">
-        <v>24.9</v>
+        <v>29.3</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>92.3</v>
+        <v>59.2</v>
       </c>
       <c r="U41" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="V41" s="8" t="n">
-        <v>28.1</v>
+        <v>2.2</v>
+      </c>
+      <c r="V41" s="3" t="n">
+        <v>7.8</v>
       </c>
       <c r="W41" s="3" t="n">
-        <v>23.4</v>
+        <v>23.8</v>
       </c>
       <c r="X41" s="3" t="n">
-        <v>28</v>
-      </c>
-      <c r="Y41" s="3" t="n">
-        <v>22</v>
-      </c>
+        <v>26.9</v>
+      </c>
+      <c r="Y41" s="3" t="n"/>
       <c r="Z41" s="3" t="n">
-        <v>8.9</v>
+        <v>1</v>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
@@ -3993,76 +4143,76 @@
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>236.3</v>
+        <v>26.5</v>
       </c>
       <c r="D42" s="10" t="n">
         <v>31.6</v>
       </c>
       <c r="E42" s="10" t="n">
-        <v>20.3</v>
+        <v>19.6</v>
       </c>
       <c r="F42" s="10" t="n">
-        <v>25.9</v>
+        <v>25.6</v>
       </c>
       <c r="G42" s="10" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="H42" s="8" t="n">
-        <v>20</v>
+        <v>12</v>
+      </c>
+      <c r="H42" s="3" t="n">
+        <v>18.6</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J42" s="3" t="n">
         <v>1.6</v>
       </c>
       <c r="K42" s="3" t="n">
-        <v>28.7</v>
+        <v>4.6</v>
       </c>
       <c r="L42" s="3" t="n">
-        <v>21.9</v>
-      </c>
-      <c r="M42" s="8" t="n">
-        <v>21.8</v>
+        <v>19.9</v>
+      </c>
+      <c r="M42" s="3" t="n">
+        <v>19.8</v>
       </c>
       <c r="N42" s="3" t="n">
-        <v>83</v>
+        <v>23</v>
       </c>
       <c r="O42" s="3" t="n">
-        <v>199</v>
-      </c>
-      <c r="P42" s="3" t="n">
-        <v>0.2</v>
+        <v>99</v>
+      </c>
+      <c r="P42" s="8" t="n">
+        <v>12.6</v>
       </c>
       <c r="Q42" s="3" t="n">
-        <v>24.1</v>
+        <v>22.3</v>
       </c>
       <c r="R42" s="3" t="n">
-        <v>23.8</v>
+        <v>21.4</v>
       </c>
       <c r="S42" s="3" t="n">
-        <v>89.3</v>
+        <v>24.9</v>
       </c>
       <c r="T42" s="3" t="n">
-        <v>97.7</v>
+        <v>92.3</v>
       </c>
       <c r="U42" s="3" t="n">
-        <v>0.7</v>
+        <v>2.8</v>
       </c>
       <c r="V42" s="3" t="n">
-        <v>85.90000000000001</v>
+        <v>4.6</v>
       </c>
       <c r="W42" s="3" t="n">
-        <v>23.5</v>
+        <v>23.4</v>
       </c>
       <c r="X42" s="3" t="n">
-        <v>28.2</v>
+        <v>28.1</v>
       </c>
       <c r="Y42" s="3" t="n">
-        <v>90.59999999999999</v>
+        <v>90.5</v>
       </c>
       <c r="Z42" s="3" t="n">
-        <v>8.9</v>
+        <v>2.9</v>
       </c>
       <c r="AA42" s="3" t="inlineStr">
         <is>
@@ -4078,77 +4228,75 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>372.2</v>
-      </c>
-      <c r="D43" s="10" t="n">
-        <v>30</v>
-      </c>
-      <c r="E43" s="10" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="F43" s="10" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="G43" s="10" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="H43" s="8" t="n">
-        <v>19.8</v>
+        <v>236.3</v>
+      </c>
+      <c r="D43" s="8" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="G43" s="3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H43" s="3" t="n">
+        <v>20.6</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>2</v>
+        <v>6.7</v>
       </c>
       <c r="J43" s="3" t="n">
         <v>1.5</v>
       </c>
       <c r="K43" s="3" t="n">
-        <v>10</v>
+        <v>88.7</v>
       </c>
       <c r="L43" s="3" t="n">
-        <v>21.6</v>
+        <v>21.9</v>
       </c>
       <c r="M43" s="3" t="n">
-        <v>21.5</v>
+        <v>21.8</v>
       </c>
       <c r="N43" s="3" t="n">
-        <v>95.59999999999999</v>
+        <v>26</v>
       </c>
       <c r="O43" s="3" t="n">
-        <v>99</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="P43" s="3" t="n">
-        <v>0.2</v>
+        <v>6.2</v>
       </c>
       <c r="Q43" s="3" t="n">
-        <v>29.1</v>
+        <v>24.1</v>
       </c>
       <c r="R43" s="3" t="n">
-        <v>25.5</v>
+        <v>23.8</v>
       </c>
       <c r="S43" s="3" t="n">
-        <v>30.4</v>
+        <v>29.3</v>
       </c>
       <c r="T43" s="3" t="n">
-        <v>75.59999999999999</v>
+        <v>97.2</v>
       </c>
       <c r="U43" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>87.2</v>
       </c>
       <c r="V43" s="3" t="n">
-        <v>27.8</v>
+        <v>24.7</v>
       </c>
       <c r="W43" s="3" t="n">
-        <v>84.7</v>
+        <v>23.5</v>
       </c>
       <c r="X43" s="3" t="n">
-        <v>9.1</v>
+        <v>88.2</v>
       </c>
       <c r="Y43" s="3" t="n">
-        <v>78</v>
-      </c>
-      <c r="Z43" s="3" t="n">
-        <v>9.199999999999999</v>
-      </c>
+        <v>96.59999999999999</v>
+      </c>
+      <c r="Z43" s="3" t="n"/>
       <c r="AA43" s="3" t="inlineStr">
         <is>
           <t>30</t>
@@ -4163,77 +4311,75 @@
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>365.9</v>
+        <v>32.2</v>
       </c>
       <c r="D44" s="10" t="n">
-        <v>32.6</v>
+        <v>29.9</v>
       </c>
       <c r="E44" s="10" t="n">
         <v>21.3</v>
       </c>
       <c r="F44" s="10" t="n">
-        <v>26.9</v>
+        <v>25.6</v>
       </c>
       <c r="G44" s="10" t="n">
-        <v>11.3</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="H44" s="3" t="n">
-        <v>19.4</v>
+        <v>19.8</v>
       </c>
       <c r="I44" s="3" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="K44" s="3" t="n">
-        <v>0</v>
+        <v>3.7</v>
+      </c>
+      <c r="K44" s="8" t="n">
+        <v>6</v>
       </c>
       <c r="L44" s="3" t="n">
-        <v>22.3</v>
+        <v>21.6</v>
       </c>
       <c r="M44" s="3" t="n">
-        <v>82.3</v>
+        <v>21.5</v>
       </c>
       <c r="N44" s="3" t="n">
-        <v>26.9</v>
+        <v>25.6</v>
       </c>
       <c r="O44" s="3" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="P44" s="3" t="n">
-        <v>80</v>
+        <v>1.8</v>
       </c>
       <c r="Q44" s="3" t="n">
-        <v>22.6</v>
+        <v>29.1</v>
       </c>
       <c r="R44" s="3" t="n">
-        <v>26.4</v>
+        <v>25.5</v>
       </c>
       <c r="S44" s="3" t="n">
         <v>30.4</v>
       </c>
       <c r="T44" s="3" t="n">
-        <v>62</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="U44" s="3" t="n">
-        <v>18.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="V44" s="3" t="n">
-        <v>88.5</v>
+        <v>2.8</v>
       </c>
       <c r="W44" s="3" t="n">
-        <v>26.3</v>
+        <v>24.2</v>
       </c>
       <c r="X44" s="3" t="n">
-        <v>22.8</v>
+        <v>1.1</v>
       </c>
       <c r="Y44" s="3" t="n">
-        <v>84.40000000000001</v>
-      </c>
-      <c r="Z44" s="3" t="n">
-        <v>6</v>
-      </c>
+        <v>31.2</v>
+      </c>
+      <c r="Z44" s="3" t="n"/>
       <c r="AA44" s="3" t="inlineStr">
         <is>
           <t>31</t>
@@ -4248,76 +4394,85 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>20.8</v>
+        <v>365.9</v>
       </c>
       <c r="D45" s="10" t="n">
-        <v>190.6</v>
+        <v>32.5</v>
       </c>
       <c r="E45" s="10" t="n">
-        <v>121.6</v>
+        <v>21.2</v>
       </c>
       <c r="F45" s="10" t="n">
-        <v>156.1</v>
-      </c>
-      <c r="G45" s="10" t="n">
-        <v>69.09999999999999</v>
+        <v>26.9</v>
+      </c>
+      <c r="G45" s="3" t="n">
+        <v>1.3</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>427.4</v>
-      </c>
-      <c r="I45" s="3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="J45" s="3" t="n">
-        <v>18.8</v>
+        <v>49.4</v>
+      </c>
+      <c r="I45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">79727222
+785
+</t>
+        </is>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">79272
+1
+77
+</t>
+        </is>
       </c>
       <c r="K45" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L45" s="3" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="M45" s="3" t="n">
         <v>22.3</v>
-      </c>
-      <c r="M45" s="3" t="n">
-        <v>1825.9</v>
       </c>
       <c r="N45" s="3" t="n">
         <v>26.9</v>
       </c>
       <c r="O45" s="3" t="n">
-        <v>5983.8</v>
+        <v>40</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Q45" s="3" t="n">
-        <v>172.8</v>
+        <v>32.6</v>
       </c>
       <c r="R45" s="3" t="n">
-        <v>29.7</v>
+        <v>26.4</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>0.7</v>
+        <v>30.8</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>25.8</v>
+        <v>18.6</v>
       </c>
       <c r="V45" s="3" t="n">
-        <v>5.8</v>
+        <v>828.5</v>
       </c>
       <c r="W45" s="3" t="n">
-        <v>144.9</v>
+        <v>26.3</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>77.5</v>
+        <v>32.8</v>
       </c>
       <c r="Y45" s="3" t="n">
-        <v>503.7</v>
+        <v>84.8</v>
       </c>
       <c r="Z45" s="3" t="n">
-        <v>8</v>
+        <v>60.6</v>
       </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -4333,22 +4488,22 @@
         </is>
       </c>
       <c r="C46" s="3" t="n">
-        <v>237.6</v>
-      </c>
-      <c r="D46" s="10" t="n">
-        <v>31.7</v>
-      </c>
-      <c r="E46" s="10" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="F46" s="10" t="n">
-        <v>25.9</v>
-      </c>
-      <c r="G46" s="10" t="n">
-        <v>11.5</v>
+        <v>22.2</v>
+      </c>
+      <c r="D46" s="23" t="n">
+        <v>90.59999999999999</v>
+      </c>
+      <c r="E46" s="23" t="n">
+        <v>797.5</v>
+      </c>
+      <c r="F46" s="17" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="G46" s="3" t="n">
+        <v>69.09999999999999</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>19.1</v>
+        <v>7.7</v>
       </c>
       <c r="I46" s="3" t="n">
         <v>1.7</v>
@@ -4356,51 +4511,49 @@
       <c r="J46" s="3" t="n">
         <v>3.1</v>
       </c>
-      <c r="K46" s="3" t="n"/>
-      <c r="L46" s="3" t="n">
-        <v>21.1</v>
+      <c r="K46" s="3" t="n">
+        <v>98.3</v>
+      </c>
+      <c r="L46" s="8" t="n">
+        <v>26.5</v>
       </c>
       <c r="M46" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="N46" s="3" t="n">
-        <v>84.8</v>
-      </c>
+        <v>9.699999999999999</v>
+      </c>
+      <c r="N46" s="3" t="n"/>
       <c r="O46" s="3" t="n">
-        <v>99</v>
+        <v>593.8</v>
       </c>
       <c r="P46" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Q46" s="3" t="n">
-        <v>28.8</v>
+        <v>1.3</v>
+      </c>
+      <c r="Q46" s="8" t="n">
+        <v>72.8</v>
       </c>
       <c r="R46" s="3" t="n">
-        <v>21.8</v>
+        <v>79.7</v>
       </c>
       <c r="S46" s="3" t="n">
-        <v>29</v>
+        <v>72.7</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>75</v>
+        <v>7.7</v>
       </c>
       <c r="U46" s="3" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="V46" s="3" t="n">
-        <v>26.3</v>
-      </c>
-      <c r="W46" s="8" t="n">
-        <v>14.1</v>
-      </c>
+        <v>68.59999999999999</v>
+      </c>
+      <c r="V46" s="8" t="n">
+        <v>58.1</v>
+      </c>
+      <c r="W46" s="3" t="n"/>
       <c r="X46" s="3" t="n">
-        <v>28.7</v>
+        <v>0.3</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>23.9</v>
+        <v>23.7</v>
       </c>
       <c r="Z46" s="3" t="n">
-        <v>5.7</v>
+        <v>2</v>
       </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>

--- a/results/05_transient_transcription_output/203/203_196905_SF.JPG_stage_recalc_multi_day_tot_and_avgs.xlsx
+++ b/results/05_transient_transcription_output/203/203_196905_SF.JPG_stage_recalc_multi_day_tot_and_avgs.xlsx
@@ -26,7 +26,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -41,8 +41,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00CC3300"/>
-        <bgColor rgb="00CC3300"/>
+        <fgColor rgb="0075696F"/>
+        <bgColor rgb="0075696F"/>
       </patternFill>
     </fill>
     <fill>
@@ -53,8 +53,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="0075696F"/>
-        <bgColor rgb="0075696F"/>
+        <fgColor rgb="00CC3300"/>
+        <bgColor rgb="00CC3300"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC0CB"/>
+        <bgColor rgb="00FFC0CB"/>
       </patternFill>
     </fill>
   </fills>
@@ -125,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -141,6 +147,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -185,7 +200,16 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -802,7 +826,7 @@
         <v>186.2</v>
       </c>
       <c r="D4" s="10" t="n">
-        <v>28.2</v>
+        <v>28.1</v>
       </c>
       <c r="E4" s="10" t="n">
         <v>20</v>
@@ -811,64 +835,62 @@
         <v>24.1</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="H4" s="3" t="n">
-        <v>18.2</v>
+        <v>18.7</v>
+      </c>
+      <c r="H4" s="8" t="n">
+        <v>118.2</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>2.9</v>
+        <v>12.9</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="L4" s="3" t="n">
-        <v>2.2</v>
+        <v>0</v>
+      </c>
+      <c r="L4" s="8" t="n">
+        <v>20.2</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="N4" s="3" t="n">
-        <v>23.4</v>
+        <v>20.1</v>
+      </c>
+      <c r="N4" s="8" t="n">
+        <v>83.40000000000001</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>9</v>
+        <v>199</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Q4" s="3" t="n">
-        <v>28.2</v>
-      </c>
+        <v>10.2</v>
+      </c>
+      <c r="Q4" s="3" t="inlineStr"/>
       <c r="R4" s="3" t="n">
         <v>24.1</v>
       </c>
-      <c r="S4" s="3" t="n">
+      <c r="S4" s="8" t="n">
         <v>27.1</v>
       </c>
       <c r="T4" s="3" t="n">
         <v>68.90000000000001</v>
       </c>
-      <c r="U4" s="3" t="n">
+      <c r="U4" s="8" t="n">
         <v>12.2</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>25.8</v>
+        <v>25.2</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="X4" s="3" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="X4" s="8" t="n">
         <v>26.2</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>81.8</v>
+        <v>1811.8</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>5.8</v>
+        <v>15.8</v>
       </c>
       <c r="AA4" s="3" t="inlineStr">
         <is>
@@ -884,7 +906,7 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>438.5</v>
+        <v>2903.8</v>
       </c>
       <c r="D5" s="10" t="n">
         <v>32.6</v>
@@ -895,11 +917,11 @@
       <c r="F5" s="10" t="n">
         <v>25.4</v>
       </c>
-      <c r="G5" s="10" t="n">
-        <v>14.4</v>
+      <c r="G5" s="3" t="n">
+        <v>34.1</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>6.2</v>
+        <v>16.8</v>
       </c>
       <c r="I5" s="3" t="n">
         <v>3.5</v>
@@ -908,52 +930,52 @@
         <v>5.5</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="L5" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="L5" s="8" t="n">
         <v>18.9</v>
       </c>
       <c r="M5" s="3" t="n">
         <v>18.8</v>
       </c>
-      <c r="N5" s="3" t="n">
+      <c r="N5" s="8" t="n">
         <v>21.6</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>9</v>
+        <v>199</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>0.2</v>
+        <v>10.2</v>
       </c>
       <c r="Q5" s="3" t="n">
         <v>32.6</v>
       </c>
-      <c r="R5" s="3" t="n">
+      <c r="R5" s="8" t="n">
         <v>25.4</v>
       </c>
       <c r="S5" s="3" t="n">
         <v>27.8</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>56.6</v>
+        <v>156.6</v>
       </c>
       <c r="U5" s="3" t="n">
         <v>21.2</v>
       </c>
-      <c r="V5" s="3" t="n">
-        <v>87.2</v>
-      </c>
-      <c r="W5" s="3" t="n">
-        <v>24.6</v>
-      </c>
-      <c r="X5" s="3" t="n">
-        <v>2.8</v>
+      <c r="V5" s="8" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="W5" s="8" t="n">
+        <v>24</v>
+      </c>
+      <c r="X5" s="8" t="n">
+        <v>27.8</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AA5" s="3" t="inlineStr">
         <is>
@@ -969,60 +991,60 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>22.3</v>
+        <v>1422.3</v>
       </c>
       <c r="D6" s="10" t="n">
         <v>34.2</v>
       </c>
       <c r="E6" s="10" t="n">
-        <v>18.2</v>
+        <v>18.8</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="G6" s="3" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="G6" s="10" t="n">
         <v>15.4</v>
       </c>
-      <c r="H6" s="3" t="n">
-        <v>17.2</v>
+      <c r="H6" s="8" t="n">
+        <v>872.6</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>4.6</v>
+        <v>14.6</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>0.7</v>
+        <v>7.2</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L6" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="M6" s="8" t="n">
-        <v>66</v>
+      <c r="M6" s="3" t="n">
+        <v>20</v>
       </c>
       <c r="N6" s="3" t="n">
         <v>23.3</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="3" t="n">
-        <v>32.7</v>
+        <v>10</v>
+      </c>
+      <c r="Q6" s="8" t="n">
+        <v>21.7</v>
       </c>
       <c r="R6" s="3" t="n">
         <v>25.7</v>
       </c>
-      <c r="S6" s="3" t="n">
+      <c r="S6" s="8" t="n">
         <v>28.6</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>51.8</v>
-      </c>
-      <c r="U6" s="3" t="n">
+        <v>2929.8</v>
+      </c>
+      <c r="U6" s="8" t="n">
         <v>20.7</v>
       </c>
       <c r="V6" s="3" t="n">
@@ -1035,10 +1057,10 @@
         <v>26.1</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>66.40000000000001</v>
+        <v>166.4</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>13.2</v>
+        <v>13.8</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
@@ -1054,76 +1076,76 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>4778.5</v>
+        <v>4785.1</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>24.7</v>
+        <v>34.7</v>
       </c>
       <c r="E7" s="10" t="n">
-        <v>9.300000000000001</v>
+        <v>19.9</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>17</v>
-      </c>
-      <c r="G7" s="10" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="G7" s="3" t="n">
         <v>15.4</v>
       </c>
       <c r="H7" s="3" t="n">
         <v>18.2</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>2.3</v>
+        <v>4.3</v>
       </c>
       <c r="J7" s="3" t="n">
         <v>7.9</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L7" s="3" t="n">
         <v>20.1</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="N7" s="8" t="n">
-        <v>35.1</v>
+        <v>20.1</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>23.5</v>
       </c>
       <c r="O7" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="P7" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="P7" s="3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Q7" s="3" t="n">
+      <c r="Q7" s="8" t="n">
         <v>34.2</v>
       </c>
-      <c r="R7" s="3" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="S7" s="3" t="n">
-        <v>22.1</v>
+      <c r="R7" s="8" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="S7" s="8" t="n">
+        <v>27.1</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>50.6</v>
-      </c>
-      <c r="U7" s="3" t="n">
+        <v>120.6</v>
+      </c>
+      <c r="U7" s="8" t="n">
         <v>26.5</v>
       </c>
-      <c r="V7" s="3" t="n">
+      <c r="V7" s="8" t="n">
         <v>29.5</v>
       </c>
-      <c r="W7" s="3" t="n">
-        <v>84.09999999999999</v>
+      <c r="W7" s="8" t="n">
+        <v>24.4</v>
       </c>
       <c r="X7" s="3" t="n">
-        <v>8.300000000000001</v>
+        <v>27.3</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>66.2</v>
+        <v>166.2</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>438.5</v>
+        <v>13.8</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1139,67 +1161,67 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>299.6</v>
+        <v>1299</v>
       </c>
       <c r="D8" s="10" t="n">
-        <v>34.41</v>
+        <v>34.6</v>
       </c>
       <c r="E8" s="10" t="n">
         <v>20.6</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>27.5</v>
+        <v>27.6</v>
       </c>
       <c r="G8" s="10" t="n">
         <v>14</v>
       </c>
-      <c r="H8" s="3" t="n">
+      <c r="H8" s="8" t="n">
         <v>19</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="K8" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="K8" s="8" t="n">
         <v>30.9</v>
       </c>
       <c r="L8" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="M8" s="3" t="n">
+      <c r="M8" s="8" t="n">
         <v>20.6</v>
       </c>
-      <c r="N8" s="8" t="n">
-        <v>40.9</v>
+      <c r="N8" s="3" t="n">
+        <v>24</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>96.5</v>
+        <v>196.5</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="Q8" s="3" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="Q8" s="8" t="n">
         <v>21.4</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>2.2</v>
+        <v>21.2</v>
       </c>
       <c r="S8" s="3" t="n">
         <v>23.1</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>28</v>
+        <v>298</v>
       </c>
       <c r="U8" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>10.4</v>
       </c>
       <c r="V8" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="W8" s="3" t="n">
-        <v>24.9</v>
+        <v>22.2</v>
+      </c>
+      <c r="W8" s="8" t="n">
+        <v>1.9</v>
       </c>
       <c r="X8" s="3" t="n">
         <v>26.1</v>
@@ -1208,7 +1230,7 @@
         <v>97.40000000000001</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>26.6</v>
+        <v>20.6</v>
       </c>
       <c r="AA8" s="3" t="inlineStr">
         <is>
@@ -1224,19 +1246,19 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>1783.5</v>
+        <v>11783.5</v>
       </c>
       <c r="D9" s="10" t="n">
-        <v>164.8</v>
+        <v>164.2</v>
       </c>
       <c r="E9" s="10" t="n">
-        <v>96.8</v>
+        <v>97.5</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>130.8</v>
-      </c>
-      <c r="G9" s="10" t="n">
-        <v>67.90000000000001</v>
+        <v>130.9</v>
+      </c>
+      <c r="G9" s="20" t="n">
+        <v>16.2</v>
       </c>
       <c r="H9" s="3" t="n">
         <v>89.40000000000001</v>
@@ -1245,22 +1267,22 @@
         <v>16.5</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>27.5</v>
+        <v>127.5</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>3.9</v>
+        <v>30.9</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>16.2</v>
+        <v>100.2</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>99.59999999999999</v>
+        <v>199.6</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>15.8</v>
+        <v>112.8</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>494.5</v>
+        <v>1494.5</v>
       </c>
       <c r="P9" s="3" t="n">
         <v>1.2</v>
@@ -1272,32 +1294,28 @@
         <v>121.9</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>135.7</v>
+        <v>1135.7</v>
       </c>
       <c r="T9" s="3" t="n">
         <v>329.9</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="V9" s="3" t="n">
         <v>132.8</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>116.8</v>
+        <v>1116.8</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>133.5</v>
+        <v>1133.5</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>388.8</v>
-      </c>
-      <c r="Z9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">222424272
-777
-</t>
-        </is>
+        <v>1388.8</v>
+      </c>
+      <c r="Z9" s="3" t="n">
+        <v>141.6</v>
       </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
@@ -1328,7 +1346,7 @@
         <v>13.6</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>12.9</v>
+        <v>17.9</v>
       </c>
       <c r="I10" s="3" t="n">
         <v>3.3</v>
@@ -1336,15 +1354,9 @@
       <c r="J10" s="3" t="n">
         <v>5.5</v>
       </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11
-2221
-</t>
-        </is>
-      </c>
+      <c r="K10" s="3" t="inlineStr"/>
       <c r="L10" s="8" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="M10" s="3" t="n">
         <v>19.9</v>
@@ -1356,37 +1368,37 @@
         <v>98.90000000000001</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Q10" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q10" s="8" t="n">
         <v>29.9</v>
       </c>
-      <c r="R10" s="3" t="n">
+      <c r="R10" s="8" t="n">
         <v>24.4</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>2.1</v>
+        <v>27.1</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>66.90000000000001</v>
+        <v>166</v>
       </c>
       <c r="U10" s="3" t="n">
-        <v>1.2</v>
+        <v>16.2</v>
       </c>
       <c r="V10" s="3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="W10" s="3" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="W10" s="8" t="n">
         <v>23.4</v>
       </c>
       <c r="X10" s="3" t="n">
         <v>26.7</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>272.8</v>
+        <v>79.8</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>41.6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
@@ -1402,7 +1414,7 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>265.6</v>
+        <v>1265.6</v>
       </c>
       <c r="D11" s="10" t="n">
         <v>30.1</v>
@@ -1413,42 +1425,37 @@
       <c r="F11" s="10" t="n">
         <v>24.9</v>
       </c>
-      <c r="G11" s="3" t="n">
-        <v>1.3</v>
+      <c r="G11" s="10" t="n">
+        <v>10.3</v>
       </c>
       <c r="H11" s="3" t="n">
         <v>18.2</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>1.6</v>
+        <v>11.6</v>
       </c>
       <c r="J11" s="3" t="n">
         <v>2.8</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L11" s="3" t="n">
         <v>21.2</v>
       </c>
-      <c r="M11" s="3" t="n">
+      <c r="M11" s="8" t="n">
         <v>20.9</v>
       </c>
-      <c r="N11" s="3" t="n">
+      <c r="N11" s="8" t="n">
         <v>24.5</v>
       </c>
-      <c r="O11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">897
-505
-1799
-</t>
-        </is>
+      <c r="O11" s="3" t="n">
+        <v>927.3</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="Q11" s="8" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="Q11" s="3" t="n">
         <v>29.9</v>
       </c>
       <c r="R11" s="3" t="n">
@@ -1458,13 +1465,13 @@
         <v>29.8</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>720.6</v>
+        <v>170.6</v>
       </c>
       <c r="U11" s="3" t="n">
         <v>12.4</v>
       </c>
-      <c r="V11" s="3" t="n">
-        <v>2.1</v>
+      <c r="V11" s="8" t="n">
+        <v>27.1</v>
       </c>
       <c r="W11" s="3" t="n">
         <v>24.9</v>
@@ -1473,14 +1480,10 @@
         <v>30.1</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="Z11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">244
-744
-</t>
-        </is>
+        <v>684</v>
+      </c>
+      <c r="Z11" s="3" t="n">
+        <v>5.1</v>
       </c>
       <c r="AA11" s="3" t="inlineStr">
         <is>
@@ -1496,7 +1499,7 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>342.4</v>
+        <v>247.1</v>
       </c>
       <c r="D12" s="10" t="n">
         <v>31.8</v>
@@ -1510,32 +1513,32 @@
       <c r="G12" s="10" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="H12" s="3" t="n">
+      <c r="H12" s="8" t="n">
         <v>21.2</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>2.7</v>
+        <v>22.1</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>4.6</v>
+        <v>14.6</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="L12" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="L12" s="8" t="n">
         <v>23.3</v>
       </c>
-      <c r="M12" s="3" t="n">
+      <c r="M12" s="8" t="n">
         <v>23</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>2.9</v>
+        <v>21.9</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>9.300000000000001</v>
+        <v>27.5</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0.5</v>
+        <v>10.8</v>
       </c>
       <c r="Q12" s="3" t="n">
         <v>31.8</v>
@@ -1547,25 +1550,25 @@
         <v>27.1</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>57.8</v>
+        <v>59.8</v>
       </c>
       <c r="U12" s="3" t="n">
-        <v>1.8</v>
+        <v>19.8</v>
       </c>
       <c r="V12" s="3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="W12" s="3" t="n">
-        <v>24.6</v>
+        <v>27.9</v>
+      </c>
+      <c r="W12" s="8" t="n">
+        <v>284.6</v>
       </c>
       <c r="X12" s="3" t="n">
         <v>28.8</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>7.7</v>
+        <v>76.7</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>57.2</v>
+        <v>181.7</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1581,34 +1584,34 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>428.6</v>
+        <v>1428.6</v>
       </c>
       <c r="D13" s="10" t="n">
-        <v>32.8</v>
+        <v>33.1</v>
       </c>
       <c r="E13" s="10" t="n">
-        <v>20.4</v>
+        <v>20.1</v>
       </c>
       <c r="F13" s="10" t="n">
         <v>26.6</v>
       </c>
-      <c r="G13" s="10" t="n">
+      <c r="G13" s="3" t="n">
         <v>12.4</v>
       </c>
       <c r="H13" s="3" t="n">
         <v>19.9</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>3.3</v>
+        <v>13.3</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>2.1</v>
+        <v>22.1</v>
       </c>
       <c r="M13" s="3" t="n">
         <v>21.9</v>
@@ -1617,15 +1620,15 @@
         <v>26.1</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>9.5</v>
+        <v>98</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>26.4</v>
+        <v>0.4</v>
       </c>
       <c r="Q13" s="3" t="n">
         <v>32.6</v>
       </c>
-      <c r="R13" s="3" t="n">
+      <c r="R13" s="8" t="n">
         <v>24.6</v>
       </c>
       <c r="S13" s="3" t="n">
@@ -1637,8 +1640,8 @@
       <c r="U13" s="3" t="n">
         <v>23.3</v>
       </c>
-      <c r="V13" s="3" t="n">
-        <v>28.6</v>
+      <c r="V13" s="8" t="n">
+        <v>28</v>
       </c>
       <c r="W13" s="3" t="n">
         <v>24.8</v>
@@ -1647,10 +1650,10 @@
         <v>29.3</v>
       </c>
       <c r="Y13" s="3" t="n">
-        <v>7.6</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="Z13" s="3" t="n">
-        <v>23.1</v>
+        <v>18.3</v>
       </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
@@ -1680,32 +1683,32 @@
       <c r="G14" s="10" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="H14" s="3" t="n">
-        <v>2.3</v>
+      <c r="H14" s="8" t="n">
+        <v>20.3</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J14" s="3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="K14" s="8" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="L14" s="3" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="M14" s="3" t="n">
         <v>22.1</v>
       </c>
-      <c r="K14" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="L14" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="M14" s="3" t="n">
-        <v>2.1</v>
-      </c>
       <c r="N14" s="3" t="n">
-        <v>26.4</v>
+        <v>264</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>98.09999999999999</v>
+        <v>197.3</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>0.7</v>
+        <v>0.1</v>
       </c>
       <c r="Q14" s="3" t="n">
         <v>22.4</v>
@@ -1713,29 +1716,29 @@
       <c r="R14" s="3" t="n">
         <v>21.1</v>
       </c>
-      <c r="S14" s="3" t="n">
+      <c r="S14" s="8" t="n">
         <v>24.2</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>89</v>
+        <v>189</v>
       </c>
       <c r="U14" s="3" t="n">
         <v>2.9</v>
       </c>
       <c r="V14" s="3" t="n">
-        <v>26</v>
-      </c>
-      <c r="W14" s="8" t="n">
-        <v>41.6</v>
-      </c>
-      <c r="X14" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="W14" s="3" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="X14" s="8" t="n">
         <v>25.5</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>96</v>
+        <v>196</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>2.5</v>
+        <v>9.1</v>
       </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
@@ -1751,31 +1754,31 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>5.6</v>
+        <v>359.6</v>
       </c>
       <c r="D15" s="10" t="n">
         <v>32.5</v>
       </c>
       <c r="E15" s="10" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="F15" s="10" t="n">
         <v>26.7</v>
       </c>
-      <c r="G15" s="3" t="n">
-        <v>1.7</v>
+      <c r="G15" s="10" t="n">
+        <v>11.7</v>
       </c>
       <c r="H15" s="3" t="n">
         <v>19.6</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>2.4</v>
+        <v>18.4</v>
       </c>
       <c r="J15" s="3" t="n">
         <v>3.9</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>25.7</v>
+        <v>25.1</v>
       </c>
       <c r="L15" s="3" t="n">
         <v>21.6</v>
@@ -1787,12 +1790,12 @@
         <v>25.8</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>9.300000000000001</v>
+        <v>1100</v>
       </c>
       <c r="P15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q15" s="8" t="n">
         <v>32</v>
       </c>
       <c r="R15" s="3" t="n">
@@ -1802,7 +1805,7 @@
         <v>29.2</v>
       </c>
       <c r="T15" s="3" t="n">
-        <v>61.7</v>
+        <v>161.7</v>
       </c>
       <c r="U15" s="3" t="n">
         <v>18.2</v>
@@ -1810,8 +1813,8 @@
       <c r="V15" s="3" t="n">
         <v>28.7</v>
       </c>
-      <c r="W15" s="3" t="n">
-        <v>4.8</v>
+      <c r="W15" s="8" t="n">
+        <v>24.8</v>
       </c>
       <c r="X15" s="3" t="n">
         <v>28.8</v>
@@ -1820,7 +1823,7 @@
         <v>73.09999999999999</v>
       </c>
       <c r="Z15" s="3" t="n">
-        <v>20.9</v>
+        <v>10.1</v>
       </c>
       <c r="AA15" s="3" t="inlineStr">
         <is>
@@ -1836,13 +1839,13 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1591.2</v>
+        <v>1291.2</v>
       </c>
       <c r="D16" s="10" t="n">
-        <v>157.9</v>
+        <v>158.2</v>
       </c>
       <c r="E16" s="10" t="n">
-        <v>105.6</v>
+        <v>105.2</v>
       </c>
       <c r="F16" s="10" t="n">
         <v>131.7</v>
@@ -1851,42 +1854,28 @@
         <v>52.4</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>929.2</v>
+        <v>99.2</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>11.5</v>
+        <v>111.5</v>
       </c>
       <c r="J16" s="3" t="n">
         <v>19.4</v>
       </c>
-      <c r="K16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">790691
-22
-5682
-</t>
-        </is>
+      <c r="K16" s="3" t="n">
+        <v>36.8</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>10.6</v>
+        <v>1110.6</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="N16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">791727
-14
-000
-</t>
-        </is>
-      </c>
-      <c r="O16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11722
-77218
-</t>
-        </is>
+        <v>109.5</v>
+      </c>
+      <c r="N16" s="3" t="n">
+        <v>1130.7</v>
+      </c>
+      <c r="O16" s="3" t="n">
+        <v>27490.1</v>
       </c>
       <c r="P16" s="3" t="n">
         <v>2.2</v>
@@ -1895,47 +1884,31 @@
         <v>148.7</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>121.9</v>
+        <v>1121.9</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>136.1</v>
+        <v>1136.1</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>31.8</v>
+        <v>331.8</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>76.59999999999999</v>
-      </c>
-      <c r="V16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7277978
-7566
-</t>
-        </is>
-      </c>
-      <c r="W16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22414
-8711011466 7
-</t>
-        </is>
-      </c>
-      <c r="X16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">36595
-99781
-</t>
-        </is>
-      </c>
-      <c r="Y16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5555
-5721
-</t>
-        </is>
+        <v>176.6</v>
+      </c>
+      <c r="V16" s="3" t="n">
+        <v>133.7</v>
+      </c>
+      <c r="W16" s="3" t="n">
+        <v>1120.7</v>
+      </c>
+      <c r="X16" s="3" t="n">
+        <v>162.5</v>
+      </c>
+      <c r="Y16" s="3" t="n">
+        <v>1407.4</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>741.1</v>
+        <v>34.4</v>
       </c>
       <c r="AA16" s="3" t="inlineStr">
         <is>
@@ -1951,7 +1924,7 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>38.2</v>
+        <v>1318.2</v>
       </c>
       <c r="D17" s="10" t="n">
         <v>31.6</v>
@@ -1965,32 +1938,30 @@
       <c r="G17" s="10" t="n">
         <v>10.5</v>
       </c>
-      <c r="H17" s="8" t="n">
-        <v>292.8</v>
+      <c r="H17" s="3" t="n">
+        <v>19.8</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>2.3</v>
+        <v>12.3</v>
       </c>
       <c r="J17" s="3" t="n">
         <v>3.9</v>
       </c>
-      <c r="K17" s="3" t="n">
-        <v>36.8</v>
-      </c>
+      <c r="K17" s="3" t="inlineStr"/>
       <c r="L17" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="M17" s="3" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="M17" s="8" t="n">
         <v>21.9</v>
       </c>
-      <c r="N17" s="8" t="n">
-        <v>30.7</v>
+      <c r="N17" s="3" t="n">
+        <v>26.1</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>490.1</v>
+        <v>98</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="Q17" s="3" t="n">
         <v>29.7</v>
@@ -1998,29 +1969,29 @@
       <c r="R17" s="3" t="n">
         <v>24.4</v>
       </c>
-      <c r="S17" s="3" t="n">
-        <v>2.2</v>
+      <c r="S17" s="8" t="n">
+        <v>28.2</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>6.4</v>
+        <v>166.4</v>
       </c>
       <c r="U17" s="3" t="n">
         <v>15.3</v>
       </c>
       <c r="V17" s="8" t="n">
-        <v>33.7</v>
+        <v>26.7</v>
       </c>
       <c r="W17" s="8" t="n">
-        <v>26.7</v>
-      </c>
-      <c r="X17" s="8" t="n">
-        <v>42.5</v>
+        <v>24.1</v>
+      </c>
+      <c r="X17" s="3" t="n">
+        <v>28.5</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>47.6</v>
+        <v>181.5</v>
       </c>
       <c r="Z17" s="3" t="n">
-        <v>6.9</v>
+        <v>16.9</v>
       </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
@@ -2036,19 +2007,19 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>368</v>
+        <v>1368</v>
       </c>
       <c r="D18" s="10" t="n">
-        <v>32.2</v>
+        <v>32.6</v>
       </c>
       <c r="E18" s="10" t="n">
-        <v>21.3</v>
+        <v>20.6</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>26.6</v>
+        <v>26.7</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>16.9</v>
+        <v>10.9</v>
       </c>
       <c r="H18" s="3" t="n">
         <v>20.4</v>
@@ -2056,31 +2027,23 @@
       <c r="I18" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="J18" s="3" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="K18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-222
-</t>
-        </is>
+      <c r="J18" s="8" t="n">
+        <v>46.3</v>
+      </c>
+      <c r="K18" s="8" t="n">
+        <v>10.4</v>
       </c>
       <c r="L18" s="3" t="n">
-        <v>24.4</v>
+        <v>21.4</v>
       </c>
       <c r="M18" s="3" t="n">
         <v>21.1</v>
       </c>
-      <c r="N18" s="3" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="O18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">27844
-171719
-</t>
-        </is>
+      <c r="N18" s="8" t="n">
+        <v>224.8</v>
+      </c>
+      <c r="O18" s="3" t="n">
+        <v>97.3</v>
       </c>
       <c r="P18" s="3" t="n">
         <v>0.6</v>
@@ -2088,40 +2051,32 @@
       <c r="Q18" s="3" t="n">
         <v>32.1</v>
       </c>
-      <c r="R18" s="3" t="n">
+      <c r="R18" s="8" t="n">
         <v>25.2</v>
       </c>
-      <c r="S18" s="3" t="n">
-        <v>7.7</v>
+      <c r="S18" s="8" t="n">
+        <v>27.7</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>58.5</v>
+        <v>98</v>
       </c>
       <c r="U18" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="V18" s="3" t="n">
-        <v>26.7</v>
-      </c>
-      <c r="W18" s="3" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="X18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7444
-1779 7
-</t>
-        </is>
-      </c>
-      <c r="Y18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">09442
-77 7
-</t>
-        </is>
+      <c r="V18" s="8" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="W18" s="8" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="X18" s="3" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="Y18" s="3" t="n">
+        <v>71.2</v>
       </c>
       <c r="Z18" s="3" t="n">
-        <v>17.1</v>
+        <v>111</v>
       </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
@@ -2137,13 +2092,13 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>265.6</v>
+        <v>2260.6</v>
       </c>
       <c r="D19" s="10" t="n">
-        <v>30</v>
+        <v>30.4</v>
       </c>
       <c r="E19" s="10" t="n">
-        <v>22.2</v>
+        <v>22.6</v>
       </c>
       <c r="F19" s="10" t="n">
         <v>26.5</v>
@@ -2151,32 +2106,32 @@
       <c r="G19" s="3" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="H19" s="3" t="n">
+      <c r="H19" s="8" t="n">
         <v>21.4</v>
       </c>
       <c r="I19" s="3" t="n">
         <v>1.6</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>2.8</v>
+        <v>12.8</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="L19" s="3" t="n">
-        <v>2.3</v>
+        <v>11.2</v>
+      </c>
+      <c r="L19" s="8" t="n">
+        <v>22.3</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>24.8</v>
+        <v>86.3</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>297.3</v>
+        <v>197.6</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>0.6</v>
+        <v>10.6</v>
       </c>
       <c r="Q19" s="3" t="n">
         <v>29.9</v>
@@ -2193,20 +2148,20 @@
       <c r="U19" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="V19" s="3" t="n">
-        <v>28.5</v>
+      <c r="V19" s="8" t="n">
+        <v>24.3</v>
       </c>
       <c r="W19" s="3" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="X19" s="3" t="n">
-        <v>2.9</v>
+        <v>22.9</v>
+      </c>
+      <c r="X19" s="8" t="n">
+        <v>71.09999999999999</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>7218.7</v>
+        <v>89</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>3.3</v>
+        <v>78.3</v>
       </c>
       <c r="AA19" s="3" t="inlineStr">
         <is>
@@ -2225,28 +2180,28 @@
         <v>365.9</v>
       </c>
       <c r="D20" s="10" t="n">
-        <v>31.4</v>
+        <v>31.5</v>
       </c>
       <c r="E20" s="10" t="n">
         <v>21.6</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>26.5</v>
-      </c>
-      <c r="G20" s="10" t="n">
-        <v>9.9</v>
+        <v>26.4</v>
+      </c>
+      <c r="G20" s="3" t="n">
+        <v>19.9</v>
       </c>
       <c r="H20" s="3" t="n">
         <v>20.6</v>
       </c>
-      <c r="I20" s="3" t="n">
-        <v>2.5</v>
+      <c r="I20" s="8" t="n">
+        <v>28.1</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>4.5</v>
+        <v>14.5</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>1.2</v>
+        <v>10</v>
       </c>
       <c r="L20" s="3" t="n">
         <v>21.6</v>
@@ -2254,42 +2209,44 @@
       <c r="M20" s="3" t="n">
         <v>21.4</v>
       </c>
-      <c r="N20" s="3" t="n">
-        <v>26.3</v>
+      <c r="N20" s="8" t="n">
+        <v>35.4</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="P20" s="3" t="n"/>
+        <v>98</v>
+      </c>
+      <c r="P20" s="3" t="n">
+        <v>0.4</v>
+      </c>
       <c r="Q20" s="3" t="n">
-        <v>30.7</v>
-      </c>
-      <c r="R20" s="3" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="R20" s="8" t="n">
         <v>24.8</v>
       </c>
       <c r="S20" s="3" t="n">
         <v>27.5</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>62.3</v>
+        <v>162.3</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>1.6</v>
+        <v>16.6</v>
       </c>
       <c r="V20" s="3" t="n">
-        <v>24.3</v>
-      </c>
-      <c r="W20" s="3" t="n">
-        <v>2.9</v>
+        <v>27.3</v>
+      </c>
+      <c r="W20" s="8" t="n">
+        <v>23.8</v>
       </c>
       <c r="X20" s="3" t="n">
-        <v>27.1</v>
+        <v>27.2</v>
       </c>
       <c r="Y20" s="3" t="n">
-        <v>89</v>
+        <v>715</v>
       </c>
       <c r="Z20" s="3" t="n">
-        <v>9.1</v>
+        <v>19.1</v>
       </c>
       <c r="AA20" s="3" t="inlineStr">
         <is>
@@ -2311,13 +2268,13 @@
         <v>30.6</v>
       </c>
       <c r="E21" s="10" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="F21" s="10" t="n">
         <v>25.9</v>
       </c>
-      <c r="G21" s="10" t="n">
-        <v>9.5</v>
+      <c r="G21" s="3" t="n">
+        <v>29.5</v>
       </c>
       <c r="H21" s="3" t="n">
         <v>19.6</v>
@@ -2329,22 +2286,22 @@
         <v>3.4</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" s="3" t="n">
-        <v>2.6</v>
+        <v>10</v>
+      </c>
+      <c r="L21" s="8" t="n">
+        <v>18.6</v>
       </c>
       <c r="M21" s="3" t="n">
         <v>21.5</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>25.4</v>
+        <v>25.6</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>986</v>
+        <v>199</v>
       </c>
       <c r="P21" s="3" t="n">
-        <v>6.2</v>
+        <v>10.2</v>
       </c>
       <c r="Q21" s="3" t="n">
         <v>30.6</v>
@@ -2356,25 +2313,25 @@
         <v>31.2</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>4.2</v>
+        <v>71.2</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="V21" s="3" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="W21" s="3" t="n">
-        <v>23.8</v>
+        <v>12.6</v>
+      </c>
+      <c r="V21" s="8" t="n">
+        <v>78.8</v>
+      </c>
+      <c r="W21" s="8" t="n">
+        <v>16.6</v>
       </c>
       <c r="X21" s="3" t="n">
-        <v>7.2</v>
+        <v>28.9</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>75</v>
+        <v>77.3</v>
       </c>
       <c r="Z21" s="3" t="n">
-        <v>8.4</v>
+        <v>18.4</v>
       </c>
       <c r="AA21" s="3" t="inlineStr">
         <is>
@@ -2390,49 +2347,46 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>395.3</v>
+        <v>399.3</v>
       </c>
       <c r="D22" s="10" t="n">
-        <v>-66.40000000000001</v>
-      </c>
-      <c r="E22" s="3" t="n">
+        <v>32.9</v>
+      </c>
+      <c r="E22" s="10" t="n">
         <v>21.1</v>
       </c>
       <c r="F22" s="10" t="n">
-        <v>-73</v>
+        <v>27</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>14.8</v>
+        <v>12.8</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>12.8</v>
+        <v>19.8</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>2.5</v>
+        <v>12.5</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>4.3</v>
+        <v>14.3</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>0.6</v>
+        <v>2.1</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>2.3</v>
+        <v>21.3</v>
       </c>
       <c r="M22" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="N22" s="3" t="n">
-        <v>25.6</v>
+      <c r="N22" s="8" t="n">
+        <v>24.7</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>99.59999999999999</v>
-      </c>
-      <c r="P22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">68 2
-</t>
-        </is>
+        <v>97.5</v>
+      </c>
+      <c r="P22" s="3" t="n">
+        <v>0.4</v>
       </c>
       <c r="Q22" s="3" t="n">
         <v>32.4</v>
@@ -2443,29 +2397,26 @@
       <c r="S22" s="3" t="n">
         <v>89.3</v>
       </c>
-      <c r="T22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">65 2
-</t>
-        </is>
+      <c r="T22" s="3" t="n">
+        <v>160.5</v>
       </c>
       <c r="U22" s="3" t="n">
         <v>19.2</v>
       </c>
       <c r="V22" s="3" t="n">
-        <v>27.8</v>
+        <v>26.8</v>
       </c>
       <c r="W22" s="3" t="n">
         <v>24.6</v>
       </c>
-      <c r="X22" s="3" t="n">
-        <v>84.90000000000001</v>
+      <c r="X22" s="8" t="n">
+        <v>29.1</v>
       </c>
       <c r="Y22" s="3" t="n">
-        <v>72.3</v>
+        <v>186</v>
       </c>
       <c r="Z22" s="3" t="n">
-        <v>4.9</v>
+        <v>14.9</v>
       </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
@@ -2481,62 +2432,43 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>739.6</v>
+        <v>17439.6</v>
       </c>
       <c r="D23" s="10" t="n">
-        <v>57.8</v>
-      </c>
-      <c r="E23" s="17" t="n">
-        <v>7.2</v>
+        <v>158</v>
+      </c>
+      <c r="E23" s="10" t="n">
+        <v>107</v>
       </c>
       <c r="F23" s="10" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="G23" s="3" t="n">
-        <v>50.3</v>
-      </c>
-      <c r="H23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">41444444
-1
-8684
-</t>
-        </is>
-      </c>
-      <c r="I23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">27955
-42
-12141
-</t>
-        </is>
-      </c>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">212
-1141089
-</t>
-        </is>
+        <v>132.5</v>
+      </c>
+      <c r="G23" s="20" t="n">
+        <v>25</v>
+      </c>
+      <c r="H23" s="3" t="n">
+        <v>1101.8</v>
+      </c>
+      <c r="I23" s="3" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="J23" s="3" t="n">
+        <v>19.3</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>7.7</v>
+        <v>19.3</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>18.2</v>
+        <v>108.2</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>17</v>
+        <v>1107</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="O23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">418686866
-50756012
-1441
-</t>
-        </is>
+        <v>1126.8</v>
+      </c>
+      <c r="O23" s="3" t="n">
+        <v>1489.4</v>
       </c>
       <c r="P23" s="3" t="n">
         <v>2.2</v>
@@ -2548,28 +2480,28 @@
         <v>128.1</v>
       </c>
       <c r="S23" s="3" t="n">
-        <v>146.8</v>
+        <v>1146.8</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>325.7</v>
+        <v>325.1</v>
       </c>
       <c r="U23" s="3" t="n">
         <v>79.40000000000001</v>
       </c>
       <c r="V23" s="3" t="n">
-        <v>86.5</v>
+        <v>134.4</v>
       </c>
       <c r="W23" s="3" t="n">
-        <v>24.6</v>
+        <v>120.3</v>
       </c>
       <c r="X23" s="3" t="n">
-        <v>2.7</v>
+        <v>140.8</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>860.6</v>
+        <v>2399</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>3.7</v>
+        <v>36.7</v>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -2585,84 +2517,74 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>739.6</v>
+        <v>347.9</v>
       </c>
       <c r="D24" s="10" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="E24" s="17" t="n">
-        <v>7.2</v>
+        <v>31.6</v>
+      </c>
+      <c r="E24" s="10" t="n">
+        <v>21.4</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="G24" s="3" t="n">
-        <v>50.3</v>
-      </c>
-      <c r="H24" s="8" t="n">
-        <v>1.8</v>
+        <v>26.5</v>
+      </c>
+      <c r="G24" s="10" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="H24" s="3" t="n">
+        <v>20.4</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>1.9</v>
+        <v>12.2</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="K24" s="3" t="n">
-        <v>19.3</v>
-      </c>
+        <v>3.9</v>
+      </c>
+      <c r="K24" s="3" t="inlineStr"/>
       <c r="L24" s="3" t="n">
-        <v>18.2</v>
+        <v>21.6</v>
       </c>
       <c r="M24" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="N24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6169690911
-2929
-</t>
-        </is>
+        <v>21.4</v>
+      </c>
+      <c r="N24" s="8" t="n">
+        <v>22.4</v>
       </c>
       <c r="O24" s="3" t="n">
         <v>97.90000000000001</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q24" s="8" t="n">
-        <v>55.7</v>
-      </c>
-      <c r="R24" s="8" t="n">
-        <v>28.1</v>
-      </c>
-      <c r="S24" s="8" t="n">
-        <v>46.8</v>
+        <v>0.4</v>
+      </c>
+      <c r="Q24" s="3" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="S24" s="3" t="n">
+        <v>29.4</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>325.7</v>
+        <v>165.1</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>79.40000000000001</v>
-      </c>
-      <c r="V24" s="8" t="n">
-        <v>34.4</v>
-      </c>
-      <c r="W24" s="3" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="X24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">74950
-448468
-</t>
-        </is>
+        <v>15.9</v>
+      </c>
+      <c r="V24" s="3" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="W24" s="8" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="X24" s="8" t="n">
+        <v>282.2</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>399</v>
+        <v>79.8</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>7.3</v>
+        <v>17.3</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2678,77 +2600,73 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>34.9</v>
+        <v>106.7</v>
       </c>
       <c r="D25" s="10" t="n">
-        <v>31.6</v>
+        <v>26.4</v>
       </c>
       <c r="E25" s="10" t="n">
-        <v>21.5</v>
+        <v>20.7</v>
       </c>
       <c r="F25" s="10" t="n">
-        <v>26.4</v>
+        <v>23.5</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>1.1</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>20.4</v>
+        <v>20.2</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>3.9</v>
+        <v>0.5</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>19.3</v>
+        <v>23.7</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>21.6</v>
+        <v>22.4</v>
       </c>
       <c r="M25" s="3" t="n">
-        <v>21.4</v>
-      </c>
-      <c r="N25" s="8" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="N25" s="3" t="n">
+        <v>264.4</v>
+      </c>
+      <c r="O25" s="3" t="n">
+        <v>97</v>
+      </c>
+      <c r="P25" s="3" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="Q25" s="3" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="R25" s="8" t="n">
+        <v>284.1</v>
+      </c>
+      <c r="S25" s="8" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="T25" s="3" t="n">
+        <v>184.4</v>
+      </c>
+      <c r="U25" s="3" t="inlineStr"/>
+      <c r="V25" s="3" t="n">
+        <v>244.1</v>
+      </c>
+      <c r="W25" s="3" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="X25" s="8" t="n">
         <v>26.8</v>
       </c>
-      <c r="O25" s="3" t="n">
-        <v>97.90000000000001</v>
-      </c>
-      <c r="P25" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="Q25" s="3" t="n">
-        <v>31.1</v>
-      </c>
-      <c r="R25" s="3" t="n">
-        <v>156.1</v>
-      </c>
-      <c r="S25" s="3" t="n">
-        <v>29.4</v>
-      </c>
-      <c r="T25" s="3" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="U25" s="3" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="V25" s="3" t="n">
-        <v>26.9</v>
-      </c>
-      <c r="W25" s="3" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="X25" s="8" t="n">
-        <v>40.8</v>
-      </c>
       <c r="Y25" s="3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Z25" s="3" t="n">
-        <v>7.3</v>
-      </c>
+        <v>81.7</v>
+      </c>
+      <c r="Z25" s="3" t="inlineStr"/>
       <c r="AA25" s="3" t="inlineStr">
         <is>
           <t>16</t>
@@ -2763,92 +2681,76 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>16.7</v>
+        <v>290</v>
       </c>
       <c r="D26" s="10" t="n">
-        <v>26.4</v>
+        <v>37.2</v>
       </c>
       <c r="E26" s="10" t="n">
-        <v>20.6</v>
+        <v>21</v>
       </c>
       <c r="F26" s="10" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="G26" s="10" t="n">
-        <v>5.7</v>
+        <v>29.1</v>
+      </c>
+      <c r="G26" s="3" t="n">
+        <v>14.1</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="I26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">215852
-147
-</t>
-        </is>
+        <v>19.2</v>
+      </c>
+      <c r="I26" s="3" t="n">
+        <v>10.9</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="K26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-77
-</t>
-        </is>
+        <v>0.7</v>
+      </c>
+      <c r="K26" s="3" t="n">
+        <v>16.1</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>22.4</v>
+        <v>21.4</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>24.1</v>
+        <v>21.4</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>25.4</v>
+        <v>25.5</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>6.7</v>
+        <v>10</v>
       </c>
       <c r="Q26" s="3" t="n">
-        <v>26.2</v>
-      </c>
-      <c r="R26" s="3" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="S26" s="3" t="n">
-        <v>28.7</v>
+        <v>24.3</v>
+      </c>
+      <c r="R26" s="8" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="S26" s="8" t="n">
+        <v>280.9</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>84.40000000000001</v>
+        <v>192</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>5.3</v>
+        <v>12.9</v>
       </c>
       <c r="V26" s="3" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="W26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7771717
-11811408 7
-</t>
-        </is>
-      </c>
-      <c r="X26" s="3" t="n">
-        <v>2.2</v>
+        <v>23.8</v>
+      </c>
+      <c r="W26" s="3" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="X26" s="8" t="n">
+        <v>79.09999999999999</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>87.7</v>
-      </c>
-      <c r="Z26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">88
-893
-</t>
-        </is>
+        <v>191.8</v>
+      </c>
+      <c r="Z26" s="3" t="n">
+        <v>2.4</v>
       </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
@@ -2864,69 +2766,73 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>90</v>
+        <v>2322</v>
       </c>
       <c r="D27" s="10" t="n">
-        <v>25.2</v>
+        <v>30.4</v>
       </c>
       <c r="E27" s="10" t="n">
-        <v>21.1</v>
+        <v>20.6</v>
       </c>
       <c r="F27" s="10" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="G27" s="10" t="n">
-        <v>4.1</v>
+        <v>25.5</v>
+      </c>
+      <c r="G27" s="3" t="n">
+        <v>19.9</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="I27" s="3" t="n"/>
-      <c r="J27" s="3" t="n"/>
-      <c r="K27" s="3" t="n"/>
+        <v>19.1</v>
+      </c>
+      <c r="I27" s="3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J27" s="3" t="inlineStr"/>
+      <c r="K27" s="3" t="n">
+        <v>10</v>
+      </c>
       <c r="L27" s="3" t="n">
-        <v>21.4</v>
+        <v>20.7</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>2.4</v>
+        <v>20.5</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>26.4</v>
-      </c>
-      <c r="O27" s="3" t="n"/>
+        <v>24</v>
+      </c>
+      <c r="O27" s="3" t="n">
+        <v>198</v>
+      </c>
       <c r="P27" s="3" t="n">
-        <v>8</v>
+        <v>0.4</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="R27" s="3" t="n">
-        <v>23.3</v>
+        <v>28.8</v>
+      </c>
+      <c r="R27" s="8" t="n">
+        <v>24.9</v>
       </c>
       <c r="S27" s="8" t="n">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="T27" s="3" t="n">
-        <v>926</v>
+        <v>73.2</v>
       </c>
       <c r="U27" s="3" t="n">
-        <v>2.4</v>
+        <v>10.5</v>
       </c>
       <c r="V27" s="3" t="n">
-        <v>23.8</v>
+        <v>26.9</v>
       </c>
       <c r="W27" s="3" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="X27" s="3" t="n">
-        <v>26.8</v>
+        <v>24.4</v>
+      </c>
+      <c r="X27" s="8" t="n">
+        <v>29</v>
       </c>
       <c r="Y27" s="3" t="n">
-        <v>91.8</v>
-      </c>
-      <c r="Z27" s="3" t="n">
-        <v>3.8</v>
-      </c>
+        <v>81.8</v>
+      </c>
+      <c r="Z27" s="3" t="inlineStr"/>
       <c r="AA27" s="3" t="inlineStr">
         <is>
           <t>18</t>
@@ -2941,80 +2847,74 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>322</v>
+        <v>1290.7</v>
       </c>
       <c r="D28" s="10" t="n">
-        <v>30.4</v>
+        <v>19.5</v>
       </c>
       <c r="E28" s="10" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="F28" s="10" t="n">
+        <v>36.1</v>
+      </c>
+      <c r="G28" s="8" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="H28" s="3" t="inlineStr"/>
+      <c r="I28" s="3" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J28" s="3" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K28" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="L28" s="8" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="M28" s="3" t="n">
         <v>20.6</v>
       </c>
-      <c r="F28" s="10" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="G28" s="10" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="H28" s="8" t="n">
-        <v>29.1</v>
-      </c>
-      <c r="I28" s="3" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="J28" s="3" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="K28" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="L28" s="3" t="n">
-        <v>20.7</v>
-      </c>
-      <c r="M28" s="3" t="n">
-        <v>26.5</v>
-      </c>
-      <c r="N28" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="O28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">280
-2923
-</t>
-        </is>
+      <c r="N28" s="8" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="O28" s="3" t="n">
+        <v>297.3</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>16.4</v>
+        <v>10.8</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>28.8</v>
-      </c>
-      <c r="R28" s="3" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="S28" s="3" t="n">
-        <v>29</v>
+        <v>31.2</v>
+      </c>
+      <c r="R28" s="8" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="S28" s="8" t="n">
+        <v>27.2</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>73.2</v>
+        <v>160.2</v>
       </c>
       <c r="U28" s="3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V28" s="3" t="n">
-        <v>26.9</v>
+        <v>18.1</v>
+      </c>
+      <c r="V28" s="8" t="n">
+        <v>28.6</v>
       </c>
       <c r="W28" s="3" t="n">
-        <v>2.8</v>
+        <v>24.6</v>
       </c>
       <c r="X28" s="3" t="n">
-        <v>27.1</v>
+        <v>28.4</v>
       </c>
       <c r="Y28" s="3" t="n">
-        <v>81.8</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="Z28" s="3" t="n">
-        <v>2.4</v>
+        <v>10.7</v>
       </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
@@ -3030,80 +2930,74 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>290.7</v>
+        <v>12146.8</v>
       </c>
       <c r="D29" s="10" t="n">
-        <v>31.7</v>
+        <v>31.5</v>
       </c>
       <c r="E29" s="10" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="F29" s="10" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="G29" s="10" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="H29" s="3" t="n">
-        <v>18.9</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="G29" s="8" t="n">
+        <v>18</v>
+      </c>
+      <c r="H29" s="3" t="inlineStr"/>
       <c r="I29" s="3" t="n">
-        <v>1.9</v>
+        <v>11.6</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>3.8</v>
+        <v>2.6</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>21.9</v>
-      </c>
-      <c r="M29" s="3" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="M29" s="8" t="n">
         <v>20.6</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="O29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">280
-2923
-</t>
-        </is>
+        <v>23.9</v>
+      </c>
+      <c r="O29" s="3" t="n">
+        <v>95.3</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>31.2</v>
-      </c>
-      <c r="R29" s="3" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="S29" s="3" t="n">
-        <v>27.2</v>
+        <v>85.3</v>
+      </c>
+      <c r="R29" s="8" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="S29" s="8" t="n">
+        <v>28</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>60.2</v>
+        <v>87</v>
       </c>
       <c r="U29" s="3" t="n">
-        <v>18.1</v>
+        <v>14.2</v>
       </c>
       <c r="V29" s="3" t="n">
-        <v>28.6</v>
+        <v>22.4</v>
       </c>
       <c r="W29" s="3" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="X29" s="3" t="n">
-        <v>29.1</v>
+        <v>21.3</v>
+      </c>
+      <c r="X29" s="8" t="n">
+        <v>14.6</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>724.6</v>
+        <v>90.8</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>1.3</v>
+        <v>22.5</v>
       </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
@@ -3119,76 +3013,76 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>846.2</v>
+        <v>11056.2</v>
       </c>
       <c r="D30" s="10" t="n">
-        <v>145.3</v>
+        <v>145</v>
       </c>
       <c r="E30" s="10" t="n">
-        <v>104.2</v>
+        <v>103.3</v>
       </c>
       <c r="F30" s="10" t="n">
-        <v>124.6</v>
-      </c>
-      <c r="G30" s="3" t="n">
-        <v>1</v>
+        <v>140.2</v>
+      </c>
+      <c r="G30" s="20" t="n">
+        <v>14.2</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>12.2</v>
+        <v>196.6</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>2.2</v>
+        <v>7.1</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>2.6</v>
+        <v>111</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>8.4</v>
+        <v>38.8</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>21.1</v>
+        <v>1106.5</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>20.6</v>
+        <v>1105.2</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>23.9</v>
+        <v>123.9</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>95.3</v>
+        <v>487.6</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>1.1</v>
+        <v>12.8</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>825.3</v>
+        <v>11135.8</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>23.6</v>
+        <v>120.1</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>28</v>
+        <v>1140.9</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>8</v>
+        <v>396.8</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>4.1</v>
+        <v>18.5</v>
       </c>
       <c r="V30" s="3" t="n">
-        <v>2.4</v>
+        <v>1126.1</v>
       </c>
       <c r="W30" s="3" t="n">
-        <v>24.6</v>
+        <v>1115.9</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>2.4</v>
+        <v>135.9</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>4.2</v>
+        <v>1424.7</v>
       </c>
       <c r="Z30" s="3" t="n">
-        <v>1.3</v>
+        <v>21.8</v>
       </c>
       <c r="AA30" s="3" t="inlineStr">
         <is>
@@ -3204,76 +3098,74 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>15.2</v>
+        <v>211.2</v>
       </c>
       <c r="D31" s="10" t="n">
-        <v>29.1</v>
+        <v>29</v>
       </c>
       <c r="E31" s="10" t="n">
-        <v>20.8</v>
+        <v>20.6</v>
       </c>
       <c r="F31" s="10" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="G31" s="10" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="H31" s="3" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="I31" s="3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J31" s="3" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="K31" s="3" t="inlineStr"/>
+      <c r="L31" s="3" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="M31" s="8" t="n">
+        <v>28</v>
+      </c>
+      <c r="N31" s="8" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="O31" s="3" t="n">
+        <v>97.5</v>
+      </c>
+      <c r="P31" s="3" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="Q31" s="3" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="R31" s="8" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="S31" s="3" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="T31" s="3" t="n">
+        <v>79.40000000000001</v>
+      </c>
+      <c r="U31" s="8" t="n">
+        <v>88.8</v>
+      </c>
+      <c r="V31" s="8" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="W31" s="3" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="X31" s="3" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="Y31" s="3" t="n">
         <v>24.9</v>
       </c>
-      <c r="G31" s="3" t="n">
-        <v>42</v>
-      </c>
-      <c r="H31" s="3" t="n">
-        <v>96.59999999999999</v>
-      </c>
-      <c r="I31" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="J31" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="K31" s="3" t="n">
-        <v>38.8</v>
-      </c>
-      <c r="L31" s="3" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="M31" s="3" t="n">
-        <v>15.1</v>
-      </c>
-      <c r="N31" s="8" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="O31" s="3" t="n">
-        <v>487.6</v>
-      </c>
-      <c r="P31" s="3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Q31" s="8" t="n">
-        <v>35.8</v>
-      </c>
-      <c r="R31" s="8" t="n">
-        <v>280.7</v>
-      </c>
-      <c r="S31" s="8" t="n">
-        <v>40.9</v>
-      </c>
-      <c r="T31" s="3" t="n">
-        <v>396.8</v>
-      </c>
-      <c r="U31" s="8" t="n">
-        <v>81.5</v>
-      </c>
-      <c r="V31" s="8" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="W31" s="3" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="X31" s="3" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="Y31" s="3" t="n">
-        <v>44.2</v>
-      </c>
       <c r="Z31" s="3" t="n">
-        <v>2.5</v>
+        <v>145.2</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -3289,74 +3181,72 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>211.2</v>
+        <v>384.7</v>
       </c>
       <c r="D32" s="10" t="n">
-        <v>29</v>
+        <v>31.1</v>
       </c>
       <c r="E32" s="10" t="n">
-        <v>20.6</v>
+        <v>19.3</v>
       </c>
       <c r="F32" s="10" t="n">
-        <v>24.8</v>
+        <v>25.2</v>
       </c>
       <c r="G32" s="10" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="H32" s="3" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="H32" s="8" t="n">
+        <v>18</v>
+      </c>
+      <c r="I32" s="3" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="J32" s="3" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="K32" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="L32" s="3" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="M32" s="3" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="N32" s="3" t="inlineStr"/>
+      <c r="O32" s="3" t="n">
+        <v>1100</v>
+      </c>
+      <c r="P32" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="R32" s="8" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="S32" s="3" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="T32" s="3" t="n">
+        <v>161</v>
+      </c>
+      <c r="U32" s="8" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="V32" s="3" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="W32" s="3" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="X32" s="3" t="inlineStr"/>
+      <c r="Y32" s="3" t="n">
+        <v>174.6</v>
+      </c>
+      <c r="Z32" s="3" t="n">
         <v>19.3</v>
-      </c>
-      <c r="I32" s="3" t="n">
-        <v>72.09999999999999</v>
-      </c>
-      <c r="J32" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="K32" s="3" t="n"/>
-      <c r="L32" s="3" t="n">
-        <v>41.3</v>
-      </c>
-      <c r="M32" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="N32" s="3" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="O32" s="3" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="P32" s="3" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="Q32" s="3" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="R32" s="3" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="S32" s="3" t="n">
-        <v>28.2</v>
-      </c>
-      <c r="T32" s="3" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="U32" s="3" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="V32" s="3" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="W32" s="8" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="X32" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Y32" s="3" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="Z32" s="3" t="n">
-        <v>5.8</v>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -3372,74 +3262,72 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>384.7</v>
+        <v>213.3</v>
       </c>
       <c r="D33" s="10" t="n">
-        <v>31.1</v>
+        <v>29.2</v>
       </c>
       <c r="E33" s="10" t="n">
-        <v>19.3</v>
+        <v>19.6</v>
       </c>
       <c r="F33" s="10" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="G33" s="10" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="H33" s="3" t="n">
-        <v>18</v>
+        <v>24.4</v>
+      </c>
+      <c r="G33" s="3" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="H33" s="8" t="n">
+        <v>18.8</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>1.4</v>
+        <v>11</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>4.4</v>
+        <v>1.6</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>20</v>
+        <v>4.8</v>
       </c>
       <c r="L33" s="8" t="n">
-        <v>20.1</v>
+        <v>21.5</v>
       </c>
       <c r="M33" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="N33" s="3" t="n">
-        <v>23.3</v>
-      </c>
+        <v>21.4</v>
+      </c>
+      <c r="N33" s="3" t="inlineStr"/>
       <c r="O33" s="3" t="n">
-        <v>10</v>
+        <v>299</v>
       </c>
       <c r="P33" s="3" t="n">
-        <v>6</v>
+        <v>10.2</v>
       </c>
       <c r="Q33" s="3" t="n">
-        <v>31.1</v>
-      </c>
-      <c r="R33" s="3" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="S33" s="3" t="n">
-        <v>2.5</v>
+        <v>28.9</v>
+      </c>
+      <c r="R33" s="8" t="n">
+        <v>206.6</v>
+      </c>
+      <c r="S33" s="8" t="n">
+        <v>28.2</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>61</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="U33" s="3" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="V33" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="W33" s="3" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="X33" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Y33" s="3" t="n"/>
+        <v>16.5</v>
+      </c>
+      <c r="V33" s="8" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="W33" s="8" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="X33" s="3" t="inlineStr"/>
+      <c r="Y33" s="3" t="n">
+        <v>861.4</v>
+      </c>
       <c r="Z33" s="3" t="n">
-        <v>5.2</v>
+        <v>14.5</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3455,72 +3343,76 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>213.3</v>
+        <v>311.6</v>
       </c>
       <c r="D34" s="10" t="n">
-        <v>29.2</v>
+        <v>31.9</v>
       </c>
       <c r="E34" s="10" t="n">
-        <v>19.6</v>
+        <v>21.5</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>24.4</v>
+        <v>26.7</v>
       </c>
       <c r="G34" s="10" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>18.8</v>
+        <v>20.2</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>1.1</v>
+        <v>3.5</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="L34" s="3" t="n">
-        <v>21.5</v>
+        <v>0.2</v>
+      </c>
+      <c r="L34" s="8" t="n">
+        <v>21.8</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>21.4</v>
+        <v>21.7</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>25.4</v>
+        <v>25.9</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>992.6</v>
+        <v>199</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0.2</v>
+        <v>10.2</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>28.9</v>
+        <v>30.5</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>4.6</v>
+        <v>25.8</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>98.90000000000001</v>
+        <v>30.2</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>2720.9</v>
+        <v>169.4</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>11.5</v>
+        <v>13.3</v>
       </c>
       <c r="V34" s="3" t="n">
-        <v>25.6</v>
+        <v>27.3</v>
       </c>
       <c r="W34" s="3" t="n">
-        <v>83.8</v>
-      </c>
-      <c r="X34" s="3" t="n"/>
-      <c r="Y34" s="3" t="n"/>
+        <v>24.8</v>
+      </c>
+      <c r="X34" s="3" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="Y34" s="3" t="n">
+        <v>82.8</v>
+      </c>
       <c r="Z34" s="3" t="n">
-        <v>2.3</v>
+        <v>16.5</v>
       </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
@@ -3536,88 +3428,76 @@
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>311.6</v>
+        <v>353.4</v>
       </c>
       <c r="D35" s="10" t="n">
-        <v>31.9</v>
+        <v>31.1</v>
       </c>
       <c r="E35" s="10" t="n">
-        <v>21.5</v>
+        <v>20.8</v>
       </c>
       <c r="F35" s="10" t="n">
-        <v>26.6</v>
-      </c>
-      <c r="G35" s="3" t="n">
-        <v>1.5</v>
+        <v>25.9</v>
+      </c>
+      <c r="G35" s="10" t="n">
+        <v>10.3</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="I35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20
-9217
-</t>
-        </is>
+        <v>19.7</v>
+      </c>
+      <c r="I35" s="3" t="n">
+        <v>2.4</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>3.5</v>
+        <v>14</v>
       </c>
       <c r="K35" s="3" t="n">
-        <v>6.2</v>
+        <v>10</v>
       </c>
       <c r="L35" s="3" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="M35" s="8" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="N35" s="3" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="O35" s="3" t="n">
+        <v>197.2</v>
+      </c>
+      <c r="P35" s="3" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="Q35" s="3" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="R35" s="8" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="S35" s="8" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="T35" s="3" t="n">
+        <v>1614.3</v>
+      </c>
+      <c r="U35" s="3" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="V35" s="8" t="n">
         <v>21.8</v>
       </c>
-      <c r="M35" s="3" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="N35" s="3" t="n">
-        <v>25.9</v>
-      </c>
-      <c r="O35" s="3" t="n">
-        <v>996</v>
-      </c>
-      <c r="P35" s="3" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="Q35" s="3" t="n">
-        <v>30.5</v>
-      </c>
-      <c r="R35" s="3" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="S35" s="3" t="n">
-        <v>30.2</v>
-      </c>
-      <c r="T35" s="3" t="n">
-        <v>69.40000000000001</v>
-      </c>
-      <c r="U35" s="3" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="V35" s="8" t="n">
-        <v>27.3</v>
-      </c>
-      <c r="W35" s="3" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="X35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">242461
-289
-</t>
-        </is>
-      </c>
-      <c r="Y35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">26282
-79794
-</t>
-        </is>
+      <c r="W35" s="8" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="X35" s="8" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="Y35" s="3" t="n">
+        <v>19.8</v>
       </c>
       <c r="Z35" s="3" t="n">
-        <v>4.5</v>
+        <v>18.4</v>
       </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
@@ -3633,76 +3513,76 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>353.4</v>
+        <v>430.7</v>
       </c>
       <c r="D36" s="10" t="n">
-        <v>31</v>
+        <v>32.1</v>
       </c>
       <c r="E36" s="10" t="n">
-        <v>20.7</v>
+        <v>20.9</v>
       </c>
       <c r="F36" s="10" t="n">
-        <v>25.9</v>
+        <v>26.5</v>
       </c>
       <c r="G36" s="10" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="H36" s="3" t="n"/>
+        <v>11.2</v>
+      </c>
+      <c r="H36" s="3" t="n">
+        <v>19.8</v>
+      </c>
       <c r="I36" s="3" t="n">
-        <v>22.4</v>
+        <v>2.4</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>14.4</v>
+      </c>
+      <c r="K36" s="8" t="n">
+        <v>30.6</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="M36" s="3" t="n">
-        <v>21.3</v>
+        <v>21</v>
+      </c>
+      <c r="M36" s="8" t="n">
+        <v>20.1</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>25.1</v>
+        <v>26.2</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>97.2</v>
+        <v>918.5</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0.7</v>
+        <v>10.6</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>31.1</v>
+        <v>32.1</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>24.9</v>
+        <v>26</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>27.5</v>
+        <v>29.7</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>6.3</v>
+        <v>62.2</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>17.4</v>
+        <v>18</v>
       </c>
       <c r="V36" s="3" t="n">
-        <v>27.8</v>
+        <v>28.7</v>
       </c>
       <c r="W36" s="3" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="X36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">242461
-289
-</t>
-        </is>
-      </c>
-      <c r="Y36" s="3" t="n"/>
+        <v>24.6</v>
+      </c>
+      <c r="X36" s="8" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="Y36" s="3" t="n">
+        <v>42.4</v>
+      </c>
       <c r="Z36" s="3" t="n">
-        <v>8.4</v>
+        <v>211</v>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -3718,70 +3598,76 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>430.7</v>
+        <v>1693.7</v>
       </c>
       <c r="D37" s="10" t="n">
-        <v>152.2</v>
+        <v>155.4</v>
       </c>
       <c r="E37" s="10" t="n">
-        <v>101.7</v>
+        <v>102.1</v>
       </c>
       <c r="F37" s="10" t="n">
-        <v>126.9</v>
-      </c>
-      <c r="G37" s="3" t="n"/>
+        <v>128.7</v>
+      </c>
+      <c r="G37" s="10" t="n">
+        <v>53.4</v>
+      </c>
       <c r="H37" s="3" t="n">
-        <v>13.8</v>
+        <v>96.5</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>2.4</v>
+        <v>110.1</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>4.4</v>
+        <v>18.1</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>30.6</v>
+        <v>135.6</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>21</v>
+        <v>1106</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>20.7</v>
+        <v>1803.2</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>242.8</v>
+        <v>121.1</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>9.5</v>
+        <v>492.9</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>0.6</v>
+        <v>1.7</v>
       </c>
       <c r="Q37" s="3" t="n">
-        <v>32.1</v>
+        <v>143.1</v>
       </c>
       <c r="R37" s="3" t="n">
-        <v>26</v>
+        <v>1126.2</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>29.7</v>
+        <v>1143.1</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>62.2</v>
+        <v>13821.8</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>18.4</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="V37" s="3" t="n">
-        <v>28.7</v>
+        <v>136.8</v>
       </c>
       <c r="W37" s="3" t="n">
-        <v>26.6</v>
-      </c>
-      <c r="X37" s="3" t="n"/>
-      <c r="Y37" s="3" t="n"/>
+        <v>121.6</v>
+      </c>
+      <c r="X37" s="3" t="n">
+        <v>1142.4</v>
+      </c>
+      <c r="Y37" s="3" t="n">
+        <v>398.2</v>
+      </c>
       <c r="Z37" s="3" t="n">
-        <v>7909.7</v>
+        <v>1392.7</v>
       </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
@@ -3797,83 +3683,75 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>693.7</v>
+        <v>338.7</v>
       </c>
       <c r="D38" s="10" t="n">
-        <v>30.4</v>
+        <v>31</v>
       </c>
       <c r="E38" s="10" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="F38" s="10" t="n">
-        <v>28.7</v>
+        <v>25.7</v>
       </c>
       <c r="G38" s="10" t="n">
-        <v>53.4</v>
+        <v>10.6</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>96.5</v>
+        <v>19.3</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="J38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">887 1
-18 74
-</t>
-        </is>
-      </c>
-      <c r="K38" s="3" t="n">
-        <v>35.6</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="J38" s="3" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K38" s="3" t="inlineStr"/>
       <c r="L38" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="M38" s="8" t="n">
-        <v>185.8</v>
-      </c>
-      <c r="N38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">42477
-114111
-</t>
-        </is>
-      </c>
-      <c r="O38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24268701
-6888
-</t>
-        </is>
+        <v>21.2</v>
+      </c>
+      <c r="M38" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="N38" s="3" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="O38" s="3" t="n">
+        <v>98.5</v>
       </c>
       <c r="P38" s="3" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Q38" s="8" t="n">
-        <v>53.7</v>
+        <v>10.3</v>
+      </c>
+      <c r="Q38" s="3" t="n">
+        <v>20.7</v>
       </c>
       <c r="R38" s="8" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="S38" s="8" t="n">
-        <v>43.1</v>
+        <v>25.2</v>
+      </c>
+      <c r="S38" s="3" t="n">
+        <v>28.6</v>
       </c>
       <c r="T38" s="3" t="n">
-        <v>324.8</v>
+        <v>169</v>
       </c>
       <c r="U38" s="3" t="n">
-        <v>77.7</v>
+        <v>13.5</v>
       </c>
       <c r="V38" s="8" t="n">
-        <v>36.8</v>
-      </c>
-      <c r="W38" s="8" t="n">
-        <v>24.6</v>
-      </c>
-      <c r="X38" s="3" t="n"/>
-      <c r="Y38" s="3" t="n"/>
-      <c r="Z38" s="3" t="n"/>
+        <v>87.40000000000001</v>
+      </c>
+      <c r="W38" s="3" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="X38" s="3" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="Y38" s="3" t="n">
+        <v>78.90000000000001</v>
+      </c>
+      <c r="Z38" s="3" t="n">
+        <v>2.9</v>
+      </c>
       <c r="AA38" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -3888,78 +3766,74 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>38.7</v>
-      </c>
-      <c r="D39" s="3" t="n">
-        <v>31.8</v>
-      </c>
-      <c r="E39" s="23" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="F39" s="3" t="n">
-        <v>25.7</v>
-      </c>
-      <c r="G39" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="H39" s="3" t="n">
+        <v>332.5</v>
+      </c>
+      <c r="D39" s="10" t="n">
+        <v>32</v>
+      </c>
+      <c r="E39" s="10" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="F39" s="10" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="G39" s="10" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="H39" s="8" t="n">
         <v>19.3</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>20.6</v>
+        <v>1.7</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="K39" s="3" t="n"/>
-      <c r="L39" s="3" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="M39" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="K39" s="3" t="inlineStr"/>
+      <c r="L39" s="8" t="n">
         <v>21</v>
       </c>
-      <c r="N39" s="8" t="n">
-        <v>24.1</v>
+      <c r="M39" s="8" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="N39" s="3" t="n">
+        <v>24.6</v>
       </c>
       <c r="O39" s="3" t="n">
-        <v>492.7</v>
+        <v>99</v>
       </c>
       <c r="P39" s="3" t="n">
-        <v>0.3</v>
+        <v>10.2</v>
       </c>
       <c r="Q39" s="3" t="n">
-        <v>36.7</v>
-      </c>
-      <c r="R39" s="3" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="S39" s="3" t="n">
-        <v>28.6</v>
+        <v>31.9</v>
+      </c>
+      <c r="R39" s="8" t="n">
+        <v>126</v>
+      </c>
+      <c r="S39" s="8" t="n">
+        <v>29.8</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>65</v>
+        <v>163.2</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="V39" s="3" t="n">
-        <v>32.4</v>
-      </c>
-      <c r="W39" s="8" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="X39" s="8" t="n">
-        <v>88.5</v>
-      </c>
-      <c r="Y39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">177
-1
-</t>
-        </is>
+        <v>17.3</v>
+      </c>
+      <c r="V39" s="8" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="W39" s="3" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="X39" s="3" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="Y39" s="3" t="n">
+        <v>288.2</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>2.9</v>
+        <v>13.6</v>
       </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -3975,76 +3849,76 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>32.5</v>
+        <v>1453.1</v>
       </c>
       <c r="D40" s="10" t="n">
-        <v>31.9</v>
+        <v>32.9</v>
       </c>
       <c r="E40" s="10" t="n">
-        <v>20.3</v>
+        <v>18.9</v>
       </c>
       <c r="F40" s="10" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="G40" s="10" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="H40" s="3" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="I40" s="3" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="J40" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="K40" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="L40" s="3" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="M40" s="8" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="N40" s="3" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="O40" s="3" t="n">
+        <v>1797.8</v>
+      </c>
+      <c r="P40" s="3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Q40" s="3" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="R40" s="8" t="n">
         <v>26</v>
       </c>
-      <c r="G40" s="10" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="H40" s="3" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="I40" s="3" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="J40" s="3" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="K40" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="L40" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="M40" s="3" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="N40" s="3" t="n">
+      <c r="S40" s="3" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="T40" s="3" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="U40" s="3" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="V40" s="3" t="n">
         <v>24.8</v>
       </c>
-      <c r="O40" s="3" t="n">
-        <v>98.5</v>
-      </c>
-      <c r="P40" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Q40" s="3" t="n">
-        <v>31.9</v>
-      </c>
-      <c r="R40" s="3" t="n">
-        <v>26</v>
-      </c>
-      <c r="S40" s="3" t="n">
-        <v>89.8</v>
-      </c>
-      <c r="T40" s="3" t="n">
-        <v>63.2</v>
-      </c>
-      <c r="U40" s="8" t="n">
-        <v>27.3</v>
-      </c>
-      <c r="V40" s="3" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="W40" s="3" t="n">
-        <v>24.3</v>
+      <c r="W40" s="8" t="n">
+        <v>23.8</v>
       </c>
       <c r="X40" s="3" t="n">
-        <v>2.5</v>
+        <v>26.9</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>88.2</v>
+        <v>72</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>0.8</v>
+        <v>10.4</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -4060,74 +3934,76 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>453.7</v>
-      </c>
-      <c r="D41" s="23" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="E41" s="3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="F41" s="3" t="n">
-        <v>25.9</v>
-      </c>
-      <c r="G41" s="3" t="n">
-        <v>4.1</v>
+        <v>269.6</v>
+      </c>
+      <c r="D41" s="10" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="E41" s="10" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="F41" s="10" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="G41" s="10" t="n">
+        <v>12</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>18.2</v>
+        <v>18</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>2.7</v>
+        <v>1.2</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="K41" s="3" t="n">
-        <v>0</v>
+        <v>1.6</v>
+      </c>
+      <c r="K41" s="8" t="n">
+        <v>43.6</v>
       </c>
       <c r="L41" s="3" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="M41" s="3" t="n">
         <v>19.8</v>
       </c>
-      <c r="M41" s="3" t="n">
-        <v>19.6</v>
-      </c>
       <c r="N41" s="3" t="n">
-        <v>4.6</v>
+        <v>23</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>97.8</v>
+        <v>199</v>
       </c>
       <c r="P41" s="3" t="n">
-        <v>0.5</v>
+        <v>10.2</v>
       </c>
       <c r="Q41" s="3" t="n">
-        <v>32.8</v>
-      </c>
-      <c r="R41" s="8" t="n">
-        <v>66</v>
+        <v>22.3</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>21.4</v>
       </c>
       <c r="S41" s="3" t="n">
-        <v>29.3</v>
+        <v>24.9</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>59.2</v>
+        <v>192.8</v>
       </c>
       <c r="U41" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="V41" s="3" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="W41" s="3" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="X41" s="3" t="n">
-        <v>26.9</v>
-      </c>
-      <c r="Y41" s="3" t="n"/>
+        <v>12</v>
+      </c>
+      <c r="V41" s="8" t="n">
+        <v>816.6</v>
+      </c>
+      <c r="W41" s="8" t="n">
+        <v>83.40000000000001</v>
+      </c>
+      <c r="X41" s="8" t="n">
+        <v>28</v>
+      </c>
+      <c r="Y41" s="3" t="n">
+        <v>190.5</v>
+      </c>
       <c r="Z41" s="3" t="n">
-        <v>1</v>
+        <v>2.9</v>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
@@ -4143,77 +4019,75 @@
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>26.5</v>
+        <v>1236.3</v>
       </c>
       <c r="D42" s="10" t="n">
-        <v>31.6</v>
+        <v>31.5</v>
       </c>
       <c r="E42" s="10" t="n">
-        <v>19.6</v>
+        <v>20.2</v>
       </c>
       <c r="F42" s="10" t="n">
-        <v>25.6</v>
+        <v>25.9</v>
       </c>
       <c r="G42" s="10" t="n">
-        <v>12</v>
+        <v>11.3</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>18.6</v>
+        <v>20</v>
       </c>
       <c r="I42" s="3" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="J42" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="J42" s="3" t="n">
-        <v>1.6</v>
-      </c>
       <c r="K42" s="3" t="n">
-        <v>4.6</v>
+        <v>28.1</v>
       </c>
       <c r="L42" s="3" t="n">
-        <v>19.9</v>
+        <v>21.9</v>
       </c>
       <c r="M42" s="3" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="N42" s="3" t="n">
-        <v>23</v>
+        <v>21.8</v>
+      </c>
+      <c r="N42" s="8" t="n">
+        <v>26</v>
       </c>
       <c r="O42" s="3" t="n">
-        <v>99</v>
-      </c>
-      <c r="P42" s="8" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="Q42" s="3" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="R42" s="3" t="n">
-        <v>21.4</v>
-      </c>
-      <c r="S42" s="3" t="n">
-        <v>24.9</v>
+        <v>199</v>
+      </c>
+      <c r="P42" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q42" s="8" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="R42" s="8" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="S42" s="8" t="n">
+        <v>29.3</v>
       </c>
       <c r="T42" s="3" t="n">
-        <v>92.3</v>
+        <v>197.7</v>
       </c>
       <c r="U42" s="3" t="n">
-        <v>2.8</v>
+        <v>10.1</v>
       </c>
       <c r="V42" s="3" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="W42" s="3" t="n">
-        <v>23.4</v>
+        <v>21.7</v>
+      </c>
+      <c r="W42" s="8" t="n">
+        <v>23.5</v>
       </c>
       <c r="X42" s="3" t="n">
-        <v>28.1</v>
+        <v>28.2</v>
       </c>
       <c r="Y42" s="3" t="n">
-        <v>90.5</v>
-      </c>
-      <c r="Z42" s="3" t="n">
-        <v>2.9</v>
-      </c>
+        <v>190.6</v>
+      </c>
+      <c r="Z42" s="3" t="inlineStr"/>
       <c r="AA42" s="3" t="inlineStr">
         <is>
           <t>29</t>
@@ -4228,75 +4102,77 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>236.3</v>
-      </c>
-      <c r="D43" s="8" t="n">
-        <v>16.1</v>
-      </c>
-      <c r="E43" s="3" t="n">
-        <v>20.3</v>
-      </c>
-      <c r="F43" s="3" t="n">
-        <v>25.9</v>
-      </c>
-      <c r="G43" s="3" t="n">
-        <v>1.3</v>
+        <v>372.2</v>
+      </c>
+      <c r="D43" s="10" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="E43" s="10" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="F43" s="10" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="G43" s="10" t="n">
+        <v>8.699999999999999</v>
       </c>
       <c r="H43" s="3" t="n">
-        <v>20.6</v>
+        <v>19.8</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>6.7</v>
+        <v>12</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>1.5</v>
+        <v>3.7</v>
       </c>
       <c r="K43" s="3" t="n">
-        <v>88.7</v>
+        <v>10</v>
       </c>
       <c r="L43" s="3" t="n">
-        <v>21.9</v>
+        <v>21.6</v>
       </c>
       <c r="M43" s="3" t="n">
-        <v>21.8</v>
+        <v>21.5</v>
       </c>
       <c r="N43" s="3" t="n">
-        <v>26</v>
+        <v>25.6</v>
       </c>
       <c r="O43" s="3" t="n">
-        <v>99.59999999999999</v>
+        <v>199</v>
       </c>
       <c r="P43" s="3" t="n">
-        <v>6.2</v>
+        <v>0.2</v>
       </c>
       <c r="Q43" s="3" t="n">
-        <v>24.1</v>
+        <v>29.1</v>
       </c>
       <c r="R43" s="3" t="n">
-        <v>23.8</v>
+        <v>25.5</v>
       </c>
       <c r="S43" s="3" t="n">
-        <v>29.3</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="T43" s="3" t="n">
-        <v>97.2</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="U43" s="3" t="n">
-        <v>87.2</v>
-      </c>
-      <c r="V43" s="3" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="V43" s="8" t="n">
+        <v>79.8</v>
+      </c>
+      <c r="W43" s="3" t="n">
         <v>24.7</v>
       </c>
-      <c r="W43" s="3" t="n">
-        <v>23.5</v>
-      </c>
       <c r="X43" s="3" t="n">
-        <v>88.2</v>
+        <v>29.1</v>
       </c>
       <c r="Y43" s="3" t="n">
-        <v>96.59999999999999</v>
-      </c>
-      <c r="Z43" s="3" t="n"/>
+        <v>18</v>
+      </c>
+      <c r="Z43" s="3" t="n">
+        <v>18.2</v>
+      </c>
       <c r="AA43" s="3" t="inlineStr">
         <is>
           <t>30</t>
@@ -4311,75 +4187,77 @@
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>32.2</v>
+        <v>365.9</v>
       </c>
       <c r="D44" s="10" t="n">
-        <v>29.9</v>
+        <v>32.5</v>
       </c>
       <c r="E44" s="10" t="n">
         <v>21.3</v>
       </c>
       <c r="F44" s="10" t="n">
-        <v>25.6</v>
+        <v>26.9</v>
       </c>
       <c r="G44" s="10" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="H44" s="3" t="n">
-        <v>19.8</v>
+        <v>11.3</v>
+      </c>
+      <c r="H44" s="8" t="n">
+        <v>19.4</v>
       </c>
       <c r="I44" s="3" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="K44" s="8" t="n">
-        <v>6</v>
+        <v>19.6</v>
+      </c>
+      <c r="K44" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="L44" s="3" t="n">
-        <v>21.6</v>
+        <v>28.3</v>
       </c>
       <c r="M44" s="3" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="N44" s="3" t="n">
-        <v>25.6</v>
+        <v>22.3</v>
+      </c>
+      <c r="N44" s="8" t="n">
+        <v>26.9</v>
       </c>
       <c r="O44" s="3" t="n">
-        <v>99</v>
+        <v>1100</v>
       </c>
       <c r="P44" s="3" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q44" s="3" t="n">
-        <v>29.1</v>
+        <v>32.6</v>
       </c>
       <c r="R44" s="3" t="n">
-        <v>25.5</v>
+        <v>26.4</v>
       </c>
       <c r="S44" s="3" t="n">
-        <v>30.4</v>
+        <v>30.1</v>
       </c>
       <c r="T44" s="3" t="n">
-        <v>75.59999999999999</v>
-      </c>
-      <c r="U44" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>162</v>
+      </c>
+      <c r="U44" s="8" t="n">
+        <v>18.6</v>
       </c>
       <c r="V44" s="3" t="n">
-        <v>2.8</v>
+        <v>28.5</v>
       </c>
       <c r="W44" s="3" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="X44" s="3" t="n">
-        <v>1.1</v>
+        <v>26.3</v>
+      </c>
+      <c r="X44" s="8" t="n">
+        <v>32.2</v>
       </c>
       <c r="Y44" s="3" t="n">
-        <v>31.2</v>
-      </c>
-      <c r="Z44" s="3" t="n"/>
+        <v>84.40000000000001</v>
+      </c>
+      <c r="Z44" s="3" t="n">
+        <v>166</v>
+      </c>
       <c r="AA44" s="3" t="inlineStr">
         <is>
           <t>31</t>
@@ -4393,86 +4271,67 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C45" s="3" t="n">
-        <v>365.9</v>
-      </c>
+      <c r="C45" s="3" t="inlineStr"/>
       <c r="D45" s="10" t="n">
-        <v>32.5</v>
+        <v>190.6</v>
       </c>
       <c r="E45" s="10" t="n">
-        <v>21.2</v>
+        <v>121.6</v>
       </c>
       <c r="F45" s="10" t="n">
-        <v>26.9</v>
-      </c>
-      <c r="G45" s="3" t="n">
+        <v>156</v>
+      </c>
+      <c r="G45" s="20" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="H45" s="3" t="n">
+        <v>114.7</v>
+      </c>
+      <c r="I45" s="3" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="J45" s="3" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="K45" s="3" t="n">
+        <v>172.3</v>
+      </c>
+      <c r="L45" s="3" t="n">
+        <v>1166.9</v>
+      </c>
+      <c r="M45" s="3" t="n">
+        <v>122.9</v>
+      </c>
+      <c r="N45" s="3" t="n">
+        <v>148.7</v>
+      </c>
+      <c r="O45" s="3" t="n">
+        <v>293.8</v>
+      </c>
+      <c r="P45" s="3" t="n">
         <v>1.3</v>
       </c>
-      <c r="H45" s="3" t="n">
-        <v>49.4</v>
-      </c>
-      <c r="I45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">79727222
-785
-</t>
-        </is>
-      </c>
-      <c r="J45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">79272
-1
-77
-</t>
-        </is>
-      </c>
-      <c r="K45" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L45" s="3" t="n">
-        <v>28.3</v>
-      </c>
-      <c r="M45" s="3" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="N45" s="3" t="n">
-        <v>26.9</v>
-      </c>
-      <c r="O45" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="P45" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="Q45" s="3" t="n">
-        <v>32.6</v>
+        <v>1752.8</v>
       </c>
       <c r="R45" s="3" t="n">
-        <v>26.4</v>
-      </c>
-      <c r="S45" s="3" t="n">
-        <v>30.8</v>
-      </c>
-      <c r="T45" s="3" t="n">
-        <v>6</v>
-      </c>
+        <v>149.1</v>
+      </c>
+      <c r="S45" s="3" t="inlineStr"/>
+      <c r="T45" s="3" t="inlineStr"/>
       <c r="U45" s="3" t="n">
-        <v>18.6</v>
+        <v>168.6</v>
       </c>
       <c r="V45" s="3" t="n">
-        <v>828.5</v>
-      </c>
-      <c r="W45" s="3" t="n">
-        <v>26.3</v>
-      </c>
-      <c r="X45" s="3" t="n">
-        <v>32.8</v>
-      </c>
+        <v>138.1</v>
+      </c>
+      <c r="W45" s="3" t="inlineStr"/>
+      <c r="X45" s="3" t="inlineStr"/>
       <c r="Y45" s="3" t="n">
-        <v>84.8</v>
+        <v>3503.7</v>
       </c>
       <c r="Z45" s="3" t="n">
-        <v>60.6</v>
+        <v>9316</v>
       </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -4488,72 +4347,74 @@
         </is>
       </c>
       <c r="C46" s="3" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="D46" s="23" t="n">
-        <v>90.59999999999999</v>
-      </c>
-      <c r="E46" s="23" t="n">
-        <v>797.5</v>
-      </c>
-      <c r="F46" s="17" t="n">
-        <v>16.1</v>
-      </c>
-      <c r="G46" s="3" t="n">
-        <v>69.09999999999999</v>
+        <v>2337.6</v>
+      </c>
+      <c r="D46" s="10" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="E46" s="10" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="F46" s="10" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="G46" s="8" t="n">
+        <v>11.5</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>7.7</v>
+        <v>19.1</v>
       </c>
       <c r="I46" s="3" t="n">
         <v>1.7</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="K46" s="3" t="n">
-        <v>98.3</v>
-      </c>
+        <v>53.1</v>
+      </c>
+      <c r="K46" s="3" t="inlineStr"/>
       <c r="L46" s="8" t="n">
-        <v>26.5</v>
-      </c>
-      <c r="M46" s="3" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="N46" s="3" t="n"/>
+        <v>11.1</v>
+      </c>
+      <c r="M46" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="N46" s="3" t="n">
+        <v>24.8</v>
+      </c>
       <c r="O46" s="3" t="n">
-        <v>593.8</v>
+        <v>99</v>
       </c>
       <c r="P46" s="3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Q46" s="8" t="n">
-        <v>72.8</v>
-      </c>
-      <c r="R46" s="3" t="n">
-        <v>79.7</v>
-      </c>
-      <c r="S46" s="3" t="n">
-        <v>72.7</v>
+        <v>10.2</v>
+      </c>
+      <c r="Q46" s="3" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="R46" s="8" t="n">
+        <v>216.8</v>
+      </c>
+      <c r="S46" s="8" t="n">
+        <v>29</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>7.7</v>
+        <v>729</v>
       </c>
       <c r="U46" s="3" t="n">
-        <v>68.59999999999999</v>
+        <v>11.4</v>
       </c>
       <c r="V46" s="8" t="n">
-        <v>58.1</v>
-      </c>
-      <c r="W46" s="3" t="n"/>
+        <v>643.4</v>
+      </c>
+      <c r="W46" s="8" t="n">
+        <v>24.1</v>
+      </c>
       <c r="X46" s="3" t="n">
-        <v>0.3</v>
+        <v>28.1</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>23.7</v>
+        <v>283.9</v>
       </c>
       <c r="Z46" s="3" t="n">
-        <v>2</v>
+        <v>15.7</v>
       </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>

--- a/results/05_transient_transcription_output/203/203_196905_SF.JPG_stage_recalc_multi_day_tot_and_avgs.xlsx
+++ b/results/05_transient_transcription_output/203/203_196905_SF.JPG_stage_recalc_multi_day_tot_and_avgs.xlsx
@@ -26,7 +26,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -55,12 +55,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00CC3300"/>
         <bgColor rgb="00CC3300"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC0CB"/>
-        <bgColor rgb="00FFC0CB"/>
       </patternFill>
     </fill>
   </fills>
@@ -131,7 +125,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -146,9 +140,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -158,10 +149,7 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -197,19 +185,7 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -823,74 +799,76 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>186.2</v>
+        <v>136.2</v>
       </c>
       <c r="D4" s="10" t="n">
         <v>28.1</v>
       </c>
       <c r="E4" s="10" t="n">
-        <v>20</v>
+        <v>20.9</v>
       </c>
       <c r="F4" s="10" t="n">
         <v>24.1</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="H4" s="8" t="n">
-        <v>118.2</v>
+        <v>81.7</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>18.2</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>12.9</v>
+        <v>2.9</v>
       </c>
       <c r="K4" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L4" s="8" t="n">
+      <c r="L4" s="3" t="n">
         <v>20.2</v>
       </c>
       <c r="M4" s="3" t="n">
         <v>20.1</v>
       </c>
-      <c r="N4" s="8" t="n">
-        <v>83.40000000000001</v>
+      <c r="N4" s="3" t="n">
+        <v>23.4</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>199</v>
+        <v>99</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="Q4" s="3" t="inlineStr"/>
+        <v>0.2</v>
+      </c>
+      <c r="Q4" s="3" t="n">
+        <v>28.8</v>
+      </c>
       <c r="R4" s="3" t="n">
         <v>24.1</v>
       </c>
-      <c r="S4" s="8" t="n">
-        <v>27.1</v>
+      <c r="S4" s="3" t="n">
+        <v>22.1</v>
       </c>
       <c r="T4" s="3" t="n">
         <v>68.90000000000001</v>
       </c>
-      <c r="U4" s="8" t="n">
+      <c r="U4" s="3" t="n">
         <v>12.2</v>
       </c>
       <c r="V4" s="3" t="n">
         <v>25.2</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="X4" s="8" t="n">
+        <v>82.8</v>
+      </c>
+      <c r="X4" s="3" t="n">
         <v>26.2</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>1811.8</v>
+        <v>181.8</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>15.8</v>
+        <v>5.8</v>
       </c>
       <c r="AA4" s="3" t="inlineStr">
         <is>
@@ -906,7 +884,7 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>2903.8</v>
+        <v>203.8</v>
       </c>
       <c r="D5" s="10" t="n">
         <v>32.6</v>
@@ -917,8 +895,8 @@
       <c r="F5" s="10" t="n">
         <v>25.4</v>
       </c>
-      <c r="G5" s="3" t="n">
-        <v>34.1</v>
+      <c r="G5" s="10" t="n">
+        <v>14.4</v>
       </c>
       <c r="H5" s="3" t="n">
         <v>16.8</v>
@@ -930,52 +908,52 @@
         <v>5.5</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L5" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" s="3" t="n">
         <v>18.9</v>
       </c>
       <c r="M5" s="3" t="n">
         <v>18.8</v>
       </c>
-      <c r="N5" s="8" t="n">
+      <c r="N5" s="3" t="n">
         <v>21.6</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>199</v>
+        <v>909</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>10.2</v>
+        <v>0.2</v>
       </c>
       <c r="Q5" s="3" t="n">
         <v>32.6</v>
       </c>
-      <c r="R5" s="8" t="n">
+      <c r="R5" s="3" t="n">
         <v>25.4</v>
       </c>
       <c r="S5" s="3" t="n">
         <v>27.8</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>156.6</v>
+        <v>56.6</v>
       </c>
       <c r="U5" s="3" t="n">
         <v>21.2</v>
       </c>
-      <c r="V5" s="8" t="n">
+      <c r="V5" s="3" t="n">
         <v>27.2</v>
       </c>
-      <c r="W5" s="8" t="n">
+      <c r="W5" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="X5" s="8" t="n">
-        <v>27.8</v>
+      <c r="X5" s="11" t="n">
+        <v>72.8</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>11</v>
+        <v>141.1</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AA5" s="3" t="inlineStr">
         <is>
@@ -991,7 +969,7 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>1422.3</v>
+        <v>122.3</v>
       </c>
       <c r="D6" s="10" t="n">
         <v>34.2</v>
@@ -1005,8 +983,8 @@
       <c r="G6" s="10" t="n">
         <v>15.4</v>
       </c>
-      <c r="H6" s="8" t="n">
-        <v>872.6</v>
+      <c r="H6" s="11" t="n">
+        <v>184.6</v>
       </c>
       <c r="I6" s="3" t="n">
         <v>14.6</v>
@@ -1015,7 +993,7 @@
         <v>7.2</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L6" s="3" t="n">
         <v>20</v>
@@ -1029,38 +1007,38 @@
       <c r="O6" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="P6" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q6" s="8" t="n">
-        <v>21.7</v>
+      <c r="P6" s="11" t="n">
+        <v>80</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>32.7</v>
       </c>
       <c r="R6" s="3" t="n">
         <v>25.7</v>
       </c>
-      <c r="S6" s="8" t="n">
+      <c r="S6" s="3" t="n">
         <v>28.6</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>2929.8</v>
-      </c>
-      <c r="U6" s="8" t="n">
-        <v>20.7</v>
+        <v>22.8</v>
+      </c>
+      <c r="U6" s="3" t="n">
+        <v>20.4</v>
       </c>
       <c r="V6" s="3" t="n">
         <v>28.2</v>
       </c>
-      <c r="W6" s="3" t="n">
-        <v>23.7</v>
+      <c r="W6" s="11" t="n">
+        <v>31.7</v>
       </c>
       <c r="X6" s="3" t="n">
         <v>26.1</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>166.4</v>
+        <v>16614.1</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>13.8</v>
+        <v>13.2</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
@@ -1076,16 +1054,16 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>4785.1</v>
+        <v>6472.5</v>
       </c>
       <c r="D7" s="10" t="n">
         <v>34.7</v>
       </c>
       <c r="E7" s="10" t="n">
-        <v>19.9</v>
+        <v>7.3</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>27.3</v>
+        <v>21</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>15.4</v>
@@ -1094,13 +1072,13 @@
         <v>18.2</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>4.3</v>
+        <v>47.9</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>7.9</v>
+        <v>1.9</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L7" s="3" t="n">
         <v>20.1</v>
@@ -1115,37 +1093,37 @@
         <v>100</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q7" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q7" s="3" t="n">
         <v>34.2</v>
       </c>
-      <c r="R7" s="8" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="S7" s="8" t="n">
+      <c r="R7" s="3" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="S7" s="3" t="n">
         <v>27.1</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>120.6</v>
-      </c>
-      <c r="U7" s="8" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="U7" s="3" t="n">
         <v>26.5</v>
       </c>
-      <c r="V7" s="8" t="n">
+      <c r="V7" s="11" t="n">
         <v>29.5</v>
       </c>
-      <c r="W7" s="8" t="n">
+      <c r="W7" s="3" t="n">
         <v>24.4</v>
       </c>
       <c r="X7" s="3" t="n">
         <v>27.3</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>166.2</v>
+        <v>66.2</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>13.8</v>
+        <v>15.8</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1161,7 +1139,7 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>1299</v>
+        <v>299</v>
       </c>
       <c r="D8" s="10" t="n">
         <v>34.6</v>
@@ -1175,59 +1153,59 @@
       <c r="G8" s="10" t="n">
         <v>14</v>
       </c>
-      <c r="H8" s="8" t="n">
-        <v>19</v>
+      <c r="H8" s="11" t="n">
+        <v>12</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="K8" s="8" t="n">
+        <v>16</v>
+      </c>
+      <c r="K8" s="3" t="n">
         <v>30.9</v>
       </c>
       <c r="L8" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="M8" s="8" t="n">
+      <c r="M8" s="3" t="n">
         <v>20.6</v>
       </c>
       <c r="N8" s="3" t="n">
         <v>24</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>196.5</v>
+        <v>96.5</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="Q8" s="8" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="Q8" s="3" t="n">
         <v>21.4</v>
       </c>
       <c r="R8" s="3" t="n">
         <v>21.2</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>23.1</v>
+        <v>25.1</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>298</v>
+        <v>98</v>
       </c>
       <c r="U8" s="3" t="n">
-        <v>10.4</v>
+        <v>0.4</v>
       </c>
       <c r="V8" s="3" t="n">
         <v>22.2</v>
       </c>
-      <c r="W8" s="8" t="n">
-        <v>1.9</v>
+      <c r="W8" s="3" t="n">
+        <v>21.9</v>
       </c>
       <c r="X8" s="3" t="n">
         <v>26.1</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>97.40000000000001</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="Z8" s="3" t="n">
         <v>20.6</v>
@@ -1246,28 +1224,28 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>11783.5</v>
+        <v>1781.2</v>
       </c>
       <c r="D9" s="10" t="n">
         <v>164.2</v>
       </c>
       <c r="E9" s="10" t="n">
-        <v>97.5</v>
+        <v>85.8</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>130.9</v>
-      </c>
-      <c r="G9" s="20" t="n">
-        <v>16.2</v>
+        <v>124.6</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>65.90000000000001</v>
       </c>
       <c r="H9" s="3" t="n">
         <v>89.40000000000001</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>16.5</v>
+        <v>16.6</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>127.5</v>
+        <v>12.8</v>
       </c>
       <c r="K9" s="3" t="n">
         <v>30.9</v>
@@ -1276,31 +1254,31 @@
         <v>100.2</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>199.6</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="N9" s="3" t="n">
         <v>112.8</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>1494.5</v>
+        <v>894.2</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>1.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>149.6</v>
+        <v>1179.6</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>121.9</v>
+        <v>122.9</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>1135.7</v>
+        <v>155.1</v>
       </c>
       <c r="T9" s="3" t="n">
         <v>329.9</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>96</v>
+        <v>81</v>
       </c>
       <c r="V9" s="3" t="n">
         <v>132.8</v>
@@ -1309,10 +1287,10 @@
         <v>1116.8</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>1133.5</v>
+        <v>133.5</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>1388.8</v>
+        <v>388.8</v>
       </c>
       <c r="Z9" s="3" t="n">
         <v>141.6</v>
@@ -1331,7 +1309,7 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>356.7</v>
+        <v>8188.5</v>
       </c>
       <c r="D10" s="10" t="n">
         <v>33</v>
@@ -1346,16 +1324,16 @@
         <v>13.6</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>17.9</v>
+        <v>11.9</v>
       </c>
       <c r="I10" s="3" t="n">
         <v>3.3</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>5.5</v>
+        <v>2.9</v>
       </c>
       <c r="K10" s="3" t="inlineStr"/>
-      <c r="L10" s="8" t="n">
+      <c r="L10" s="3" t="n">
         <v>20</v>
       </c>
       <c r="M10" s="3" t="n">
@@ -1370,17 +1348,17 @@
       <c r="P10" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q10" s="8" t="n">
+      <c r="Q10" s="3" t="n">
         <v>29.9</v>
       </c>
-      <c r="R10" s="8" t="n">
-        <v>24.4</v>
+      <c r="R10" s="3" t="n">
+        <v>94.40000000000001</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>27.1</v>
+        <v>27.8</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>166</v>
+        <v>66</v>
       </c>
       <c r="U10" s="3" t="n">
         <v>16.2</v>
@@ -1388,17 +1366,17 @@
       <c r="V10" s="3" t="n">
         <v>26.6</v>
       </c>
-      <c r="W10" s="8" t="n">
+      <c r="W10" s="3" t="n">
         <v>23.4</v>
       </c>
-      <c r="X10" s="3" t="n">
-        <v>26.7</v>
+      <c r="X10" s="11" t="n">
+        <v>16.2</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>79.8</v>
+        <v>72.8</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>8.300000000000001</v>
+        <v>18.3</v>
       </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
@@ -1417,10 +1395,10 @@
         <v>1265.6</v>
       </c>
       <c r="D11" s="10" t="n">
-        <v>30.1</v>
+        <v>30</v>
       </c>
       <c r="E11" s="10" t="n">
-        <v>19.8</v>
+        <v>19.7</v>
       </c>
       <c r="F11" s="10" t="n">
         <v>24.9</v>
@@ -1432,28 +1410,28 @@
         <v>18.2</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>11.6</v>
+        <v>1.6</v>
       </c>
       <c r="J11" s="3" t="n">
         <v>2.8</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L11" s="3" t="n">
         <v>21.2</v>
       </c>
-      <c r="M11" s="8" t="n">
+      <c r="M11" s="3" t="n">
         <v>20.9</v>
       </c>
-      <c r="N11" s="8" t="n">
-        <v>24.5</v>
+      <c r="N11" s="3" t="n">
+        <v>24.3</v>
       </c>
       <c r="O11" s="3" t="n">
         <v>927.3</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>10.6</v>
+        <v>0.6</v>
       </c>
       <c r="Q11" s="3" t="n">
         <v>29.9</v>
@@ -1461,29 +1439,29 @@
       <c r="R11" s="3" t="n">
         <v>25.5</v>
       </c>
-      <c r="S11" s="3" t="n">
+      <c r="S11" s="11" t="n">
         <v>29.8</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>170.6</v>
+        <v>720.6</v>
       </c>
       <c r="U11" s="3" t="n">
         <v>12.4</v>
       </c>
-      <c r="V11" s="8" t="n">
-        <v>27.1</v>
-      </c>
-      <c r="W11" s="3" t="n">
-        <v>24.9</v>
+      <c r="V11" s="11" t="n">
+        <v>72.09999999999999</v>
+      </c>
+      <c r="W11" s="11" t="n">
+        <v>16.9</v>
       </c>
       <c r="X11" s="3" t="n">
         <v>30.1</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>684</v>
+        <v>2894</v>
       </c>
       <c r="Z11" s="3" t="n">
-        <v>5.1</v>
+        <v>11.8</v>
       </c>
       <c r="AA11" s="3" t="inlineStr">
         <is>
@@ -1499,46 +1477,46 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>247.1</v>
+        <v>347.1</v>
       </c>
       <c r="D12" s="10" t="n">
-        <v>31.8</v>
+        <v>32.4</v>
       </c>
       <c r="E12" s="10" t="n">
         <v>22.6</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>27.2</v>
-      </c>
-      <c r="G12" s="10" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="G12" s="3" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="H12" s="8" t="n">
+      <c r="H12" s="3" t="n">
         <v>21.2</v>
       </c>
-      <c r="I12" s="3" t="n">
-        <v>22.1</v>
+      <c r="I12" s="11" t="n">
+        <v>227.1</v>
       </c>
       <c r="J12" s="3" t="n">
         <v>14.6</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L12" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="3" t="n">
         <v>23.3</v>
       </c>
-      <c r="M12" s="8" t="n">
-        <v>23</v>
-      </c>
-      <c r="N12" s="3" t="n">
-        <v>21.9</v>
+      <c r="M12" s="11" t="n">
+        <v>350.5</v>
+      </c>
+      <c r="N12" s="11" t="n">
+        <v>17.9</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>27.5</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>10.8</v>
+        <v>0.5</v>
       </c>
       <c r="Q12" s="3" t="n">
         <v>31.8</v>
@@ -1547,19 +1525,19 @@
         <v>24.9</v>
       </c>
       <c r="S12" s="3" t="n">
-        <v>27.1</v>
+        <v>21.1</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>59.8</v>
+        <v>51.8</v>
       </c>
       <c r="U12" s="3" t="n">
         <v>19.8</v>
       </c>
       <c r="V12" s="3" t="n">
-        <v>27.9</v>
-      </c>
-      <c r="W12" s="8" t="n">
-        <v>284.6</v>
+        <v>21.9</v>
+      </c>
+      <c r="W12" s="3" t="n">
+        <v>24.6</v>
       </c>
       <c r="X12" s="3" t="n">
         <v>28.8</v>
@@ -1568,7 +1546,7 @@
         <v>76.7</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>181.7</v>
+        <v>21.6</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1584,31 +1562,31 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>1428.6</v>
+        <v>428.6</v>
       </c>
       <c r="D13" s="10" t="n">
-        <v>33.1</v>
+        <v>32.8</v>
       </c>
       <c r="E13" s="10" t="n">
-        <v>20.1</v>
+        <v>20.4</v>
       </c>
       <c r="F13" s="10" t="n">
         <v>26.6</v>
       </c>
-      <c r="G13" s="3" t="n">
+      <c r="G13" s="10" t="n">
         <v>12.4</v>
       </c>
       <c r="H13" s="3" t="n">
         <v>19.9</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>13.3</v>
+        <v>18.3</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L13" s="3" t="n">
         <v>22.1</v>
@@ -1628,32 +1606,32 @@
       <c r="Q13" s="3" t="n">
         <v>32.6</v>
       </c>
-      <c r="R13" s="8" t="n">
+      <c r="R13" s="3" t="n">
         <v>24.6</v>
       </c>
-      <c r="S13" s="3" t="n">
-        <v>25.8</v>
+      <c r="S13" s="11" t="n">
+        <v>21.8</v>
       </c>
       <c r="T13" s="3" t="n">
-        <v>52.7</v>
+        <v>427.4</v>
       </c>
       <c r="U13" s="3" t="n">
         <v>23.3</v>
       </c>
-      <c r="V13" s="8" t="n">
+      <c r="V13" s="3" t="n">
         <v>28</v>
       </c>
       <c r="W13" s="3" t="n">
         <v>24.8</v>
       </c>
       <c r="X13" s="3" t="n">
-        <v>29.3</v>
+        <v>29.5</v>
       </c>
       <c r="Y13" s="3" t="n">
         <v>77.59999999999999</v>
       </c>
       <c r="Z13" s="3" t="n">
-        <v>18.3</v>
+        <v>18.5</v>
       </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
@@ -1683,7 +1661,7 @@
       <c r="G14" s="10" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="H14" s="8" t="n">
+      <c r="H14" s="3" t="n">
         <v>20.3</v>
       </c>
       <c r="I14" s="3" t="n">
@@ -1692,9 +1670,7 @@
       <c r="J14" s="3" t="n">
         <v>2.1</v>
       </c>
-      <c r="K14" s="8" t="n">
-        <v>11.1</v>
-      </c>
+      <c r="K14" s="3" t="inlineStr"/>
       <c r="L14" s="3" t="n">
         <v>22.4</v>
       </c>
@@ -1702,25 +1678,25 @@
         <v>22.1</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>264</v>
+        <v>26.4</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>197.3</v>
+        <v>97.3</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>0.1</v>
+        <v>0.7</v>
       </c>
       <c r="Q14" s="3" t="n">
-        <v>22.4</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="R14" s="3" t="n">
         <v>21.1</v>
       </c>
-      <c r="S14" s="8" t="n">
+      <c r="S14" s="3" t="n">
         <v>24.2</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>189</v>
+        <v>89</v>
       </c>
       <c r="U14" s="3" t="n">
         <v>2.9</v>
@@ -1728,17 +1704,17 @@
       <c r="V14" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="W14" s="3" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="X14" s="8" t="n">
+      <c r="W14" s="11" t="n">
+        <v>211.6</v>
+      </c>
+      <c r="X14" s="3" t="n">
         <v>25.5</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>196</v>
+        <v>96</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>9.1</v>
+        <v>10.9</v>
       </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
@@ -1754,16 +1730,16 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>359.6</v>
+        <v>282.8</v>
       </c>
       <c r="D15" s="10" t="n">
-        <v>32.5</v>
+        <v>32.6</v>
       </c>
       <c r="E15" s="10" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="F15" s="10" t="n">
-        <v>26.7</v>
+        <v>26.6</v>
       </c>
       <c r="G15" s="10" t="n">
         <v>11.7</v>
@@ -1772,30 +1748,30 @@
         <v>19.6</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>18.4</v>
+        <v>8.4</v>
       </c>
       <c r="J15" s="3" t="n">
         <v>3.9</v>
       </c>
-      <c r="K15" s="3" t="n">
-        <v>25.1</v>
+      <c r="K15" s="11" t="n">
+        <v>51.7</v>
       </c>
       <c r="L15" s="3" t="n">
         <v>21.6</v>
       </c>
-      <c r="M15" s="3" t="n">
+      <c r="M15" s="11" t="n">
         <v>21.6</v>
       </c>
       <c r="N15" s="3" t="n">
         <v>25.8</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>1100</v>
+        <v>100</v>
       </c>
       <c r="P15" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q15" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q15" s="3" t="n">
         <v>32</v>
       </c>
       <c r="R15" s="3" t="n">
@@ -1805,7 +1781,7 @@
         <v>29.2</v>
       </c>
       <c r="T15" s="3" t="n">
-        <v>161.7</v>
+        <v>61.7</v>
       </c>
       <c r="U15" s="3" t="n">
         <v>18.2</v>
@@ -1813,17 +1789,17 @@
       <c r="V15" s="3" t="n">
         <v>28.7</v>
       </c>
-      <c r="W15" s="8" t="n">
+      <c r="W15" s="3" t="n">
         <v>24.8</v>
       </c>
       <c r="X15" s="3" t="n">
         <v>28.8</v>
       </c>
       <c r="Y15" s="3" t="n">
-        <v>73.09999999999999</v>
+        <v>738.1</v>
       </c>
       <c r="Z15" s="3" t="n">
-        <v>10.1</v>
+        <v>100.6</v>
       </c>
       <c r="AA15" s="3" t="inlineStr">
         <is>
@@ -1842,13 +1818,13 @@
         <v>1291.2</v>
       </c>
       <c r="D16" s="10" t="n">
-        <v>158.2</v>
+        <v>158.5</v>
       </c>
       <c r="E16" s="10" t="n">
-        <v>105.2</v>
+        <v>105.5</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>131.7</v>
+        <v>132</v>
       </c>
       <c r="G16" s="3" t="n">
         <v>52.4</v>
@@ -1857,7 +1833,7 @@
         <v>99.2</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>111.5</v>
+        <v>11.5</v>
       </c>
       <c r="J16" s="3" t="n">
         <v>19.4</v>
@@ -1872,10 +1848,10 @@
         <v>109.5</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>1130.7</v>
+        <v>1230.7</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>27490.1</v>
+        <v>2490.1</v>
       </c>
       <c r="P16" s="3" t="n">
         <v>2.2</v>
@@ -1884,28 +1860,28 @@
         <v>148.7</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>1121.9</v>
+        <v>121.9</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>1136.1</v>
+        <v>1136.2</v>
       </c>
       <c r="T16" s="3" t="n">
         <v>331.8</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>176.6</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="V16" s="3" t="n">
         <v>133.7</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>1120.7</v>
+        <v>120.7</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>162.5</v>
+        <v>142.5</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>1407.4</v>
+        <v>1407.6</v>
       </c>
       <c r="Z16" s="3" t="n">
         <v>34.4</v>
@@ -1924,16 +1900,16 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>1318.2</v>
+        <v>318.2</v>
       </c>
       <c r="D17" s="10" t="n">
-        <v>31.6</v>
+        <v>31.7</v>
       </c>
       <c r="E17" s="10" t="n">
         <v>21.1</v>
       </c>
       <c r="F17" s="10" t="n">
-        <v>26.3</v>
+        <v>26.4</v>
       </c>
       <c r="G17" s="10" t="n">
         <v>10.5</v>
@@ -1947,48 +1923,50 @@
       <c r="J17" s="3" t="n">
         <v>3.9</v>
       </c>
-      <c r="K17" s="3" t="inlineStr"/>
+      <c r="K17" s="3" t="n">
+        <v>1.1</v>
+      </c>
       <c r="L17" s="3" t="n">
         <v>22.1</v>
       </c>
-      <c r="M17" s="8" t="n">
+      <c r="M17" s="3" t="n">
         <v>21.9</v>
       </c>
       <c r="N17" s="3" t="n">
         <v>26.1</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>98</v>
+        <v>398</v>
       </c>
       <c r="P17" s="3" t="n">
         <v>0.4</v>
       </c>
       <c r="Q17" s="3" t="n">
-        <v>29.7</v>
+        <v>29.1</v>
       </c>
       <c r="R17" s="3" t="n">
         <v>24.4</v>
       </c>
-      <c r="S17" s="8" t="n">
-        <v>28.2</v>
+      <c r="S17" s="3" t="n">
+        <v>22.2</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>166.4</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="U17" s="3" t="n">
-        <v>15.3</v>
-      </c>
-      <c r="V17" s="8" t="n">
-        <v>26.7</v>
-      </c>
-      <c r="W17" s="8" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="X17" s="3" t="n">
-        <v>28.5</v>
+        <v>15.8</v>
+      </c>
+      <c r="V17" s="3" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="W17" s="11" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="X17" s="11" t="n">
+        <v>84.59999999999999</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>181.5</v>
+        <v>81.5</v>
       </c>
       <c r="Z17" s="3" t="n">
         <v>16.9</v>
@@ -2007,31 +1985,31 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>1368</v>
+        <v>368</v>
       </c>
       <c r="D18" s="10" t="n">
-        <v>32.6</v>
+        <v>32</v>
       </c>
       <c r="E18" s="10" t="n">
-        <v>20.6</v>
+        <v>21.2</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>26.7</v>
-      </c>
-      <c r="G18" s="3" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="G18" s="10" t="n">
         <v>10.9</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>20.4</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="I18" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="J18" s="8" t="n">
-        <v>46.3</v>
-      </c>
-      <c r="K18" s="8" t="n">
-        <v>10.4</v>
+      <c r="J18" s="3" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="K18" s="11" t="n">
+        <v>6.4</v>
       </c>
       <c r="L18" s="3" t="n">
         <v>21.4</v>
@@ -2039,11 +2017,11 @@
       <c r="M18" s="3" t="n">
         <v>21.1</v>
       </c>
-      <c r="N18" s="8" t="n">
-        <v>224.8</v>
+      <c r="N18" s="11" t="n">
+        <v>12.8</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>97.3</v>
+        <v>91.3</v>
       </c>
       <c r="P18" s="3" t="n">
         <v>0.6</v>
@@ -2051,29 +2029,29 @@
       <c r="Q18" s="3" t="n">
         <v>32.1</v>
       </c>
-      <c r="R18" s="8" t="n">
+      <c r="R18" s="11" t="n">
         <v>25.2</v>
       </c>
-      <c r="S18" s="8" t="n">
+      <c r="S18" s="3" t="n">
         <v>27.7</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>98</v>
+        <v>28</v>
       </c>
       <c r="U18" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="V18" s="8" t="n">
+      <c r="V18" s="3" t="n">
         <v>28.5</v>
       </c>
-      <c r="W18" s="8" t="n">
+      <c r="W18" s="3" t="n">
         <v>24.4</v>
       </c>
       <c r="X18" s="3" t="n">
         <v>21.9</v>
       </c>
       <c r="Y18" s="3" t="n">
-        <v>71.2</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="Z18" s="3" t="n">
         <v>111</v>
@@ -2092,55 +2070,55 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>2260.6</v>
+        <v>265.6</v>
       </c>
       <c r="D19" s="10" t="n">
         <v>30.4</v>
       </c>
       <c r="E19" s="10" t="n">
-        <v>22.6</v>
+        <v>22.2</v>
       </c>
       <c r="F19" s="10" t="n">
-        <v>26.5</v>
-      </c>
-      <c r="G19" s="3" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="G19" s="10" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="H19" s="8" t="n">
+      <c r="H19" s="3" t="n">
         <v>21.4</v>
       </c>
       <c r="I19" s="3" t="n">
         <v>1.6</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>12.8</v>
+        <v>2.8</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="L19" s="8" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="L19" s="3" t="n">
         <v>22.3</v>
       </c>
       <c r="M19" s="3" t="n">
         <v>22</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>86.3</v>
+        <v>26.3</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>197.6</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="Q19" s="3" t="n">
+        <v>80.59999999999999</v>
+      </c>
+      <c r="Q19" s="11" t="n">
         <v>29.9</v>
       </c>
       <c r="R19" s="3" t="n">
         <v>26</v>
       </c>
       <c r="S19" s="3" t="n">
-        <v>31.1</v>
+        <v>51.1</v>
       </c>
       <c r="T19" s="3" t="n">
         <v>73.7</v>
@@ -2148,20 +2126,20 @@
       <c r="U19" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="V19" s="8" t="n">
-        <v>24.3</v>
-      </c>
-      <c r="W19" s="3" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="X19" s="8" t="n">
-        <v>71.09999999999999</v>
+      <c r="V19" s="11" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="W19" s="11" t="n">
+        <v>289.8</v>
+      </c>
+      <c r="X19" s="3" t="n">
+        <v>24.1</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>89</v>
+        <v>829</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>78.3</v>
+        <v>185.9</v>
       </c>
       <c r="AA19" s="3" t="inlineStr">
         <is>
@@ -2177,13 +2155,13 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>365.9</v>
+        <v>3865.9</v>
       </c>
       <c r="D20" s="10" t="n">
-        <v>31.5</v>
+        <v>31.4</v>
       </c>
       <c r="E20" s="10" t="n">
-        <v>21.6</v>
+        <v>21.5</v>
       </c>
       <c r="F20" s="10" t="n">
         <v>26.4</v>
@@ -2194,8 +2172,8 @@
       <c r="H20" s="3" t="n">
         <v>20.6</v>
       </c>
-      <c r="I20" s="8" t="n">
-        <v>28.1</v>
+      <c r="I20" s="3" t="n">
+        <v>12.5</v>
       </c>
       <c r="J20" s="3" t="n">
         <v>14.5</v>
@@ -2209,26 +2187,26 @@
       <c r="M20" s="3" t="n">
         <v>21.4</v>
       </c>
-      <c r="N20" s="8" t="n">
-        <v>35.4</v>
+      <c r="N20" s="3" t="n">
+        <v>25.4</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>98</v>
+        <v>928</v>
       </c>
       <c r="P20" s="3" t="n">
         <v>0.4</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>30.1</v>
-      </c>
-      <c r="R20" s="8" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="R20" s="3" t="n">
         <v>24.8</v>
       </c>
       <c r="S20" s="3" t="n">
         <v>27.5</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>162.3</v>
+        <v>12.3</v>
       </c>
       <c r="U20" s="3" t="n">
         <v>16.6</v>
@@ -2236,14 +2214,14 @@
       <c r="V20" s="3" t="n">
         <v>27.3</v>
       </c>
-      <c r="W20" s="8" t="n">
-        <v>23.8</v>
+      <c r="W20" s="11" t="n">
+        <v>28.8</v>
       </c>
       <c r="X20" s="3" t="n">
-        <v>27.2</v>
+        <v>21.2</v>
       </c>
       <c r="Y20" s="3" t="n">
-        <v>715</v>
+        <v>125</v>
       </c>
       <c r="Z20" s="3" t="n">
         <v>19.1</v>
@@ -2273,8 +2251,8 @@
       <c r="F21" s="10" t="n">
         <v>25.9</v>
       </c>
-      <c r="G21" s="3" t="n">
-        <v>29.5</v>
+      <c r="G21" s="10" t="n">
+        <v>9.5</v>
       </c>
       <c r="H21" s="3" t="n">
         <v>19.6</v>
@@ -2286,22 +2264,22 @@
         <v>3.4</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L21" s="8" t="n">
-        <v>18.6</v>
+        <v>0</v>
+      </c>
+      <c r="L21" s="3" t="n">
+        <v>21.6</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>21.5</v>
+        <v>21.9</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>25.6</v>
+        <v>23.6</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>199</v>
+        <v>99</v>
       </c>
       <c r="P21" s="3" t="n">
-        <v>10.2</v>
+        <v>0.2</v>
       </c>
       <c r="Q21" s="3" t="n">
         <v>30.6</v>
@@ -2310,7 +2288,7 @@
         <v>26.2</v>
       </c>
       <c r="S21" s="3" t="n">
-        <v>31.2</v>
+        <v>91.2</v>
       </c>
       <c r="T21" s="3" t="n">
         <v>71.2</v>
@@ -2318,20 +2296,20 @@
       <c r="U21" s="3" t="n">
         <v>12.6</v>
       </c>
-      <c r="V21" s="8" t="n">
-        <v>78.8</v>
-      </c>
-      <c r="W21" s="8" t="n">
-        <v>16.6</v>
+      <c r="V21" s="3" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="W21" s="11" t="n">
+        <v>46.6</v>
       </c>
       <c r="X21" s="3" t="n">
         <v>28.9</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>77.3</v>
+        <v>712.3</v>
       </c>
       <c r="Z21" s="3" t="n">
-        <v>18.4</v>
+        <v>8.4</v>
       </c>
       <c r="AA21" s="3" t="inlineStr">
         <is>
@@ -2365,21 +2343,21 @@
         <v>19.8</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>12.5</v>
+        <v>2.5</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>14.3</v>
+        <v>4.3</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
       <c r="L22" s="3" t="n">
         <v>21.3</v>
       </c>
       <c r="M22" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="N22" s="8" t="n">
+        <v>22</v>
+      </c>
+      <c r="N22" s="3" t="n">
         <v>24.7</v>
       </c>
       <c r="O22" s="3" t="n">
@@ -2398,25 +2376,25 @@
         <v>89.3</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>160.5</v>
+        <v>60.5</v>
       </c>
       <c r="U22" s="3" t="n">
-        <v>19.2</v>
+        <v>15.2</v>
       </c>
       <c r="V22" s="3" t="n">
-        <v>26.8</v>
+        <v>86.5</v>
       </c>
       <c r="W22" s="3" t="n">
         <v>24.6</v>
       </c>
-      <c r="X22" s="8" t="n">
-        <v>29.1</v>
+      <c r="X22" s="11" t="n">
+        <v>29.4</v>
       </c>
       <c r="Y22" s="3" t="n">
-        <v>186</v>
+        <v>86</v>
       </c>
       <c r="Z22" s="3" t="n">
-        <v>14.9</v>
+        <v>1244.9</v>
       </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
@@ -2432,31 +2410,31 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>17439.6</v>
+        <v>8519.6</v>
       </c>
       <c r="D23" s="10" t="n">
-        <v>158</v>
+        <v>157.3</v>
       </c>
       <c r="E23" s="10" t="n">
-        <v>107</v>
+        <v>107.1</v>
       </c>
       <c r="F23" s="10" t="n">
-        <v>132.5</v>
-      </c>
-      <c r="G23" s="20" t="n">
-        <v>25</v>
+        <v>132.2</v>
+      </c>
+      <c r="G23" s="3" t="n">
+        <v>50.3</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>1101.8</v>
+        <v>101.8</v>
       </c>
       <c r="I23" s="3" t="n">
         <v>10.9</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>19.3</v>
+        <v>104.5</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>19.3</v>
+        <v>495.1</v>
       </c>
       <c r="L23" s="3" t="n">
         <v>108.2</v>
@@ -2465,31 +2443,31 @@
         <v>1107</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>1126.8</v>
+        <v>126.8</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>1489.4</v>
+        <v>489.4</v>
       </c>
       <c r="P23" s="3" t="n">
         <v>2.2</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>155.7</v>
+        <v>1565.7</v>
       </c>
       <c r="R23" s="3" t="n">
         <v>128.1</v>
       </c>
       <c r="S23" s="3" t="n">
-        <v>1146.8</v>
+        <v>146.8</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>325.1</v>
+        <v>3325.1</v>
       </c>
       <c r="U23" s="3" t="n">
         <v>79.40000000000001</v>
       </c>
       <c r="V23" s="3" t="n">
-        <v>134.4</v>
+        <v>138.4</v>
       </c>
       <c r="W23" s="3" t="n">
         <v>120.3</v>
@@ -2498,10 +2476,10 @@
         <v>140.8</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>2399</v>
+        <v>399</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>36.7</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -2517,16 +2495,16 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>347.9</v>
+        <v>343.9</v>
       </c>
       <c r="D24" s="10" t="n">
         <v>31.6</v>
       </c>
       <c r="E24" s="10" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>26.5</v>
+        <v>26.4</v>
       </c>
       <c r="G24" s="10" t="n">
         <v>10.1</v>
@@ -2540,21 +2518,23 @@
       <c r="J24" s="3" t="n">
         <v>3.9</v>
       </c>
-      <c r="K24" s="3" t="inlineStr"/>
+      <c r="K24" s="3" t="n">
+        <v>1.1</v>
+      </c>
       <c r="L24" s="3" t="n">
         <v>21.6</v>
       </c>
       <c r="M24" s="3" t="n">
         <v>21.4</v>
       </c>
-      <c r="N24" s="8" t="n">
-        <v>22.4</v>
+      <c r="N24" s="3" t="n">
+        <v>25.4</v>
       </c>
       <c r="O24" s="3" t="n">
         <v>97.90000000000001</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>0.4</v>
+        <v>10.4</v>
       </c>
       <c r="Q24" s="3" t="n">
         <v>31.1</v>
@@ -2563,10 +2543,10 @@
         <v>25.6</v>
       </c>
       <c r="S24" s="3" t="n">
-        <v>29.4</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>165.1</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="U24" s="3" t="n">
         <v>15.9</v>
@@ -2574,17 +2554,17 @@
       <c r="V24" s="3" t="n">
         <v>26.9</v>
       </c>
-      <c r="W24" s="8" t="n">
+      <c r="W24" s="3" t="n">
         <v>24.1</v>
       </c>
-      <c r="X24" s="8" t="n">
-        <v>282.2</v>
+      <c r="X24" s="11" t="n">
+        <v>29.2</v>
       </c>
       <c r="Y24" s="3" t="n">
         <v>79.8</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>17.3</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2603,16 +2583,16 @@
         <v>106.7</v>
       </c>
       <c r="D25" s="10" t="n">
-        <v>26.4</v>
+        <v>26.3</v>
       </c>
       <c r="E25" s="10" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="F25" s="10" t="n">
         <v>23.5</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>9.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="H25" s="3" t="n">
         <v>20.2</v>
@@ -2624,7 +2604,7 @@
         <v>0.5</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>23.7</v>
+        <v>23.4</v>
       </c>
       <c r="L25" s="3" t="n">
         <v>22.4</v>
@@ -2633,38 +2613,38 @@
         <v>22.1</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>264.4</v>
+        <v>26.4</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>97</v>
+        <v>914</v>
       </c>
       <c r="P25" s="3" t="n">
-        <v>10.7</v>
+        <v>0.7</v>
       </c>
       <c r="Q25" s="3" t="n">
         <v>26.2</v>
       </c>
-      <c r="R25" s="8" t="n">
-        <v>284.1</v>
-      </c>
-      <c r="S25" s="8" t="n">
+      <c r="R25" s="3" t="n">
+        <v>84.09999999999999</v>
+      </c>
+      <c r="S25" s="3" t="n">
         <v>28.7</v>
       </c>
       <c r="T25" s="3" t="n">
-        <v>184.4</v>
-      </c>
-      <c r="U25" s="3" t="inlineStr"/>
-      <c r="V25" s="3" t="n">
-        <v>244.1</v>
-      </c>
+        <v>84.40000000000001</v>
+      </c>
+      <c r="U25" s="3" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="V25" s="3" t="inlineStr"/>
       <c r="W25" s="3" t="n">
         <v>22.8</v>
       </c>
-      <c r="X25" s="8" t="n">
+      <c r="X25" s="11" t="n">
         <v>26.8</v>
       </c>
       <c r="Y25" s="3" t="n">
-        <v>81.7</v>
+        <v>8417.4</v>
       </c>
       <c r="Z25" s="3" t="inlineStr"/>
       <c r="AA25" s="3" t="inlineStr">
@@ -2683,29 +2663,29 @@
       <c r="C26" s="3" t="n">
         <v>290</v>
       </c>
-      <c r="D26" s="10" t="n">
-        <v>37.2</v>
-      </c>
-      <c r="E26" s="10" t="n">
-        <v>21</v>
-      </c>
-      <c r="F26" s="10" t="n">
-        <v>29.1</v>
+      <c r="D26" s="3" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>23.1</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>14.1</v>
+        <v>12.1</v>
       </c>
       <c r="H26" s="3" t="n">
         <v>19.2</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>10.9</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>0.7</v>
+        <v>4.1</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>16.1</v>
+        <v>6.1</v>
       </c>
       <c r="L26" s="3" t="n">
         <v>21.4</v>
@@ -2714,28 +2694,28 @@
         <v>21.4</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>25.5</v>
+        <v>25.9</v>
       </c>
       <c r="O26" s="3" t="n">
         <v>100</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q26" s="3" t="n">
         <v>24.3</v>
       </c>
-      <c r="R26" s="8" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="S26" s="8" t="n">
-        <v>280.9</v>
+      <c r="R26" s="3" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="S26" s="3" t="n">
+        <v>28</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>192</v>
+        <v>92</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>12.9</v>
+        <v>2.4</v>
       </c>
       <c r="V26" s="3" t="n">
         <v>23.8</v>
@@ -2743,14 +2723,14 @@
       <c r="W26" s="3" t="n">
         <v>22.8</v>
       </c>
-      <c r="X26" s="8" t="n">
-        <v>79.09999999999999</v>
+      <c r="X26" s="11" t="n">
+        <v>71.09999999999999</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>191.8</v>
+        <v>91.8</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>2.4</v>
+        <v>124.5</v>
       </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
@@ -2766,16 +2746,16 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>2322</v>
-      </c>
-      <c r="D27" s="10" t="n">
-        <v>30.4</v>
-      </c>
-      <c r="E27" s="10" t="n">
+        <v>322</v>
+      </c>
+      <c r="D27" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="E27" s="3" t="n">
         <v>20.6</v>
       </c>
-      <c r="F27" s="10" t="n">
-        <v>25.5</v>
+      <c r="F27" s="18" t="n">
+        <v>35.4</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>19.9</v>
@@ -2786,12 +2766,14 @@
       <c r="I27" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="J27" s="3" t="inlineStr"/>
+      <c r="J27" s="3" t="n">
+        <v>3.4</v>
+      </c>
       <c r="K27" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>20.7</v>
+        <v>50.3</v>
       </c>
       <c r="M27" s="3" t="n">
         <v>20.5</v>
@@ -2800,7 +2782,7 @@
         <v>24</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>198</v>
+        <v>98</v>
       </c>
       <c r="P27" s="3" t="n">
         <v>0.4</v>
@@ -2808,31 +2790,33 @@
       <c r="Q27" s="3" t="n">
         <v>28.8</v>
       </c>
-      <c r="R27" s="8" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="S27" s="8" t="n">
-        <v>89</v>
+      <c r="R27" s="11" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="S27" s="3" t="n">
+        <v>29</v>
       </c>
       <c r="T27" s="3" t="n">
-        <v>73.2</v>
+        <v>23.2</v>
       </c>
       <c r="U27" s="3" t="n">
         <v>10.5</v>
       </c>
       <c r="V27" s="3" t="n">
-        <v>26.9</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="W27" s="3" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="X27" s="8" t="n">
-        <v>29</v>
+        <v>94.40000000000001</v>
+      </c>
+      <c r="X27" s="11" t="n">
+        <v>289</v>
       </c>
       <c r="Y27" s="3" t="n">
         <v>81.8</v>
       </c>
-      <c r="Z27" s="3" t="inlineStr"/>
+      <c r="Z27" s="3" t="n">
+        <v>12.4</v>
+      </c>
       <c r="AA27" s="3" t="inlineStr">
         <is>
           <t>18</t>
@@ -2847,21 +2831,23 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>1290.7</v>
+        <v>290.7</v>
       </c>
       <c r="D28" s="10" t="n">
-        <v>19.5</v>
+        <v>31.7</v>
       </c>
       <c r="E28" s="10" t="n">
         <v>20.5</v>
       </c>
       <c r="F28" s="10" t="n">
-        <v>36.1</v>
-      </c>
-      <c r="G28" s="8" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="G28" s="10" t="n">
         <v>11.3</v>
       </c>
-      <c r="H28" s="3" t="inlineStr"/>
+      <c r="H28" s="3" t="n">
+        <v>18.9</v>
+      </c>
       <c r="I28" s="3" t="n">
         <v>2.2</v>
       </c>
@@ -2869,39 +2855,39 @@
         <v>3.8</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L28" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" s="3" t="n">
         <v>20.9</v>
       </c>
       <c r="M28" s="3" t="n">
         <v>20.6</v>
       </c>
-      <c r="N28" s="8" t="n">
+      <c r="N28" s="3" t="n">
         <v>24.1</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>297.3</v>
+        <v>97.3</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>10.8</v>
+        <v>0.8</v>
       </c>
       <c r="Q28" s="3" t="n">
         <v>31.2</v>
       </c>
-      <c r="R28" s="8" t="n">
+      <c r="R28" s="3" t="n">
         <v>24.8</v>
       </c>
-      <c r="S28" s="8" t="n">
+      <c r="S28" s="3" t="n">
         <v>27.2</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>160.2</v>
+        <v>60.2</v>
       </c>
       <c r="U28" s="3" t="n">
         <v>18.1</v>
       </c>
-      <c r="V28" s="8" t="n">
+      <c r="V28" s="3" t="n">
         <v>28.6</v>
       </c>
       <c r="W28" s="3" t="n">
@@ -2914,7 +2900,7 @@
         <v>72.59999999999999</v>
       </c>
       <c r="Z28" s="3" t="n">
-        <v>10.7</v>
+        <v>107.4</v>
       </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
@@ -2930,26 +2916,28 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>12146.8</v>
-      </c>
-      <c r="D29" s="10" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="E29" s="10" t="n">
+        <v>246.8</v>
+      </c>
+      <c r="D29" s="11" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="E29" s="3" t="n">
         <v>20.5</v>
       </c>
-      <c r="F29" s="10" t="n">
-        <v>26</v>
-      </c>
-      <c r="G29" s="8" t="n">
-        <v>18</v>
-      </c>
-      <c r="H29" s="3" t="inlineStr"/>
+      <c r="F29" s="18" t="n">
+        <v>96</v>
+      </c>
+      <c r="G29" s="11" t="n">
+        <v>11</v>
+      </c>
+      <c r="H29" s="3" t="n">
+        <v>19.2</v>
+      </c>
       <c r="I29" s="3" t="n">
-        <v>11.6</v>
+        <v>1.6</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>2.6</v>
+        <v>12.6</v>
       </c>
       <c r="K29" s="3" t="n">
         <v>8.4</v>
@@ -2957,7 +2945,7 @@
       <c r="L29" s="3" t="n">
         <v>21.1</v>
       </c>
-      <c r="M29" s="8" t="n">
+      <c r="M29" s="3" t="n">
         <v>20.6</v>
       </c>
       <c r="N29" s="3" t="n">
@@ -2970,16 +2958,16 @@
         <v>1.1</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>85.3</v>
-      </c>
-      <c r="R29" s="8" t="n">
+        <v>85.90000000000001</v>
+      </c>
+      <c r="R29" s="3" t="n">
         <v>23.6</v>
       </c>
-      <c r="S29" s="8" t="n">
+      <c r="S29" s="3" t="n">
         <v>28</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>87</v>
+        <v>821</v>
       </c>
       <c r="U29" s="3" t="n">
         <v>14.2</v>
@@ -2990,14 +2978,14 @@
       <c r="W29" s="3" t="n">
         <v>21.3</v>
       </c>
-      <c r="X29" s="8" t="n">
-        <v>14.6</v>
+      <c r="X29" s="11" t="n">
+        <v>16.6</v>
       </c>
       <c r="Y29" s="3" t="n">
         <v>90.8</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>22.5</v>
+        <v>2.5</v>
       </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
@@ -3016,16 +3004,16 @@
         <v>11056.2</v>
       </c>
       <c r="D30" s="10" t="n">
-        <v>145</v>
+        <v>1145.2</v>
       </c>
       <c r="E30" s="10" t="n">
-        <v>103.3</v>
+        <v>1103.2</v>
       </c>
       <c r="F30" s="10" t="n">
-        <v>140.2</v>
-      </c>
-      <c r="G30" s="20" t="n">
-        <v>14.2</v>
+        <v>1124.2</v>
+      </c>
+      <c r="G30" s="10" t="n">
+        <v>42</v>
       </c>
       <c r="H30" s="3" t="n">
         <v>196.6</v>
@@ -3037,52 +3025,52 @@
         <v>111</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>38.8</v>
+        <v>28.8</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>1106.5</v>
+        <v>106.5</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>1105.2</v>
+        <v>105.2</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>123.9</v>
+        <v>125.9</v>
       </c>
       <c r="O30" s="3" t="n">
         <v>487.6</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>12.8</v>
+        <v>2.8</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>11135.8</v>
+        <v>1135.8</v>
       </c>
       <c r="R30" s="3" t="n">
         <v>120.1</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>1140.9</v>
+        <v>140.9</v>
       </c>
       <c r="T30" s="3" t="n">
         <v>396.8</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="V30" s="3" t="n">
         <v>1126.1</v>
       </c>
       <c r="W30" s="3" t="n">
-        <v>1115.9</v>
+        <v>115.8</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>135.9</v>
+        <v>132.9</v>
       </c>
       <c r="Y30" s="3" t="n">
         <v>1424.7</v>
       </c>
       <c r="Z30" s="3" t="n">
-        <v>21.8</v>
+        <v>28.1</v>
       </c>
       <c r="AA30" s="3" t="inlineStr">
         <is>
@@ -3100,16 +3088,16 @@
       <c r="C31" s="3" t="n">
         <v>211.2</v>
       </c>
-      <c r="D31" s="10" t="n">
-        <v>29</v>
-      </c>
-      <c r="E31" s="10" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="F31" s="10" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="G31" s="10" t="n">
+      <c r="D31" s="18" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E31" s="23" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="F31" s="23" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="G31" s="3" t="n">
         <v>8.4</v>
       </c>
       <c r="H31" s="3" t="n">
@@ -3121,26 +3109,28 @@
       <c r="J31" s="3" t="n">
         <v>2.2</v>
       </c>
-      <c r="K31" s="3" t="inlineStr"/>
+      <c r="K31" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="L31" s="3" t="n">
         <v>21.3</v>
       </c>
-      <c r="M31" s="8" t="n">
-        <v>28</v>
-      </c>
-      <c r="N31" s="8" t="n">
+      <c r="M31" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="N31" s="3" t="n">
         <v>24.8</v>
       </c>
       <c r="O31" s="3" t="n">
         <v>97.5</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>10.6</v>
+        <v>0.6</v>
       </c>
       <c r="Q31" s="3" t="n">
         <v>27.2</v>
       </c>
-      <c r="R31" s="8" t="n">
+      <c r="R31" s="3" t="n">
         <v>24.1</v>
       </c>
       <c r="S31" s="3" t="n">
@@ -3149,23 +3139,23 @@
       <c r="T31" s="3" t="n">
         <v>79.40000000000001</v>
       </c>
-      <c r="U31" s="8" t="n">
-        <v>88.8</v>
-      </c>
-      <c r="V31" s="8" t="n">
+      <c r="U31" s="3" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="V31" s="3" t="n">
         <v>25.2</v>
       </c>
       <c r="W31" s="3" t="n">
         <v>23.2</v>
       </c>
       <c r="X31" s="3" t="n">
-        <v>27.2</v>
+        <v>97.2</v>
       </c>
       <c r="Y31" s="3" t="n">
         <v>24.9</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>145.2</v>
+        <v>4.2</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -3181,7 +3171,7 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>384.7</v>
+        <v>8816.9</v>
       </c>
       <c r="D32" s="10" t="n">
         <v>31.1</v>
@@ -3195,17 +3185,17 @@
       <c r="G32" s="10" t="n">
         <v>11.8</v>
       </c>
-      <c r="H32" s="8" t="n">
+      <c r="H32" s="11" t="n">
         <v>18</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>12.3</v>
+        <v>2.9</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>14.6</v>
+        <v>4.6</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L32" s="3" t="n">
         <v>20.1</v>
@@ -3213,9 +3203,11 @@
       <c r="M32" s="3" t="n">
         <v>20.1</v>
       </c>
-      <c r="N32" s="3" t="inlineStr"/>
+      <c r="N32" s="3" t="n">
+        <v>23.9</v>
+      </c>
       <c r="O32" s="3" t="n">
-        <v>1100</v>
+        <v>100</v>
       </c>
       <c r="P32" s="3" t="n">
         <v>0</v>
@@ -3223,17 +3215,17 @@
       <c r="Q32" s="3" t="n">
         <v>31.1</v>
       </c>
-      <c r="R32" s="8" t="n">
+      <c r="R32" s="3" t="n">
         <v>24.9</v>
       </c>
-      <c r="S32" s="3" t="n">
-        <v>27.5</v>
+      <c r="S32" s="11" t="n">
+        <v>72.5</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>161</v>
-      </c>
-      <c r="U32" s="8" t="n">
-        <v>18.5</v>
+        <v>61</v>
+      </c>
+      <c r="U32" s="3" t="n">
+        <v>14.5</v>
       </c>
       <c r="V32" s="3" t="n">
         <v>27.4</v>
@@ -3241,9 +3233,11 @@
       <c r="W32" s="3" t="n">
         <v>23.8</v>
       </c>
-      <c r="X32" s="3" t="inlineStr"/>
+      <c r="X32" s="3" t="n">
+        <v>97.2</v>
+      </c>
       <c r="Y32" s="3" t="n">
-        <v>174.6</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="Z32" s="3" t="n">
         <v>19.3</v>
@@ -3273,61 +3267,65 @@
       <c r="F33" s="10" t="n">
         <v>24.4</v>
       </c>
-      <c r="G33" s="3" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="H33" s="8" t="n">
+      <c r="G33" s="10" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="H33" s="3" t="n">
         <v>18.8</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="J33" s="3" t="n">
         <v>1.6</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="L33" s="8" t="n">
-        <v>21.5</v>
+        <v>14.8</v>
+      </c>
+      <c r="L33" s="3" t="n">
+        <v>81.5</v>
       </c>
       <c r="M33" s="3" t="n">
         <v>21.4</v>
       </c>
-      <c r="N33" s="3" t="inlineStr"/>
+      <c r="N33" s="3" t="n">
+        <v>17.8</v>
+      </c>
       <c r="O33" s="3" t="n">
-        <v>299</v>
+        <v>99</v>
       </c>
       <c r="P33" s="3" t="n">
-        <v>10.2</v>
+        <v>0.2</v>
       </c>
       <c r="Q33" s="3" t="n">
-        <v>28.9</v>
-      </c>
-      <c r="R33" s="8" t="n">
-        <v>206.6</v>
-      </c>
-      <c r="S33" s="8" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="S33" s="3" t="n">
         <v>28.2</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>70.90000000000001</v>
+        <v>20.9</v>
       </c>
       <c r="U33" s="3" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="V33" s="8" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="V33" s="3" t="n">
         <v>25.6</v>
       </c>
-      <c r="W33" s="8" t="n">
+      <c r="W33" s="11" t="n">
         <v>23.8</v>
       </c>
-      <c r="X33" s="3" t="inlineStr"/>
+      <c r="X33" s="3" t="n">
+        <v>28.3</v>
+      </c>
       <c r="Y33" s="3" t="n">
-        <v>861.4</v>
+        <v>86.2</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3349,13 +3347,13 @@
         <v>31.9</v>
       </c>
       <c r="E34" s="10" t="n">
-        <v>21.5</v>
+        <v>21.4</v>
       </c>
       <c r="F34" s="10" t="n">
         <v>26.7</v>
       </c>
       <c r="G34" s="10" t="n">
-        <v>10.5</v>
+        <v>10.4</v>
       </c>
       <c r="H34" s="3" t="n">
         <v>20.2</v>
@@ -3364,12 +3362,12 @@
         <v>2</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>3.5</v>
+        <v>39.5</v>
       </c>
       <c r="K34" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="L34" s="8" t="n">
+      <c r="L34" s="3" t="n">
         <v>21.8</v>
       </c>
       <c r="M34" s="3" t="n">
@@ -3379,22 +3377,22 @@
         <v>25.9</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>199</v>
+        <v>99</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>10.2</v>
+        <v>0.2</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>30.5</v>
+        <v>3</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>25.8</v>
+        <v>23.8</v>
       </c>
       <c r="S34" s="3" t="n">
         <v>30.2</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>169.4</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="U34" s="3" t="n">
         <v>13.3</v>
@@ -3409,7 +3407,7 @@
         <v>29.7</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>82.8</v>
+        <v>182.8</v>
       </c>
       <c r="Z34" s="3" t="n">
         <v>16.5</v>
@@ -3449,55 +3447,55 @@
         <v>2.4</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="K35" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L35" s="3" t="n">
         <v>21.6</v>
       </c>
-      <c r="M35" s="8" t="n">
+      <c r="M35" s="3" t="n">
         <v>21.3</v>
       </c>
       <c r="N35" s="3" t="n">
         <v>25.1</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>197.2</v>
+        <v>97.2</v>
       </c>
       <c r="P35" s="3" t="n">
-        <v>10.7</v>
+        <v>7.1</v>
       </c>
       <c r="Q35" s="3" t="n">
         <v>31.1</v>
       </c>
-      <c r="R35" s="8" t="n">
-        <v>26.9</v>
-      </c>
-      <c r="S35" s="8" t="n">
+      <c r="R35" s="3" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="S35" s="3" t="n">
         <v>27.8</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>1614.3</v>
+        <v>61.3</v>
       </c>
       <c r="U35" s="3" t="n">
         <v>17.4</v>
       </c>
-      <c r="V35" s="8" t="n">
+      <c r="V35" s="3" t="n">
         <v>21.8</v>
       </c>
-      <c r="W35" s="8" t="n">
+      <c r="W35" s="11" t="n">
         <v>16.6</v>
       </c>
-      <c r="X35" s="8" t="n">
+      <c r="X35" s="3" t="n">
         <v>28.9</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>19.8</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="Z35" s="3" t="n">
-        <v>18.4</v>
+        <v>811.1</v>
       </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
@@ -3534,25 +3532,25 @@
         <v>2.4</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="K36" s="8" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K36" s="3" t="n">
         <v>30.6</v>
       </c>
       <c r="L36" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="M36" s="8" t="n">
-        <v>20.1</v>
+      <c r="M36" s="3" t="n">
+        <v>20.7</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>26.2</v>
+        <v>24.2</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>918.5</v>
+        <v>98.5</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>10.6</v>
+        <v>0.6</v>
       </c>
       <c r="Q36" s="3" t="n">
         <v>32.1</v>
@@ -3575,14 +3573,14 @@
       <c r="W36" s="3" t="n">
         <v>24.6</v>
       </c>
-      <c r="X36" s="8" t="n">
-        <v>28.3</v>
+      <c r="X36" s="11" t="n">
+        <v>83.90000000000001</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>42.4</v>
+        <v>172</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>211</v>
+        <v>11</v>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -3604,7 +3602,7 @@
         <v>155.4</v>
       </c>
       <c r="E37" s="10" t="n">
-        <v>102.1</v>
+        <v>102</v>
       </c>
       <c r="F37" s="10" t="n">
         <v>128.7</v>
@@ -3622,52 +3620,52 @@
         <v>18.1</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>135.6</v>
+        <v>35.6</v>
       </c>
       <c r="L37" s="3" t="n">
         <v>1106</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>1803.2</v>
+        <v>105.2</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>121.1</v>
+        <v>126.1</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>492.9</v>
+        <v>492.7</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>1.7</v>
+        <v>17.1</v>
       </c>
       <c r="Q37" s="3" t="n">
+        <v>153.1</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>126.2</v>
+      </c>
+      <c r="S37" s="3" t="n">
         <v>143.1</v>
       </c>
-      <c r="R37" s="3" t="n">
-        <v>1126.2</v>
-      </c>
-      <c r="S37" s="3" t="n">
-        <v>1143.1</v>
-      </c>
       <c r="T37" s="3" t="n">
-        <v>13821.8</v>
+        <v>8216.799999999999</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>79.09999999999999</v>
+        <v>11.7</v>
       </c>
       <c r="V37" s="3" t="n">
-        <v>136.8</v>
+        <v>126.8</v>
       </c>
       <c r="W37" s="3" t="n">
         <v>121.6</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>1142.4</v>
+        <v>102.4</v>
       </c>
       <c r="Y37" s="3" t="n">
         <v>398.2</v>
       </c>
       <c r="Z37" s="3" t="n">
-        <v>1392.7</v>
+        <v>892.1</v>
       </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
@@ -3698,10 +3696,10 @@
         <v>10.6</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>19.3</v>
+        <v>19.8</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="J38" s="3" t="n">
         <v>3.6</v>
@@ -3720,37 +3718,37 @@
         <v>98.5</v>
       </c>
       <c r="P38" s="3" t="n">
-        <v>10.3</v>
+        <v>0.3</v>
       </c>
       <c r="Q38" s="3" t="n">
-        <v>20.7</v>
-      </c>
-      <c r="R38" s="8" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="R38" s="11" t="n">
         <v>25.2</v>
       </c>
       <c r="S38" s="3" t="n">
         <v>28.6</v>
       </c>
       <c r="T38" s="3" t="n">
-        <v>169</v>
+        <v>62</v>
       </c>
       <c r="U38" s="3" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="V38" s="8" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="V38" s="3" t="n">
         <v>87.40000000000001</v>
       </c>
       <c r="W38" s="3" t="n">
-        <v>26.3</v>
+        <v>24.3</v>
       </c>
       <c r="X38" s="3" t="n">
-        <v>28.5</v>
+        <v>88.5</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>78.90000000000001</v>
+        <v>78</v>
       </c>
       <c r="Z38" s="3" t="n">
-        <v>2.9</v>
+        <v>566.1</v>
       </c>
       <c r="AA38" s="3" t="inlineStr">
         <is>
@@ -3766,21 +3764,21 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>332.5</v>
+        <v>3232.5</v>
       </c>
       <c r="D39" s="10" t="n">
-        <v>32</v>
+        <v>32.2</v>
       </c>
       <c r="E39" s="10" t="n">
-        <v>20.2</v>
+        <v>20.6</v>
       </c>
       <c r="F39" s="10" t="n">
         <v>26.1</v>
       </c>
-      <c r="G39" s="10" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="H39" s="8" t="n">
+      <c r="G39" s="11" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="H39" s="3" t="n">
         <v>19.3</v>
       </c>
       <c r="I39" s="3" t="n">
@@ -3789,11 +3787,13 @@
       <c r="J39" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="K39" s="3" t="inlineStr"/>
-      <c r="L39" s="8" t="n">
+      <c r="K39" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L39" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="M39" s="8" t="n">
+      <c r="M39" s="3" t="n">
         <v>20.9</v>
       </c>
       <c r="N39" s="3" t="n">
@@ -3803,37 +3803,37 @@
         <v>99</v>
       </c>
       <c r="P39" s="3" t="n">
-        <v>10.2</v>
+        <v>0.2</v>
       </c>
       <c r="Q39" s="3" t="n">
-        <v>31.9</v>
-      </c>
-      <c r="R39" s="8" t="n">
-        <v>126</v>
-      </c>
-      <c r="S39" s="8" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="R39" s="11" t="n">
+        <v>26</v>
+      </c>
+      <c r="S39" s="3" t="n">
         <v>29.8</v>
       </c>
       <c r="T39" s="3" t="n">
         <v>163.2</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>17.3</v>
-      </c>
-      <c r="V39" s="8" t="n">
-        <v>24.9</v>
+        <v>11.9</v>
+      </c>
+      <c r="V39" s="11" t="n">
+        <v>49.1</v>
       </c>
       <c r="W39" s="3" t="n">
-        <v>23.2</v>
+        <v>22.2</v>
       </c>
       <c r="X39" s="3" t="n">
-        <v>27.6</v>
+        <v>2.7</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>288.2</v>
+        <v>88.2</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>13.6</v>
+        <v>8.6</v>
       </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -3849,13 +3849,13 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>1453.1</v>
+        <v>1534.1</v>
       </c>
       <c r="D40" s="10" t="n">
-        <v>32.9</v>
+        <v>33</v>
       </c>
       <c r="E40" s="10" t="n">
-        <v>18.9</v>
+        <v>18.8</v>
       </c>
       <c r="F40" s="10" t="n">
         <v>25.9</v>
@@ -3867,33 +3867,33 @@
         <v>18.2</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>12.7</v>
+        <v>2.1</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L40" s="3" t="n">
         <v>19.8</v>
       </c>
-      <c r="M40" s="8" t="n">
+      <c r="M40" s="3" t="n">
         <v>19.6</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>28.6</v>
+        <v>22.6</v>
       </c>
       <c r="O40" s="3" t="n">
-        <v>1797.8</v>
+        <v>97.8</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>10.5</v>
+        <v>0.5</v>
       </c>
       <c r="Q40" s="3" t="n">
         <v>32.8</v>
       </c>
-      <c r="R40" s="8" t="n">
+      <c r="R40" s="3" t="n">
         <v>26</v>
       </c>
       <c r="S40" s="3" t="n">
@@ -3906,19 +3906,19 @@
         <v>20.2</v>
       </c>
       <c r="V40" s="3" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="W40" s="8" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="W40" s="11" t="n">
         <v>23.8</v>
       </c>
       <c r="X40" s="3" t="n">
         <v>26.9</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>72</v>
+        <v>22.8</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>10.4</v>
+        <v>101.6</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3934,7 +3934,7 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>269.6</v>
+        <v>965.6</v>
       </c>
       <c r="D41" s="10" t="n">
         <v>31.6</v>
@@ -3957,8 +3957,8 @@
       <c r="J41" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="K41" s="8" t="n">
-        <v>43.6</v>
+      <c r="K41" s="3" t="n">
+        <v>4.6</v>
       </c>
       <c r="L41" s="3" t="n">
         <v>19.9</v>
@@ -3970,10 +3970,10 @@
         <v>23</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>199</v>
+        <v>98</v>
       </c>
       <c r="P41" s="3" t="n">
-        <v>10.2</v>
+        <v>0.2</v>
       </c>
       <c r="Q41" s="3" t="n">
         <v>22.3</v>
@@ -3985,25 +3985,25 @@
         <v>24.9</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>192.8</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="U41" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="V41" s="8" t="n">
-        <v>816.6</v>
-      </c>
-      <c r="W41" s="8" t="n">
-        <v>83.40000000000001</v>
-      </c>
-      <c r="X41" s="8" t="n">
-        <v>28</v>
+        <v>2.8</v>
+      </c>
+      <c r="V41" s="11" t="n">
+        <v>46.6</v>
+      </c>
+      <c r="W41" s="3" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="X41" s="11" t="n">
+        <v>9218</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>190.5</v>
+        <v>90.5</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>2.9</v>
+        <v>18.9</v>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
@@ -4019,10 +4019,10 @@
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>1236.3</v>
+        <v>836.3</v>
       </c>
       <c r="D42" s="10" t="n">
-        <v>31.5</v>
+        <v>31.6</v>
       </c>
       <c r="E42" s="10" t="n">
         <v>20.2</v>
@@ -4037,12 +4037,12 @@
         <v>20</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>10.7</v>
+        <v>0.7</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="K42" s="3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="K42" s="11" t="n">
         <v>28.1</v>
       </c>
       <c r="L42" s="3" t="n">
@@ -4051,43 +4051,45 @@
       <c r="M42" s="3" t="n">
         <v>21.8</v>
       </c>
-      <c r="N42" s="8" t="n">
-        <v>26</v>
+      <c r="N42" s="3" t="n">
+        <v>26.2</v>
       </c>
       <c r="O42" s="3" t="n">
-        <v>199</v>
+        <v>1899</v>
       </c>
       <c r="P42" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q42" s="8" t="n">
+      <c r="Q42" s="3" t="n">
         <v>24.1</v>
       </c>
-      <c r="R42" s="8" t="n">
+      <c r="R42" s="3" t="n">
         <v>23.8</v>
       </c>
-      <c r="S42" s="8" t="n">
+      <c r="S42" s="3" t="n">
         <v>29.3</v>
       </c>
       <c r="T42" s="3" t="n">
-        <v>197.7</v>
+        <v>97.7</v>
       </c>
       <c r="U42" s="3" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="V42" s="3" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="W42" s="8" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="X42" s="3" t="n">
-        <v>28.2</v>
+        <v>0.8</v>
+      </c>
+      <c r="V42" s="11" t="n">
+        <v>822.9</v>
+      </c>
+      <c r="W42" s="11" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="X42" s="11" t="n">
+        <v>88.2</v>
       </c>
       <c r="Y42" s="3" t="n">
-        <v>190.6</v>
-      </c>
-      <c r="Z42" s="3" t="inlineStr"/>
+        <v>90.59999999999999</v>
+      </c>
+      <c r="Z42" s="3" t="n">
+        <v>2.9</v>
+      </c>
       <c r="AA42" s="3" t="inlineStr">
         <is>
           <t>29</t>
@@ -4105,10 +4107,10 @@
         <v>372.2</v>
       </c>
       <c r="D43" s="10" t="n">
-        <v>30.1</v>
+        <v>29.9</v>
       </c>
       <c r="E43" s="10" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="F43" s="10" t="n">
         <v>25.6</v>
@@ -4120,13 +4122,13 @@
         <v>19.8</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>3.7</v>
+        <v>13.7</v>
       </c>
       <c r="K43" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L43" s="3" t="n">
         <v>21.6</v>
@@ -4138,7 +4140,7 @@
         <v>25.6</v>
       </c>
       <c r="O43" s="3" t="n">
-        <v>199</v>
+        <v>99</v>
       </c>
       <c r="P43" s="3" t="n">
         <v>0.2</v>
@@ -4147,22 +4149,22 @@
         <v>29.1</v>
       </c>
       <c r="R43" s="3" t="n">
-        <v>25.5</v>
+        <v>25.6</v>
       </c>
       <c r="S43" s="3" t="n">
         <v>80.40000000000001</v>
       </c>
       <c r="T43" s="3" t="n">
-        <v>79.59999999999999</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="U43" s="3" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="V43" s="8" t="n">
-        <v>79.8</v>
-      </c>
-      <c r="W43" s="3" t="n">
-        <v>24.7</v>
+        <v>9.800000000000001</v>
+      </c>
+      <c r="V43" s="3" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="W43" s="11" t="n">
+        <v>41.4</v>
       </c>
       <c r="X43" s="3" t="n">
         <v>29.1</v>
@@ -4171,7 +4173,7 @@
         <v>18</v>
       </c>
       <c r="Z43" s="3" t="n">
-        <v>18.2</v>
+        <v>198.2</v>
       </c>
       <c r="AA43" s="3" t="inlineStr">
         <is>
@@ -4187,7 +4189,7 @@
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>365.9</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="D44" s="10" t="n">
         <v>32.5</v>
@@ -4201,47 +4203,47 @@
       <c r="G44" s="10" t="n">
         <v>11.3</v>
       </c>
-      <c r="H44" s="8" t="n">
-        <v>19.4</v>
+      <c r="H44" s="3" t="n">
+        <v>89.40000000000001</v>
       </c>
       <c r="I44" s="3" t="n">
         <v>1.9</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>19.6</v>
+        <v>9.6</v>
       </c>
       <c r="K44" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L44" s="3" t="n">
-        <v>28.3</v>
+        <v>22.3</v>
       </c>
       <c r="M44" s="3" t="n">
         <v>22.3</v>
       </c>
-      <c r="N44" s="8" t="n">
+      <c r="N44" s="3" t="n">
         <v>26.9</v>
       </c>
       <c r="O44" s="3" t="n">
-        <v>1100</v>
+        <v>100</v>
       </c>
       <c r="P44" s="3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q44" s="3" t="n">
         <v>32.6</v>
       </c>
-      <c r="R44" s="3" t="n">
+      <c r="R44" s="11" t="n">
         <v>26.4</v>
       </c>
       <c r="S44" s="3" t="n">
-        <v>30.1</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="T44" s="3" t="n">
         <v>162</v>
       </c>
-      <c r="U44" s="8" t="n">
-        <v>18.6</v>
+      <c r="U44" s="3" t="n">
+        <v>8.6</v>
       </c>
       <c r="V44" s="3" t="n">
         <v>28.5</v>
@@ -4249,14 +4251,14 @@
       <c r="W44" s="3" t="n">
         <v>26.3</v>
       </c>
-      <c r="X44" s="8" t="n">
-        <v>32.2</v>
+      <c r="X44" s="3" t="n">
+        <v>82.8</v>
       </c>
       <c r="Y44" s="3" t="n">
         <v>84.40000000000001</v>
       </c>
       <c r="Z44" s="3" t="n">
-        <v>166</v>
+        <v>16</v>
       </c>
       <c r="AA44" s="3" t="inlineStr">
         <is>
@@ -4271,67 +4273,77 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C45" s="3" t="inlineStr"/>
+      <c r="C45" s="3" t="n">
+        <v>2026.2</v>
+      </c>
       <c r="D45" s="10" t="n">
-        <v>190.6</v>
+        <v>190.8</v>
       </c>
       <c r="E45" s="10" t="n">
-        <v>121.6</v>
+        <v>121.8</v>
       </c>
       <c r="F45" s="10" t="n">
         <v>156</v>
       </c>
-      <c r="G45" s="20" t="n">
-        <v>10.9</v>
+      <c r="G45" s="3" t="n">
+        <v>9.1</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>114.7</v>
+        <v>1114.2</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>10.7</v>
+        <v>1101</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>18.4</v>
+        <v>118.4</v>
       </c>
       <c r="K45" s="3" t="n">
-        <v>172.3</v>
+        <v>743.1</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>1166.9</v>
+        <v>11665.9</v>
       </c>
       <c r="M45" s="3" t="n">
-        <v>122.9</v>
+        <v>128.9</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>148.7</v>
+        <v>1148.8</v>
       </c>
       <c r="O45" s="3" t="n">
-        <v>293.8</v>
+        <v>292.8</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="Q45" s="3" t="n">
-        <v>1752.8</v>
+        <v>172.8</v>
       </c>
       <c r="R45" s="3" t="n">
-        <v>149.1</v>
-      </c>
-      <c r="S45" s="3" t="inlineStr"/>
-      <c r="T45" s="3" t="inlineStr"/>
+        <v>1469.1</v>
+      </c>
+      <c r="S45" s="3" t="n">
+        <v>174.1</v>
+      </c>
+      <c r="T45" s="3" t="n">
+        <v>1450.8</v>
+      </c>
       <c r="U45" s="3" t="n">
-        <v>168.6</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="V45" s="3" t="n">
-        <v>138.1</v>
-      </c>
-      <c r="W45" s="3" t="inlineStr"/>
-      <c r="X45" s="3" t="inlineStr"/>
+        <v>158.1</v>
+      </c>
+      <c r="W45" s="3" t="n">
+        <v>172.2</v>
+      </c>
+      <c r="X45" s="3" t="n">
+        <v>84.5</v>
+      </c>
       <c r="Y45" s="3" t="n">
-        <v>3503.7</v>
+        <v>900.1</v>
       </c>
       <c r="Z45" s="3" t="n">
-        <v>9316</v>
+        <v>56</v>
       </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -4347,19 +4359,19 @@
         </is>
       </c>
       <c r="C46" s="3" t="n">
-        <v>2337.6</v>
+        <v>237.6</v>
       </c>
       <c r="D46" s="10" t="n">
         <v>31.8</v>
       </c>
       <c r="E46" s="10" t="n">
-        <v>20.9</v>
+        <v>20.3</v>
       </c>
       <c r="F46" s="10" t="n">
-        <v>26.4</v>
-      </c>
-      <c r="G46" s="8" t="n">
-        <v>11.5</v>
+        <v>26</v>
+      </c>
+      <c r="G46" s="11" t="n">
+        <v>21.5</v>
       </c>
       <c r="H46" s="3" t="n">
         <v>19.1</v>
@@ -4368,13 +4380,15 @@
         <v>1.7</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>53.1</v>
-      </c>
-      <c r="K46" s="3" t="inlineStr"/>
-      <c r="L46" s="8" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K46" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L46" s="11" t="n">
         <v>11.1</v>
       </c>
-      <c r="M46" s="8" t="n">
+      <c r="M46" s="3" t="n">
         <v>20</v>
       </c>
       <c r="N46" s="3" t="n">
@@ -4384,37 +4398,37 @@
         <v>99</v>
       </c>
       <c r="P46" s="3" t="n">
-        <v>10.2</v>
+        <v>0.2</v>
       </c>
       <c r="Q46" s="3" t="n">
         <v>28.8</v>
       </c>
-      <c r="R46" s="8" t="n">
-        <v>216.8</v>
-      </c>
-      <c r="S46" s="8" t="n">
+      <c r="R46" s="3" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="S46" s="3" t="n">
         <v>29</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>729</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="U46" s="3" t="n">
         <v>11.4</v>
       </c>
-      <c r="V46" s="8" t="n">
-        <v>643.4</v>
-      </c>
-      <c r="W46" s="8" t="n">
+      <c r="V46" s="3" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="W46" s="3" t="n">
         <v>24.1</v>
       </c>
       <c r="X46" s="3" t="n">
-        <v>28.1</v>
+        <v>28.7</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>283.9</v>
+        <v>83.8</v>
       </c>
       <c r="Z46" s="3" t="n">
-        <v>15.7</v>
+        <v>62.5</v>
       </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>

--- a/results/05_transient_transcription_output/203/203_196905_SF.JPG_stage_recalc_multi_day_tot_and_avgs.xlsx
+++ b/results/05_transient_transcription_output/203/203_196905_SF.JPG_stage_recalc_multi_day_tot_and_avgs.xlsx
@@ -140,15 +140,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -170,7 +161,7 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -185,7 +176,16 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -799,25 +799,25 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>136.2</v>
+        <v>186.2</v>
       </c>
       <c r="D4" s="10" t="n">
-        <v>28.1</v>
+        <v>28.6</v>
       </c>
       <c r="E4" s="10" t="n">
-        <v>20.9</v>
+        <v>20.5</v>
       </c>
       <c r="F4" s="10" t="n">
         <v>24.1</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>81.7</v>
+        <v>87.2</v>
       </c>
       <c r="H4" s="3" t="n">
         <v>18.2</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>1.7</v>
+        <v>11.8</v>
       </c>
       <c r="J4" s="3" t="n">
         <v>2.9</v>
@@ -841,13 +841,13 @@
         <v>0.2</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>28.8</v>
+        <v>28.7</v>
       </c>
       <c r="R4" s="3" t="n">
         <v>24.1</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>22.1</v>
+        <v>27.1</v>
       </c>
       <c r="T4" s="3" t="n">
         <v>68.90000000000001</v>
@@ -859,13 +859,13 @@
         <v>25.2</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>82.8</v>
+        <v>22.8</v>
       </c>
       <c r="X4" s="3" t="n">
         <v>26.2</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>181.8</v>
+        <v>81.8</v>
       </c>
       <c r="Z4" s="3" t="n">
         <v>5.8</v>
@@ -884,7 +884,7 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>203.8</v>
+        <v>403.8</v>
       </c>
       <c r="D5" s="10" t="n">
         <v>32.6</v>
@@ -908,7 +908,7 @@
         <v>5.5</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L5" s="3" t="n">
         <v>18.9</v>
@@ -920,7 +920,7 @@
         <v>21.6</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>909</v>
+        <v>99</v>
       </c>
       <c r="P5" s="3" t="n">
         <v>0.2</v>
@@ -946,11 +946,11 @@
       <c r="W5" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="X5" s="11" t="n">
-        <v>72.8</v>
+      <c r="X5" s="3" t="n">
+        <v>27.8</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>141.1</v>
+        <v>7174</v>
       </c>
       <c r="Z5" s="3" t="n">
         <v>8.199999999999999</v>
@@ -969,7 +969,7 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>122.3</v>
+        <v>422.3</v>
       </c>
       <c r="D6" s="10" t="n">
         <v>34.2</v>
@@ -983,8 +983,8 @@
       <c r="G6" s="10" t="n">
         <v>15.4</v>
       </c>
-      <c r="H6" s="11" t="n">
-        <v>184.6</v>
+      <c r="H6" s="8" t="n">
+        <v>15.2</v>
       </c>
       <c r="I6" s="3" t="n">
         <v>14.6</v>
@@ -1007,8 +1007,8 @@
       <c r="O6" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="P6" s="11" t="n">
-        <v>80</v>
+      <c r="P6" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="Q6" s="3" t="n">
         <v>32.7</v>
@@ -1020,22 +1020,22 @@
         <v>28.6</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>22.8</v>
+        <v>92.8</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>20.4</v>
+        <v>20.7</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>28.2</v>
-      </c>
-      <c r="W6" s="11" t="n">
-        <v>31.7</v>
+        <v>28.1</v>
+      </c>
+      <c r="W6" s="3" t="n">
+        <v>23.7</v>
       </c>
       <c r="X6" s="3" t="n">
         <v>26.1</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>16614.1</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="Z6" s="3" t="n">
         <v>13.2</v>
@@ -1054,28 +1054,28 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>6472.5</v>
+        <v>472.5</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>34.7</v>
+        <v>34.8</v>
       </c>
       <c r="E7" s="10" t="n">
-        <v>7.3</v>
+        <v>19.3</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>21</v>
-      </c>
-      <c r="G7" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="G7" s="10" t="n">
         <v>15.4</v>
       </c>
       <c r="H7" s="3" t="n">
         <v>18.2</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>47.9</v>
+        <v>84.7</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>1.9</v>
+        <v>7.9</v>
       </c>
       <c r="K7" s="3" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
         <v>34.2</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>22.2</v>
+        <v>2.2</v>
       </c>
       <c r="S7" s="3" t="n">
         <v>27.1</v>
@@ -1110,7 +1110,7 @@
       <c r="U7" s="3" t="n">
         <v>26.5</v>
       </c>
-      <c r="V7" s="11" t="n">
+      <c r="V7" s="3" t="n">
         <v>29.5</v>
       </c>
       <c r="W7" s="3" t="n">
@@ -1123,7 +1123,7 @@
         <v>66.2</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>15.8</v>
+        <v>13.8</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1153,14 +1153,14 @@
       <c r="G8" s="10" t="n">
         <v>14</v>
       </c>
-      <c r="H8" s="11" t="n">
+      <c r="H8" s="8" t="n">
         <v>12</v>
       </c>
       <c r="I8" s="3" t="n">
         <v>2</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="K8" s="3" t="n">
         <v>30.9</v>
@@ -1175,7 +1175,7 @@
         <v>24</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>96.5</v>
+        <v>296.5</v>
       </c>
       <c r="P8" s="3" t="n">
         <v>0.8</v>
@@ -1205,7 +1205,7 @@
         <v>26.1</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>91.40000000000001</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="Z8" s="3" t="n">
         <v>20.6</v>
@@ -1224,28 +1224,28 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>1781.2</v>
+        <v>1783.2</v>
       </c>
       <c r="D9" s="10" t="n">
-        <v>164.2</v>
+        <v>164.9</v>
       </c>
       <c r="E9" s="10" t="n">
-        <v>85.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>124.6</v>
-      </c>
-      <c r="G9" s="3" t="n">
-        <v>65.90000000000001</v>
+        <v>130.9</v>
+      </c>
+      <c r="G9" s="10" t="n">
+        <v>67.90000000000001</v>
       </c>
       <c r="H9" s="3" t="n">
         <v>89.40000000000001</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>16.6</v>
+        <v>16.8</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>12.8</v>
+        <v>27.5</v>
       </c>
       <c r="K9" s="3" t="n">
         <v>30.9</v>
@@ -1260,40 +1260,40 @@
         <v>112.8</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>894.2</v>
+        <v>494.2</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>11.2</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>1179.6</v>
+        <v>149.6</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>122.9</v>
+        <v>121.9</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>155.1</v>
+        <v>135.7</v>
       </c>
       <c r="T9" s="3" t="n">
         <v>329.9</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="V9" s="3" t="n">
         <v>132.8</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>1116.8</v>
+        <v>116.8</v>
       </c>
       <c r="X9" s="3" t="n">
         <v>133.5</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>388.8</v>
+        <v>3788.8</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>141.6</v>
+        <v>41.6</v>
       </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>8188.5</v>
+        <v>35.4</v>
       </c>
       <c r="D10" s="10" t="n">
         <v>33</v>
@@ -1318,21 +1318,23 @@
         <v>19.4</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>26.2</v>
+        <v>26.4</v>
       </c>
       <c r="G10" s="10" t="n">
         <v>13.6</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>11.9</v>
+        <v>17.9</v>
       </c>
       <c r="I10" s="3" t="n">
         <v>3.3</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="K10" s="3" t="inlineStr"/>
+        <v>5.5</v>
+      </c>
+      <c r="K10" s="3" t="n">
+        <v>11.1</v>
+      </c>
       <c r="L10" s="3" t="n">
         <v>20</v>
       </c>
@@ -1348,14 +1350,14 @@
       <c r="P10" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q10" s="3" t="n">
+      <c r="Q10" s="8" t="n">
         <v>29.9</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>94.40000000000001</v>
+        <v>24.4</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>27.8</v>
+        <v>27.1</v>
       </c>
       <c r="T10" s="3" t="n">
         <v>66</v>
@@ -1369,14 +1371,14 @@
       <c r="W10" s="3" t="n">
         <v>23.4</v>
       </c>
-      <c r="X10" s="11" t="n">
-        <v>16.2</v>
+      <c r="X10" s="3" t="n">
+        <v>26.7</v>
       </c>
       <c r="Y10" s="3" t="n">
         <v>72.8</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>18.3</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
@@ -1392,7 +1394,7 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>1265.6</v>
+        <v>265.6</v>
       </c>
       <c r="D11" s="10" t="n">
         <v>30</v>
@@ -1410,7 +1412,7 @@
         <v>18.2</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="J11" s="3" t="n">
         <v>2.8</v>
@@ -1425,10 +1427,10 @@
         <v>20.9</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>24.3</v>
+        <v>24.5</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>927.3</v>
+        <v>21.3</v>
       </c>
       <c r="P11" s="3" t="n">
         <v>0.6</v>
@@ -1437,31 +1439,31 @@
         <v>29.9</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="S11" s="11" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="S11" s="3" t="n">
         <v>29.8</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>720.6</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="U11" s="3" t="n">
         <v>12.4</v>
       </c>
-      <c r="V11" s="11" t="n">
-        <v>72.09999999999999</v>
-      </c>
-      <c r="W11" s="11" t="n">
-        <v>16.9</v>
+      <c r="V11" s="3" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="W11" s="3" t="n">
+        <v>94.90000000000001</v>
       </c>
       <c r="X11" s="3" t="n">
         <v>30.1</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>2894</v>
+        <v>894</v>
       </c>
       <c r="Z11" s="3" t="n">
-        <v>11.8</v>
+        <v>5.8</v>
       </c>
       <c r="AA11" s="3" t="inlineStr">
         <is>
@@ -1477,25 +1479,25 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>347.1</v>
+        <v>242.1</v>
       </c>
       <c r="D12" s="10" t="n">
-        <v>32.4</v>
+        <v>31.8</v>
       </c>
       <c r="E12" s="10" t="n">
         <v>22.6</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>27.6</v>
-      </c>
-      <c r="G12" s="3" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="G12" s="10" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="H12" s="3" t="n">
         <v>21.2</v>
       </c>
-      <c r="I12" s="11" t="n">
-        <v>227.1</v>
+      <c r="I12" s="3" t="n">
+        <v>2.7</v>
       </c>
       <c r="J12" s="3" t="n">
         <v>14.6</v>
@@ -1506,14 +1508,14 @@
       <c r="L12" s="3" t="n">
         <v>23.3</v>
       </c>
-      <c r="M12" s="11" t="n">
-        <v>350.5</v>
-      </c>
-      <c r="N12" s="11" t="n">
-        <v>17.9</v>
+      <c r="M12" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="N12" s="3" t="n">
+        <v>27.9</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>97.40000000000001</v>
+        <v>927.5</v>
       </c>
       <c r="P12" s="3" t="n">
         <v>0.5</v>
@@ -1525,10 +1527,10 @@
         <v>24.9</v>
       </c>
       <c r="S12" s="3" t="n">
-        <v>21.1</v>
+        <v>27.1</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>51.8</v>
+        <v>59.8</v>
       </c>
       <c r="U12" s="3" t="n">
         <v>19.8</v>
@@ -1546,7 +1548,7 @@
         <v>76.7</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>21.6</v>
+        <v>81.7</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1580,10 +1582,10 @@
         <v>19.9</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>18.3</v>
+        <v>3.3</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="K13" s="3" t="n">
         <v>0</v>
@@ -1609,11 +1611,11 @@
       <c r="R13" s="3" t="n">
         <v>24.6</v>
       </c>
-      <c r="S13" s="11" t="n">
-        <v>21.8</v>
+      <c r="S13" s="3" t="n">
+        <v>25.8</v>
       </c>
       <c r="T13" s="3" t="n">
-        <v>427.4</v>
+        <v>52.7</v>
       </c>
       <c r="U13" s="3" t="n">
         <v>23.3</v>
@@ -1625,7 +1627,7 @@
         <v>24.8</v>
       </c>
       <c r="X13" s="3" t="n">
-        <v>29.5</v>
+        <v>29.3</v>
       </c>
       <c r="Y13" s="3" t="n">
         <v>77.59999999999999</v>
@@ -1665,12 +1667,14 @@
         <v>20.3</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>1.5</v>
+        <v>11.5</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="K14" s="3" t="inlineStr"/>
+        <v>82.09999999999999</v>
+      </c>
+      <c r="K14" s="3" t="n">
+        <v>11.1</v>
+      </c>
       <c r="L14" s="3" t="n">
         <v>22.4</v>
       </c>
@@ -1704,8 +1708,8 @@
       <c r="V14" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="W14" s="11" t="n">
-        <v>211.6</v>
+      <c r="W14" s="3" t="n">
+        <v>21.6</v>
       </c>
       <c r="X14" s="3" t="n">
         <v>25.5</v>
@@ -1713,9 +1717,7 @@
       <c r="Y14" s="3" t="n">
         <v>96</v>
       </c>
-      <c r="Z14" s="3" t="n">
-        <v>10.9</v>
-      </c>
+      <c r="Z14" s="3" t="inlineStr"/>
       <c r="AA14" s="3" t="inlineStr">
         <is>
           <t>9</t>
@@ -1730,7 +1732,7 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>282.8</v>
+        <v>359.6</v>
       </c>
       <c r="D15" s="10" t="n">
         <v>32.6</v>
@@ -1748,28 +1750,28 @@
         <v>19.6</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>8.4</v>
+        <v>2.4</v>
       </c>
       <c r="J15" s="3" t="n">
         <v>3.9</v>
       </c>
-      <c r="K15" s="11" t="n">
-        <v>51.7</v>
+      <c r="K15" s="3" t="n">
+        <v>23.7</v>
       </c>
       <c r="L15" s="3" t="n">
         <v>21.6</v>
       </c>
-      <c r="M15" s="11" t="n">
+      <c r="M15" s="3" t="n">
         <v>21.6</v>
       </c>
       <c r="N15" s="3" t="n">
         <v>25.8</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>100</v>
+        <v>100.2</v>
       </c>
       <c r="P15" s="3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q15" s="3" t="n">
         <v>32</v>
@@ -1796,10 +1798,10 @@
         <v>28.8</v>
       </c>
       <c r="Y15" s="3" t="n">
-        <v>738.1</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="Z15" s="3" t="n">
-        <v>100.6</v>
+        <v>10.6</v>
       </c>
       <c r="AA15" s="3" t="inlineStr">
         <is>
@@ -1815,16 +1817,16 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1291.2</v>
+        <v>1221.2</v>
       </c>
       <c r="D16" s="10" t="n">
-        <v>158.5</v>
+        <v>157.9</v>
       </c>
       <c r="E16" s="10" t="n">
         <v>105.5</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>132</v>
+        <v>131.6</v>
       </c>
       <c r="G16" s="3" t="n">
         <v>52.4</v>
@@ -1842,16 +1844,16 @@
         <v>36.8</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>1110.6</v>
+        <v>110.6</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>109.5</v>
+        <v>109.8</v>
       </c>
       <c r="N16" s="3" t="n">
         <v>1230.7</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>2490.1</v>
+        <v>1490.1</v>
       </c>
       <c r="P16" s="3" t="n">
         <v>2.2</v>
@@ -1860,10 +1862,10 @@
         <v>148.7</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>121.9</v>
+        <v>1221.9</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>1136.2</v>
+        <v>1136.1</v>
       </c>
       <c r="T16" s="3" t="n">
         <v>331.8</v>
@@ -1903,10 +1905,10 @@
         <v>318.2</v>
       </c>
       <c r="D17" s="10" t="n">
-        <v>31.7</v>
+        <v>31.5</v>
       </c>
       <c r="E17" s="10" t="n">
-        <v>21.1</v>
+        <v>21</v>
       </c>
       <c r="F17" s="10" t="n">
         <v>26.4</v>
@@ -1918,13 +1920,13 @@
         <v>19.8</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>12.3</v>
+        <v>2.3</v>
       </c>
       <c r="J17" s="3" t="n">
         <v>3.9</v>
       </c>
-      <c r="K17" s="3" t="n">
-        <v>1.1</v>
+      <c r="K17" s="8" t="n">
+        <v>6</v>
       </c>
       <c r="L17" s="3" t="n">
         <v>22.1</v>
@@ -1936,13 +1938,13 @@
         <v>26.1</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>398</v>
+        <v>928</v>
       </c>
       <c r="P17" s="3" t="n">
         <v>0.4</v>
       </c>
       <c r="Q17" s="3" t="n">
-        <v>29.1</v>
+        <v>29.7</v>
       </c>
       <c r="R17" s="3" t="n">
         <v>24.4</v>
@@ -1954,16 +1956,16 @@
         <v>66.40000000000001</v>
       </c>
       <c r="U17" s="3" t="n">
-        <v>15.8</v>
+        <v>15.3</v>
       </c>
       <c r="V17" s="3" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="W17" s="11" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="X17" s="11" t="n">
-        <v>84.59999999999999</v>
+        <v>8.300000000000001</v>
+      </c>
+      <c r="W17" s="3" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="X17" s="3" t="n">
+        <v>28.5</v>
       </c>
       <c r="Y17" s="3" t="n">
         <v>81.5</v>
@@ -1988,7 +1990,7 @@
         <v>368</v>
       </c>
       <c r="D18" s="10" t="n">
-        <v>32</v>
+        <v>32.1</v>
       </c>
       <c r="E18" s="10" t="n">
         <v>21.2</v>
@@ -1996,9 +1998,7 @@
       <c r="F18" s="10" t="n">
         <v>26.6</v>
       </c>
-      <c r="G18" s="10" t="n">
-        <v>10.9</v>
-      </c>
+      <c r="G18" s="3" t="inlineStr"/>
       <c r="H18" s="3" t="n">
         <v>80.40000000000001</v>
       </c>
@@ -2006,10 +2006,10 @@
         <v>2.5</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="K18" s="11" t="n">
-        <v>6.4</v>
+        <v>14.3</v>
+      </c>
+      <c r="K18" s="3" t="n">
+        <v>10.4</v>
       </c>
       <c r="L18" s="3" t="n">
         <v>21.4</v>
@@ -2017,11 +2017,11 @@
       <c r="M18" s="3" t="n">
         <v>21.1</v>
       </c>
-      <c r="N18" s="11" t="n">
-        <v>12.8</v>
+      <c r="N18" s="3" t="n">
+        <v>24.8</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>91.3</v>
+        <v>97.3</v>
       </c>
       <c r="P18" s="3" t="n">
         <v>0.6</v>
@@ -2029,14 +2029,14 @@
       <c r="Q18" s="3" t="n">
         <v>32.1</v>
       </c>
-      <c r="R18" s="11" t="n">
+      <c r="R18" s="3" t="n">
         <v>25.2</v>
       </c>
       <c r="S18" s="3" t="n">
         <v>27.7</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="U18" s="3" t="n">
         <v>20</v>
@@ -2051,10 +2051,10 @@
         <v>21.9</v>
       </c>
       <c r="Y18" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="Z18" s="3" t="n">
-        <v>111</v>
+        <v>11</v>
       </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
@@ -2084,8 +2084,8 @@
       <c r="G19" s="10" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="H19" s="3" t="n">
-        <v>21.4</v>
+      <c r="H19" s="8" t="n">
+        <v>91.40000000000001</v>
       </c>
       <c r="I19" s="3" t="n">
         <v>1.6</v>
@@ -2109,16 +2109,16 @@
         <v>97.59999999999999</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>80.59999999999999</v>
-      </c>
-      <c r="Q19" s="11" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="Q19" s="8" t="n">
         <v>29.9</v>
       </c>
       <c r="R19" s="3" t="n">
         <v>26</v>
       </c>
       <c r="S19" s="3" t="n">
-        <v>51.1</v>
+        <v>31.1</v>
       </c>
       <c r="T19" s="3" t="n">
         <v>73.7</v>
@@ -2126,20 +2126,20 @@
       <c r="U19" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="V19" s="11" t="n">
-        <v>16.3</v>
-      </c>
-      <c r="W19" s="11" t="n">
-        <v>289.8</v>
+      <c r="V19" s="3" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="W19" s="8" t="n">
+        <v>28.9</v>
       </c>
       <c r="X19" s="3" t="n">
-        <v>24.1</v>
+        <v>27.1</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>829</v>
+        <v>89</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>185.9</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AA19" s="3" t="inlineStr">
         <is>
@@ -2155,31 +2155,31 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>3865.9</v>
+        <v>365.9</v>
       </c>
       <c r="D20" s="10" t="n">
-        <v>31.4</v>
+        <v>38.5</v>
       </c>
       <c r="E20" s="10" t="n">
-        <v>21.5</v>
+        <v>18.5</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>26.4</v>
-      </c>
-      <c r="G20" s="3" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="G20" s="10" t="n">
         <v>19.9</v>
       </c>
       <c r="H20" s="3" t="n">
         <v>20.6</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>12.5</v>
+        <v>2.5</v>
       </c>
       <c r="J20" s="3" t="n">
         <v>14.5</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L20" s="3" t="n">
         <v>21.6</v>
@@ -2191,19 +2191,19 @@
         <v>25.4</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>928</v>
+        <v>98</v>
       </c>
       <c r="P20" s="3" t="n">
         <v>0.4</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>20.9</v>
+        <v>30.7</v>
       </c>
       <c r="R20" s="3" t="n">
         <v>24.8</v>
       </c>
-      <c r="S20" s="3" t="n">
-        <v>27.5</v>
+      <c r="S20" s="8" t="n">
+        <v>17.5</v>
       </c>
       <c r="T20" s="3" t="n">
         <v>12.3</v>
@@ -2214,17 +2214,17 @@
       <c r="V20" s="3" t="n">
         <v>27.3</v>
       </c>
-      <c r="W20" s="11" t="n">
-        <v>28.8</v>
+      <c r="W20" s="3" t="n">
+        <v>22.8</v>
       </c>
       <c r="X20" s="3" t="n">
-        <v>21.2</v>
+        <v>27.2</v>
       </c>
       <c r="Y20" s="3" t="n">
-        <v>125</v>
+        <v>725</v>
       </c>
       <c r="Z20" s="3" t="n">
-        <v>19.1</v>
+        <v>9.1</v>
       </c>
       <c r="AA20" s="3" t="inlineStr">
         <is>
@@ -2246,7 +2246,7 @@
         <v>30.6</v>
       </c>
       <c r="E21" s="10" t="n">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="F21" s="10" t="n">
         <v>25.9</v>
@@ -2270,10 +2270,10 @@
         <v>21.6</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>21.9</v>
+        <v>21.5</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>23.6</v>
+        <v>25.6</v>
       </c>
       <c r="O21" s="3" t="n">
         <v>99</v>
@@ -2288,7 +2288,7 @@
         <v>26.2</v>
       </c>
       <c r="S21" s="3" t="n">
-        <v>91.2</v>
+        <v>31.2</v>
       </c>
       <c r="T21" s="3" t="n">
         <v>71.2</v>
@@ -2299,14 +2299,14 @@
       <c r="V21" s="3" t="n">
         <v>27.8</v>
       </c>
-      <c r="W21" s="11" t="n">
-        <v>46.6</v>
+      <c r="W21" s="8" t="n">
+        <v>26.6</v>
       </c>
       <c r="X21" s="3" t="n">
         <v>28.9</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>712.3</v>
+        <v>72.3</v>
       </c>
       <c r="Z21" s="3" t="n">
         <v>8.4</v>
@@ -2336,8 +2336,8 @@
       <c r="F22" s="10" t="n">
         <v>27</v>
       </c>
-      <c r="G22" s="3" t="n">
-        <v>12.8</v>
+      <c r="G22" s="10" t="n">
+        <v>11.8</v>
       </c>
       <c r="H22" s="3" t="n">
         <v>19.8</v>
@@ -2349,13 +2349,13 @@
         <v>4.3</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="L22" s="3" t="n">
         <v>21.3</v>
       </c>
       <c r="M22" s="3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N22" s="3" t="n">
         <v>24.7</v>
@@ -2370,7 +2370,7 @@
         <v>32.4</v>
       </c>
       <c r="R22" s="3" t="n">
-        <v>25.9</v>
+        <v>29.9</v>
       </c>
       <c r="S22" s="3" t="n">
         <v>89.3</v>
@@ -2379,22 +2379,22 @@
         <v>60.5</v>
       </c>
       <c r="U22" s="3" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="V22" s="3" t="n">
-        <v>86.5</v>
+        <v>19.2</v>
+      </c>
+      <c r="V22" s="8" t="n">
+        <v>26.5</v>
       </c>
       <c r="W22" s="3" t="n">
         <v>24.6</v>
       </c>
-      <c r="X22" s="11" t="n">
-        <v>29.4</v>
+      <c r="X22" s="3" t="n">
+        <v>29.7</v>
       </c>
       <c r="Y22" s="3" t="n">
         <v>86</v>
       </c>
       <c r="Z22" s="3" t="n">
-        <v>1244.9</v>
+        <v>144.9</v>
       </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
@@ -2410,19 +2410,19 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>8519.6</v>
+        <v>1739.6</v>
       </c>
       <c r="D23" s="10" t="n">
-        <v>157.3</v>
+        <v>164.5</v>
       </c>
       <c r="E23" s="10" t="n">
-        <v>107.1</v>
+        <v>104.2</v>
       </c>
       <c r="F23" s="10" t="n">
-        <v>132.2</v>
+        <v>134.3</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>50.3</v>
+        <v>20.3</v>
       </c>
       <c r="H23" s="3" t="n">
         <v>101.8</v>
@@ -2431,10 +2431,10 @@
         <v>10.9</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>104.5</v>
+        <v>10.4</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>495.1</v>
+        <v>49.1</v>
       </c>
       <c r="L23" s="3" t="n">
         <v>108.2</v>
@@ -2452,7 +2452,7 @@
         <v>2.2</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>1565.7</v>
+        <v>155.7</v>
       </c>
       <c r="R23" s="3" t="n">
         <v>128.1</v>
@@ -2461,16 +2461,16 @@
         <v>146.8</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>3325.1</v>
+        <v>325.1</v>
       </c>
       <c r="U23" s="3" t="n">
         <v>79.40000000000001</v>
       </c>
       <c r="V23" s="3" t="n">
-        <v>138.4</v>
+        <v>134.4</v>
       </c>
       <c r="W23" s="3" t="n">
-        <v>120.3</v>
+        <v>20.3</v>
       </c>
       <c r="X23" s="3" t="n">
         <v>140.8</v>
@@ -2479,7 +2479,7 @@
         <v>399</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>92.09999999999999</v>
+        <v>362.5</v>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -2495,13 +2495,13 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>343.9</v>
+        <v>343.2</v>
       </c>
       <c r="D24" s="10" t="n">
-        <v>31.6</v>
+        <v>31.2</v>
       </c>
       <c r="E24" s="10" t="n">
-        <v>21.5</v>
+        <v>21.1</v>
       </c>
       <c r="F24" s="10" t="n">
         <v>26.4</v>
@@ -2513,13 +2513,13 @@
         <v>20.4</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>12.2</v>
+        <v>2.2</v>
       </c>
       <c r="J24" s="3" t="n">
         <v>3.9</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>1.1</v>
+        <v>0.1</v>
       </c>
       <c r="L24" s="3" t="n">
         <v>21.6</v>
@@ -2540,10 +2540,10 @@
         <v>31.1</v>
       </c>
       <c r="R24" s="3" t="n">
-        <v>25.6</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="S24" s="3" t="n">
-        <v>89.40000000000001</v>
+        <v>29.4</v>
       </c>
       <c r="T24" s="3" t="n">
         <v>65.09999999999999</v>
@@ -2557,14 +2557,14 @@
       <c r="W24" s="3" t="n">
         <v>24.1</v>
       </c>
-      <c r="X24" s="11" t="n">
-        <v>29.2</v>
+      <c r="X24" s="3" t="n">
+        <v>23.2</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>79.8</v>
+        <v>2981.3</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>8.300000000000001</v>
+        <v>7.3</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2591,8 +2591,8 @@
       <c r="F25" s="10" t="n">
         <v>23.5</v>
       </c>
-      <c r="G25" s="3" t="n">
-        <v>8.6</v>
+      <c r="G25" s="10" t="n">
+        <v>5.7</v>
       </c>
       <c r="H25" s="3" t="n">
         <v>20.2</v>
@@ -2604,7 +2604,7 @@
         <v>0.5</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>23.4</v>
+        <v>23.7</v>
       </c>
       <c r="L25" s="3" t="n">
         <v>22.4</v>
@@ -2616,7 +2616,7 @@
         <v>26.4</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>914</v>
+        <v>97</v>
       </c>
       <c r="P25" s="3" t="n">
         <v>0.7</v>
@@ -2625,7 +2625,7 @@
         <v>26.2</v>
       </c>
       <c r="R25" s="3" t="n">
-        <v>84.09999999999999</v>
+        <v>24.1</v>
       </c>
       <c r="S25" s="3" t="n">
         <v>28.7</v>
@@ -2634,17 +2634,19 @@
         <v>84.40000000000001</v>
       </c>
       <c r="U25" s="3" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="V25" s="3" t="inlineStr"/>
+        <v>5.3</v>
+      </c>
+      <c r="V25" s="8" t="n">
+        <v>14.4</v>
+      </c>
       <c r="W25" s="3" t="n">
         <v>22.8</v>
       </c>
-      <c r="X25" s="11" t="n">
+      <c r="X25" s="3" t="n">
         <v>26.8</v>
       </c>
       <c r="Y25" s="3" t="n">
-        <v>8417.4</v>
+        <v>8781.700000000001</v>
       </c>
       <c r="Z25" s="3" t="inlineStr"/>
       <c r="AA25" s="3" t="inlineStr">
@@ -2663,26 +2665,26 @@
       <c r="C26" s="3" t="n">
         <v>290</v>
       </c>
-      <c r="D26" s="3" t="n">
+      <c r="D26" s="10" t="n">
         <v>25.1</v>
       </c>
-      <c r="E26" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="F26" s="3" t="n">
+      <c r="E26" s="10" t="n">
+        <v>21</v>
+      </c>
+      <c r="F26" s="10" t="n">
         <v>23.1</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>12.1</v>
+        <v>14.1</v>
       </c>
       <c r="H26" s="3" t="n">
         <v>19.2</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>89.90000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>4.1</v>
+        <v>0.7</v>
       </c>
       <c r="K26" s="3" t="n">
         <v>6.1</v>
@@ -2694,7 +2696,7 @@
         <v>21.4</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>25.9</v>
+        <v>25.5</v>
       </c>
       <c r="O26" s="3" t="n">
         <v>100</v>
@@ -2706,13 +2708,13 @@
         <v>24.3</v>
       </c>
       <c r="R26" s="3" t="n">
-        <v>23.5</v>
+        <v>23.3</v>
       </c>
       <c r="S26" s="3" t="n">
         <v>28</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>92</v>
+        <v>192</v>
       </c>
       <c r="U26" s="3" t="n">
         <v>2.4</v>
@@ -2723,14 +2725,14 @@
       <c r="W26" s="3" t="n">
         <v>22.8</v>
       </c>
-      <c r="X26" s="11" t="n">
-        <v>71.09999999999999</v>
+      <c r="X26" s="3" t="n">
+        <v>27.1</v>
       </c>
       <c r="Y26" s="3" t="n">
         <v>91.8</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>124.5</v>
+        <v>2.4</v>
       </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
@@ -2748,14 +2750,14 @@
       <c r="C27" s="3" t="n">
         <v>322</v>
       </c>
-      <c r="D27" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="E27" s="3" t="n">
+      <c r="D27" s="10" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="E27" s="10" t="n">
         <v>20.6</v>
       </c>
-      <c r="F27" s="18" t="n">
-        <v>35.4</v>
+      <c r="F27" s="10" t="n">
+        <v>25.5</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>19.9</v>
@@ -2773,7 +2775,7 @@
         <v>0</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>50.3</v>
+        <v>50.4</v>
       </c>
       <c r="M27" s="3" t="n">
         <v>20.5</v>
@@ -2790,8 +2792,8 @@
       <c r="Q27" s="3" t="n">
         <v>28.8</v>
       </c>
-      <c r="R27" s="11" t="n">
-        <v>16.9</v>
+      <c r="R27" s="3" t="n">
+        <v>24.9</v>
       </c>
       <c r="S27" s="3" t="n">
         <v>29</v>
@@ -2802,20 +2804,20 @@
       <c r="U27" s="3" t="n">
         <v>10.5</v>
       </c>
-      <c r="V27" s="3" t="n">
-        <v>86.90000000000001</v>
+      <c r="V27" s="8" t="n">
+        <v>826.9</v>
       </c>
       <c r="W27" s="3" t="n">
-        <v>94.40000000000001</v>
-      </c>
-      <c r="X27" s="11" t="n">
-        <v>289</v>
+        <v>24.4</v>
+      </c>
+      <c r="X27" s="8" t="n">
+        <v>89</v>
       </c>
       <c r="Y27" s="3" t="n">
         <v>81.8</v>
       </c>
       <c r="Z27" s="3" t="n">
-        <v>12.4</v>
+        <v>6.4</v>
       </c>
       <c r="AA27" s="3" t="inlineStr">
         <is>
@@ -2834,7 +2836,7 @@
         <v>290.7</v>
       </c>
       <c r="D28" s="10" t="n">
-        <v>31.7</v>
+        <v>31.8</v>
       </c>
       <c r="E28" s="10" t="n">
         <v>20.5</v>
@@ -2867,10 +2869,10 @@
         <v>24.1</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>97.3</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>0.8</v>
+        <v>1.8</v>
       </c>
       <c r="Q28" s="3" t="n">
         <v>31.2</v>
@@ -2900,7 +2902,7 @@
         <v>72.59999999999999</v>
       </c>
       <c r="Z28" s="3" t="n">
-        <v>107.4</v>
+        <v>10.7</v>
       </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
@@ -2918,16 +2920,16 @@
       <c r="C29" s="3" t="n">
         <v>246.8</v>
       </c>
-      <c r="D29" s="11" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="E29" s="3" t="n">
+      <c r="D29" s="10" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="E29" s="10" t="n">
         <v>20.5</v>
       </c>
-      <c r="F29" s="18" t="n">
-        <v>96</v>
-      </c>
-      <c r="G29" s="11" t="n">
+      <c r="F29" s="10" t="n">
+        <v>26</v>
+      </c>
+      <c r="G29" s="10" t="n">
         <v>11</v>
       </c>
       <c r="H29" s="3" t="n">
@@ -2937,7 +2939,7 @@
         <v>1.6</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>12.6</v>
+        <v>2.6</v>
       </c>
       <c r="K29" s="3" t="n">
         <v>8.4</v>
@@ -2958,7 +2960,7 @@
         <v>1.1</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>85.90000000000001</v>
+        <v>25.3</v>
       </c>
       <c r="R29" s="3" t="n">
         <v>23.6</v>
@@ -2967,10 +2969,10 @@
         <v>28</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>821</v>
+        <v>827</v>
       </c>
       <c r="U29" s="3" t="n">
-        <v>14.2</v>
+        <v>94.2</v>
       </c>
       <c r="V29" s="3" t="n">
         <v>22.4</v>
@@ -2978,8 +2980,8 @@
       <c r="W29" s="3" t="n">
         <v>21.3</v>
       </c>
-      <c r="X29" s="11" t="n">
-        <v>16.6</v>
+      <c r="X29" s="8" t="n">
+        <v>14.6</v>
       </c>
       <c r="Y29" s="3" t="n">
         <v>90.8</v>
@@ -3004,19 +3006,19 @@
         <v>11056.2</v>
       </c>
       <c r="D30" s="10" t="n">
-        <v>1145.2</v>
+        <v>145.2</v>
       </c>
       <c r="E30" s="10" t="n">
-        <v>1103.2</v>
+        <v>103.2</v>
       </c>
       <c r="F30" s="10" t="n">
-        <v>1124.2</v>
+        <v>124.2</v>
       </c>
       <c r="G30" s="10" t="n">
         <v>42</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>196.6</v>
+        <v>296.6</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>7.1</v>
@@ -3025,7 +3027,7 @@
         <v>111</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>28.8</v>
+        <v>328.8</v>
       </c>
       <c r="L30" s="3" t="n">
         <v>106.5</v>
@@ -3034,7 +3036,7 @@
         <v>105.2</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>125.9</v>
+        <v>123.9</v>
       </c>
       <c r="O30" s="3" t="n">
         <v>487.6</v>
@@ -3046,31 +3048,29 @@
         <v>1135.8</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>120.1</v>
+        <v>120.7</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>140.9</v>
+        <v>1240.9</v>
       </c>
       <c r="T30" s="3" t="n">
         <v>396.8</v>
       </c>
-      <c r="U30" s="3" t="n">
-        <v>18</v>
-      </c>
+      <c r="U30" s="3" t="inlineStr"/>
       <c r="V30" s="3" t="n">
-        <v>1126.1</v>
+        <v>126.1</v>
       </c>
       <c r="W30" s="3" t="n">
-        <v>115.8</v>
+        <v>115.9</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>132.9</v>
+        <v>135.9</v>
       </c>
       <c r="Y30" s="3" t="n">
         <v>1424.7</v>
       </c>
       <c r="Z30" s="3" t="n">
-        <v>28.1</v>
+        <v>85.8</v>
       </c>
       <c r="AA30" s="3" t="inlineStr">
         <is>
@@ -3088,14 +3088,14 @@
       <c r="C31" s="3" t="n">
         <v>211.2</v>
       </c>
-      <c r="D31" s="18" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="E31" s="23" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="F31" s="23" t="n">
-        <v>14.8</v>
+      <c r="D31" s="10" t="n">
+        <v>29</v>
+      </c>
+      <c r="E31" s="10" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="F31" s="10" t="n">
+        <v>24.8</v>
       </c>
       <c r="G31" s="3" t="n">
         <v>8.4</v>
@@ -3110,7 +3110,7 @@
         <v>2.2</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="L31" s="3" t="n">
         <v>21.3</v>
@@ -3122,7 +3122,7 @@
         <v>24.8</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>97.5</v>
+        <v>927.5</v>
       </c>
       <c r="P31" s="3" t="n">
         <v>0.6</v>
@@ -3140,7 +3140,7 @@
         <v>79.40000000000001</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>18.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="V31" s="3" t="n">
         <v>25.2</v>
@@ -3149,13 +3149,13 @@
         <v>23.2</v>
       </c>
       <c r="X31" s="3" t="n">
-        <v>97.2</v>
+        <v>27.2</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>24.9</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>4.2</v>
+        <v>5.2</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -3171,25 +3171,25 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>8816.9</v>
+        <v>384.7</v>
       </c>
       <c r="D32" s="10" t="n">
         <v>31.1</v>
       </c>
       <c r="E32" s="10" t="n">
-        <v>19.3</v>
+        <v>15.3</v>
       </c>
       <c r="F32" s="10" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="G32" s="10" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="G32" s="3" t="n">
         <v>11.8</v>
       </c>
-      <c r="H32" s="11" t="n">
+      <c r="H32" s="8" t="n">
         <v>18</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
       <c r="J32" s="3" t="n">
         <v>4.6</v>
@@ -3204,7 +3204,7 @@
         <v>20.1</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>23.9</v>
+        <v>23.5</v>
       </c>
       <c r="O32" s="3" t="n">
         <v>100</v>
@@ -3218,26 +3218,26 @@
       <c r="R32" s="3" t="n">
         <v>24.9</v>
       </c>
-      <c r="S32" s="11" t="n">
-        <v>72.5</v>
+      <c r="S32" s="3" t="n">
+        <v>27.5</v>
       </c>
       <c r="T32" s="3" t="n">
         <v>61</v>
       </c>
       <c r="U32" s="3" t="n">
-        <v>14.5</v>
+        <v>17.5</v>
       </c>
       <c r="V32" s="3" t="n">
-        <v>27.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="W32" s="3" t="n">
-        <v>23.8</v>
+        <v>83.8</v>
       </c>
       <c r="X32" s="3" t="n">
-        <v>97.2</v>
+        <v>27.2</v>
       </c>
       <c r="Y32" s="3" t="n">
-        <v>76.09999999999999</v>
+        <v>7641.6</v>
       </c>
       <c r="Z32" s="3" t="n">
         <v>19.3</v>
@@ -3283,13 +3283,13 @@
         <v>14.8</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>81.5</v>
+        <v>21.5</v>
       </c>
       <c r="M33" s="3" t="n">
         <v>21.4</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>17.8</v>
+        <v>23.9</v>
       </c>
       <c r="O33" s="3" t="n">
         <v>99</v>
@@ -3298,16 +3298,16 @@
         <v>0.2</v>
       </c>
       <c r="Q33" s="3" t="n">
-        <v>22.9</v>
+        <v>28.9</v>
       </c>
       <c r="R33" s="3" t="n">
-        <v>20.6</v>
+        <v>28.6</v>
       </c>
       <c r="S33" s="3" t="n">
         <v>28.2</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>20.9</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="U33" s="3" t="n">
         <v>11.5</v>
@@ -3315,17 +3315,17 @@
       <c r="V33" s="3" t="n">
         <v>25.6</v>
       </c>
-      <c r="W33" s="11" t="n">
+      <c r="W33" s="3" t="n">
         <v>23.8</v>
       </c>
       <c r="X33" s="3" t="n">
         <v>28.3</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>86.2</v>
+        <v>26.1</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>12.5</v>
+        <v>144.5</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3347,13 +3347,13 @@
         <v>31.9</v>
       </c>
       <c r="E34" s="10" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>26.7</v>
+        <v>26.6</v>
       </c>
       <c r="G34" s="10" t="n">
-        <v>10.4</v>
+        <v>10.5</v>
       </c>
       <c r="H34" s="3" t="n">
         <v>20.2</v>
@@ -3362,7 +3362,7 @@
         <v>2</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>39.5</v>
+        <v>9.5</v>
       </c>
       <c r="K34" s="3" t="n">
         <v>0.2</v>
@@ -3383,10 +3383,10 @@
         <v>0.2</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>3</v>
+        <v>30.5</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>23.8</v>
+        <v>25.8</v>
       </c>
       <c r="S34" s="3" t="n">
         <v>30.2</v>
@@ -3407,7 +3407,7 @@
         <v>29.7</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>182.8</v>
+        <v>82.8</v>
       </c>
       <c r="Z34" s="3" t="n">
         <v>16.5</v>
@@ -3432,7 +3432,7 @@
         <v>31.1</v>
       </c>
       <c r="E35" s="10" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="F35" s="10" t="n">
         <v>25.9</v>
@@ -3465,16 +3465,16 @@
         <v>97.2</v>
       </c>
       <c r="P35" s="3" t="n">
-        <v>7.1</v>
+        <v>0.7</v>
       </c>
       <c r="Q35" s="3" t="n">
         <v>31.1</v>
       </c>
-      <c r="R35" s="3" t="n">
-        <v>24.9</v>
+      <c r="R35" s="8" t="n">
+        <v>46.9</v>
       </c>
       <c r="S35" s="3" t="n">
-        <v>27.8</v>
+        <v>21.8</v>
       </c>
       <c r="T35" s="3" t="n">
         <v>61.3</v>
@@ -3483,19 +3483,19 @@
         <v>17.4</v>
       </c>
       <c r="V35" s="3" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="W35" s="11" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="W35" s="8" t="n">
         <v>16.6</v>
       </c>
       <c r="X35" s="3" t="n">
         <v>28.9</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>77.90000000000001</v>
+        <v>3.2</v>
       </c>
       <c r="Z35" s="3" t="n">
-        <v>811.1</v>
+        <v>8.4</v>
       </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
@@ -3547,7 +3547,7 @@
         <v>24.2</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>98.5</v>
+        <v>97.5</v>
       </c>
       <c r="P36" s="3" t="n">
         <v>0.6</v>
@@ -3570,17 +3570,17 @@
       <c r="V36" s="3" t="n">
         <v>28.7</v>
       </c>
-      <c r="W36" s="3" t="n">
-        <v>24.6</v>
-      </c>
-      <c r="X36" s="11" t="n">
-        <v>83.90000000000001</v>
+      <c r="W36" s="8" t="n">
+        <v>46.6</v>
+      </c>
+      <c r="X36" s="3" t="n">
+        <v>28.8</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>172</v>
+        <v>72</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>11</v>
+        <v>1411</v>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -3626,10 +3626,10 @@
         <v>1106</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>105.2</v>
+        <v>103.2</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>126.1</v>
+        <v>124.1</v>
       </c>
       <c r="O37" s="3" t="n">
         <v>492.7</v>
@@ -3638,7 +3638,7 @@
         <v>17.1</v>
       </c>
       <c r="Q37" s="3" t="n">
-        <v>153.1</v>
+        <v>153.7</v>
       </c>
       <c r="R37" s="3" t="n">
         <v>126.2</v>
@@ -3647,25 +3647,25 @@
         <v>143.1</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>8216.799999999999</v>
+        <v>324.8</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>11.7</v>
+        <v>19.7</v>
       </c>
       <c r="V37" s="3" t="n">
-        <v>126.8</v>
+        <v>136.8</v>
       </c>
       <c r="W37" s="3" t="n">
         <v>121.6</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>102.4</v>
+        <v>122.4</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>398.2</v>
+        <v>3928.2</v>
       </c>
       <c r="Z37" s="3" t="n">
-        <v>892.1</v>
+        <v>39.7</v>
       </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
@@ -3696,7 +3696,7 @@
         <v>10.6</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>19.8</v>
+        <v>19.3</v>
       </c>
       <c r="I38" s="3" t="n">
         <v>2</v>
@@ -3723,20 +3723,20 @@
       <c r="Q38" s="3" t="n">
         <v>30.7</v>
       </c>
-      <c r="R38" s="11" t="n">
+      <c r="R38" s="3" t="n">
         <v>25.2</v>
       </c>
       <c r="S38" s="3" t="n">
         <v>28.6</v>
       </c>
       <c r="T38" s="3" t="n">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="U38" s="3" t="n">
-        <v>12.5</v>
+        <v>15.5</v>
       </c>
       <c r="V38" s="3" t="n">
-        <v>87.40000000000001</v>
+        <v>27.4</v>
       </c>
       <c r="W38" s="3" t="n">
         <v>24.3</v>
@@ -3748,7 +3748,7 @@
         <v>78</v>
       </c>
       <c r="Z38" s="3" t="n">
-        <v>566.1</v>
+        <v>7.9</v>
       </c>
       <c r="AA38" s="3" t="inlineStr">
         <is>
@@ -3764,21 +3764,21 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>3232.5</v>
+        <v>332.5</v>
       </c>
       <c r="D39" s="10" t="n">
-        <v>32.2</v>
+        <v>31.9</v>
       </c>
       <c r="E39" s="10" t="n">
-        <v>20.6</v>
+        <v>20.2</v>
       </c>
       <c r="F39" s="10" t="n">
         <v>26.1</v>
       </c>
-      <c r="G39" s="11" t="n">
+      <c r="G39" s="8" t="n">
         <v>21.7</v>
       </c>
-      <c r="H39" s="3" t="n">
+      <c r="H39" s="8" t="n">
         <v>19.3</v>
       </c>
       <c r="I39" s="3" t="n">
@@ -3788,7 +3788,7 @@
         <v>3</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="L39" s="3" t="n">
         <v>21</v>
@@ -3806,9 +3806,9 @@
         <v>0.2</v>
       </c>
       <c r="Q39" s="3" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="R39" s="11" t="n">
+        <v>91.90000000000001</v>
+      </c>
+      <c r="R39" s="3" t="n">
         <v>26</v>
       </c>
       <c r="S39" s="3" t="n">
@@ -3818,13 +3818,13 @@
         <v>163.2</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="V39" s="11" t="n">
-        <v>49.1</v>
+        <v>11.3</v>
+      </c>
+      <c r="V39" s="3" t="n">
+        <v>24.9</v>
       </c>
       <c r="W39" s="3" t="n">
-        <v>22.2</v>
+        <v>23.2</v>
       </c>
       <c r="X39" s="3" t="n">
         <v>2.7</v>
@@ -3833,7 +3833,7 @@
         <v>88.2</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>8.6</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -3849,7 +3849,7 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>1534.1</v>
+        <v>153.7</v>
       </c>
       <c r="D40" s="10" t="n">
         <v>33</v>
@@ -3867,10 +3867,10 @@
         <v>18.2</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>2.1</v>
+        <v>2.7</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K40" s="3" t="n">
         <v>0</v>
@@ -3900,7 +3900,7 @@
         <v>29.3</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>39.2</v>
+        <v>59.2</v>
       </c>
       <c r="U40" s="3" t="n">
         <v>20.2</v>
@@ -3908,14 +3908,14 @@
       <c r="V40" s="3" t="n">
         <v>27.8</v>
       </c>
-      <c r="W40" s="11" t="n">
+      <c r="W40" s="3" t="n">
         <v>23.8</v>
       </c>
-      <c r="X40" s="3" t="n">
-        <v>26.9</v>
+      <c r="X40" s="8" t="n">
+        <v>86.90000000000001</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>22.8</v>
+        <v>72</v>
       </c>
       <c r="Z40" s="3" t="n">
         <v>101.6</v>
@@ -3934,7 +3934,7 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>965.6</v>
+        <v>8985.6</v>
       </c>
       <c r="D41" s="10" t="n">
         <v>31.6</v>
@@ -3970,7 +3970,7 @@
         <v>23</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="P41" s="3" t="n">
         <v>0.2</v>
@@ -3981,29 +3981,29 @@
       <c r="R41" s="3" t="n">
         <v>21.4</v>
       </c>
-      <c r="S41" s="3" t="n">
-        <v>24.9</v>
+      <c r="S41" s="8" t="n">
+        <v>16.9</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>92.90000000000001</v>
+        <v>92.3</v>
       </c>
       <c r="U41" s="3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="V41" s="11" t="n">
-        <v>46.6</v>
+        <v>2</v>
+      </c>
+      <c r="V41" s="3" t="n">
+        <v>22.6</v>
       </c>
       <c r="W41" s="3" t="n">
         <v>23.4</v>
       </c>
-      <c r="X41" s="11" t="n">
-        <v>9218</v>
+      <c r="X41" s="3" t="n">
+        <v>98</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>90.5</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>18.9</v>
+        <v>8.9</v>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
@@ -4025,7 +4025,7 @@
         <v>31.6</v>
       </c>
       <c r="E42" s="10" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="F42" s="10" t="n">
         <v>25.9</v>
@@ -4039,11 +4039,11 @@
       <c r="I42" s="3" t="n">
         <v>0.7</v>
       </c>
-      <c r="J42" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="K42" s="11" t="n">
-        <v>28.1</v>
+      <c r="J42" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="K42" s="3" t="n">
+        <v>28.4</v>
       </c>
       <c r="L42" s="3" t="n">
         <v>21.9</v>
@@ -4052,10 +4052,10 @@
         <v>21.8</v>
       </c>
       <c r="N42" s="3" t="n">
-        <v>26.2</v>
+        <v>26</v>
       </c>
       <c r="O42" s="3" t="n">
-        <v>1899</v>
+        <v>89</v>
       </c>
       <c r="P42" s="3" t="n">
         <v>0.2</v>
@@ -4075,14 +4075,14 @@
       <c r="U42" s="3" t="n">
         <v>0.8</v>
       </c>
-      <c r="V42" s="11" t="n">
-        <v>822.9</v>
-      </c>
-      <c r="W42" s="11" t="n">
-        <v>82.5</v>
-      </c>
-      <c r="X42" s="11" t="n">
-        <v>88.2</v>
+      <c r="V42" s="3" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="W42" s="3" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="X42" s="8" t="n">
+        <v>828.2</v>
       </c>
       <c r="Y42" s="3" t="n">
         <v>90.59999999999999</v>
@@ -4107,15 +4107,15 @@
         <v>372.2</v>
       </c>
       <c r="D43" s="10" t="n">
-        <v>29.9</v>
+        <v>28.1</v>
       </c>
       <c r="E43" s="10" t="n">
         <v>21.3</v>
       </c>
       <c r="F43" s="10" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="G43" s="10" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="G43" s="3" t="n">
         <v>8.699999999999999</v>
       </c>
       <c r="H43" s="3" t="n">
@@ -4125,7 +4125,7 @@
         <v>2</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>13.7</v>
+        <v>3.7</v>
       </c>
       <c r="K43" s="3" t="n">
         <v>0</v>
@@ -4149,7 +4149,7 @@
         <v>29.1</v>
       </c>
       <c r="R43" s="3" t="n">
-        <v>25.6</v>
+        <v>25.5</v>
       </c>
       <c r="S43" s="3" t="n">
         <v>80.40000000000001</v>
@@ -4163,17 +4163,17 @@
       <c r="V43" s="3" t="n">
         <v>21.8</v>
       </c>
-      <c r="W43" s="11" t="n">
-        <v>41.4</v>
+      <c r="W43" s="3" t="n">
+        <v>24.7</v>
       </c>
       <c r="X43" s="3" t="n">
         <v>29.1</v>
       </c>
       <c r="Y43" s="3" t="n">
-        <v>18</v>
+        <v>78</v>
       </c>
       <c r="Z43" s="3" t="n">
-        <v>198.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AA43" s="3" t="inlineStr">
         <is>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>65.90000000000001</v>
+        <v>365.9</v>
       </c>
       <c r="D44" s="10" t="n">
         <v>32.5</v>
@@ -4203,8 +4203,8 @@
       <c r="G44" s="10" t="n">
         <v>11.3</v>
       </c>
-      <c r="H44" s="3" t="n">
-        <v>89.40000000000001</v>
+      <c r="H44" s="8" t="n">
+        <v>19.4</v>
       </c>
       <c r="I44" s="3" t="n">
         <v>1.9</v>
@@ -4215,11 +4215,11 @@
       <c r="K44" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L44" s="3" t="n">
-        <v>22.3</v>
+      <c r="L44" s="8" t="n">
+        <v>82.3</v>
       </c>
       <c r="M44" s="3" t="n">
-        <v>22.3</v>
+        <v>82.3</v>
       </c>
       <c r="N44" s="3" t="n">
         <v>26.9</v>
@@ -4228,31 +4228,31 @@
         <v>100</v>
       </c>
       <c r="P44" s="3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q44" s="3" t="n">
         <v>32.6</v>
       </c>
-      <c r="R44" s="11" t="n">
+      <c r="R44" s="3" t="n">
         <v>26.4</v>
       </c>
       <c r="S44" s="3" t="n">
-        <v>80.59999999999999</v>
+        <v>30.4</v>
       </c>
       <c r="T44" s="3" t="n">
-        <v>162</v>
+        <v>62</v>
       </c>
       <c r="U44" s="3" t="n">
-        <v>8.6</v>
+        <v>18.6</v>
       </c>
       <c r="V44" s="3" t="n">
-        <v>28.5</v>
+        <v>28.3</v>
       </c>
       <c r="W44" s="3" t="n">
         <v>26.3</v>
       </c>
-      <c r="X44" s="3" t="n">
-        <v>82.8</v>
+      <c r="X44" s="8" t="n">
+        <v>28.2</v>
       </c>
       <c r="Y44" s="3" t="n">
         <v>84.40000000000001</v>
@@ -4277,73 +4277,73 @@
         <v>2026.2</v>
       </c>
       <c r="D45" s="10" t="n">
-        <v>190.8</v>
+        <v>188.7</v>
       </c>
       <c r="E45" s="10" t="n">
-        <v>121.8</v>
+        <v>121.5</v>
       </c>
       <c r="F45" s="10" t="n">
-        <v>156</v>
+        <v>155.1</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>9.1</v>
+        <v>2.1</v>
       </c>
       <c r="H45" s="3" t="n">
         <v>1114.2</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>1101</v>
+        <v>11</v>
       </c>
       <c r="J45" s="3" t="n">
         <v>118.4</v>
       </c>
       <c r="K45" s="3" t="n">
-        <v>743.1</v>
+        <v>783.6</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>11665.9</v>
+        <v>1166.5</v>
       </c>
       <c r="M45" s="3" t="n">
-        <v>128.9</v>
+        <v>123.9</v>
       </c>
       <c r="N45" s="3" t="n">
         <v>1148.8</v>
       </c>
       <c r="O45" s="3" t="n">
-        <v>292.8</v>
+        <v>293.8</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="Q45" s="3" t="n">
         <v>172.8</v>
       </c>
       <c r="R45" s="3" t="n">
-        <v>1469.1</v>
+        <v>149.1</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>174.1</v>
+        <v>121.1</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>1450.8</v>
+        <v>1230</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>65.59999999999999</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="V45" s="3" t="n">
         <v>158.1</v>
       </c>
       <c r="W45" s="3" t="n">
+        <v>128.2</v>
+      </c>
+      <c r="X45" s="3" t="n">
         <v>172.2</v>
       </c>
-      <c r="X45" s="3" t="n">
-        <v>84.5</v>
-      </c>
       <c r="Y45" s="3" t="n">
-        <v>900.1</v>
+        <v>503.4</v>
       </c>
       <c r="Z45" s="3" t="n">
-        <v>56</v>
+        <v>16</v>
       </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -4362,15 +4362,15 @@
         <v>237.6</v>
       </c>
       <c r="D46" s="10" t="n">
-        <v>31.8</v>
+        <v>31.7</v>
       </c>
       <c r="E46" s="10" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="F46" s="10" t="n">
         <v>26</v>
       </c>
-      <c r="G46" s="11" t="n">
+      <c r="G46" s="3" t="n">
         <v>21.5</v>
       </c>
       <c r="H46" s="3" t="n">
@@ -4382,11 +4382,9 @@
       <c r="J46" s="3" t="n">
         <v>3.1</v>
       </c>
-      <c r="K46" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="L46" s="11" t="n">
-        <v>11.1</v>
+      <c r="K46" s="3" t="inlineStr"/>
+      <c r="L46" s="3" t="n">
+        <v>21.1</v>
       </c>
       <c r="M46" s="3" t="n">
         <v>20</v>
@@ -4395,7 +4393,7 @@
         <v>24.8</v>
       </c>
       <c r="O46" s="3" t="n">
-        <v>99</v>
+        <v>199</v>
       </c>
       <c r="P46" s="3" t="n">
         <v>0.2</v>
@@ -4410,7 +4408,7 @@
         <v>29</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>72.90000000000001</v>
+        <v>22.9</v>
       </c>
       <c r="U46" s="3" t="n">
         <v>11.4</v>
@@ -4425,10 +4423,10 @@
         <v>28.7</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>83.8</v>
+        <v>88.8</v>
       </c>
       <c r="Z46" s="3" t="n">
-        <v>62.5</v>
+        <v>6.2</v>
       </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>

--- a/results/05_transient_transcription_output/203/203_196905_SF.JPG_stage_recalc_multi_day_tot_and_avgs.xlsx
+++ b/results/05_transient_transcription_output/203/203_196905_SF.JPG_stage_recalc_multi_day_tot_and_avgs.xlsx
@@ -125,7 +125,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -152,40 +152,10 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -822,52 +792,52 @@
       <c r="J4" s="3" t="n">
         <v>2.9</v>
       </c>
-      <c r="K4" s="3" t="n">
+      <c r="K4" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="L4" s="3" t="n">
+      <c r="L4" s="10" t="n">
         <v>20.2</v>
       </c>
-      <c r="M4" s="3" t="n">
+      <c r="M4" s="10" t="n">
         <v>20.1</v>
       </c>
-      <c r="N4" s="3" t="n">
+      <c r="N4" s="10" t="n">
         <v>23.4</v>
       </c>
-      <c r="O4" s="3" t="n">
+      <c r="O4" s="10" t="n">
         <v>99</v>
       </c>
-      <c r="P4" s="3" t="n">
+      <c r="P4" s="10" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q4" s="3" t="n">
+      <c r="Q4" s="10" t="n">
         <v>28.7</v>
       </c>
-      <c r="R4" s="3" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="S4" s="3" t="n">
+      <c r="R4" s="10" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="S4" s="10" t="n">
         <v>27.1</v>
       </c>
-      <c r="T4" s="3" t="n">
+      <c r="T4" s="10" t="n">
         <v>68.90000000000001</v>
       </c>
-      <c r="U4" s="3" t="n">
+      <c r="U4" s="10" t="n">
         <v>12.2</v>
       </c>
-      <c r="V4" s="3" t="n">
+      <c r="V4" s="10" t="n">
         <v>25.2</v>
       </c>
-      <c r="W4" s="3" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="X4" s="3" t="n">
+      <c r="W4" s="10" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="X4" s="10" t="n">
         <v>26.2</v>
       </c>
-      <c r="Y4" s="3" t="n">
+      <c r="Y4" s="10" t="n">
         <v>81.8</v>
       </c>
-      <c r="Z4" s="3" t="n">
+      <c r="Z4" s="10" t="n">
         <v>5.8</v>
       </c>
       <c r="AA4" s="3" t="inlineStr">
@@ -907,53 +877,53 @@
       <c r="J5" s="3" t="n">
         <v>5.5</v>
       </c>
-      <c r="K5" s="3" t="n">
+      <c r="K5" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="L5" s="3" t="n">
+      <c r="L5" s="10" t="n">
         <v>18.9</v>
       </c>
-      <c r="M5" s="3" t="n">
+      <c r="M5" s="10" t="n">
         <v>18.8</v>
       </c>
-      <c r="N5" s="3" t="n">
+      <c r="N5" s="10" t="n">
         <v>21.6</v>
       </c>
-      <c r="O5" s="3" t="n">
+      <c r="O5" s="10" t="n">
         <v>99</v>
       </c>
-      <c r="P5" s="3" t="n">
+      <c r="P5" s="10" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q5" s="3" t="n">
+      <c r="Q5" s="10" t="n">
         <v>32.6</v>
       </c>
-      <c r="R5" s="3" t="n">
-        <v>25.4</v>
-      </c>
-      <c r="S5" s="3" t="n">
+      <c r="R5" s="10" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="S5" s="10" t="n">
         <v>27.8</v>
       </c>
-      <c r="T5" s="3" t="n">
+      <c r="T5" s="10" t="n">
         <v>56.6</v>
       </c>
-      <c r="U5" s="3" t="n">
+      <c r="U5" s="10" t="n">
         <v>21.2</v>
       </c>
-      <c r="V5" s="3" t="n">
+      <c r="V5" s="10" t="n">
         <v>27.2</v>
       </c>
-      <c r="W5" s="3" t="n">
+      <c r="W5" s="10" t="n">
         <v>24</v>
       </c>
-      <c r="X5" s="3" t="n">
-        <v>27.8</v>
-      </c>
-      <c r="Y5" s="3" t="n">
-        <v>7174</v>
-      </c>
-      <c r="Z5" s="3" t="n">
-        <v>8.199999999999999</v>
+      <c r="X5" s="10" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="Y5" s="10" t="n">
+        <v>82.7</v>
+      </c>
+      <c r="Z5" s="10" t="n">
+        <v>6.2</v>
       </c>
       <c r="AA5" s="3" t="inlineStr">
         <is>
@@ -992,25 +962,25 @@
       <c r="J6" s="3" t="n">
         <v>7.2</v>
       </c>
-      <c r="K6" s="3" t="n">
+      <c r="K6" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="L6" s="3" t="n">
+      <c r="L6" s="10" t="n">
         <v>20</v>
       </c>
-      <c r="M6" s="3" t="n">
+      <c r="M6" s="10" t="n">
         <v>20</v>
       </c>
-      <c r="N6" s="3" t="n">
+      <c r="N6" s="10" t="n">
         <v>23.3</v>
       </c>
-      <c r="O6" s="3" t="n">
+      <c r="O6" s="10" t="n">
         <v>100</v>
       </c>
-      <c r="P6" s="3" t="n">
+      <c r="P6" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="Q6" s="3" t="n">
+      <c r="Q6" s="10" t="n">
         <v>32.7</v>
       </c>
       <c r="R6" s="3" t="n">
@@ -1025,19 +995,19 @@
       <c r="U6" s="3" t="n">
         <v>20.7</v>
       </c>
-      <c r="V6" s="3" t="n">
-        <v>28.1</v>
-      </c>
-      <c r="W6" s="3" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="X6" s="3" t="n">
+      <c r="V6" s="10" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="W6" s="10" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="X6" s="10" t="n">
         <v>26.1</v>
       </c>
-      <c r="Y6" s="3" t="n">
+      <c r="Y6" s="10" t="n">
         <v>66.40000000000001</v>
       </c>
-      <c r="Z6" s="3" t="n">
+      <c r="Z6" s="10" t="n">
         <v>13.2</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
@@ -1077,28 +1047,28 @@
       <c r="J7" s="3" t="n">
         <v>7.9</v>
       </c>
-      <c r="K7" s="3" t="n">
+      <c r="K7" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="L7" s="3" t="n">
+      <c r="L7" s="10" t="n">
         <v>20.1</v>
       </c>
-      <c r="M7" s="3" t="n">
+      <c r="M7" s="10" t="n">
         <v>20.1</v>
       </c>
-      <c r="N7" s="3" t="n">
+      <c r="N7" s="10" t="n">
         <v>23.5</v>
       </c>
-      <c r="O7" s="3" t="n">
+      <c r="O7" s="10" t="n">
         <v>100</v>
       </c>
-      <c r="P7" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q7" s="3" t="n">
+      <c r="P7" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="10" t="n">
         <v>34.2</v>
       </c>
-      <c r="R7" s="3" t="n">
+      <c r="R7" s="12" t="n">
         <v>2.2</v>
       </c>
       <c r="S7" s="3" t="n">
@@ -1110,20 +1080,20 @@
       <c r="U7" s="3" t="n">
         <v>26.5</v>
       </c>
-      <c r="V7" s="3" t="n">
+      <c r="V7" s="10" t="n">
         <v>29.5</v>
       </c>
-      <c r="W7" s="3" t="n">
+      <c r="W7" s="10" t="n">
         <v>24.4</v>
       </c>
-      <c r="X7" s="3" t="n">
-        <v>27.3</v>
-      </c>
-      <c r="Y7" s="3" t="n">
-        <v>66.2</v>
-      </c>
-      <c r="Z7" s="3" t="n">
-        <v>13.8</v>
+      <c r="X7" s="10" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="Y7" s="10" t="n">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="Z7" s="10" t="n">
+        <v>10.7</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1162,53 +1132,53 @@
       <c r="J8" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="K8" s="3" t="n">
+      <c r="K8" s="10" t="n">
         <v>30.9</v>
       </c>
-      <c r="L8" s="3" t="n">
+      <c r="L8" s="10" t="n">
         <v>21</v>
       </c>
-      <c r="M8" s="3" t="n">
+      <c r="M8" s="10" t="n">
         <v>20.6</v>
       </c>
-      <c r="N8" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="O8" s="3" t="n">
-        <v>296.5</v>
-      </c>
-      <c r="P8" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="Q8" s="3" t="n">
+      <c r="N8" s="10" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="O8" s="10" t="n">
+        <v>97.59999999999999</v>
+      </c>
+      <c r="P8" s="10" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Q8" s="10" t="n">
         <v>21.4</v>
       </c>
-      <c r="R8" s="3" t="n">
+      <c r="R8" s="10" t="n">
         <v>21.2</v>
       </c>
-      <c r="S8" s="3" t="n">
+      <c r="S8" s="10" t="n">
         <v>25.1</v>
       </c>
-      <c r="T8" s="3" t="n">
-        <v>98</v>
-      </c>
-      <c r="U8" s="3" t="n">
+      <c r="T8" s="10" t="n">
+        <v>98.40000000000001</v>
+      </c>
+      <c r="U8" s="10" t="n">
         <v>0.4</v>
       </c>
-      <c r="V8" s="3" t="n">
+      <c r="V8" s="10" t="n">
         <v>22.2</v>
       </c>
-      <c r="W8" s="3" t="n">
+      <c r="W8" s="10" t="n">
         <v>21.9</v>
       </c>
-      <c r="X8" s="3" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="Y8" s="3" t="n">
-        <v>97.40000000000001</v>
-      </c>
-      <c r="Z8" s="3" t="n">
-        <v>20.6</v>
+      <c r="X8" s="10" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="Y8" s="10" t="n">
+        <v>98.2</v>
+      </c>
+      <c r="Z8" s="10" t="n">
+        <v>0.5</v>
       </c>
       <c r="AA8" s="3" t="inlineStr">
         <is>
@@ -1247,28 +1217,28 @@
       <c r="J9" s="3" t="n">
         <v>27.5</v>
       </c>
-      <c r="K9" s="3" t="n">
+      <c r="K9" s="10" t="n">
         <v>30.9</v>
       </c>
-      <c r="L9" s="3" t="n">
+      <c r="L9" s="10" t="n">
         <v>100.2</v>
       </c>
-      <c r="M9" s="3" t="n">
+      <c r="M9" s="10" t="n">
         <v>99.59999999999999</v>
       </c>
-      <c r="N9" s="3" t="n">
-        <v>112.8</v>
-      </c>
-      <c r="O9" s="3" t="n">
-        <v>494.2</v>
-      </c>
-      <c r="P9" s="3" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="Q9" s="3" t="n">
+      <c r="N9" s="10" t="n">
+        <v>1032.5</v>
+      </c>
+      <c r="O9" s="10" t="n">
+        <v>97.8</v>
+      </c>
+      <c r="P9" s="10" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="Q9" s="10" t="n">
         <v>149.6</v>
       </c>
-      <c r="R9" s="3" t="n">
+      <c r="R9" s="13" t="n">
         <v>121.9</v>
       </c>
       <c r="S9" s="3" t="n">
@@ -1280,10 +1250,10 @@
       <c r="U9" s="3" t="n">
         <v>82</v>
       </c>
-      <c r="V9" s="3" t="n">
+      <c r="V9" s="10" t="n">
         <v>132.8</v>
       </c>
-      <c r="W9" s="3" t="n">
+      <c r="W9" s="10" t="n">
         <v>116.8</v>
       </c>
       <c r="X9" s="3" t="n">
@@ -1335,25 +1305,25 @@
       <c r="K10" s="3" t="n">
         <v>11.1</v>
       </c>
-      <c r="L10" s="3" t="n">
+      <c r="L10" s="10" t="n">
         <v>20</v>
       </c>
-      <c r="M10" s="3" t="n">
+      <c r="M10" s="10" t="n">
         <v>19.9</v>
       </c>
-      <c r="N10" s="3" t="n">
+      <c r="N10" s="10" t="n">
         <v>23.2</v>
       </c>
-      <c r="O10" s="3" t="n">
-        <v>98.90000000000001</v>
-      </c>
-      <c r="P10" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Q10" s="8" t="n">
+      <c r="O10" s="10" t="n">
+        <v>99.40000000000001</v>
+      </c>
+      <c r="P10" s="10" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Q10" s="10" t="n">
         <v>29.9</v>
       </c>
-      <c r="R10" s="3" t="n">
+      <c r="R10" s="13" t="n">
         <v>24.4</v>
       </c>
       <c r="S10" s="3" t="n">
@@ -1365,20 +1335,20 @@
       <c r="U10" s="3" t="n">
         <v>16.2</v>
       </c>
-      <c r="V10" s="3" t="n">
+      <c r="V10" s="10" t="n">
         <v>26.6</v>
       </c>
-      <c r="W10" s="3" t="n">
+      <c r="W10" s="10" t="n">
         <v>23.4</v>
       </c>
-      <c r="X10" s="3" t="n">
-        <v>26.7</v>
-      </c>
-      <c r="Y10" s="3" t="n">
-        <v>72.8</v>
-      </c>
-      <c r="Z10" s="3" t="n">
-        <v>8.300000000000001</v>
+      <c r="X10" s="10" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="Y10" s="10" t="n">
+        <v>82.59999999999999</v>
+      </c>
+      <c r="Z10" s="10" t="n">
+        <v>6.1</v>
       </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
@@ -1420,40 +1390,40 @@
       <c r="K11" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L11" s="3" t="n">
+      <c r="L11" s="10" t="n">
         <v>21.2</v>
       </c>
-      <c r="M11" s="3" t="n">
+      <c r="M11" s="10" t="n">
         <v>20.9</v>
       </c>
-      <c r="N11" s="3" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="O11" s="3" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="P11" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="Q11" s="3" t="n">
+      <c r="N11" s="10" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="O11" s="10" t="n">
+        <v>98.2</v>
+      </c>
+      <c r="P11" s="10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q11" s="10" t="n">
         <v>29.9</v>
       </c>
-      <c r="R11" s="3" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="S11" s="3" t="n">
+      <c r="R11" s="10" t="n">
+        <v>24</v>
+      </c>
+      <c r="S11" s="10" t="n">
         <v>29.8</v>
       </c>
-      <c r="T11" s="3" t="n">
+      <c r="T11" s="10" t="n">
         <v>70.59999999999999</v>
       </c>
-      <c r="U11" s="3" t="n">
+      <c r="U11" s="10" t="n">
         <v>12.4</v>
       </c>
       <c r="V11" s="3" t="n">
         <v>27.1</v>
       </c>
-      <c r="W11" s="3" t="n">
+      <c r="W11" s="12" t="n">
         <v>94.90000000000001</v>
       </c>
       <c r="X11" s="3" t="n">
@@ -1505,19 +1475,19 @@
       <c r="K12" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L12" s="3" t="n">
+      <c r="L12" s="10" t="n">
         <v>23.3</v>
       </c>
-      <c r="M12" s="3" t="n">
+      <c r="M12" s="10" t="n">
         <v>23</v>
       </c>
-      <c r="N12" s="3" t="n">
-        <v>27.9</v>
-      </c>
-      <c r="O12" s="3" t="n">
-        <v>927.5</v>
-      </c>
-      <c r="P12" s="3" t="n">
+      <c r="N12" s="10" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="O12" s="10" t="n">
+        <v>98.2</v>
+      </c>
+      <c r="P12" s="10" t="n">
         <v>0.5</v>
       </c>
       <c r="Q12" s="3" t="n">
@@ -1590,34 +1560,34 @@
       <c r="K13" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L13" s="3" t="n">
+      <c r="L13" s="10" t="n">
         <v>22.1</v>
       </c>
-      <c r="M13" s="3" t="n">
+      <c r="M13" s="10" t="n">
         <v>21.9</v>
       </c>
-      <c r="N13" s="3" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="O13" s="3" t="n">
-        <v>98</v>
-      </c>
-      <c r="P13" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="Q13" s="3" t="n">
+      <c r="N13" s="10" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="O13" s="10" t="n">
+        <v>98.8</v>
+      </c>
+      <c r="P13" s="10" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Q13" s="10" t="n">
         <v>32.6</v>
       </c>
-      <c r="R13" s="3" t="n">
-        <v>24.6</v>
-      </c>
-      <c r="S13" s="3" t="n">
+      <c r="R13" s="10" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="S13" s="10" t="n">
         <v>25.8</v>
       </c>
-      <c r="T13" s="3" t="n">
+      <c r="T13" s="10" t="n">
         <v>52.7</v>
       </c>
-      <c r="U13" s="3" t="n">
+      <c r="U13" s="10" t="n">
         <v>23.3</v>
       </c>
       <c r="V13" s="3" t="n">
@@ -1675,22 +1645,22 @@
       <c r="K14" s="3" t="n">
         <v>11.1</v>
       </c>
-      <c r="L14" s="3" t="n">
+      <c r="L14" s="10" t="n">
         <v>22.4</v>
       </c>
-      <c r="M14" s="3" t="n">
+      <c r="M14" s="10" t="n">
         <v>22.1</v>
       </c>
-      <c r="N14" s="3" t="n">
+      <c r="N14" s="10" t="n">
         <v>26.4</v>
       </c>
-      <c r="O14" s="3" t="n">
+      <c r="O14" s="10" t="n">
         <v>97.3</v>
       </c>
-      <c r="P14" s="3" t="n">
+      <c r="P14" s="10" t="n">
         <v>0.7</v>
       </c>
-      <c r="Q14" s="3" t="n">
+      <c r="Q14" s="12" t="n">
         <v>82.40000000000001</v>
       </c>
       <c r="R14" s="3" t="n">
@@ -1758,49 +1728,49 @@
       <c r="K15" s="3" t="n">
         <v>23.7</v>
       </c>
-      <c r="L15" s="3" t="n">
+      <c r="L15" s="10" t="n">
         <v>21.6</v>
       </c>
-      <c r="M15" s="3" t="n">
+      <c r="M15" s="10" t="n">
         <v>21.6</v>
       </c>
-      <c r="N15" s="3" t="n">
+      <c r="N15" s="10" t="n">
         <v>25.8</v>
       </c>
-      <c r="O15" s="3" t="n">
+      <c r="O15" s="10" t="n">
         <v>100.2</v>
       </c>
-      <c r="P15" s="3" t="n">
+      <c r="P15" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="Q15" s="3" t="n">
+      <c r="Q15" s="10" t="n">
         <v>32</v>
       </c>
-      <c r="R15" s="3" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="S15" s="3" t="n">
+      <c r="R15" s="10" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="S15" s="10" t="n">
         <v>29.2</v>
       </c>
-      <c r="T15" s="3" t="n">
+      <c r="T15" s="10" t="n">
         <v>61.7</v>
       </c>
-      <c r="U15" s="3" t="n">
+      <c r="U15" s="10" t="n">
         <v>18.2</v>
       </c>
-      <c r="V15" s="3" t="n">
+      <c r="V15" s="10" t="n">
         <v>28.7</v>
       </c>
-      <c r="W15" s="3" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="X15" s="3" t="n">
+      <c r="W15" s="10" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="X15" s="10" t="n">
         <v>28.8</v>
       </c>
-      <c r="Y15" s="3" t="n">
+      <c r="Y15" s="10" t="n">
         <v>73.09999999999999</v>
       </c>
-      <c r="Z15" s="3" t="n">
+      <c r="Z15" s="10" t="n">
         <v>10.6</v>
       </c>
       <c r="AA15" s="3" t="inlineStr">
@@ -1840,14 +1810,14 @@
       <c r="J16" s="3" t="n">
         <v>19.4</v>
       </c>
-      <c r="K16" s="3" t="n">
+      <c r="K16" s="13" t="n">
         <v>36.8</v>
       </c>
-      <c r="L16" s="3" t="n">
+      <c r="L16" s="10" t="n">
         <v>110.6</v>
       </c>
-      <c r="M16" s="3" t="n">
-        <v>109.8</v>
+      <c r="M16" s="10" t="n">
+        <v>109.5</v>
       </c>
       <c r="N16" s="3" t="n">
         <v>1230.7</v>
@@ -1858,10 +1828,10 @@
       <c r="P16" s="3" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q16" s="3" t="n">
+      <c r="Q16" s="13" t="n">
         <v>148.7</v>
       </c>
-      <c r="R16" s="3" t="n">
+      <c r="R16" s="13" t="n">
         <v>1221.9</v>
       </c>
       <c r="S16" s="3" t="n">
@@ -1873,10 +1843,10 @@
       <c r="U16" s="3" t="n">
         <v>76.59999999999999</v>
       </c>
-      <c r="V16" s="3" t="n">
+      <c r="V16" s="13" t="n">
         <v>133.7</v>
       </c>
-      <c r="W16" s="3" t="n">
+      <c r="W16" s="13" t="n">
         <v>120.7</v>
       </c>
       <c r="X16" s="3" t="n">
@@ -1928,25 +1898,25 @@
       <c r="K17" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="L17" s="3" t="n">
+      <c r="L17" s="10" t="n">
         <v>22.1</v>
       </c>
-      <c r="M17" s="3" t="n">
+      <c r="M17" s="10" t="n">
         <v>21.9</v>
       </c>
-      <c r="N17" s="3" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="O17" s="3" t="n">
-        <v>928</v>
-      </c>
-      <c r="P17" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="Q17" s="3" t="n">
+      <c r="N17" s="10" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="O17" s="10" t="n">
+        <v>98.8</v>
+      </c>
+      <c r="P17" s="10" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Q17" s="13" t="n">
         <v>29.7</v>
       </c>
-      <c r="R17" s="3" t="n">
+      <c r="R17" s="13" t="n">
         <v>24.4</v>
       </c>
       <c r="S17" s="3" t="n">
@@ -1958,10 +1928,10 @@
       <c r="U17" s="3" t="n">
         <v>15.3</v>
       </c>
-      <c r="V17" s="3" t="n">
+      <c r="V17" s="13" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="W17" s="3" t="n">
+      <c r="W17" s="13" t="n">
         <v>24.1</v>
       </c>
       <c r="X17" s="3" t="n">
@@ -2011,22 +1981,22 @@
       <c r="K18" s="3" t="n">
         <v>10.4</v>
       </c>
-      <c r="L18" s="3" t="n">
+      <c r="L18" s="10" t="n">
         <v>21.4</v>
       </c>
-      <c r="M18" s="3" t="n">
+      <c r="M18" s="10" t="n">
         <v>21.1</v>
       </c>
-      <c r="N18" s="3" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="O18" s="3" t="n">
-        <v>97.3</v>
-      </c>
-      <c r="P18" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="Q18" s="3" t="n">
+      <c r="N18" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="O18" s="10" t="n">
+        <v>98.2</v>
+      </c>
+      <c r="P18" s="10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q18" s="10" t="n">
         <v>32.1</v>
       </c>
       <c r="R18" s="3" t="n">
@@ -2041,7 +2011,7 @@
       <c r="U18" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="V18" s="3" t="n">
+      <c r="V18" s="10" t="n">
         <v>28.5</v>
       </c>
       <c r="W18" s="3" t="n">
@@ -2096,37 +2066,37 @@
       <c r="K19" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="L19" s="3" t="n">
+      <c r="L19" s="10" t="n">
         <v>22.3</v>
       </c>
-      <c r="M19" s="3" t="n">
+      <c r="M19" s="10" t="n">
         <v>22</v>
       </c>
-      <c r="N19" s="3" t="n">
-        <v>26.3</v>
-      </c>
-      <c r="O19" s="3" t="n">
-        <v>97.59999999999999</v>
-      </c>
-      <c r="P19" s="3" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="Q19" s="8" t="n">
+      <c r="N19" s="10" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="O19" s="10" t="n">
+        <v>98.2</v>
+      </c>
+      <c r="P19" s="10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q19" s="10" t="n">
         <v>29.9</v>
       </c>
-      <c r="R19" s="3" t="n">
-        <v>26</v>
-      </c>
-      <c r="S19" s="3" t="n">
+      <c r="R19" s="10" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="S19" s="10" t="n">
         <v>31.1</v>
       </c>
-      <c r="T19" s="3" t="n">
+      <c r="T19" s="10" t="n">
         <v>73.7</v>
       </c>
-      <c r="U19" s="3" t="n">
+      <c r="U19" s="10" t="n">
         <v>11</v>
       </c>
-      <c r="V19" s="3" t="n">
+      <c r="V19" s="10" t="n">
         <v>24.3</v>
       </c>
       <c r="W19" s="8" t="n">
@@ -2181,22 +2151,22 @@
       <c r="K20" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L20" s="3" t="n">
+      <c r="L20" s="10" t="n">
         <v>21.6</v>
       </c>
-      <c r="M20" s="3" t="n">
+      <c r="M20" s="10" t="n">
         <v>21.4</v>
       </c>
-      <c r="N20" s="3" t="n">
-        <v>25.4</v>
-      </c>
-      <c r="O20" s="3" t="n">
-        <v>98</v>
-      </c>
-      <c r="P20" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="Q20" s="3" t="n">
+      <c r="N20" s="10" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="O20" s="10" t="n">
+        <v>98.8</v>
+      </c>
+      <c r="P20" s="10" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Q20" s="10" t="n">
         <v>30.7</v>
       </c>
       <c r="R20" s="3" t="n">
@@ -2211,7 +2181,7 @@
       <c r="U20" s="3" t="n">
         <v>16.6</v>
       </c>
-      <c r="V20" s="3" t="n">
+      <c r="V20" s="10" t="n">
         <v>27.3</v>
       </c>
       <c r="W20" s="3" t="n">
@@ -2266,37 +2236,37 @@
       <c r="K21" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L21" s="3" t="n">
+      <c r="L21" s="10" t="n">
         <v>21.6</v>
       </c>
-      <c r="M21" s="3" t="n">
+      <c r="M21" s="10" t="n">
         <v>21.5</v>
       </c>
-      <c r="N21" s="3" t="n">
+      <c r="N21" s="10" t="n">
         <v>25.6</v>
       </c>
-      <c r="O21" s="3" t="n">
-        <v>99</v>
-      </c>
-      <c r="P21" s="3" t="n">
+      <c r="O21" s="10" t="n">
+        <v>99.40000000000001</v>
+      </c>
+      <c r="P21" s="10" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q21" s="3" t="n">
+      <c r="Q21" s="10" t="n">
         <v>30.6</v>
       </c>
-      <c r="R21" s="3" t="n">
-        <v>26.2</v>
-      </c>
-      <c r="S21" s="3" t="n">
+      <c r="R21" s="10" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="S21" s="10" t="n">
         <v>31.2</v>
       </c>
-      <c r="T21" s="3" t="n">
+      <c r="T21" s="10" t="n">
         <v>71.2</v>
       </c>
-      <c r="U21" s="3" t="n">
+      <c r="U21" s="10" t="n">
         <v>12.6</v>
       </c>
-      <c r="V21" s="3" t="n">
+      <c r="V21" s="10" t="n">
         <v>27.8</v>
       </c>
       <c r="W21" s="8" t="n">
@@ -2351,22 +2321,22 @@
       <c r="K22" s="3" t="n">
         <v>2.7</v>
       </c>
-      <c r="L22" s="3" t="n">
+      <c r="L22" s="10" t="n">
         <v>21.3</v>
       </c>
-      <c r="M22" s="3" t="n">
+      <c r="M22" s="10" t="n">
         <v>21</v>
       </c>
-      <c r="N22" s="3" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="O22" s="3" t="n">
-        <v>97.5</v>
-      </c>
-      <c r="P22" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="Q22" s="3" t="n">
+      <c r="N22" s="10" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="O22" s="10" t="n">
+        <v>98.2</v>
+      </c>
+      <c r="P22" s="10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q22" s="10" t="n">
         <v>32.4</v>
       </c>
       <c r="R22" s="3" t="n">
@@ -2381,7 +2351,7 @@
       <c r="U22" s="3" t="n">
         <v>19.2</v>
       </c>
-      <c r="V22" s="8" t="n">
+      <c r="V22" s="10" t="n">
         <v>26.5</v>
       </c>
       <c r="W22" s="3" t="n">
@@ -2433,14 +2403,14 @@
       <c r="J23" s="3" t="n">
         <v>10.4</v>
       </c>
-      <c r="K23" s="3" t="n">
+      <c r="K23" s="13" t="n">
         <v>49.1</v>
       </c>
-      <c r="L23" s="3" t="n">
+      <c r="L23" s="10" t="n">
         <v>108.2</v>
       </c>
-      <c r="M23" s="3" t="n">
-        <v>1107</v>
+      <c r="M23" s="10" t="n">
+        <v>107</v>
       </c>
       <c r="N23" s="3" t="n">
         <v>126.8</v>
@@ -2451,10 +2421,10 @@
       <c r="P23" s="3" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q23" s="3" t="n">
+      <c r="Q23" s="10" t="n">
         <v>155.7</v>
       </c>
-      <c r="R23" s="3" t="n">
+      <c r="R23" s="13" t="n">
         <v>128.1</v>
       </c>
       <c r="S23" s="3" t="n">
@@ -2466,10 +2436,10 @@
       <c r="U23" s="3" t="n">
         <v>79.40000000000001</v>
       </c>
-      <c r="V23" s="3" t="n">
+      <c r="V23" s="10" t="n">
         <v>134.4</v>
       </c>
-      <c r="W23" s="3" t="n">
+      <c r="W23" s="13" t="n">
         <v>20.3</v>
       </c>
       <c r="X23" s="3" t="n">
@@ -2521,40 +2491,40 @@
       <c r="K24" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="L24" s="3" t="n">
+      <c r="L24" s="10" t="n">
         <v>21.6</v>
       </c>
-      <c r="M24" s="3" t="n">
+      <c r="M24" s="10" t="n">
         <v>21.4</v>
       </c>
-      <c r="N24" s="3" t="n">
-        <v>25.4</v>
-      </c>
-      <c r="O24" s="3" t="n">
-        <v>97.90000000000001</v>
-      </c>
-      <c r="P24" s="3" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="Q24" s="3" t="n">
+      <c r="N24" s="10" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="O24" s="10" t="n">
+        <v>98.8</v>
+      </c>
+      <c r="P24" s="10" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Q24" s="10" t="n">
         <v>31.1</v>
       </c>
-      <c r="R24" s="3" t="n">
-        <v>85.59999999999999</v>
-      </c>
-      <c r="S24" s="3" t="n">
+      <c r="R24" s="10" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="S24" s="10" t="n">
         <v>29.4</v>
       </c>
-      <c r="T24" s="3" t="n">
+      <c r="T24" s="10" t="n">
         <v>65.09999999999999</v>
       </c>
-      <c r="U24" s="3" t="n">
+      <c r="U24" s="10" t="n">
         <v>15.9</v>
       </c>
-      <c r="V24" s="3" t="n">
+      <c r="V24" s="10" t="n">
         <v>26.9</v>
       </c>
-      <c r="W24" s="3" t="n">
+      <c r="W24" s="13" t="n">
         <v>24.1</v>
       </c>
       <c r="X24" s="3" t="n">
@@ -2606,40 +2576,40 @@
       <c r="K25" s="3" t="n">
         <v>23.7</v>
       </c>
-      <c r="L25" s="3" t="n">
+      <c r="L25" s="10" t="n">
         <v>22.4</v>
       </c>
-      <c r="M25" s="3" t="n">
+      <c r="M25" s="10" t="n">
         <v>22.1</v>
       </c>
-      <c r="N25" s="3" t="n">
+      <c r="N25" s="10" t="n">
         <v>26.4</v>
       </c>
-      <c r="O25" s="3" t="n">
-        <v>97</v>
-      </c>
-      <c r="P25" s="3" t="n">
+      <c r="O25" s="10" t="n">
+        <v>97.5</v>
+      </c>
+      <c r="P25" s="10" t="n">
         <v>0.7</v>
       </c>
-      <c r="Q25" s="3" t="n">
+      <c r="Q25" s="10" t="n">
         <v>26.2</v>
       </c>
-      <c r="R25" s="3" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="S25" s="3" t="n">
+      <c r="R25" s="10" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="S25" s="10" t="n">
         <v>28.7</v>
       </c>
-      <c r="T25" s="3" t="n">
+      <c r="T25" s="10" t="n">
         <v>84.40000000000001</v>
       </c>
-      <c r="U25" s="3" t="n">
+      <c r="U25" s="10" t="n">
         <v>5.3</v>
       </c>
       <c r="V25" s="8" t="n">
         <v>14.4</v>
       </c>
-      <c r="W25" s="3" t="n">
+      <c r="W25" s="10" t="n">
         <v>22.8</v>
       </c>
       <c r="X25" s="3" t="n">
@@ -2689,49 +2659,49 @@
       <c r="K26" s="3" t="n">
         <v>6.1</v>
       </c>
-      <c r="L26" s="3" t="n">
+      <c r="L26" s="10" t="n">
         <v>21.4</v>
       </c>
-      <c r="M26" s="3" t="n">
+      <c r="M26" s="10" t="n">
         <v>21.4</v>
       </c>
-      <c r="N26" s="3" t="n">
+      <c r="N26" s="10" t="n">
         <v>25.5</v>
       </c>
-      <c r="O26" s="3" t="n">
+      <c r="O26" s="10" t="n">
         <v>100</v>
       </c>
-      <c r="P26" s="3" t="n">
+      <c r="P26" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="Q26" s="3" t="n">
+      <c r="Q26" s="10" t="n">
         <v>24.3</v>
       </c>
-      <c r="R26" s="3" t="n">
+      <c r="R26" s="10" t="n">
         <v>23.3</v>
       </c>
-      <c r="S26" s="3" t="n">
-        <v>28</v>
-      </c>
-      <c r="T26" s="3" t="n">
-        <v>192</v>
-      </c>
-      <c r="U26" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="V26" s="3" t="n">
+      <c r="S26" s="10" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="T26" s="10" t="n">
+        <v>94.2</v>
+      </c>
+      <c r="U26" s="10" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="V26" s="10" t="n">
         <v>23.8</v>
       </c>
-      <c r="W26" s="3" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="X26" s="3" t="n">
+      <c r="W26" s="10" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="X26" s="10" t="n">
         <v>27.1</v>
       </c>
-      <c r="Y26" s="3" t="n">
+      <c r="Y26" s="10" t="n">
         <v>91.8</v>
       </c>
-      <c r="Z26" s="3" t="n">
+      <c r="Z26" s="10" t="n">
         <v>2.4</v>
       </c>
       <c r="AA26" s="3" t="inlineStr">
@@ -2774,13 +2744,13 @@
       <c r="K27" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L27" s="3" t="n">
+      <c r="L27" s="12" t="n">
         <v>50.4</v>
       </c>
-      <c r="M27" s="3" t="n">
+      <c r="M27" s="10" t="n">
         <v>20.5</v>
       </c>
-      <c r="N27" s="3" t="n">
+      <c r="N27" s="10" t="n">
         <v>24</v>
       </c>
       <c r="O27" s="3" t="n">
@@ -2789,25 +2759,25 @@
       <c r="P27" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q27" s="3" t="n">
+      <c r="Q27" s="10" t="n">
         <v>28.8</v>
       </c>
-      <c r="R27" s="3" t="n">
+      <c r="R27" s="10" t="n">
         <v>24.9</v>
       </c>
-      <c r="S27" s="3" t="n">
-        <v>29</v>
-      </c>
-      <c r="T27" s="3" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="U27" s="3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="V27" s="8" t="n">
-        <v>826.9</v>
-      </c>
-      <c r="W27" s="3" t="n">
+      <c r="S27" s="10" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="T27" s="10" t="n">
+        <v>79.5</v>
+      </c>
+      <c r="U27" s="10" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="V27" s="12" t="n">
+        <v>82.69</v>
+      </c>
+      <c r="W27" s="10" t="n">
         <v>24.4</v>
       </c>
       <c r="X27" s="8" t="n">
@@ -2862,10 +2832,10 @@
       <c r="L28" s="3" t="n">
         <v>20.9</v>
       </c>
-      <c r="M28" s="3" t="n">
+      <c r="M28" s="10" t="n">
         <v>20.6</v>
       </c>
-      <c r="N28" s="3" t="n">
+      <c r="N28" s="10" t="n">
         <v>24.1</v>
       </c>
       <c r="O28" s="3" t="n">
@@ -2874,34 +2844,34 @@
       <c r="P28" s="3" t="n">
         <v>1.8</v>
       </c>
-      <c r="Q28" s="3" t="n">
+      <c r="Q28" s="10" t="n">
         <v>31.2</v>
       </c>
-      <c r="R28" s="3" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="S28" s="3" t="n">
+      <c r="R28" s="10" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="S28" s="10" t="n">
         <v>27.2</v>
       </c>
-      <c r="T28" s="3" t="n">
+      <c r="T28" s="10" t="n">
         <v>60.2</v>
       </c>
-      <c r="U28" s="3" t="n">
+      <c r="U28" s="10" t="n">
         <v>18.1</v>
       </c>
-      <c r="V28" s="3" t="n">
+      <c r="V28" s="10" t="n">
         <v>28.6</v>
       </c>
-      <c r="W28" s="3" t="n">
-        <v>24.6</v>
-      </c>
-      <c r="X28" s="3" t="n">
+      <c r="W28" s="10" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="X28" s="10" t="n">
         <v>28.4</v>
       </c>
-      <c r="Y28" s="3" t="n">
+      <c r="Y28" s="10" t="n">
         <v>72.59999999999999</v>
       </c>
-      <c r="Z28" s="3" t="n">
+      <c r="Z28" s="10" t="n">
         <v>10.7</v>
       </c>
       <c r="AA28" s="3" t="inlineStr">
@@ -2947,7 +2917,7 @@
       <c r="L29" s="3" t="n">
         <v>21.1</v>
       </c>
-      <c r="M29" s="3" t="n">
+      <c r="M29" s="10" t="n">
         <v>20.6</v>
       </c>
       <c r="N29" s="3" t="n">
@@ -2959,25 +2929,25 @@
       <c r="P29" s="3" t="n">
         <v>1.1</v>
       </c>
-      <c r="Q29" s="3" t="n">
+      <c r="Q29" s="10" t="n">
         <v>25.3</v>
       </c>
-      <c r="R29" s="3" t="n">
+      <c r="R29" s="10" t="n">
         <v>23.6</v>
       </c>
-      <c r="S29" s="3" t="n">
-        <v>28</v>
-      </c>
-      <c r="T29" s="3" t="n">
-        <v>827</v>
-      </c>
-      <c r="U29" s="3" t="n">
-        <v>94.2</v>
+      <c r="S29" s="10" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="T29" s="10" t="n">
+        <v>90.3</v>
+      </c>
+      <c r="U29" s="10" t="n">
+        <v>3.1</v>
       </c>
       <c r="V29" s="3" t="n">
         <v>22.4</v>
       </c>
-      <c r="W29" s="3" t="n">
+      <c r="W29" s="10" t="n">
         <v>21.3</v>
       </c>
       <c r="X29" s="8" t="n">
@@ -3026,13 +2996,13 @@
       <c r="J30" s="3" t="n">
         <v>111</v>
       </c>
-      <c r="K30" s="3" t="n">
+      <c r="K30" s="13" t="n">
         <v>328.8</v>
       </c>
-      <c r="L30" s="3" t="n">
+      <c r="L30" s="13" t="n">
         <v>106.5</v>
       </c>
-      <c r="M30" s="3" t="n">
+      <c r="M30" s="10" t="n">
         <v>105.2</v>
       </c>
       <c r="N30" s="3" t="n">
@@ -3044,10 +3014,10 @@
       <c r="P30" s="3" t="n">
         <v>2.8</v>
       </c>
-      <c r="Q30" s="3" t="n">
-        <v>1135.8</v>
-      </c>
-      <c r="R30" s="3" t="n">
+      <c r="Q30" s="10" t="n">
+        <v>135.8</v>
+      </c>
+      <c r="R30" s="10" t="n">
         <v>120.7</v>
       </c>
       <c r="S30" s="3" t="n">
@@ -3057,10 +3027,10 @@
         <v>396.8</v>
       </c>
       <c r="U30" s="3" t="inlineStr"/>
-      <c r="V30" s="3" t="n">
+      <c r="V30" s="13" t="n">
         <v>126.1</v>
       </c>
-      <c r="W30" s="3" t="n">
+      <c r="W30" s="10" t="n">
         <v>115.9</v>
       </c>
       <c r="X30" s="3" t="n">
@@ -3112,40 +3082,40 @@
       <c r="K31" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="L31" s="3" t="n">
+      <c r="L31" s="10" t="n">
         <v>21.3</v>
       </c>
-      <c r="M31" s="3" t="n">
+      <c r="M31" s="10" t="n">
         <v>21</v>
       </c>
-      <c r="N31" s="3" t="n">
+      <c r="N31" s="10" t="n">
         <v>24.8</v>
       </c>
-      <c r="O31" s="3" t="n">
-        <v>927.5</v>
-      </c>
-      <c r="P31" s="3" t="n">
+      <c r="O31" s="10" t="n">
+        <v>97.90000000000001</v>
+      </c>
+      <c r="P31" s="10" t="n">
         <v>0.6</v>
       </c>
-      <c r="Q31" s="3" t="n">
+      <c r="Q31" s="10" t="n">
         <v>27.2</v>
       </c>
-      <c r="R31" s="3" t="n">
+      <c r="R31" s="10" t="n">
         <v>24.1</v>
       </c>
-      <c r="S31" s="3" t="n">
-        <v>28.2</v>
-      </c>
-      <c r="T31" s="3" t="n">
-        <v>79.40000000000001</v>
-      </c>
-      <c r="U31" s="3" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="V31" s="3" t="n">
+      <c r="S31" s="10" t="n">
+        <v>30</v>
+      </c>
+      <c r="T31" s="10" t="n">
+        <v>83.2</v>
+      </c>
+      <c r="U31" s="10" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="V31" s="13" t="n">
         <v>25.2</v>
       </c>
-      <c r="W31" s="3" t="n">
+      <c r="W31" s="10" t="n">
         <v>23.2</v>
       </c>
       <c r="X31" s="3" t="n">
@@ -3197,40 +3167,40 @@
       <c r="K32" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L32" s="3" t="n">
+      <c r="L32" s="10" t="n">
         <v>20.1</v>
       </c>
-      <c r="M32" s="3" t="n">
+      <c r="M32" s="10" t="n">
         <v>20.1</v>
       </c>
-      <c r="N32" s="3" t="n">
+      <c r="N32" s="10" t="n">
         <v>23.5</v>
       </c>
-      <c r="O32" s="3" t="n">
+      <c r="O32" s="10" t="n">
         <v>100</v>
       </c>
-      <c r="P32" s="3" t="n">
+      <c r="P32" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="Q32" s="3" t="n">
+      <c r="Q32" s="10" t="n">
         <v>31.1</v>
       </c>
-      <c r="R32" s="3" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="S32" s="3" t="n">
+      <c r="R32" s="10" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="S32" s="10" t="n">
         <v>27.5</v>
       </c>
-      <c r="T32" s="3" t="n">
+      <c r="T32" s="10" t="n">
         <v>61</v>
       </c>
-      <c r="U32" s="3" t="n">
+      <c r="U32" s="10" t="n">
         <v>17.5</v>
       </c>
       <c r="V32" s="3" t="n">
         <v>9.300000000000001</v>
       </c>
-      <c r="W32" s="3" t="n">
+      <c r="W32" s="12" t="n">
         <v>83.8</v>
       </c>
       <c r="X32" s="3" t="n">
@@ -3282,34 +3252,34 @@
       <c r="K33" s="3" t="n">
         <v>14.8</v>
       </c>
-      <c r="L33" s="3" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="M33" s="3" t="n">
-        <v>21.4</v>
-      </c>
-      <c r="N33" s="3" t="n">
+      <c r="L33" s="10" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="M33" s="10" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="N33" s="10" t="n">
         <v>23.9</v>
       </c>
-      <c r="O33" s="3" t="n">
+      <c r="O33" s="10" t="n">
         <v>99</v>
       </c>
-      <c r="P33" s="3" t="n">
+      <c r="P33" s="10" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q33" s="3" t="n">
+      <c r="Q33" s="10" t="n">
         <v>28.9</v>
       </c>
-      <c r="R33" s="3" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="S33" s="3" t="n">
+      <c r="R33" s="10" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="S33" s="10" t="n">
         <v>28.2</v>
       </c>
-      <c r="T33" s="3" t="n">
+      <c r="T33" s="10" t="n">
         <v>70.90000000000001</v>
       </c>
-      <c r="U33" s="3" t="n">
+      <c r="U33" s="10" t="n">
         <v>11.5</v>
       </c>
       <c r="V33" s="3" t="n">
@@ -3367,34 +3337,34 @@
       <c r="K34" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="L34" s="3" t="n">
+      <c r="L34" s="10" t="n">
         <v>21.8</v>
       </c>
-      <c r="M34" s="3" t="n">
+      <c r="M34" s="10" t="n">
         <v>21.7</v>
       </c>
-      <c r="N34" s="3" t="n">
+      <c r="N34" s="10" t="n">
         <v>25.9</v>
       </c>
-      <c r="O34" s="3" t="n">
-        <v>99</v>
-      </c>
-      <c r="P34" s="3" t="n">
+      <c r="O34" s="10" t="n">
+        <v>99.40000000000001</v>
+      </c>
+      <c r="P34" s="10" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q34" s="3" t="n">
+      <c r="Q34" s="10" t="n">
         <v>30.5</v>
       </c>
-      <c r="R34" s="3" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="S34" s="3" t="n">
+      <c r="R34" s="10" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="S34" s="10" t="n">
         <v>30.2</v>
       </c>
-      <c r="T34" s="3" t="n">
+      <c r="T34" s="10" t="n">
         <v>69.40000000000001</v>
       </c>
-      <c r="U34" s="3" t="n">
+      <c r="U34" s="10" t="n">
         <v>13.3</v>
       </c>
       <c r="V34" s="3" t="n">
@@ -3452,25 +3422,25 @@
       <c r="K35" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L35" s="3" t="n">
+      <c r="L35" s="10" t="n">
         <v>21.6</v>
       </c>
-      <c r="M35" s="3" t="n">
+      <c r="M35" s="10" t="n">
         <v>21.3</v>
       </c>
-      <c r="N35" s="3" t="n">
+      <c r="N35" s="10" t="n">
         <v>25.1</v>
       </c>
-      <c r="O35" s="3" t="n">
+      <c r="O35" s="10" t="n">
         <v>97.2</v>
       </c>
-      <c r="P35" s="3" t="n">
+      <c r="P35" s="10" t="n">
         <v>0.7</v>
       </c>
-      <c r="Q35" s="3" t="n">
+      <c r="Q35" s="10" t="n">
         <v>31.1</v>
       </c>
-      <c r="R35" s="8" t="n">
+      <c r="R35" s="12" t="n">
         <v>46.9</v>
       </c>
       <c r="S35" s="3" t="n">
@@ -3537,40 +3507,40 @@
       <c r="K36" s="3" t="n">
         <v>30.6</v>
       </c>
-      <c r="L36" s="3" t="n">
+      <c r="L36" s="10" t="n">
         <v>21</v>
       </c>
-      <c r="M36" s="3" t="n">
+      <c r="M36" s="10" t="n">
         <v>20.7</v>
       </c>
-      <c r="N36" s="3" t="n">
+      <c r="N36" s="10" t="n">
         <v>24.2</v>
       </c>
-      <c r="O36" s="3" t="n">
+      <c r="O36" s="10" t="n">
         <v>97.5</v>
       </c>
-      <c r="P36" s="3" t="n">
+      <c r="P36" s="10" t="n">
         <v>0.6</v>
       </c>
-      <c r="Q36" s="3" t="n">
+      <c r="Q36" s="10" t="n">
         <v>32.1</v>
       </c>
-      <c r="R36" s="3" t="n">
-        <v>26</v>
-      </c>
-      <c r="S36" s="3" t="n">
+      <c r="R36" s="10" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="S36" s="10" t="n">
         <v>29.7</v>
       </c>
-      <c r="T36" s="3" t="n">
+      <c r="T36" s="10" t="n">
         <v>62.2</v>
       </c>
-      <c r="U36" s="3" t="n">
+      <c r="U36" s="10" t="n">
         <v>18</v>
       </c>
       <c r="V36" s="3" t="n">
         <v>28.7</v>
       </c>
-      <c r="W36" s="8" t="n">
+      <c r="W36" s="12" t="n">
         <v>46.6</v>
       </c>
       <c r="X36" s="3" t="n">
@@ -3619,14 +3589,14 @@
       <c r="J37" s="3" t="n">
         <v>18.1</v>
       </c>
-      <c r="K37" s="3" t="n">
+      <c r="K37" s="13" t="n">
         <v>35.6</v>
       </c>
-      <c r="L37" s="3" t="n">
-        <v>1106</v>
-      </c>
-      <c r="M37" s="3" t="n">
-        <v>103.2</v>
+      <c r="L37" s="10" t="n">
+        <v>105</v>
+      </c>
+      <c r="M37" s="10" t="n">
+        <v>104.2</v>
       </c>
       <c r="N37" s="3" t="n">
         <v>124.1</v>
@@ -3637,10 +3607,10 @@
       <c r="P37" s="3" t="n">
         <v>17.1</v>
       </c>
-      <c r="Q37" s="3" t="n">
+      <c r="Q37" s="10" t="n">
         <v>153.7</v>
       </c>
-      <c r="R37" s="3" t="n">
+      <c r="R37" s="13" t="n">
         <v>126.2</v>
       </c>
       <c r="S37" s="3" t="n">
@@ -3652,10 +3622,10 @@
       <c r="U37" s="3" t="n">
         <v>19.7</v>
       </c>
-      <c r="V37" s="3" t="n">
+      <c r="V37" s="13" t="n">
         <v>136.8</v>
       </c>
-      <c r="W37" s="3" t="n">
+      <c r="W37" s="13" t="n">
         <v>121.6</v>
       </c>
       <c r="X37" s="3" t="n">
@@ -3705,25 +3675,25 @@
         <v>3.6</v>
       </c>
       <c r="K38" s="3" t="inlineStr"/>
-      <c r="L38" s="3" t="n">
+      <c r="L38" s="10" t="n">
         <v>21.2</v>
       </c>
-      <c r="M38" s="3" t="n">
+      <c r="M38" s="10" t="n">
         <v>21</v>
       </c>
-      <c r="N38" s="3" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="O38" s="3" t="n">
-        <v>98.5</v>
-      </c>
-      <c r="P38" s="3" t="n">
+      <c r="N38" s="10" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="O38" s="10" t="n">
+        <v>98.8</v>
+      </c>
+      <c r="P38" s="10" t="n">
         <v>0.3</v>
       </c>
-      <c r="Q38" s="3" t="n">
+      <c r="Q38" s="10" t="n">
         <v>30.7</v>
       </c>
-      <c r="R38" s="3" t="n">
+      <c r="R38" s="13" t="n">
         <v>25.2</v>
       </c>
       <c r="S38" s="3" t="n">
@@ -3735,10 +3705,10 @@
       <c r="U38" s="3" t="n">
         <v>15.5</v>
       </c>
-      <c r="V38" s="3" t="n">
+      <c r="V38" s="13" t="n">
         <v>27.4</v>
       </c>
-      <c r="W38" s="3" t="n">
+      <c r="W38" s="13" t="n">
         <v>24.3</v>
       </c>
       <c r="X38" s="3" t="n">
@@ -3790,25 +3760,25 @@
       <c r="K39" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="L39" s="3" t="n">
+      <c r="L39" s="10" t="n">
         <v>21</v>
       </c>
-      <c r="M39" s="3" t="n">
+      <c r="M39" s="10" t="n">
         <v>20.9</v>
       </c>
-      <c r="N39" s="3" t="n">
+      <c r="N39" s="10" t="n">
         <v>24.6</v>
       </c>
-      <c r="O39" s="3" t="n">
+      <c r="O39" s="10" t="n">
         <v>99</v>
       </c>
-      <c r="P39" s="3" t="n">
+      <c r="P39" s="10" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q39" s="3" t="n">
+      <c r="Q39" s="12" t="n">
         <v>91.90000000000001</v>
       </c>
-      <c r="R39" s="3" t="n">
+      <c r="R39" s="10" t="n">
         <v>26</v>
       </c>
       <c r="S39" s="3" t="n">
@@ -3823,7 +3793,7 @@
       <c r="V39" s="3" t="n">
         <v>24.9</v>
       </c>
-      <c r="W39" s="3" t="n">
+      <c r="W39" s="10" t="n">
         <v>23.2</v>
       </c>
       <c r="X39" s="3" t="n">
@@ -3875,40 +3845,40 @@
       <c r="K40" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L40" s="3" t="n">
+      <c r="L40" s="10" t="n">
         <v>19.8</v>
       </c>
-      <c r="M40" s="3" t="n">
+      <c r="M40" s="10" t="n">
         <v>19.6</v>
       </c>
-      <c r="N40" s="3" t="n">
+      <c r="N40" s="10" t="n">
         <v>22.6</v>
       </c>
-      <c r="O40" s="3" t="n">
+      <c r="O40" s="10" t="n">
         <v>97.8</v>
       </c>
-      <c r="P40" s="3" t="n">
+      <c r="P40" s="10" t="n">
         <v>0.5</v>
       </c>
-      <c r="Q40" s="3" t="n">
+      <c r="Q40" s="10" t="n">
         <v>32.8</v>
       </c>
-      <c r="R40" s="3" t="n">
-        <v>26</v>
-      </c>
-      <c r="S40" s="3" t="n">
+      <c r="R40" s="10" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="S40" s="10" t="n">
         <v>29.3</v>
       </c>
-      <c r="T40" s="3" t="n">
+      <c r="T40" s="10" t="n">
         <v>59.2</v>
       </c>
-      <c r="U40" s="3" t="n">
+      <c r="U40" s="10" t="n">
         <v>20.2</v>
       </c>
       <c r="V40" s="3" t="n">
         <v>27.8</v>
       </c>
-      <c r="W40" s="3" t="n">
+      <c r="W40" s="10" t="n">
         <v>23.8</v>
       </c>
       <c r="X40" s="8" t="n">
@@ -3960,25 +3930,25 @@
       <c r="K41" s="3" t="n">
         <v>4.6</v>
       </c>
-      <c r="L41" s="3" t="n">
+      <c r="L41" s="10" t="n">
         <v>19.9</v>
       </c>
-      <c r="M41" s="3" t="n">
+      <c r="M41" s="10" t="n">
         <v>19.8</v>
       </c>
-      <c r="N41" s="3" t="n">
+      <c r="N41" s="10" t="n">
         <v>23</v>
       </c>
-      <c r="O41" s="3" t="n">
+      <c r="O41" s="10" t="n">
         <v>99</v>
       </c>
-      <c r="P41" s="3" t="n">
+      <c r="P41" s="10" t="n">
         <v>0.2</v>
       </c>
       <c r="Q41" s="3" t="n">
         <v>22.3</v>
       </c>
-      <c r="R41" s="3" t="n">
+      <c r="R41" s="10" t="n">
         <v>21.4</v>
       </c>
       <c r="S41" s="8" t="n">
@@ -3993,7 +3963,7 @@
       <c r="V41" s="3" t="n">
         <v>22.6</v>
       </c>
-      <c r="W41" s="3" t="n">
+      <c r="W41" s="10" t="n">
         <v>23.4</v>
       </c>
       <c r="X41" s="3" t="n">
@@ -4060,25 +4030,25 @@
       <c r="P42" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q42" s="3" t="n">
+      <c r="Q42" s="10" t="n">
         <v>24.1</v>
       </c>
-      <c r="R42" s="3" t="n">
+      <c r="R42" s="10" t="n">
         <v>23.8</v>
       </c>
-      <c r="S42" s="3" t="n">
+      <c r="S42" s="10" t="n">
         <v>29.3</v>
       </c>
-      <c r="T42" s="3" t="n">
+      <c r="T42" s="10" t="n">
         <v>97.7</v>
       </c>
-      <c r="U42" s="3" t="n">
+      <c r="U42" s="10" t="n">
         <v>0.8</v>
       </c>
       <c r="V42" s="3" t="n">
         <v>22.7</v>
       </c>
-      <c r="W42" s="3" t="n">
+      <c r="W42" s="10" t="n">
         <v>22.5</v>
       </c>
       <c r="X42" s="8" t="n">
@@ -4148,7 +4118,7 @@
       <c r="Q43" s="3" t="n">
         <v>29.1</v>
       </c>
-      <c r="R43" s="3" t="n">
+      <c r="R43" s="10" t="n">
         <v>25.5</v>
       </c>
       <c r="S43" s="3" t="n">
@@ -4160,19 +4130,19 @@
       <c r="U43" s="3" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="V43" s="3" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="W43" s="3" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="X43" s="3" t="n">
+      <c r="V43" s="10" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="W43" s="10" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="X43" s="10" t="n">
         <v>29.1</v>
       </c>
-      <c r="Y43" s="3" t="n">
+      <c r="Y43" s="10" t="n">
         <v>78</v>
       </c>
-      <c r="Z43" s="3" t="n">
+      <c r="Z43" s="10" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AA43" s="3" t="inlineStr">
@@ -4215,40 +4185,40 @@
       <c r="K44" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L44" s="8" t="n">
-        <v>82.3</v>
-      </c>
-      <c r="M44" s="3" t="n">
-        <v>82.3</v>
-      </c>
-      <c r="N44" s="3" t="n">
+      <c r="L44" s="10" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="M44" s="10" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="N44" s="10" t="n">
         <v>26.9</v>
       </c>
-      <c r="O44" s="3" t="n">
+      <c r="O44" s="10" t="n">
         <v>100</v>
       </c>
-      <c r="P44" s="3" t="n">
+      <c r="P44" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="Q44" s="3" t="n">
+      <c r="Q44" s="10" t="n">
         <v>32.6</v>
       </c>
-      <c r="R44" s="3" t="n">
-        <v>26.4</v>
-      </c>
-      <c r="S44" s="3" t="n">
+      <c r="R44" s="10" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="S44" s="10" t="n">
         <v>30.4</v>
       </c>
-      <c r="T44" s="3" t="n">
+      <c r="T44" s="10" t="n">
         <v>62</v>
       </c>
-      <c r="U44" s="3" t="n">
+      <c r="U44" s="10" t="n">
         <v>18.6</v>
       </c>
       <c r="V44" s="3" t="n">
         <v>28.3</v>
       </c>
-      <c r="W44" s="3" t="n">
+      <c r="W44" s="10" t="n">
         <v>26.3</v>
       </c>
       <c r="X44" s="8" t="n">
@@ -4297,13 +4267,13 @@
       <c r="J45" s="3" t="n">
         <v>118.4</v>
       </c>
-      <c r="K45" s="3" t="n">
+      <c r="K45" s="13" t="n">
         <v>783.6</v>
       </c>
-      <c r="L45" s="3" t="n">
+      <c r="L45" s="13" t="n">
         <v>1166.5</v>
       </c>
-      <c r="M45" s="3" t="n">
+      <c r="M45" s="13" t="n">
         <v>123.9</v>
       </c>
       <c r="N45" s="3" t="n">
@@ -4315,10 +4285,10 @@
       <c r="P45" s="3" t="n">
         <v>1.3</v>
       </c>
-      <c r="Q45" s="3" t="n">
+      <c r="Q45" s="13" t="n">
         <v>172.8</v>
       </c>
-      <c r="R45" s="3" t="n">
+      <c r="R45" s="10" t="n">
         <v>149.1</v>
       </c>
       <c r="S45" s="3" t="n">
@@ -4330,11 +4300,11 @@
       <c r="U45" s="3" t="n">
         <v>68.59999999999999</v>
       </c>
-      <c r="V45" s="3" t="n">
+      <c r="V45" s="13" t="n">
         <v>158.1</v>
       </c>
-      <c r="W45" s="3" t="n">
-        <v>128.2</v>
+      <c r="W45" s="10" t="n">
+        <v>142.8</v>
       </c>
       <c r="X45" s="3" t="n">
         <v>172.2</v>
@@ -4383,10 +4353,10 @@
         <v>3.1</v>
       </c>
       <c r="K46" s="3" t="inlineStr"/>
-      <c r="L46" s="3" t="n">
+      <c r="L46" s="13" t="n">
         <v>21.1</v>
       </c>
-      <c r="M46" s="3" t="n">
+      <c r="M46" s="13" t="n">
         <v>20</v>
       </c>
       <c r="N46" s="3" t="n">
@@ -4398,11 +4368,11 @@
       <c r="P46" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q46" s="3" t="n">
+      <c r="Q46" s="13" t="n">
         <v>28.8</v>
       </c>
-      <c r="R46" s="3" t="n">
-        <v>21.8</v>
+      <c r="R46" s="10" t="n">
+        <v>24.1</v>
       </c>
       <c r="S46" s="3" t="n">
         <v>29</v>
@@ -4413,10 +4383,10 @@
       <c r="U46" s="3" t="n">
         <v>11.4</v>
       </c>
-      <c r="V46" s="3" t="n">
+      <c r="V46" s="13" t="n">
         <v>26.3</v>
       </c>
-      <c r="W46" s="3" t="n">
+      <c r="W46" s="10" t="n">
         <v>24.1</v>
       </c>
       <c r="X46" s="3" t="n">

--- a/results/05_transient_transcription_output/203/203_196905_SF.JPG_stage_recalc_multi_day_tot_and_avgs.xlsx
+++ b/results/05_transient_transcription_output/203/203_196905_SF.JPG_stage_recalc_multi_day_tot_and_avgs.xlsx
@@ -41,6 +41,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00CC3300"/>
+        <bgColor rgb="00CC3300"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="0075696F"/>
         <bgColor rgb="0075696F"/>
       </patternFill>
@@ -49,12 +55,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF6DCD57"/>
         <bgColor rgb="FF6DCD57"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00CC3300"/>
-        <bgColor rgb="00CC3300"/>
       </patternFill>
     </fill>
   </fills>
@@ -143,19 +143,19 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -769,75 +769,75 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>186.2</v>
-      </c>
-      <c r="D4" s="10" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="D4" s="11" t="n">
         <v>28.6</v>
       </c>
-      <c r="E4" s="10" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="F4" s="10" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="G4" s="3" t="n">
-        <v>87.2</v>
-      </c>
-      <c r="H4" s="3" t="n">
-        <v>18.2</v>
+      <c r="E4" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="F4" s="11" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="G4" s="11" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="H4" s="8" t="n">
+        <v>88.2</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>11.8</v>
+        <v>1.7</v>
       </c>
       <c r="J4" s="3" t="n">
         <v>2.9</v>
       </c>
-      <c r="K4" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" s="10" t="n">
+      <c r="K4" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="L4" s="11" t="n">
         <v>20.2</v>
       </c>
-      <c r="M4" s="10" t="n">
+      <c r="M4" s="11" t="n">
         <v>20.1</v>
       </c>
-      <c r="N4" s="10" t="n">
+      <c r="N4" s="11" t="n">
         <v>23.4</v>
       </c>
-      <c r="O4" s="10" t="n">
+      <c r="O4" s="11" t="n">
         <v>99</v>
       </c>
-      <c r="P4" s="10" t="n">
+      <c r="P4" s="11" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q4" s="10" t="n">
+      <c r="Q4" s="11" t="n">
         <v>28.7</v>
       </c>
-      <c r="R4" s="10" t="n">
+      <c r="R4" s="11" t="n">
         <v>22.4</v>
       </c>
-      <c r="S4" s="10" t="n">
+      <c r="S4" s="11" t="n">
         <v>27.1</v>
       </c>
-      <c r="T4" s="10" t="n">
+      <c r="T4" s="11" t="n">
         <v>68.90000000000001</v>
       </c>
-      <c r="U4" s="10" t="n">
+      <c r="U4" s="11" t="n">
         <v>12.2</v>
       </c>
-      <c r="V4" s="10" t="n">
+      <c r="V4" s="11" t="n">
         <v>25.2</v>
       </c>
-      <c r="W4" s="10" t="n">
+      <c r="W4" s="11" t="n">
         <v>21.9</v>
       </c>
-      <c r="X4" s="10" t="n">
+      <c r="X4" s="11" t="n">
         <v>26.2</v>
       </c>
-      <c r="Y4" s="10" t="n">
+      <c r="Y4" s="11" t="n">
         <v>81.8</v>
       </c>
-      <c r="Z4" s="10" t="n">
+      <c r="Z4" s="11" t="n">
         <v>5.8</v>
       </c>
       <c r="AA4" s="3" t="inlineStr">
@@ -854,22 +854,22 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>403.8</v>
-      </c>
-      <c r="D5" s="10" t="n">
+        <v>240.3</v>
+      </c>
+      <c r="D5" s="11" t="n">
         <v>32.6</v>
       </c>
-      <c r="E5" s="10" t="n">
+      <c r="E5" s="11" t="n">
         <v>18.2</v>
       </c>
-      <c r="F5" s="10" t="n">
+      <c r="F5" s="11" t="n">
         <v>25.4</v>
       </c>
-      <c r="G5" s="10" t="n">
+      <c r="G5" s="11" t="n">
         <v>14.4</v>
       </c>
-      <c r="H5" s="3" t="n">
-        <v>16.8</v>
+      <c r="H5" s="8" t="n">
+        <v>416.8</v>
       </c>
       <c r="I5" s="3" t="n">
         <v>3.5</v>
@@ -877,53 +877,53 @@
       <c r="J5" s="3" t="n">
         <v>5.5</v>
       </c>
-      <c r="K5" s="10" t="n">
+      <c r="K5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L5" s="10" t="n">
+      <c r="L5" s="11" t="n">
         <v>18.9</v>
       </c>
-      <c r="M5" s="10" t="n">
+      <c r="M5" s="11" t="n">
         <v>18.8</v>
       </c>
-      <c r="N5" s="10" t="n">
+      <c r="N5" s="11" t="n">
         <v>21.6</v>
       </c>
-      <c r="O5" s="10" t="n">
+      <c r="O5" s="11" t="n">
         <v>99</v>
       </c>
-      <c r="P5" s="10" t="n">
+      <c r="P5" s="11" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q5" s="10" t="n">
+      <c r="Q5" s="11" t="n">
         <v>32.6</v>
       </c>
-      <c r="R5" s="10" t="n">
+      <c r="R5" s="11" t="n">
         <v>22.8</v>
       </c>
-      <c r="S5" s="10" t="n">
+      <c r="S5" s="11" t="n">
         <v>27.8</v>
       </c>
-      <c r="T5" s="10" t="n">
+      <c r="T5" s="11" t="n">
         <v>56.6</v>
       </c>
-      <c r="U5" s="10" t="n">
+      <c r="U5" s="11" t="n">
         <v>21.2</v>
       </c>
-      <c r="V5" s="10" t="n">
+      <c r="V5" s="3" t="n">
         <v>27.2</v>
       </c>
-      <c r="W5" s="10" t="n">
+      <c r="W5" s="11" t="n">
         <v>24</v>
       </c>
-      <c r="X5" s="10" t="n">
-        <v>29.8</v>
-      </c>
-      <c r="Y5" s="10" t="n">
-        <v>82.7</v>
-      </c>
-      <c r="Z5" s="10" t="n">
-        <v>6.2</v>
+      <c r="X5" s="3" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="Y5" s="3" t="n">
+        <v>77</v>
+      </c>
+      <c r="Z5" s="3" t="n">
+        <v>8.199999999999999</v>
       </c>
       <c r="AA5" s="3" t="inlineStr">
         <is>
@@ -941,46 +941,46 @@
       <c r="C6" s="3" t="n">
         <v>422.3</v>
       </c>
-      <c r="D6" s="10" t="n">
+      <c r="D6" s="11" t="n">
         <v>34.2</v>
       </c>
-      <c r="E6" s="10" t="n">
+      <c r="E6" s="11" t="n">
         <v>18.8</v>
       </c>
-      <c r="F6" s="10" t="n">
+      <c r="F6" s="11" t="n">
         <v>26.5</v>
       </c>
-      <c r="G6" s="10" t="n">
+      <c r="G6" s="11" t="n">
         <v>15.4</v>
       </c>
-      <c r="H6" s="8" t="n">
-        <v>15.2</v>
+      <c r="H6" s="3" t="n">
+        <v>17.2</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>14.6</v>
+        <v>4.6</v>
       </c>
       <c r="J6" s="3" t="n">
         <v>7.2</v>
       </c>
-      <c r="K6" s="10" t="n">
+      <c r="K6" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L6" s="10" t="n">
+      <c r="L6" s="11" t="n">
         <v>20</v>
       </c>
-      <c r="M6" s="10" t="n">
+      <c r="M6" s="11" t="n">
         <v>20</v>
       </c>
-      <c r="N6" s="10" t="n">
+      <c r="N6" s="11" t="n">
         <v>23.3</v>
       </c>
-      <c r="O6" s="10" t="n">
+      <c r="O6" s="11" t="n">
         <v>100</v>
       </c>
-      <c r="P6" s="10" t="n">
+      <c r="P6" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="Q6" s="10" t="n">
+      <c r="Q6" s="11" t="n">
         <v>32.7</v>
       </c>
       <c r="R6" s="3" t="n">
@@ -990,24 +990,24 @@
         <v>28.6</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>92.8</v>
+        <v>155.8</v>
       </c>
       <c r="U6" s="3" t="n">
         <v>20.7</v>
       </c>
-      <c r="V6" s="10" t="n">
+      <c r="V6" s="11" t="n">
         <v>28.7</v>
       </c>
-      <c r="W6" s="10" t="n">
+      <c r="W6" s="11" t="n">
         <v>21.8</v>
       </c>
-      <c r="X6" s="10" t="n">
+      <c r="X6" s="11" t="n">
         <v>26.1</v>
       </c>
-      <c r="Y6" s="10" t="n">
+      <c r="Y6" s="11" t="n">
         <v>66.40000000000001</v>
       </c>
-      <c r="Z6" s="10" t="n">
+      <c r="Z6" s="11" t="n">
         <v>13.2</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
@@ -1026,74 +1026,74 @@
       <c r="C7" s="3" t="n">
         <v>472.5</v>
       </c>
-      <c r="D7" s="10" t="n">
-        <v>34.8</v>
-      </c>
-      <c r="E7" s="10" t="n">
+      <c r="D7" s="11" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="E7" s="11" t="n">
         <v>19.3</v>
       </c>
-      <c r="F7" s="10" t="n">
-        <v>27</v>
-      </c>
-      <c r="G7" s="10" t="n">
+      <c r="F7" s="11" t="n">
+        <v>22</v>
+      </c>
+      <c r="G7" s="3" t="n">
         <v>15.4</v>
       </c>
       <c r="H7" s="3" t="n">
         <v>18.2</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>84.7</v>
+        <v>64.7</v>
       </c>
       <c r="J7" s="3" t="n">
         <v>7.9</v>
       </c>
-      <c r="K7" s="10" t="n">
+      <c r="K7" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L7" s="10" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="M7" s="10" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="N7" s="10" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="O7" s="10" t="n">
+      <c r="L7" s="11" t="n">
+        <v>-12.8</v>
+      </c>
+      <c r="M7" s="11" t="n">
+        <v>-12.8</v>
+      </c>
+      <c r="N7" s="11" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="O7" s="11" t="n">
         <v>100</v>
       </c>
-      <c r="P7" s="10" t="n">
+      <c r="P7" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="Q7" s="10" t="n">
+      <c r="Q7" s="11" t="n">
         <v>34.2</v>
       </c>
       <c r="R7" s="12" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="S7" s="3" t="n">
         <v>27.1</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>20.6</v>
+        <v>50.6</v>
       </c>
       <c r="U7" s="3" t="n">
-        <v>26.5</v>
-      </c>
-      <c r="V7" s="10" t="n">
-        <v>29.5</v>
-      </c>
-      <c r="W7" s="10" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="V7" s="12" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="W7" s="11" t="n">
         <v>24.4</v>
       </c>
-      <c r="X7" s="10" t="n">
-        <v>30.6</v>
-      </c>
-      <c r="Y7" s="10" t="n">
-        <v>74.09999999999999</v>
-      </c>
-      <c r="Z7" s="10" t="n">
-        <v>10.7</v>
+      <c r="X7" s="3" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Y7" s="3" t="n">
+        <v>66.2</v>
+      </c>
+      <c r="Z7" s="3" t="n">
+        <v>13.8</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1111,74 +1111,74 @@
       <c r="C8" s="3" t="n">
         <v>299</v>
       </c>
-      <c r="D8" s="10" t="n">
+      <c r="D8" s="11" t="n">
         <v>34.6</v>
       </c>
-      <c r="E8" s="10" t="n">
+      <c r="E8" s="11" t="n">
         <v>20.6</v>
       </c>
-      <c r="F8" s="10" t="n">
+      <c r="F8" s="11" t="n">
         <v>27.6</v>
       </c>
-      <c r="G8" s="10" t="n">
+      <c r="G8" s="11" t="n">
         <v>14</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="I8" s="3" t="n">
         <v>2</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="K8" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="K8" s="8" t="n">
         <v>30.9</v>
       </c>
-      <c r="L8" s="10" t="n">
+      <c r="L8" s="11" t="n">
         <v>21</v>
       </c>
-      <c r="M8" s="10" t="n">
+      <c r="M8" s="11" t="n">
         <v>20.6</v>
       </c>
-      <c r="N8" s="10" t="n">
+      <c r="N8" s="11" t="n">
         <v>24.3</v>
       </c>
-      <c r="O8" s="10" t="n">
+      <c r="O8" s="11" t="n">
         <v>97.59999999999999</v>
       </c>
-      <c r="P8" s="10" t="n">
+      <c r="P8" s="11" t="n">
         <v>0.6</v>
       </c>
-      <c r="Q8" s="10" t="n">
+      <c r="Q8" s="11" t="n">
         <v>21.4</v>
       </c>
-      <c r="R8" s="10" t="n">
+      <c r="R8" s="11" t="n">
         <v>21.2</v>
       </c>
-      <c r="S8" s="10" t="n">
+      <c r="S8" s="11" t="n">
         <v>25.1</v>
       </c>
-      <c r="T8" s="10" t="n">
+      <c r="T8" s="11" t="n">
         <v>98.40000000000001</v>
       </c>
-      <c r="U8" s="10" t="n">
+      <c r="U8" s="11" t="n">
         <v>0.4</v>
       </c>
-      <c r="V8" s="10" t="n">
+      <c r="V8" s="11" t="n">
         <v>22.2</v>
       </c>
-      <c r="W8" s="10" t="n">
+      <c r="W8" s="11" t="n">
         <v>21.9</v>
       </c>
-      <c r="X8" s="10" t="n">
-        <v>26.3</v>
-      </c>
-      <c r="Y8" s="10" t="n">
-        <v>98.2</v>
-      </c>
-      <c r="Z8" s="10" t="n">
-        <v>0.5</v>
+      <c r="X8" s="11" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="Y8" s="11" t="n">
+        <v>97.40000000000001</v>
+      </c>
+      <c r="Z8" s="11" t="n">
+        <v>0.6</v>
       </c>
       <c r="AA8" s="3" t="inlineStr">
         <is>
@@ -1194,48 +1194,48 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>1783.2</v>
-      </c>
-      <c r="D9" s="10" t="n">
-        <v>164.9</v>
-      </c>
-      <c r="E9" s="10" t="n">
+        <v>178.3</v>
+      </c>
+      <c r="D9" s="11" t="n">
+        <v>164.8</v>
+      </c>
+      <c r="E9" s="11" t="n">
         <v>96.90000000000001</v>
       </c>
-      <c r="F9" s="10" t="n">
-        <v>130.9</v>
-      </c>
-      <c r="G9" s="10" t="n">
+      <c r="F9" s="11" t="n">
+        <v>130.8</v>
+      </c>
+      <c r="G9" s="11" t="n">
         <v>67.90000000000001</v>
       </c>
       <c r="H9" s="3" t="n">
         <v>89.40000000000001</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>16.8</v>
+        <v>16.5</v>
       </c>
       <c r="J9" s="3" t="n">
         <v>27.5</v>
       </c>
-      <c r="K9" s="10" t="n">
-        <v>30.9</v>
-      </c>
-      <c r="L9" s="10" t="n">
+      <c r="K9" s="13" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="L9" s="11" t="n">
         <v>100.2</v>
       </c>
-      <c r="M9" s="10" t="n">
+      <c r="M9" s="11" t="n">
         <v>99.59999999999999</v>
       </c>
-      <c r="N9" s="10" t="n">
+      <c r="N9" s="11" t="n">
         <v>1032.5</v>
       </c>
-      <c r="O9" s="10" t="n">
+      <c r="O9" s="11" t="n">
         <v>97.8</v>
       </c>
-      <c r="P9" s="10" t="n">
+      <c r="P9" s="11" t="n">
         <v>22.9</v>
       </c>
-      <c r="Q9" s="10" t="n">
+      <c r="Q9" s="11" t="n">
         <v>149.6</v>
       </c>
       <c r="R9" s="13" t="n">
@@ -1245,22 +1245,22 @@
         <v>135.7</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>329.9</v>
+        <v>2329.9</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>82</v>
-      </c>
-      <c r="V9" s="10" t="n">
+        <v>81</v>
+      </c>
+      <c r="V9" s="13" t="n">
         <v>132.8</v>
       </c>
-      <c r="W9" s="10" t="n">
+      <c r="W9" s="11" t="n">
         <v>116.8</v>
       </c>
       <c r="X9" s="3" t="n">
         <v>133.5</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>3788.8</v>
+        <v>388.8</v>
       </c>
       <c r="Z9" s="3" t="n">
         <v>41.6</v>
@@ -1279,18 +1279,18 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>35.4</v>
-      </c>
-      <c r="D10" s="10" t="n">
+        <v>356.7</v>
+      </c>
+      <c r="D10" s="11" t="n">
         <v>33</v>
       </c>
-      <c r="E10" s="10" t="n">
+      <c r="E10" s="11" t="n">
         <v>19.4</v>
       </c>
-      <c r="F10" s="10" t="n">
-        <v>26.4</v>
-      </c>
-      <c r="G10" s="10" t="n">
+      <c r="F10" s="11" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="G10" s="11" t="n">
         <v>13.6</v>
       </c>
       <c r="H10" s="3" t="n">
@@ -1302,25 +1302,23 @@
       <c r="J10" s="3" t="n">
         <v>5.5</v>
       </c>
-      <c r="K10" s="3" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="L10" s="10" t="n">
+      <c r="K10" s="3" t="inlineStr"/>
+      <c r="L10" s="11" t="n">
         <v>20</v>
       </c>
-      <c r="M10" s="10" t="n">
+      <c r="M10" s="11" t="n">
         <v>19.9</v>
       </c>
-      <c r="N10" s="10" t="n">
+      <c r="N10" s="11" t="n">
         <v>23.2</v>
       </c>
-      <c r="O10" s="10" t="n">
+      <c r="O10" s="11" t="n">
         <v>99.40000000000001</v>
       </c>
-      <c r="P10" s="10" t="n">
+      <c r="P10" s="11" t="n">
         <v>0.1</v>
       </c>
-      <c r="Q10" s="10" t="n">
+      <c r="Q10" s="11" t="n">
         <v>29.9</v>
       </c>
       <c r="R10" s="13" t="n">
@@ -1335,20 +1333,20 @@
       <c r="U10" s="3" t="n">
         <v>16.2</v>
       </c>
-      <c r="V10" s="10" t="n">
+      <c r="V10" s="13" t="n">
         <v>26.6</v>
       </c>
-      <c r="W10" s="10" t="n">
+      <c r="W10" s="11" t="n">
         <v>23.4</v>
       </c>
-      <c r="X10" s="10" t="n">
-        <v>28.8</v>
-      </c>
-      <c r="Y10" s="10" t="n">
-        <v>82.59999999999999</v>
-      </c>
-      <c r="Z10" s="10" t="n">
-        <v>6.1</v>
+      <c r="X10" s="3" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="Y10" s="3" t="n">
+        <v>77.8</v>
+      </c>
+      <c r="Z10" s="3" t="n">
+        <v>8.300000000000001</v>
       </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
@@ -1366,74 +1364,74 @@
       <c r="C11" s="3" t="n">
         <v>265.6</v>
       </c>
-      <c r="D11" s="10" t="n">
-        <v>30</v>
-      </c>
-      <c r="E11" s="10" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="F11" s="10" t="n">
+      <c r="D11" s="11" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="E11" s="11" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="F11" s="11" t="n">
         <v>24.9</v>
       </c>
-      <c r="G11" s="10" t="n">
+      <c r="G11" s="11" t="n">
         <v>10.3</v>
       </c>
       <c r="H11" s="3" t="n">
         <v>18.2</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>0.6</v>
+        <v>11.6</v>
       </c>
       <c r="J11" s="3" t="n">
         <v>2.8</v>
       </c>
-      <c r="K11" s="3" t="n">
+      <c r="K11" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="L11" s="10" t="n">
+      <c r="L11" s="3" t="n">
         <v>21.2</v>
       </c>
-      <c r="M11" s="10" t="n">
+      <c r="M11" s="11" t="n">
         <v>20.9</v>
       </c>
-      <c r="N11" s="10" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="O11" s="10" t="n">
-        <v>98.2</v>
-      </c>
-      <c r="P11" s="10" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Q11" s="10" t="n">
+      <c r="N11" s="3" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="O11" s="3" t="n">
+        <v>97.3</v>
+      </c>
+      <c r="P11" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Q11" s="11" t="n">
         <v>29.9</v>
       </c>
-      <c r="R11" s="10" t="n">
+      <c r="R11" s="11" t="n">
         <v>24</v>
       </c>
-      <c r="S11" s="10" t="n">
+      <c r="S11" s="11" t="n">
         <v>29.8</v>
       </c>
-      <c r="T11" s="10" t="n">
+      <c r="T11" s="11" t="n">
         <v>70.59999999999999</v>
       </c>
-      <c r="U11" s="10" t="n">
+      <c r="U11" s="11" t="n">
         <v>12.4</v>
       </c>
-      <c r="V11" s="3" t="n">
+      <c r="V11" s="11" t="n">
         <v>27.1</v>
       </c>
-      <c r="W11" s="12" t="n">
-        <v>94.90000000000001</v>
+      <c r="W11" s="3" t="n">
+        <v>24.9</v>
       </c>
       <c r="X11" s="3" t="n">
         <v>30.1</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>894</v>
+        <v>84</v>
       </c>
       <c r="Z11" s="3" t="n">
-        <v>5.8</v>
+        <v>159.8</v>
       </c>
       <c r="AA11" s="3" t="inlineStr">
         <is>
@@ -1449,18 +1447,18 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>242.1</v>
-      </c>
-      <c r="D12" s="10" t="n">
+        <v>347.1</v>
+      </c>
+      <c r="D12" s="11" t="n">
         <v>31.8</v>
       </c>
-      <c r="E12" s="10" t="n">
+      <c r="E12" s="11" t="n">
         <v>22.6</v>
       </c>
-      <c r="F12" s="10" t="n">
+      <c r="F12" s="11" t="n">
         <v>27.2</v>
       </c>
-      <c r="G12" s="10" t="n">
+      <c r="G12" s="11" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="H12" s="3" t="n">
@@ -1470,55 +1468,55 @@
         <v>2.7</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="K12" s="3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K12" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="L12" s="10" t="n">
+      <c r="L12" s="11" t="n">
         <v>23.3</v>
       </c>
-      <c r="M12" s="10" t="n">
+      <c r="M12" s="11" t="n">
         <v>23</v>
       </c>
-      <c r="N12" s="10" t="n">
-        <v>28.1</v>
-      </c>
-      <c r="O12" s="10" t="n">
-        <v>98.2</v>
-      </c>
-      <c r="P12" s="10" t="n">
+      <c r="N12" s="11" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="O12" s="11" t="n">
+        <v>97.59999999999999</v>
+      </c>
+      <c r="P12" s="11" t="n">
         <v>0.5</v>
       </c>
-      <c r="Q12" s="3" t="n">
+      <c r="Q12" s="11" t="n">
         <v>31.8</v>
       </c>
-      <c r="R12" s="3" t="n">
+      <c r="R12" s="11" t="n">
         <v>24.9</v>
       </c>
-      <c r="S12" s="3" t="n">
-        <v>27.1</v>
-      </c>
-      <c r="T12" s="3" t="n">
-        <v>59.8</v>
-      </c>
-      <c r="U12" s="3" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="V12" s="3" t="n">
-        <v>21.9</v>
-      </c>
-      <c r="W12" s="3" t="n">
-        <v>24.6</v>
-      </c>
-      <c r="X12" s="3" t="n">
+      <c r="S12" s="11" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="T12" s="11" t="n">
+        <v>66.90000000000001</v>
+      </c>
+      <c r="U12" s="11" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="V12" s="11" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="W12" s="11" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="X12" s="11" t="n">
         <v>28.8</v>
       </c>
-      <c r="Y12" s="3" t="n">
+      <c r="Y12" s="11" t="n">
         <v>76.7</v>
       </c>
-      <c r="Z12" s="3" t="n">
-        <v>81.7</v>
+      <c r="Z12" s="11" t="n">
+        <v>8.699999999999999</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1536,16 +1534,16 @@
       <c r="C13" s="3" t="n">
         <v>428.6</v>
       </c>
-      <c r="D13" s="10" t="n">
+      <c r="D13" s="11" t="n">
         <v>32.8</v>
       </c>
-      <c r="E13" s="10" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="F13" s="10" t="n">
+      <c r="E13" s="11" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="F13" s="11" t="n">
         <v>26.6</v>
       </c>
-      <c r="G13" s="10" t="n">
+      <c r="G13" s="11" t="n">
         <v>12.4</v>
       </c>
       <c r="H13" s="3" t="n">
@@ -1555,46 +1553,46 @@
         <v>3.3</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="K13" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="K13" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="L13" s="10" t="n">
+      <c r="L13" s="11" t="n">
         <v>22.1</v>
       </c>
-      <c r="M13" s="10" t="n">
+      <c r="M13" s="11" t="n">
         <v>21.9</v>
       </c>
-      <c r="N13" s="10" t="n">
-        <v>26.3</v>
-      </c>
-      <c r="O13" s="10" t="n">
-        <v>98.8</v>
-      </c>
-      <c r="P13" s="10" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="Q13" s="10" t="n">
+      <c r="N13" s="11" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="O13" s="11" t="n">
+        <v>98</v>
+      </c>
+      <c r="P13" s="11" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q13" s="11" t="n">
         <v>32.6</v>
       </c>
-      <c r="R13" s="10" t="n">
+      <c r="R13" s="11" t="n">
         <v>21.6</v>
       </c>
-      <c r="S13" s="10" t="n">
+      <c r="S13" s="11" t="n">
         <v>25.8</v>
       </c>
-      <c r="T13" s="10" t="n">
+      <c r="T13" s="11" t="n">
         <v>52.7</v>
       </c>
-      <c r="U13" s="10" t="n">
+      <c r="U13" s="11" t="n">
         <v>23.3</v>
       </c>
-      <c r="V13" s="3" t="n">
+      <c r="V13" s="11" t="n">
         <v>28</v>
       </c>
-      <c r="W13" s="3" t="n">
-        <v>24.8</v>
+      <c r="W13" s="12" t="n">
+        <v>2.4</v>
       </c>
       <c r="X13" s="3" t="n">
         <v>29.3</v>
@@ -1603,7 +1601,7 @@
         <v>77.59999999999999</v>
       </c>
       <c r="Z13" s="3" t="n">
-        <v>18.5</v>
+        <v>2.5</v>
       </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
@@ -1621,73 +1619,75 @@
       <c r="C14" s="3" t="n">
         <v>190.3</v>
       </c>
-      <c r="D14" s="10" t="n">
+      <c r="D14" s="11" t="n">
         <v>30.7</v>
       </c>
-      <c r="E14" s="10" t="n">
+      <c r="E14" s="11" t="n">
         <v>21.9</v>
       </c>
-      <c r="F14" s="10" t="n">
+      <c r="F14" s="11" t="n">
         <v>26.3</v>
       </c>
-      <c r="G14" s="10" t="n">
+      <c r="G14" s="11" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="H14" s="3" t="n">
         <v>20.3</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>11.5</v>
+        <v>1.5</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>82.09999999999999</v>
-      </c>
-      <c r="K14" s="3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="K14" s="11" t="n">
         <v>11.1</v>
       </c>
-      <c r="L14" s="10" t="n">
+      <c r="L14" s="11" t="n">
         <v>22.4</v>
       </c>
-      <c r="M14" s="10" t="n">
+      <c r="M14" s="11" t="n">
         <v>22.1</v>
       </c>
-      <c r="N14" s="10" t="n">
+      <c r="N14" s="11" t="n">
         <v>26.4</v>
       </c>
-      <c r="O14" s="10" t="n">
+      <c r="O14" s="11" t="n">
         <v>97.3</v>
       </c>
-      <c r="P14" s="10" t="n">
+      <c r="P14" s="11" t="n">
         <v>0.7</v>
       </c>
-      <c r="Q14" s="12" t="n">
-        <v>82.40000000000001</v>
-      </c>
-      <c r="R14" s="3" t="n">
+      <c r="Q14" s="11" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="R14" s="11" t="n">
         <v>21.1</v>
       </c>
-      <c r="S14" s="3" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="T14" s="3" t="n">
-        <v>89</v>
-      </c>
-      <c r="U14" s="3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="V14" s="3" t="n">
+      <c r="S14" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" s="11" t="n">
+        <v>92.40000000000001</v>
+      </c>
+      <c r="U14" s="11" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="V14" s="11" t="n">
         <v>22</v>
       </c>
-      <c r="W14" s="3" t="n">
+      <c r="W14" s="11" t="n">
         <v>21.6</v>
       </c>
-      <c r="X14" s="3" t="n">
+      <c r="X14" s="11" t="n">
         <v>25.5</v>
       </c>
-      <c r="Y14" s="3" t="n">
-        <v>96</v>
-      </c>
-      <c r="Z14" s="3" t="inlineStr"/>
+      <c r="Y14" s="11" t="n">
+        <v>96.59999999999999</v>
+      </c>
+      <c r="Z14" s="11" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
           <t>9</t>
@@ -1704,16 +1704,16 @@
       <c r="C15" s="3" t="n">
         <v>359.6</v>
       </c>
-      <c r="D15" s="10" t="n">
-        <v>32.6</v>
-      </c>
-      <c r="E15" s="10" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="F15" s="10" t="n">
-        <v>26.6</v>
-      </c>
-      <c r="G15" s="10" t="n">
+      <c r="D15" s="11" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="E15" s="11" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="F15" s="11" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="G15" s="11" t="n">
         <v>11.7</v>
       </c>
       <c r="H15" s="3" t="n">
@@ -1725,52 +1725,52 @@
       <c r="J15" s="3" t="n">
         <v>3.9</v>
       </c>
-      <c r="K15" s="3" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="L15" s="10" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="M15" s="10" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="N15" s="10" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="O15" s="10" t="n">
-        <v>100.2</v>
-      </c>
-      <c r="P15" s="10" t="n">
+      <c r="K15" s="11" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="L15" s="11" t="n">
+        <v>24</v>
+      </c>
+      <c r="M15" s="11" t="n">
+        <v>24</v>
+      </c>
+      <c r="N15" s="11" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="O15" s="11" t="n">
+        <v>100</v>
+      </c>
+      <c r="P15" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="Q15" s="10" t="n">
+      <c r="Q15" s="11" t="n">
         <v>32</v>
       </c>
-      <c r="R15" s="10" t="n">
+      <c r="R15" s="11" t="n">
         <v>23.6</v>
       </c>
-      <c r="S15" s="10" t="n">
+      <c r="S15" s="11" t="n">
         <v>29.2</v>
       </c>
-      <c r="T15" s="10" t="n">
+      <c r="T15" s="11" t="n">
         <v>61.7</v>
       </c>
-      <c r="U15" s="10" t="n">
+      <c r="U15" s="11" t="n">
         <v>18.2</v>
       </c>
-      <c r="V15" s="10" t="n">
+      <c r="V15" s="11" t="n">
         <v>28.7</v>
       </c>
-      <c r="W15" s="10" t="n">
+      <c r="W15" s="11" t="n">
         <v>23.4</v>
       </c>
-      <c r="X15" s="10" t="n">
+      <c r="X15" s="11" t="n">
         <v>28.8</v>
       </c>
-      <c r="Y15" s="10" t="n">
+      <c r="Y15" s="11" t="n">
         <v>73.09999999999999</v>
       </c>
-      <c r="Z15" s="10" t="n">
+      <c r="Z15" s="11" t="n">
         <v>10.6</v>
       </c>
       <c r="AA15" s="3" t="inlineStr">
@@ -1787,19 +1787,19 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1221.2</v>
-      </c>
-      <c r="D16" s="10" t="n">
+        <v>1591.2</v>
+      </c>
+      <c r="D16" s="11" t="n">
         <v>157.9</v>
       </c>
-      <c r="E16" s="10" t="n">
+      <c r="E16" s="11" t="n">
         <v>105.5</v>
       </c>
-      <c r="F16" s="10" t="n">
-        <v>131.6</v>
-      </c>
-      <c r="G16" s="3" t="n">
-        <v>52.4</v>
+      <c r="F16" s="11" t="n">
+        <v>131.7</v>
+      </c>
+      <c r="G16" s="12" t="n">
+        <v>35.2</v>
       </c>
       <c r="H16" s="3" t="n">
         <v>99.2</v>
@@ -1810,50 +1810,50 @@
       <c r="J16" s="3" t="n">
         <v>19.4</v>
       </c>
-      <c r="K16" s="13" t="n">
+      <c r="K16" s="11" t="n">
         <v>36.8</v>
       </c>
-      <c r="L16" s="10" t="n">
-        <v>110.6</v>
-      </c>
-      <c r="M16" s="10" t="n">
+      <c r="L16" s="13" t="n">
+        <v>1110.6</v>
+      </c>
+      <c r="M16" s="11" t="n">
         <v>109.5</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>1230.7</v>
+        <v>130.7</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>1490.1</v>
+        <v>2490.1</v>
       </c>
       <c r="P16" s="3" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q16" s="13" t="n">
+      <c r="Q16" s="11" t="n">
         <v>148.7</v>
       </c>
-      <c r="R16" s="13" t="n">
-        <v>1221.9</v>
-      </c>
-      <c r="S16" s="3" t="n">
-        <v>1136.1</v>
-      </c>
-      <c r="T16" s="3" t="n">
-        <v>331.8</v>
-      </c>
-      <c r="U16" s="3" t="n">
-        <v>76.59999999999999</v>
-      </c>
-      <c r="V16" s="13" t="n">
+      <c r="R16" s="11" t="n">
+        <v>121.9</v>
+      </c>
+      <c r="S16" s="11" t="n">
+        <v>2219.6</v>
+      </c>
+      <c r="T16" s="11" t="n">
+        <v>44.7</v>
+      </c>
+      <c r="U16" s="11" t="n">
+        <v>2743.1</v>
+      </c>
+      <c r="V16" s="11" t="n">
         <v>133.7</v>
       </c>
       <c r="W16" s="13" t="n">
-        <v>120.7</v>
+        <v>2120.7</v>
       </c>
       <c r="X16" s="3" t="n">
         <v>142.5</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>1407.6</v>
+        <v>407.4</v>
       </c>
       <c r="Z16" s="3" t="n">
         <v>34.4</v>
@@ -1874,16 +1874,16 @@
       <c r="C17" s="3" t="n">
         <v>318.2</v>
       </c>
-      <c r="D17" s="10" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="E17" s="10" t="n">
-        <v>21</v>
-      </c>
-      <c r="F17" s="10" t="n">
-        <v>26.4</v>
-      </c>
-      <c r="G17" s="10" t="n">
+      <c r="D17" s="11" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="E17" s="11" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="F17" s="11" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="G17" s="11" t="n">
         <v>10.5</v>
       </c>
       <c r="H17" s="3" t="n">
@@ -1895,41 +1895,41 @@
       <c r="J17" s="3" t="n">
         <v>3.9</v>
       </c>
-      <c r="K17" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="L17" s="10" t="n">
+      <c r="K17" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L17" s="13" t="n">
         <v>22.1</v>
       </c>
-      <c r="M17" s="10" t="n">
+      <c r="M17" s="11" t="n">
         <v>21.9</v>
       </c>
-      <c r="N17" s="10" t="n">
-        <v>26.3</v>
-      </c>
-      <c r="O17" s="10" t="n">
-        <v>98.8</v>
-      </c>
-      <c r="P17" s="10" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="Q17" s="13" t="n">
+      <c r="N17" s="11" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="O17" s="3" t="n">
+        <v>298</v>
+      </c>
+      <c r="P17" s="3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Q17" s="11" t="n">
         <v>29.7</v>
       </c>
-      <c r="R17" s="13" t="n">
+      <c r="R17" s="11" t="n">
         <v>24.4</v>
       </c>
-      <c r="S17" s="3" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="T17" s="3" t="n">
-        <v>66.40000000000001</v>
-      </c>
-      <c r="U17" s="3" t="n">
-        <v>15.3</v>
-      </c>
-      <c r="V17" s="13" t="n">
-        <v>8.300000000000001</v>
+      <c r="S17" s="11" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="T17" s="11" t="n">
+        <v>73.2</v>
+      </c>
+      <c r="U17" s="11" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="V17" s="11" t="n">
+        <v>26.7</v>
       </c>
       <c r="W17" s="13" t="n">
         <v>24.1</v>
@@ -1941,7 +1941,7 @@
         <v>81.5</v>
       </c>
       <c r="Z17" s="3" t="n">
-        <v>16.9</v>
+        <v>6.9</v>
       </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
@@ -1959,69 +1959,71 @@
       <c r="C18" s="3" t="n">
         <v>368</v>
       </c>
-      <c r="D18" s="10" t="n">
+      <c r="D18" s="11" t="n">
         <v>32.1</v>
       </c>
-      <c r="E18" s="10" t="n">
+      <c r="E18" s="11" t="n">
         <v>21.2</v>
       </c>
-      <c r="F18" s="10" t="n">
-        <v>26.6</v>
-      </c>
-      <c r="G18" s="3" t="inlineStr"/>
+      <c r="F18" s="11" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="G18" s="11" t="n">
+        <v>10.9</v>
+      </c>
       <c r="H18" s="3" t="n">
-        <v>80.40000000000001</v>
+        <v>20.4</v>
       </c>
       <c r="I18" s="3" t="n">
         <v>2.5</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>14.3</v>
+        <v>4.3</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="L18" s="10" t="n">
-        <v>21.4</v>
-      </c>
-      <c r="M18" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="L18" s="3" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="M18" s="11" t="n">
         <v>21.1</v>
       </c>
-      <c r="N18" s="10" t="n">
-        <v>25</v>
-      </c>
-      <c r="O18" s="10" t="n">
-        <v>98.2</v>
-      </c>
-      <c r="P18" s="10" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Q18" s="10" t="n">
+      <c r="N18" s="3" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="O18" s="3" t="n">
+        <v>197.3</v>
+      </c>
+      <c r="P18" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Q18" s="11" t="n">
         <v>32.1</v>
       </c>
-      <c r="R18" s="3" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="S18" s="3" t="n">
+      <c r="R18" s="11" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="S18" s="11" t="n">
         <v>27.7</v>
       </c>
-      <c r="T18" s="3" t="n">
-        <v>38</v>
-      </c>
-      <c r="U18" s="3" t="n">
+      <c r="T18" s="11" t="n">
+        <v>58</v>
+      </c>
+      <c r="U18" s="11" t="n">
         <v>20</v>
       </c>
-      <c r="V18" s="10" t="n">
+      <c r="V18" s="3" t="n">
         <v>28.5</v>
       </c>
-      <c r="W18" s="3" t="n">
+      <c r="W18" s="11" t="n">
         <v>24.4</v>
       </c>
       <c r="X18" s="3" t="n">
-        <v>21.9</v>
+        <v>27.9</v>
       </c>
       <c r="Y18" s="3" t="n">
-        <v>71.90000000000001</v>
+        <v>171.7</v>
       </c>
       <c r="Z18" s="3" t="n">
         <v>11</v>
@@ -2042,20 +2044,20 @@
       <c r="C19" s="3" t="n">
         <v>265.6</v>
       </c>
-      <c r="D19" s="10" t="n">
+      <c r="D19" s="11" t="n">
         <v>30.4</v>
       </c>
-      <c r="E19" s="10" t="n">
+      <c r="E19" s="11" t="n">
         <v>22.2</v>
       </c>
-      <c r="F19" s="10" t="n">
+      <c r="F19" s="11" t="n">
         <v>26.3</v>
       </c>
-      <c r="G19" s="10" t="n">
+      <c r="G19" s="11" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="H19" s="8" t="n">
-        <v>91.40000000000001</v>
+      <c r="H19" s="3" t="n">
+        <v>21.4</v>
       </c>
       <c r="I19" s="3" t="n">
         <v>1.6</v>
@@ -2066,41 +2068,41 @@
       <c r="K19" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="L19" s="10" t="n">
+      <c r="L19" s="11" t="n">
         <v>22.3</v>
       </c>
-      <c r="M19" s="10" t="n">
+      <c r="M19" s="11" t="n">
         <v>22</v>
       </c>
-      <c r="N19" s="10" t="n">
-        <v>26.4</v>
-      </c>
-      <c r="O19" s="10" t="n">
-        <v>98.2</v>
-      </c>
-      <c r="P19" s="10" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Q19" s="10" t="n">
+      <c r="N19" s="11" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="O19" s="11" t="n">
+        <v>97.59999999999999</v>
+      </c>
+      <c r="P19" s="11" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Q19" s="11" t="n">
         <v>29.9</v>
       </c>
-      <c r="R19" s="10" t="n">
+      <c r="R19" s="11" t="n">
         <v>24.7</v>
       </c>
-      <c r="S19" s="10" t="n">
+      <c r="S19" s="11" t="n">
         <v>31.1</v>
       </c>
-      <c r="T19" s="10" t="n">
+      <c r="T19" s="11" t="n">
         <v>73.7</v>
       </c>
-      <c r="U19" s="10" t="n">
+      <c r="U19" s="11" t="n">
         <v>11</v>
       </c>
-      <c r="V19" s="10" t="n">
+      <c r="V19" s="3" t="n">
         <v>24.3</v>
       </c>
-      <c r="W19" s="8" t="n">
-        <v>28.9</v>
+      <c r="W19" s="11" t="n">
+        <v>22.9</v>
       </c>
       <c r="X19" s="3" t="n">
         <v>27.1</v>
@@ -2109,7 +2111,7 @@
         <v>89</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>8.300000000000001</v>
+        <v>12.3</v>
       </c>
       <c r="AA19" s="3" t="inlineStr">
         <is>
@@ -2127,17 +2129,17 @@
       <c r="C20" s="3" t="n">
         <v>365.9</v>
       </c>
-      <c r="D20" s="10" t="n">
-        <v>38.5</v>
-      </c>
-      <c r="E20" s="10" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="F20" s="10" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="G20" s="10" t="n">
-        <v>19.9</v>
+      <c r="D20" s="11" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="E20" s="11" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="F20" s="11" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="G20" s="3" t="n">
+        <v>29.9</v>
       </c>
       <c r="H20" s="3" t="n">
         <v>20.6</v>
@@ -2146,55 +2148,55 @@
         <v>2.5</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>14.5</v>
+        <v>4.5</v>
       </c>
       <c r="K20" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L20" s="10" t="n">
+      <c r="L20" s="3" t="n">
         <v>21.6</v>
       </c>
-      <c r="M20" s="10" t="n">
+      <c r="M20" s="11" t="n">
         <v>21.4</v>
       </c>
-      <c r="N20" s="10" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="O20" s="10" t="n">
-        <v>98.8</v>
-      </c>
-      <c r="P20" s="10" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="Q20" s="10" t="n">
+      <c r="N20" s="3" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="O20" s="3" t="n">
+        <v>98</v>
+      </c>
+      <c r="P20" s="3" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="Q20" s="11" t="n">
         <v>30.7</v>
       </c>
-      <c r="R20" s="3" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="S20" s="8" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="T20" s="3" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="U20" s="3" t="n">
+      <c r="R20" s="11" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="S20" s="11" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="T20" s="11" t="n">
+        <v>62.3</v>
+      </c>
+      <c r="U20" s="11" t="n">
         <v>16.6</v>
       </c>
-      <c r="V20" s="10" t="n">
-        <v>27.3</v>
-      </c>
-      <c r="W20" s="3" t="n">
-        <v>22.8</v>
+      <c r="V20" s="12" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="W20" s="11" t="n">
+        <v>23.8</v>
       </c>
       <c r="X20" s="3" t="n">
         <v>27.2</v>
       </c>
       <c r="Y20" s="3" t="n">
-        <v>725</v>
+        <v>85</v>
       </c>
       <c r="Z20" s="3" t="n">
-        <v>9.1</v>
+        <v>19.1</v>
       </c>
       <c r="AA20" s="3" t="inlineStr">
         <is>
@@ -2212,16 +2214,16 @@
       <c r="C21" s="3" t="n">
         <v>340.8</v>
       </c>
-      <c r="D21" s="10" t="n">
-        <v>30.6</v>
-      </c>
-      <c r="E21" s="10" t="n">
+      <c r="D21" s="11" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="E21" s="11" t="n">
         <v>21.2</v>
       </c>
-      <c r="F21" s="10" t="n">
+      <c r="F21" s="11" t="n">
         <v>25.9</v>
       </c>
-      <c r="G21" s="10" t="n">
+      <c r="G21" s="11" t="n">
         <v>9.5</v>
       </c>
       <c r="H21" s="3" t="n">
@@ -2236,41 +2238,41 @@
       <c r="K21" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L21" s="10" t="n">
+      <c r="L21" s="11" t="n">
         <v>21.6</v>
       </c>
-      <c r="M21" s="10" t="n">
+      <c r="M21" s="11" t="n">
         <v>21.5</v>
       </c>
-      <c r="N21" s="10" t="n">
+      <c r="N21" s="11" t="n">
         <v>25.6</v>
       </c>
-      <c r="O21" s="10" t="n">
-        <v>99.40000000000001</v>
-      </c>
-      <c r="P21" s="10" t="n">
+      <c r="O21" s="11" t="n">
+        <v>99.3</v>
+      </c>
+      <c r="P21" s="11" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q21" s="10" t="n">
+      <c r="Q21" s="11" t="n">
         <v>30.6</v>
       </c>
-      <c r="R21" s="10" t="n">
+      <c r="R21" s="11" t="n">
         <v>24.7</v>
       </c>
-      <c r="S21" s="10" t="n">
+      <c r="S21" s="11" t="n">
         <v>31.2</v>
       </c>
-      <c r="T21" s="10" t="n">
+      <c r="T21" s="11" t="n">
         <v>71.2</v>
       </c>
-      <c r="U21" s="10" t="n">
+      <c r="U21" s="11" t="n">
         <v>12.6</v>
       </c>
-      <c r="V21" s="10" t="n">
+      <c r="V21" s="3" t="n">
         <v>27.8</v>
       </c>
-      <c r="W21" s="8" t="n">
-        <v>26.6</v>
+      <c r="W21" s="11" t="n">
+        <v>24.6</v>
       </c>
       <c r="X21" s="3" t="n">
         <v>28.9</v>
@@ -2295,19 +2297,19 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>399.3</v>
-      </c>
-      <c r="D22" s="10" t="n">
+        <v>2399.3</v>
+      </c>
+      <c r="D22" s="11" t="n">
         <v>32.9</v>
       </c>
-      <c r="E22" s="10" t="n">
+      <c r="E22" s="11" t="n">
         <v>21.1</v>
       </c>
-      <c r="F22" s="10" t="n">
+      <c r="F22" s="11" t="n">
         <v>27</v>
       </c>
-      <c r="G22" s="10" t="n">
-        <v>11.8</v>
+      <c r="G22" s="3" t="n">
+        <v>1.1</v>
       </c>
       <c r="H22" s="3" t="n">
         <v>19.8</v>
@@ -2319,42 +2321,42 @@
         <v>4.3</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="L22" s="10" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="L22" s="3" t="n">
         <v>21.3</v>
       </c>
-      <c r="M22" s="10" t="n">
+      <c r="M22" s="11" t="n">
         <v>21</v>
       </c>
-      <c r="N22" s="10" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="O22" s="10" t="n">
-        <v>98.2</v>
-      </c>
-      <c r="P22" s="10" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Q22" s="10" t="n">
+      <c r="N22" s="11" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="O22" s="3" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="P22" s="3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Q22" s="11" t="n">
         <v>32.4</v>
       </c>
-      <c r="R22" s="3" t="n">
-        <v>29.9</v>
-      </c>
-      <c r="S22" s="3" t="n">
-        <v>89.3</v>
-      </c>
-      <c r="T22" s="3" t="n">
-        <v>60.5</v>
-      </c>
-      <c r="U22" s="3" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="V22" s="10" t="n">
+      <c r="R22" s="11" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="S22" s="11" t="n">
+        <v>33.4</v>
+      </c>
+      <c r="T22" s="11" t="n">
+        <v>68.59999999999999</v>
+      </c>
+      <c r="U22" s="11" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="V22" s="3" t="n">
         <v>26.5</v>
       </c>
-      <c r="W22" s="3" t="n">
+      <c r="W22" s="11" t="n">
         <v>24.6</v>
       </c>
       <c r="X22" s="3" t="n">
@@ -2364,7 +2366,7 @@
         <v>86</v>
       </c>
       <c r="Z22" s="3" t="n">
-        <v>144.9</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
@@ -2382,17 +2384,17 @@
       <c r="C23" s="3" t="n">
         <v>1739.6</v>
       </c>
-      <c r="D23" s="10" t="n">
-        <v>164.5</v>
-      </c>
-      <c r="E23" s="10" t="n">
-        <v>104.2</v>
-      </c>
-      <c r="F23" s="10" t="n">
-        <v>134.3</v>
-      </c>
-      <c r="G23" s="3" t="n">
-        <v>20.3</v>
+      <c r="D23" s="11" t="n">
+        <v>157.5</v>
+      </c>
+      <c r="E23" s="11" t="n">
+        <v>107.2</v>
+      </c>
+      <c r="F23" s="11" t="n">
+        <v>132.4</v>
+      </c>
+      <c r="G23" s="11" t="n">
+        <v>50.3</v>
       </c>
       <c r="H23" s="3" t="n">
         <v>101.8</v>
@@ -2401,15 +2403,15 @@
         <v>10.9</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>10.4</v>
+        <v>19.3</v>
       </c>
       <c r="K23" s="13" t="n">
-        <v>49.1</v>
-      </c>
-      <c r="L23" s="10" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="L23" s="13" t="n">
         <v>108.2</v>
       </c>
-      <c r="M23" s="10" t="n">
+      <c r="M23" s="11" t="n">
         <v>107</v>
       </c>
       <c r="N23" s="3" t="n">
@@ -2421,26 +2423,26 @@
       <c r="P23" s="3" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q23" s="10" t="n">
+      <c r="Q23" s="11" t="n">
         <v>155.7</v>
       </c>
-      <c r="R23" s="13" t="n">
+      <c r="R23" s="11" t="n">
         <v>128.1</v>
       </c>
-      <c r="S23" s="3" t="n">
-        <v>146.8</v>
-      </c>
-      <c r="T23" s="3" t="n">
-        <v>325.1</v>
-      </c>
-      <c r="U23" s="3" t="n">
-        <v>79.40000000000001</v>
-      </c>
-      <c r="V23" s="10" t="n">
+      <c r="S23" s="11" t="n">
+        <v>2701.5</v>
+      </c>
+      <c r="T23" s="11" t="n">
+        <v>44.9</v>
+      </c>
+      <c r="U23" s="11" t="n">
+        <v>3314</v>
+      </c>
+      <c r="V23" s="13" t="n">
         <v>134.4</v>
       </c>
-      <c r="W23" s="13" t="n">
-        <v>20.3</v>
+      <c r="W23" s="11" t="n">
+        <v>120.3</v>
       </c>
       <c r="X23" s="3" t="n">
         <v>140.8</v>
@@ -2449,7 +2451,7 @@
         <v>399</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>362.5</v>
+        <v>36.7</v>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -2465,18 +2467,18 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>343.2</v>
-      </c>
-      <c r="D24" s="10" t="n">
-        <v>31.2</v>
-      </c>
-      <c r="E24" s="10" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="F24" s="10" t="n">
-        <v>26.4</v>
-      </c>
-      <c r="G24" s="10" t="n">
+        <v>347.9</v>
+      </c>
+      <c r="D24" s="11" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="E24" s="11" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="F24" s="11" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="G24" s="11" t="n">
         <v>10.1</v>
       </c>
       <c r="H24" s="3" t="n">
@@ -2488,53 +2490,51 @@
       <c r="J24" s="3" t="n">
         <v>3.9</v>
       </c>
-      <c r="K24" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L24" s="10" t="n">
+      <c r="K24" s="3" t="inlineStr"/>
+      <c r="L24" s="13" t="n">
         <v>21.6</v>
       </c>
-      <c r="M24" s="10" t="n">
+      <c r="M24" s="11" t="n">
         <v>21.4</v>
       </c>
-      <c r="N24" s="10" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="O24" s="10" t="n">
-        <v>98.8</v>
-      </c>
-      <c r="P24" s="10" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="Q24" s="10" t="n">
+      <c r="N24" s="11" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="O24" s="3" t="n">
+        <v>97.90000000000001</v>
+      </c>
+      <c r="P24" s="3" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="Q24" s="11" t="n">
         <v>31.1</v>
       </c>
-      <c r="R24" s="10" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="S24" s="10" t="n">
-        <v>29.4</v>
-      </c>
-      <c r="T24" s="10" t="n">
-        <v>65.09999999999999</v>
-      </c>
-      <c r="U24" s="10" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="V24" s="10" t="n">
+      <c r="R24" s="11" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="S24" s="11" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="T24" s="11" t="n">
+        <v>72.59999999999999</v>
+      </c>
+      <c r="U24" s="11" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="V24" s="13" t="n">
         <v>26.9</v>
       </c>
-      <c r="W24" s="13" t="n">
+      <c r="W24" s="11" t="n">
         <v>24.1</v>
       </c>
       <c r="X24" s="3" t="n">
-        <v>23.2</v>
+        <v>22.2</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>2981.3</v>
+        <v>79.8</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>7.3</v>
+        <v>17.3</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2552,16 +2552,16 @@
       <c r="C25" s="3" t="n">
         <v>106.7</v>
       </c>
-      <c r="D25" s="10" t="n">
+      <c r="D25" s="11" t="n">
         <v>26.3</v>
       </c>
-      <c r="E25" s="10" t="n">
+      <c r="E25" s="11" t="n">
         <v>20.6</v>
       </c>
-      <c r="F25" s="10" t="n">
+      <c r="F25" s="11" t="n">
         <v>23.5</v>
       </c>
-      <c r="G25" s="10" t="n">
+      <c r="G25" s="11" t="n">
         <v>5.7</v>
       </c>
       <c r="H25" s="3" t="n">
@@ -2573,52 +2573,54 @@
       <c r="J25" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="K25" s="3" t="n">
+      <c r="K25" s="11" t="n">
         <v>23.7</v>
       </c>
-      <c r="L25" s="10" t="n">
+      <c r="L25" s="11" t="n">
         <v>22.4</v>
       </c>
-      <c r="M25" s="10" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="N25" s="10" t="n">
+      <c r="M25" s="12" t="n">
+        <v>98.09999999999999</v>
+      </c>
+      <c r="N25" s="3" t="n">
         <v>26.4</v>
       </c>
-      <c r="O25" s="10" t="n">
-        <v>97.5</v>
-      </c>
-      <c r="P25" s="10" t="n">
+      <c r="O25" s="3" t="n">
+        <v>97</v>
+      </c>
+      <c r="P25" s="3" t="n">
         <v>0.7</v>
       </c>
-      <c r="Q25" s="10" t="n">
+      <c r="Q25" s="3" t="n">
         <v>26.2</v>
       </c>
-      <c r="R25" s="10" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="S25" s="10" t="n">
+      <c r="R25" s="11" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="S25" s="3" t="n">
         <v>28.7</v>
       </c>
-      <c r="T25" s="10" t="n">
+      <c r="T25" s="3" t="n">
         <v>84.40000000000001</v>
       </c>
-      <c r="U25" s="10" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="V25" s="8" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="W25" s="10" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="X25" s="3" t="n">
+      <c r="U25" s="3" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="V25" s="11" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="W25" s="11" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="X25" s="11" t="n">
         <v>26.8</v>
       </c>
-      <c r="Y25" s="3" t="n">
-        <v>8781.700000000001</v>
-      </c>
-      <c r="Z25" s="3" t="inlineStr"/>
+      <c r="Y25" s="11" t="n">
+        <v>87.7</v>
+      </c>
+      <c r="Z25" s="11" t="n">
+        <v>3.8</v>
+      </c>
       <c r="AA25" s="3" t="inlineStr">
         <is>
           <t>16</t>
@@ -2635,13 +2637,13 @@
       <c r="C26" s="3" t="n">
         <v>290</v>
       </c>
-      <c r="D26" s="10" t="n">
-        <v>25.1</v>
-      </c>
-      <c r="E26" s="10" t="n">
-        <v>21</v>
-      </c>
-      <c r="F26" s="10" t="n">
+      <c r="D26" s="11" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="E26" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="F26" s="11" t="n">
         <v>23.1</v>
       </c>
       <c r="G26" s="3" t="n">
@@ -2656,53 +2658,53 @@
       <c r="J26" s="3" t="n">
         <v>0.7</v>
       </c>
-      <c r="K26" s="3" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="L26" s="10" t="n">
+      <c r="K26" s="11" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="L26" s="11" t="n">
         <v>21.4</v>
       </c>
-      <c r="M26" s="10" t="n">
+      <c r="M26" s="11" t="n">
         <v>21.4</v>
       </c>
-      <c r="N26" s="10" t="n">
+      <c r="N26" s="11" t="n">
         <v>25.5</v>
       </c>
-      <c r="O26" s="10" t="n">
+      <c r="O26" s="11" t="n">
         <v>100</v>
       </c>
-      <c r="P26" s="10" t="n">
+      <c r="P26" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="Q26" s="10" t="n">
+      <c r="Q26" s="3" t="n">
         <v>24.3</v>
       </c>
-      <c r="R26" s="10" t="n">
+      <c r="R26" s="11" t="n">
         <v>23.3</v>
       </c>
-      <c r="S26" s="10" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="T26" s="10" t="n">
-        <v>94.2</v>
-      </c>
-      <c r="U26" s="10" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="V26" s="10" t="n">
+      <c r="S26" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="T26" s="3" t="n">
+        <v>92</v>
+      </c>
+      <c r="U26" s="3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="V26" s="11" t="n">
         <v>23.8</v>
       </c>
-      <c r="W26" s="10" t="n">
-        <v>22.4</v>
-      </c>
-      <c r="X26" s="10" t="n">
-        <v>27.1</v>
-      </c>
-      <c r="Y26" s="10" t="n">
-        <v>91.8</v>
-      </c>
-      <c r="Z26" s="10" t="n">
-        <v>2.4</v>
+      <c r="W26" s="11" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="X26" s="11" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="Y26" s="11" t="n">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="Z26" s="11" t="n">
+        <v>1.7</v>
       </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
@@ -2720,17 +2722,17 @@
       <c r="C27" s="3" t="n">
         <v>322</v>
       </c>
-      <c r="D27" s="10" t="n">
-        <v>30.5</v>
-      </c>
-      <c r="E27" s="10" t="n">
+      <c r="D27" s="11" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="E27" s="11" t="n">
         <v>20.6</v>
       </c>
-      <c r="F27" s="10" t="n">
+      <c r="F27" s="11" t="n">
         <v>25.5</v>
       </c>
-      <c r="G27" s="3" t="n">
-        <v>19.9</v>
+      <c r="G27" s="11" t="n">
+        <v>9.9</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>19.1</v>
@@ -2741,53 +2743,53 @@
       <c r="J27" s="3" t="n">
         <v>3.4</v>
       </c>
-      <c r="K27" s="3" t="n">
+      <c r="K27" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="L27" s="12" t="n">
-        <v>50.4</v>
-      </c>
-      <c r="M27" s="10" t="n">
+      <c r="L27" s="11" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="M27" s="11" t="n">
         <v>20.5</v>
       </c>
-      <c r="N27" s="10" t="n">
+      <c r="N27" s="11" t="n">
         <v>24</v>
       </c>
-      <c r="O27" s="3" t="n">
-        <v>98</v>
-      </c>
-      <c r="P27" s="3" t="n">
+      <c r="O27" s="11" t="n">
+        <v>98.40000000000001</v>
+      </c>
+      <c r="P27" s="11" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q27" s="10" t="n">
+      <c r="Q27" s="3" t="n">
         <v>28.8</v>
       </c>
-      <c r="R27" s="10" t="n">
+      <c r="R27" s="11" t="n">
         <v>24.9</v>
       </c>
-      <c r="S27" s="10" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="T27" s="10" t="n">
-        <v>79.5</v>
-      </c>
-      <c r="U27" s="10" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="V27" s="12" t="n">
-        <v>82.69</v>
-      </c>
-      <c r="W27" s="10" t="n">
+      <c r="S27" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="T27" s="3" t="n">
+        <v>73.2</v>
+      </c>
+      <c r="U27" s="3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="V27" s="11" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="W27" s="11" t="n">
         <v>24.4</v>
       </c>
-      <c r="X27" s="8" t="n">
-        <v>89</v>
-      </c>
-      <c r="Y27" s="3" t="n">
-        <v>81.8</v>
-      </c>
-      <c r="Z27" s="3" t="n">
-        <v>6.4</v>
+      <c r="X27" s="11" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="Y27" s="11" t="n">
+        <v>86.2</v>
+      </c>
+      <c r="Z27" s="11" t="n">
+        <v>4.9</v>
       </c>
       <c r="AA27" s="3" t="inlineStr">
         <is>
@@ -2805,16 +2807,16 @@
       <c r="C28" s="3" t="n">
         <v>290.7</v>
       </c>
-      <c r="D28" s="10" t="n">
-        <v>31.8</v>
-      </c>
-      <c r="E28" s="10" t="n">
+      <c r="D28" s="11" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="E28" s="11" t="n">
         <v>20.5</v>
       </c>
-      <c r="F28" s="10" t="n">
+      <c r="F28" s="11" t="n">
         <v>26.1</v>
       </c>
-      <c r="G28" s="10" t="n">
+      <c r="G28" s="11" t="n">
         <v>11.3</v>
       </c>
       <c r="H28" s="3" t="n">
@@ -2826,52 +2828,52 @@
       <c r="J28" s="3" t="n">
         <v>3.8</v>
       </c>
-      <c r="K28" s="3" t="n">
+      <c r="K28" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="L28" s="3" t="n">
+      <c r="L28" s="11" t="n">
         <v>20.9</v>
       </c>
-      <c r="M28" s="10" t="n">
+      <c r="M28" s="3" t="n">
         <v>20.6</v>
       </c>
-      <c r="N28" s="10" t="n">
+      <c r="N28" s="3" t="n">
         <v>24.1</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>9.699999999999999</v>
+        <v>97.3</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Q28" s="10" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="Q28" s="3" t="n">
         <v>31.2</v>
       </c>
-      <c r="R28" s="10" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="S28" s="10" t="n">
-        <v>27.2</v>
-      </c>
-      <c r="T28" s="10" t="n">
+      <c r="R28" s="11" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="S28" s="3" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T28" s="3" t="n">
         <v>60.2</v>
       </c>
-      <c r="U28" s="10" t="n">
+      <c r="U28" s="3" t="n">
         <v>18.1</v>
       </c>
-      <c r="V28" s="10" t="n">
+      <c r="V28" s="11" t="n">
         <v>28.6</v>
       </c>
-      <c r="W28" s="10" t="n">
+      <c r="W28" s="11" t="n">
         <v>23.2</v>
       </c>
-      <c r="X28" s="10" t="n">
+      <c r="X28" s="11" t="n">
         <v>28.4</v>
       </c>
-      <c r="Y28" s="10" t="n">
+      <c r="Y28" s="11" t="n">
         <v>72.59999999999999</v>
       </c>
-      <c r="Z28" s="10" t="n">
+      <c r="Z28" s="11" t="n">
         <v>10.7</v>
       </c>
       <c r="AA28" s="3" t="inlineStr">
@@ -2890,20 +2892,20 @@
       <c r="C29" s="3" t="n">
         <v>246.8</v>
       </c>
-      <c r="D29" s="10" t="n">
+      <c r="D29" s="11" t="n">
         <v>31.5</v>
       </c>
-      <c r="E29" s="10" t="n">
+      <c r="E29" s="11" t="n">
         <v>20.5</v>
       </c>
-      <c r="F29" s="10" t="n">
+      <c r="F29" s="11" t="n">
         <v>26</v>
       </c>
-      <c r="G29" s="10" t="n">
+      <c r="G29" s="11" t="n">
         <v>11</v>
       </c>
-      <c r="H29" s="3" t="n">
-        <v>19.2</v>
+      <c r="H29" s="8" t="n">
+        <v>69.2</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>1.6</v>
@@ -2911,53 +2913,53 @@
       <c r="J29" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="K29" s="3" t="n">
+      <c r="K29" s="11" t="n">
         <v>8.4</v>
       </c>
-      <c r="L29" s="3" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="M29" s="10" t="n">
+      <c r="L29" s="11" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="M29" s="3" t="n">
         <v>20.6</v>
       </c>
       <c r="N29" s="3" t="n">
         <v>23.9</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>95.3</v>
+        <v>2.5</v>
       </c>
       <c r="P29" s="3" t="n">
         <v>1.1</v>
       </c>
-      <c r="Q29" s="10" t="n">
+      <c r="Q29" s="12" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="R29" s="11" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="S29" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="T29" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="U29" s="3" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="V29" s="11" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="W29" s="11" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="X29" s="11" t="n">
         <v>25.3</v>
       </c>
-      <c r="R29" s="10" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="S29" s="10" t="n">
-        <v>29.1</v>
-      </c>
-      <c r="T29" s="10" t="n">
-        <v>90.3</v>
-      </c>
-      <c r="U29" s="10" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="V29" s="3" t="n">
-        <v>22.4</v>
-      </c>
-      <c r="W29" s="10" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="X29" s="8" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="Y29" s="3" t="n">
-        <v>90.8</v>
-      </c>
-      <c r="Z29" s="3" t="n">
-        <v>2.5</v>
+      <c r="Y29" s="11" t="n">
+        <v>93.5</v>
+      </c>
+      <c r="Z29" s="11" t="n">
+        <v>1.8</v>
       </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
@@ -2973,18 +2975,18 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>11056.2</v>
-      </c>
-      <c r="D30" s="10" t="n">
+        <v>1056.2</v>
+      </c>
+      <c r="D30" s="11" t="n">
         <v>145.2</v>
       </c>
-      <c r="E30" s="10" t="n">
+      <c r="E30" s="11" t="n">
         <v>103.2</v>
       </c>
-      <c r="F30" s="10" t="n">
+      <c r="F30" s="11" t="n">
         <v>124.2</v>
       </c>
-      <c r="G30" s="10" t="n">
+      <c r="G30" s="11" t="n">
         <v>42</v>
       </c>
       <c r="H30" s="3" t="n">
@@ -2994,53 +2996,55 @@
         <v>7.1</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>111</v>
-      </c>
-      <c r="K30" s="13" t="n">
-        <v>328.8</v>
-      </c>
-      <c r="L30" s="13" t="n">
-        <v>106.5</v>
-      </c>
-      <c r="M30" s="10" t="n">
-        <v>105.2</v>
+        <v>11</v>
+      </c>
+      <c r="K30" s="11" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="L30" s="11" t="n">
+        <v>105.5</v>
+      </c>
+      <c r="M30" s="13" t="n">
+        <v>1605.2</v>
       </c>
       <c r="N30" s="3" t="n">
         <v>123.9</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>487.6</v>
+        <v>2487.6</v>
       </c>
       <c r="P30" s="3" t="n">
         <v>2.8</v>
       </c>
-      <c r="Q30" s="10" t="n">
-        <v>135.8</v>
-      </c>
-      <c r="R30" s="10" t="n">
+      <c r="Q30" s="13" t="n">
+        <v>1135.8</v>
+      </c>
+      <c r="R30" s="11" t="n">
         <v>120.7</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>1240.9</v>
+        <v>140.9</v>
       </c>
       <c r="T30" s="3" t="n">
         <v>396.8</v>
       </c>
-      <c r="U30" s="3" t="inlineStr"/>
-      <c r="V30" s="13" t="n">
+      <c r="U30" s="3" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="V30" s="11" t="n">
         <v>126.1</v>
       </c>
-      <c r="W30" s="10" t="n">
+      <c r="W30" s="11" t="n">
         <v>115.9</v>
       </c>
       <c r="X30" s="3" t="n">
         <v>135.9</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>1424.7</v>
+        <v>1428.7</v>
       </c>
       <c r="Z30" s="3" t="n">
-        <v>85.8</v>
+        <v>25.8</v>
       </c>
       <c r="AA30" s="3" t="inlineStr">
         <is>
@@ -3058,16 +3062,16 @@
       <c r="C31" s="3" t="n">
         <v>211.2</v>
       </c>
-      <c r="D31" s="10" t="n">
+      <c r="D31" s="11" t="n">
         <v>29</v>
       </c>
-      <c r="E31" s="10" t="n">
+      <c r="E31" s="11" t="n">
         <v>20.6</v>
       </c>
-      <c r="F31" s="10" t="n">
+      <c r="F31" s="11" t="n">
         <v>24.8</v>
       </c>
-      <c r="G31" s="3" t="n">
+      <c r="G31" s="11" t="n">
         <v>8.4</v>
       </c>
       <c r="H31" s="3" t="n">
@@ -3079,53 +3083,51 @@
       <c r="J31" s="3" t="n">
         <v>2.2</v>
       </c>
-      <c r="K31" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="L31" s="10" t="n">
+      <c r="K31" s="3" t="inlineStr"/>
+      <c r="L31" s="11" t="n">
         <v>21.3</v>
       </c>
-      <c r="M31" s="10" t="n">
+      <c r="M31" s="11" t="n">
         <v>21</v>
       </c>
-      <c r="N31" s="10" t="n">
+      <c r="N31" s="11" t="n">
         <v>24.8</v>
       </c>
-      <c r="O31" s="10" t="n">
-        <v>97.90000000000001</v>
-      </c>
-      <c r="P31" s="10" t="n">
+      <c r="O31" s="11" t="n">
+        <v>97.5</v>
+      </c>
+      <c r="P31" s="11" t="n">
         <v>0.6</v>
       </c>
-      <c r="Q31" s="10" t="n">
+      <c r="Q31" s="13" t="n">
         <v>27.2</v>
       </c>
-      <c r="R31" s="10" t="n">
+      <c r="R31" s="11" t="n">
         <v>24.1</v>
       </c>
-      <c r="S31" s="10" t="n">
-        <v>30</v>
-      </c>
-      <c r="T31" s="10" t="n">
-        <v>83.2</v>
-      </c>
-      <c r="U31" s="10" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="V31" s="13" t="n">
+      <c r="S31" s="3" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="T31" s="3" t="n">
+        <v>79.40000000000001</v>
+      </c>
+      <c r="U31" s="3" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="V31" s="11" t="n">
         <v>25.2</v>
       </c>
-      <c r="W31" s="10" t="n">
+      <c r="W31" s="11" t="n">
         <v>23.2</v>
       </c>
-      <c r="X31" s="3" t="n">
-        <v>27.2</v>
-      </c>
-      <c r="Y31" s="3" t="n">
-        <v>84.90000000000001</v>
-      </c>
-      <c r="Z31" s="3" t="n">
-        <v>5.2</v>
+      <c r="X31" s="11" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="Y31" s="11" t="n">
+        <v>88.7</v>
+      </c>
+      <c r="Z31" s="11" t="n">
+        <v>3.6</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -3143,16 +3145,16 @@
       <c r="C32" s="3" t="n">
         <v>384.7</v>
       </c>
-      <c r="D32" s="10" t="n">
+      <c r="D32" s="11" t="n">
         <v>31.1</v>
       </c>
-      <c r="E32" s="10" t="n">
-        <v>15.3</v>
-      </c>
-      <c r="F32" s="10" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="G32" s="3" t="n">
+      <c r="E32" s="11" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="F32" s="11" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="G32" s="11" t="n">
         <v>11.8</v>
       </c>
       <c r="H32" s="8" t="n">
@@ -3164,53 +3166,53 @@
       <c r="J32" s="3" t="n">
         <v>4.6</v>
       </c>
-      <c r="K32" s="3" t="n">
+      <c r="K32" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="L32" s="10" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="M32" s="10" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="N32" s="10" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="O32" s="10" t="n">
+      <c r="L32" s="11" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="M32" s="11" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="N32" s="11" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="O32" s="11" t="n">
         <v>100</v>
       </c>
-      <c r="P32" s="10" t="n">
+      <c r="P32" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="Q32" s="10" t="n">
+      <c r="Q32" s="11" t="n">
         <v>31.1</v>
       </c>
-      <c r="R32" s="10" t="n">
+      <c r="R32" s="11" t="n">
         <v>22.7</v>
       </c>
-      <c r="S32" s="10" t="n">
+      <c r="S32" s="11" t="n">
         <v>27.5</v>
       </c>
-      <c r="T32" s="10" t="n">
+      <c r="T32" s="11" t="n">
         <v>61</v>
       </c>
-      <c r="U32" s="10" t="n">
+      <c r="U32" s="11" t="n">
         <v>17.5</v>
       </c>
-      <c r="V32" s="3" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="W32" s="12" t="n">
-        <v>83.8</v>
+      <c r="V32" s="11" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="W32" s="3" t="n">
+        <v>23.8</v>
       </c>
       <c r="X32" s="3" t="n">
         <v>27.2</v>
       </c>
       <c r="Y32" s="3" t="n">
-        <v>7641.6</v>
+        <v>746.6</v>
       </c>
       <c r="Z32" s="3" t="n">
-        <v>19.3</v>
+        <v>195.3</v>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -3228,61 +3230,61 @@
       <c r="C33" s="3" t="n">
         <v>213.3</v>
       </c>
-      <c r="D33" s="10" t="n">
+      <c r="D33" s="11" t="n">
         <v>29.2</v>
       </c>
-      <c r="E33" s="10" t="n">
+      <c r="E33" s="11" t="n">
         <v>19.6</v>
       </c>
-      <c r="F33" s="10" t="n">
+      <c r="F33" s="11" t="n">
         <v>24.4</v>
       </c>
-      <c r="G33" s="10" t="n">
+      <c r="G33" s="11" t="n">
         <v>9.6</v>
       </c>
       <c r="H33" s="3" t="n">
         <v>18.8</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="J33" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="K33" s="3" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="L33" s="10" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="M33" s="10" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="N33" s="10" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="O33" s="10" t="n">
-        <v>99</v>
-      </c>
-      <c r="P33" s="10" t="n">
+      <c r="K33" s="11" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L33" s="11" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="M33" s="11" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="N33" s="11" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="O33" s="11" t="n">
+        <v>99.40000000000001</v>
+      </c>
+      <c r="P33" s="11" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q33" s="10" t="n">
+      <c r="Q33" s="11" t="n">
         <v>28.9</v>
       </c>
-      <c r="R33" s="10" t="n">
+      <c r="R33" s="11" t="n">
         <v>23.1</v>
       </c>
-      <c r="S33" s="10" t="n">
+      <c r="S33" s="11" t="n">
         <v>28.2</v>
       </c>
-      <c r="T33" s="10" t="n">
+      <c r="T33" s="11" t="n">
         <v>70.90000000000001</v>
       </c>
-      <c r="U33" s="10" t="n">
+      <c r="U33" s="11" t="n">
         <v>11.5</v>
       </c>
-      <c r="V33" s="3" t="n">
+      <c r="V33" s="11" t="n">
         <v>25.6</v>
       </c>
       <c r="W33" s="3" t="n">
@@ -3292,10 +3294,10 @@
         <v>28.3</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>26.1</v>
+        <v>0.1</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>144.5</v>
+        <v>14.5</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3313,16 +3315,16 @@
       <c r="C34" s="3" t="n">
         <v>311.6</v>
       </c>
-      <c r="D34" s="10" t="n">
+      <c r="D34" s="11" t="n">
         <v>31.9</v>
       </c>
-      <c r="E34" s="10" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="F34" s="10" t="n">
-        <v>26.6</v>
-      </c>
-      <c r="G34" s="10" t="n">
+      <c r="E34" s="11" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="F34" s="11" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="G34" s="11" t="n">
         <v>10.5</v>
       </c>
       <c r="H34" s="3" t="n">
@@ -3332,42 +3334,42 @@
         <v>2</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="K34" s="3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K34" s="11" t="n">
         <v>0.2</v>
       </c>
-      <c r="L34" s="10" t="n">
+      <c r="L34" s="11" t="n">
         <v>21.8</v>
       </c>
-      <c r="M34" s="10" t="n">
+      <c r="M34" s="11" t="n">
         <v>21.7</v>
       </c>
-      <c r="N34" s="10" t="n">
+      <c r="N34" s="11" t="n">
         <v>25.9</v>
       </c>
-      <c r="O34" s="10" t="n">
+      <c r="O34" s="11" t="n">
         <v>99.40000000000001</v>
       </c>
-      <c r="P34" s="10" t="n">
+      <c r="P34" s="11" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q34" s="10" t="n">
+      <c r="Q34" s="11" t="n">
         <v>30.5</v>
       </c>
-      <c r="R34" s="10" t="n">
+      <c r="R34" s="11" t="n">
         <v>24.2</v>
       </c>
-      <c r="S34" s="10" t="n">
+      <c r="S34" s="11" t="n">
         <v>30.2</v>
       </c>
-      <c r="T34" s="10" t="n">
+      <c r="T34" s="11" t="n">
         <v>69.40000000000001</v>
       </c>
-      <c r="U34" s="10" t="n">
+      <c r="U34" s="11" t="n">
         <v>13.3</v>
       </c>
-      <c r="V34" s="3" t="n">
+      <c r="V34" s="11" t="n">
         <v>27.3</v>
       </c>
       <c r="W34" s="3" t="n">
@@ -3377,7 +3379,7 @@
         <v>29.7</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>82.8</v>
+        <v>82</v>
       </c>
       <c r="Z34" s="3" t="n">
         <v>16.5</v>
@@ -3396,18 +3398,18 @@
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>353.4</v>
-      </c>
-      <c r="D35" s="10" t="n">
+        <v>353.1</v>
+      </c>
+      <c r="D35" s="11" t="n">
         <v>31.1</v>
       </c>
-      <c r="E35" s="10" t="n">
-        <v>20.7</v>
-      </c>
-      <c r="F35" s="10" t="n">
+      <c r="E35" s="11" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="F35" s="11" t="n">
         <v>25.9</v>
       </c>
-      <c r="G35" s="10" t="n">
+      <c r="G35" s="11" t="n">
         <v>10.3</v>
       </c>
       <c r="H35" s="3" t="n">
@@ -3419,32 +3421,32 @@
       <c r="J35" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="K35" s="3" t="n">
+      <c r="K35" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="L35" s="10" t="n">
+      <c r="L35" s="11" t="n">
         <v>21.6</v>
       </c>
-      <c r="M35" s="10" t="n">
+      <c r="M35" s="11" t="n">
         <v>21.3</v>
       </c>
-      <c r="N35" s="10" t="n">
-        <v>25.1</v>
-      </c>
-      <c r="O35" s="10" t="n">
-        <v>97.2</v>
-      </c>
-      <c r="P35" s="10" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="Q35" s="10" t="n">
+      <c r="N35" s="11" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="O35" s="11" t="n">
+        <v>98.2</v>
+      </c>
+      <c r="P35" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q35" s="11" t="n">
         <v>31.1</v>
       </c>
-      <c r="R35" s="12" t="n">
-        <v>46.9</v>
+      <c r="R35" s="11" t="n">
+        <v>22.6</v>
       </c>
       <c r="S35" s="3" t="n">
-        <v>21.8</v>
+        <v>27.8</v>
       </c>
       <c r="T35" s="3" t="n">
         <v>61.3</v>
@@ -3452,19 +3454,19 @@
       <c r="U35" s="3" t="n">
         <v>17.4</v>
       </c>
-      <c r="V35" s="3" t="n">
+      <c r="V35" s="11" t="n">
         <v>27.8</v>
       </c>
-      <c r="W35" s="8" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="X35" s="3" t="n">
+      <c r="W35" s="11" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="X35" s="11" t="n">
         <v>28.9</v>
       </c>
-      <c r="Y35" s="3" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="Z35" s="3" t="n">
+      <c r="Y35" s="11" t="n">
+        <v>77.59999999999999</v>
+      </c>
+      <c r="Z35" s="11" t="n">
         <v>8.4</v>
       </c>
       <c r="AA35" s="3" t="inlineStr">
@@ -3483,16 +3485,16 @@
       <c r="C36" s="3" t="n">
         <v>430.7</v>
       </c>
-      <c r="D36" s="10" t="n">
+      <c r="D36" s="11" t="n">
         <v>32.1</v>
       </c>
-      <c r="E36" s="10" t="n">
+      <c r="E36" s="11" t="n">
         <v>20.9</v>
       </c>
-      <c r="F36" s="10" t="n">
+      <c r="F36" s="11" t="n">
         <v>26.5</v>
       </c>
-      <c r="G36" s="10" t="n">
+      <c r="G36" s="11" t="n">
         <v>11.2</v>
       </c>
       <c r="H36" s="3" t="n">
@@ -3504,53 +3506,53 @@
       <c r="J36" s="3" t="n">
         <v>4.4</v>
       </c>
-      <c r="K36" s="3" t="n">
+      <c r="K36" s="11" t="n">
         <v>30.6</v>
       </c>
-      <c r="L36" s="10" t="n">
+      <c r="L36" s="11" t="n">
         <v>21</v>
       </c>
-      <c r="M36" s="10" t="n">
+      <c r="M36" s="11" t="n">
         <v>20.7</v>
       </c>
-      <c r="N36" s="10" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="O36" s="10" t="n">
-        <v>97.5</v>
-      </c>
-      <c r="P36" s="10" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="Q36" s="10" t="n">
+      <c r="N36" s="11" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="O36" s="11" t="n">
+        <v>98.2</v>
+      </c>
+      <c r="P36" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q36" s="11" t="n">
         <v>32.1</v>
       </c>
-      <c r="R36" s="10" t="n">
+      <c r="R36" s="11" t="n">
         <v>23.9</v>
       </c>
-      <c r="S36" s="10" t="n">
+      <c r="S36" s="11" t="n">
         <v>29.7</v>
       </c>
-      <c r="T36" s="10" t="n">
+      <c r="T36" s="11" t="n">
         <v>62.2</v>
       </c>
-      <c r="U36" s="10" t="n">
+      <c r="U36" s="11" t="n">
         <v>18</v>
       </c>
-      <c r="V36" s="3" t="n">
+      <c r="V36" s="11" t="n">
         <v>28.7</v>
       </c>
-      <c r="W36" s="12" t="n">
-        <v>46.6</v>
+      <c r="W36" s="3" t="n">
+        <v>24.6</v>
       </c>
       <c r="X36" s="3" t="n">
-        <v>28.8</v>
+        <v>28.3</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>72</v>
+        <v>172</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>1411</v>
+        <v>111</v>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -3568,16 +3570,16 @@
       <c r="C37" s="3" t="n">
         <v>1693.7</v>
       </c>
-      <c r="D37" s="10" t="n">
+      <c r="D37" s="11" t="n">
         <v>155.4</v>
       </c>
-      <c r="E37" s="10" t="n">
+      <c r="E37" s="11" t="n">
         <v>102</v>
       </c>
-      <c r="F37" s="10" t="n">
+      <c r="F37" s="11" t="n">
         <v>128.7</v>
       </c>
-      <c r="G37" s="10" t="n">
+      <c r="G37" s="11" t="n">
         <v>53.4</v>
       </c>
       <c r="H37" s="3" t="n">
@@ -3589,14 +3591,14 @@
       <c r="J37" s="3" t="n">
         <v>18.1</v>
       </c>
-      <c r="K37" s="13" t="n">
+      <c r="K37" s="11" t="n">
         <v>35.6</v>
       </c>
-      <c r="L37" s="10" t="n">
-        <v>105</v>
-      </c>
-      <c r="M37" s="10" t="n">
-        <v>104.2</v>
+      <c r="L37" s="11" t="n">
+        <v>106.3</v>
+      </c>
+      <c r="M37" s="11" t="n">
+        <v>105.2</v>
       </c>
       <c r="N37" s="3" t="n">
         <v>124.1</v>
@@ -3605,24 +3607,24 @@
         <v>492.7</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="Q37" s="10" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Q37" s="11" t="n">
         <v>153.7</v>
       </c>
-      <c r="R37" s="13" t="n">
-        <v>126.2</v>
+      <c r="R37" s="11" t="n">
+        <v>116.5</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>143.1</v>
+        <v>1143.1</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>324.8</v>
+        <v>2324.8</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="V37" s="13" t="n">
+        <v>79.7</v>
+      </c>
+      <c r="V37" s="11" t="n">
         <v>136.8</v>
       </c>
       <c r="W37" s="13" t="n">
@@ -3632,10 +3634,10 @@
         <v>122.4</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>3928.2</v>
+        <v>392.2</v>
       </c>
       <c r="Z37" s="3" t="n">
-        <v>39.7</v>
+        <v>139.7</v>
       </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
@@ -3653,16 +3655,16 @@
       <c r="C38" s="3" t="n">
         <v>338.7</v>
       </c>
-      <c r="D38" s="10" t="n">
+      <c r="D38" s="11" t="n">
         <v>31</v>
       </c>
-      <c r="E38" s="10" t="n">
+      <c r="E38" s="11" t="n">
         <v>20.4</v>
       </c>
-      <c r="F38" s="10" t="n">
+      <c r="F38" s="11" t="n">
         <v>25.7</v>
       </c>
-      <c r="G38" s="10" t="n">
+      <c r="G38" s="11" t="n">
         <v>10.6</v>
       </c>
       <c r="H38" s="3" t="n">
@@ -3675,47 +3677,47 @@
         <v>3.6</v>
       </c>
       <c r="K38" s="3" t="inlineStr"/>
-      <c r="L38" s="10" t="n">
+      <c r="L38" s="11" t="n">
         <v>21.2</v>
       </c>
-      <c r="M38" s="10" t="n">
+      <c r="M38" s="11" t="n">
         <v>21</v>
       </c>
-      <c r="N38" s="10" t="n">
+      <c r="N38" s="11" t="n">
         <v>24.9</v>
       </c>
-      <c r="O38" s="10" t="n">
+      <c r="O38" s="11" t="n">
         <v>98.8</v>
       </c>
-      <c r="P38" s="10" t="n">
+      <c r="P38" s="11" t="n">
         <v>0.3</v>
       </c>
-      <c r="Q38" s="10" t="n">
+      <c r="Q38" s="11" t="n">
         <v>30.7</v>
       </c>
-      <c r="R38" s="13" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="S38" s="3" t="n">
+      <c r="R38" s="11" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="S38" s="11" t="n">
         <v>28.6</v>
       </c>
-      <c r="T38" s="3" t="n">
-        <v>69</v>
-      </c>
-      <c r="U38" s="3" t="n">
+      <c r="T38" s="11" t="n">
+        <v>65</v>
+      </c>
+      <c r="U38" s="11" t="n">
         <v>15.5</v>
       </c>
-      <c r="V38" s="13" t="n">
+      <c r="V38" s="11" t="n">
         <v>27.4</v>
       </c>
       <c r="W38" s="13" t="n">
         <v>24.3</v>
       </c>
       <c r="X38" s="3" t="n">
-        <v>88.5</v>
+        <v>28.5</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>78</v>
+        <v>29.1</v>
       </c>
       <c r="Z38" s="3" t="n">
         <v>7.9</v>
@@ -3736,19 +3738,19 @@
       <c r="C39" s="3" t="n">
         <v>332.5</v>
       </c>
-      <c r="D39" s="10" t="n">
+      <c r="D39" s="11" t="n">
         <v>31.9</v>
       </c>
-      <c r="E39" s="10" t="n">
+      <c r="E39" s="11" t="n">
         <v>20.2</v>
       </c>
-      <c r="F39" s="10" t="n">
+      <c r="F39" s="11" t="n">
         <v>26.1</v>
       </c>
-      <c r="G39" s="8" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="H39" s="8" t="n">
+      <c r="G39" s="11" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="H39" s="3" t="n">
         <v>19.3</v>
       </c>
       <c r="I39" s="3" t="n">
@@ -3758,52 +3760,52 @@
         <v>3</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="L39" s="10" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L39" s="11" t="n">
         <v>21</v>
       </c>
-      <c r="M39" s="10" t="n">
+      <c r="M39" s="11" t="n">
         <v>20.9</v>
       </c>
-      <c r="N39" s="10" t="n">
+      <c r="N39" s="11" t="n">
         <v>24.6</v>
       </c>
-      <c r="O39" s="10" t="n">
+      <c r="O39" s="11" t="n">
         <v>99</v>
       </c>
-      <c r="P39" s="10" t="n">
+      <c r="P39" s="11" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q39" s="12" t="n">
-        <v>91.90000000000001</v>
-      </c>
-      <c r="R39" s="10" t="n">
+      <c r="Q39" s="11" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="R39" s="11" t="n">
         <v>26</v>
       </c>
-      <c r="S39" s="3" t="n">
-        <v>29.8</v>
-      </c>
-      <c r="T39" s="3" t="n">
-        <v>163.2</v>
-      </c>
-      <c r="U39" s="3" t="n">
-        <v>11.3</v>
+      <c r="S39" s="11" t="n">
+        <v>33.6</v>
+      </c>
+      <c r="T39" s="11" t="n">
+        <v>71</v>
+      </c>
+      <c r="U39" s="11" t="n">
+        <v>13.7</v>
       </c>
       <c r="V39" s="3" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="W39" s="10" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="W39" s="11" t="n">
         <v>23.2</v>
       </c>
       <c r="X39" s="3" t="n">
-        <v>2.7</v>
+        <v>27.5</v>
       </c>
       <c r="Y39" s="3" t="n">
         <v>88.2</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>82.59999999999999</v>
+        <v>23.6</v>
       </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -3819,18 +3821,18 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>153.7</v>
-      </c>
-      <c r="D40" s="10" t="n">
-        <v>33</v>
-      </c>
-      <c r="E40" s="10" t="n">
+        <v>1453.7</v>
+      </c>
+      <c r="D40" s="11" t="n">
+        <v>32.9</v>
+      </c>
+      <c r="E40" s="11" t="n">
         <v>18.8</v>
       </c>
-      <c r="F40" s="10" t="n">
+      <c r="F40" s="11" t="n">
         <v>25.9</v>
       </c>
-      <c r="G40" s="10" t="n">
+      <c r="G40" s="11" t="n">
         <v>14.1</v>
       </c>
       <c r="H40" s="3" t="n">
@@ -3845,50 +3847,50 @@
       <c r="K40" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L40" s="10" t="n">
+      <c r="L40" s="11" t="n">
         <v>19.8</v>
       </c>
-      <c r="M40" s="10" t="n">
+      <c r="M40" s="11" t="n">
         <v>19.6</v>
       </c>
-      <c r="N40" s="10" t="n">
+      <c r="N40" s="11" t="n">
         <v>22.6</v>
       </c>
-      <c r="O40" s="10" t="n">
+      <c r="O40" s="11" t="n">
         <v>97.8</v>
       </c>
-      <c r="P40" s="10" t="n">
+      <c r="P40" s="11" t="n">
         <v>0.5</v>
       </c>
-      <c r="Q40" s="10" t="n">
+      <c r="Q40" s="11" t="n">
         <v>32.8</v>
       </c>
-      <c r="R40" s="10" t="n">
+      <c r="R40" s="11" t="n">
         <v>23.7</v>
       </c>
-      <c r="S40" s="10" t="n">
+      <c r="S40" s="11" t="n">
         <v>29.3</v>
       </c>
-      <c r="T40" s="10" t="n">
+      <c r="T40" s="11" t="n">
         <v>59.2</v>
       </c>
-      <c r="U40" s="10" t="n">
+      <c r="U40" s="11" t="n">
         <v>20.2</v>
       </c>
-      <c r="V40" s="3" t="n">
+      <c r="V40" s="11" t="n">
         <v>27.8</v>
       </c>
-      <c r="W40" s="10" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="X40" s="8" t="n">
-        <v>86.90000000000001</v>
-      </c>
-      <c r="Y40" s="3" t="n">
+      <c r="W40" s="11" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="X40" s="11" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="Y40" s="11" t="n">
         <v>72</v>
       </c>
-      <c r="Z40" s="3" t="n">
-        <v>101.6</v>
+      <c r="Z40" s="11" t="n">
+        <v>10.4</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3904,18 +3906,18 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>8985.6</v>
-      </c>
-      <c r="D41" s="10" t="n">
+        <v>265.6</v>
+      </c>
+      <c r="D41" s="11" t="n">
         <v>31.6</v>
       </c>
-      <c r="E41" s="10" t="n">
+      <c r="E41" s="11" t="n">
         <v>19.6</v>
       </c>
-      <c r="F41" s="10" t="n">
+      <c r="F41" s="11" t="n">
         <v>25.6</v>
       </c>
-      <c r="G41" s="10" t="n">
+      <c r="G41" s="11" t="n">
         <v>12</v>
       </c>
       <c r="H41" s="3" t="n">
@@ -3928,52 +3930,52 @@
         <v>1.6</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="L41" s="10" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L41" s="11" t="n">
         <v>19.9</v>
       </c>
-      <c r="M41" s="10" t="n">
+      <c r="M41" s="11" t="n">
         <v>19.8</v>
       </c>
-      <c r="N41" s="10" t="n">
+      <c r="N41" s="11" t="n">
         <v>23</v>
       </c>
-      <c r="O41" s="10" t="n">
+      <c r="O41" s="11" t="n">
         <v>99</v>
       </c>
-      <c r="P41" s="10" t="n">
+      <c r="P41" s="11" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q41" s="3" t="n">
+      <c r="Q41" s="11" t="n">
         <v>22.3</v>
       </c>
-      <c r="R41" s="10" t="n">
+      <c r="R41" s="11" t="n">
         <v>21.4</v>
       </c>
-      <c r="S41" s="8" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="T41" s="3" t="n">
-        <v>92.3</v>
-      </c>
-      <c r="U41" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="V41" s="3" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="W41" s="10" t="n">
+      <c r="S41" s="11" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="T41" s="11" t="n">
+        <v>94.59999999999999</v>
+      </c>
+      <c r="U41" s="11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V41" s="8" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="W41" s="11" t="n">
         <v>23.4</v>
       </c>
       <c r="X41" s="3" t="n">
-        <v>98</v>
+        <v>28</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>90.40000000000001</v>
+        <v>190.5</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>8.9</v>
+        <v>2.9</v>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
@@ -3989,18 +3991,18 @@
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>836.3</v>
-      </c>
-      <c r="D42" s="10" t="n">
+        <v>236.3</v>
+      </c>
+      <c r="D42" s="11" t="n">
         <v>31.6</v>
       </c>
-      <c r="E42" s="10" t="n">
+      <c r="E42" s="11" t="n">
         <v>20.3</v>
       </c>
-      <c r="F42" s="10" t="n">
+      <c r="F42" s="11" t="n">
         <v>25.9</v>
       </c>
-      <c r="G42" s="10" t="n">
+      <c r="G42" s="11" t="n">
         <v>11.3</v>
       </c>
       <c r="H42" s="3" t="n">
@@ -4009,57 +4011,55 @@
       <c r="I42" s="3" t="n">
         <v>0.7</v>
       </c>
-      <c r="J42" s="8" t="n">
-        <v>8</v>
+      <c r="J42" s="3" t="n">
+        <v>1.2</v>
       </c>
       <c r="K42" s="3" t="n">
-        <v>28.4</v>
-      </c>
-      <c r="L42" s="3" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="L42" s="11" t="n">
         <v>21.9</v>
       </c>
-      <c r="M42" s="3" t="n">
+      <c r="M42" s="11" t="n">
         <v>21.8</v>
       </c>
-      <c r="N42" s="3" t="n">
-        <v>26</v>
-      </c>
-      <c r="O42" s="3" t="n">
-        <v>89</v>
-      </c>
-      <c r="P42" s="3" t="n">
+      <c r="N42" s="11" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="O42" s="11" t="n">
+        <v>99.40000000000001</v>
+      </c>
+      <c r="P42" s="11" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q42" s="10" t="n">
+      <c r="Q42" s="11" t="n">
         <v>24.1</v>
       </c>
-      <c r="R42" s="10" t="n">
+      <c r="R42" s="11" t="n">
         <v>23.8</v>
       </c>
-      <c r="S42" s="10" t="n">
-        <v>29.3</v>
-      </c>
-      <c r="T42" s="10" t="n">
-        <v>97.7</v>
-      </c>
-      <c r="U42" s="10" t="n">
-        <v>0.8</v>
+      <c r="S42" s="11" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="T42" s="11" t="n">
+        <v>98.2</v>
+      </c>
+      <c r="U42" s="11" t="n">
+        <v>0.5</v>
       </c>
       <c r="V42" s="3" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="W42" s="10" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="X42" s="8" t="n">
-        <v>828.2</v>
+        <v>24.7</v>
+      </c>
+      <c r="W42" s="11" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="X42" s="3" t="n">
+        <v>28.2</v>
       </c>
       <c r="Y42" s="3" t="n">
         <v>90.59999999999999</v>
       </c>
-      <c r="Z42" s="3" t="n">
-        <v>2.9</v>
-      </c>
+      <c r="Z42" s="3" t="inlineStr"/>
       <c r="AA42" s="3" t="inlineStr">
         <is>
           <t>29</t>
@@ -4076,16 +4076,16 @@
       <c r="C43" s="3" t="n">
         <v>372.2</v>
       </c>
-      <c r="D43" s="10" t="n">
-        <v>28.1</v>
-      </c>
-      <c r="E43" s="10" t="n">
+      <c r="D43" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="E43" s="11" t="n">
         <v>21.3</v>
       </c>
-      <c r="F43" s="10" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="G43" s="3" t="n">
+      <c r="F43" s="11" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="G43" s="11" t="n">
         <v>8.699999999999999</v>
       </c>
       <c r="H43" s="3" t="n">
@@ -4100,49 +4100,49 @@
       <c r="K43" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L43" s="3" t="n">
+      <c r="L43" s="11" t="n">
         <v>21.6</v>
       </c>
-      <c r="M43" s="3" t="n">
+      <c r="M43" s="11" t="n">
         <v>21.5</v>
       </c>
-      <c r="N43" s="3" t="n">
+      <c r="N43" s="11" t="n">
         <v>25.6</v>
       </c>
-      <c r="O43" s="3" t="n">
-        <v>99</v>
-      </c>
-      <c r="P43" s="3" t="n">
+      <c r="O43" s="11" t="n">
+        <v>99.40000000000001</v>
+      </c>
+      <c r="P43" s="11" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q43" s="3" t="n">
+      <c r="Q43" s="11" t="n">
         <v>29.1</v>
       </c>
-      <c r="R43" s="10" t="n">
+      <c r="R43" s="11" t="n">
         <v>25.5</v>
       </c>
-      <c r="S43" s="3" t="n">
-        <v>80.40000000000001</v>
-      </c>
-      <c r="T43" s="3" t="n">
-        <v>75.59999999999999</v>
-      </c>
-      <c r="U43" s="3" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="V43" s="10" t="n">
+      <c r="S43" s="11" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="T43" s="11" t="n">
+        <v>81</v>
+      </c>
+      <c r="U43" s="11" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="V43" s="3" t="n">
         <v>27.8</v>
       </c>
-      <c r="W43" s="10" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="X43" s="10" t="n">
-        <v>29.1</v>
-      </c>
-      <c r="Y43" s="10" t="n">
+      <c r="W43" s="11" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="X43" s="3" t="n">
+        <v>34.1</v>
+      </c>
+      <c r="Y43" s="3" t="n">
         <v>78</v>
       </c>
-      <c r="Z43" s="10" t="n">
+      <c r="Z43" s="3" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AA43" s="3" t="inlineStr">
@@ -4161,71 +4161,71 @@
       <c r="C44" s="3" t="n">
         <v>365.9</v>
       </c>
-      <c r="D44" s="10" t="n">
+      <c r="D44" s="11" t="n">
         <v>32.5</v>
       </c>
-      <c r="E44" s="10" t="n">
+      <c r="E44" s="11" t="n">
         <v>21.3</v>
       </c>
-      <c r="F44" s="10" t="n">
+      <c r="F44" s="11" t="n">
         <v>26.9</v>
       </c>
-      <c r="G44" s="10" t="n">
+      <c r="G44" s="11" t="n">
         <v>11.3</v>
       </c>
       <c r="H44" s="8" t="n">
-        <v>19.4</v>
+        <v>49.4</v>
       </c>
       <c r="I44" s="3" t="n">
         <v>1.9</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>9.6</v>
+        <v>8.6</v>
       </c>
       <c r="K44" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L44" s="10" t="n">
+      <c r="L44" s="11" t="n">
         <v>22.3</v>
       </c>
-      <c r="M44" s="10" t="n">
+      <c r="M44" s="11" t="n">
         <v>22.3</v>
       </c>
-      <c r="N44" s="10" t="n">
+      <c r="N44" s="11" t="n">
         <v>26.9</v>
       </c>
-      <c r="O44" s="10" t="n">
+      <c r="O44" s="11" t="n">
         <v>100</v>
       </c>
-      <c r="P44" s="10" t="n">
+      <c r="P44" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="Q44" s="10" t="n">
+      <c r="Q44" s="11" t="n">
         <v>32.6</v>
       </c>
-      <c r="R44" s="10" t="n">
+      <c r="R44" s="11" t="n">
         <v>24.3</v>
       </c>
-      <c r="S44" s="10" t="n">
+      <c r="S44" s="11" t="n">
         <v>30.4</v>
       </c>
-      <c r="T44" s="10" t="n">
+      <c r="T44" s="11" t="n">
         <v>62</v>
       </c>
-      <c r="U44" s="10" t="n">
+      <c r="U44" s="11" t="n">
         <v>18.6</v>
       </c>
       <c r="V44" s="3" t="n">
-        <v>28.3</v>
-      </c>
-      <c r="W44" s="10" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="W44" s="11" t="n">
         <v>26.3</v>
       </c>
-      <c r="X44" s="8" t="n">
-        <v>28.2</v>
+      <c r="X44" s="3" t="n">
+        <v>32.2</v>
       </c>
       <c r="Y44" s="3" t="n">
-        <v>84.40000000000001</v>
+        <v>184.4</v>
       </c>
       <c r="Z44" s="3" t="n">
         <v>16</v>
@@ -4244,40 +4244,40 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>2026.2</v>
-      </c>
-      <c r="D45" s="10" t="n">
-        <v>188.7</v>
-      </c>
-      <c r="E45" s="10" t="n">
+        <v>202.6</v>
+      </c>
+      <c r="D45" s="11" t="n">
+        <v>190.5</v>
+      </c>
+      <c r="E45" s="11" t="n">
         <v>121.5</v>
       </c>
-      <c r="F45" s="10" t="n">
-        <v>155.1</v>
+      <c r="F45" s="11" t="n">
+        <v>156.1</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>2.1</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>1114.2</v>
+        <v>1114.7</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>11</v>
+        <v>101.2</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>118.4</v>
+        <v>18.4</v>
       </c>
       <c r="K45" s="13" t="n">
-        <v>783.6</v>
-      </c>
-      <c r="L45" s="13" t="n">
-        <v>1166.5</v>
-      </c>
-      <c r="M45" s="13" t="n">
-        <v>123.9</v>
+        <v>18.3</v>
+      </c>
+      <c r="L45" s="11" t="n">
+        <v>126.5</v>
+      </c>
+      <c r="M45" s="11" t="n">
+        <v>125.9</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>1148.8</v>
+        <v>1148.7</v>
       </c>
       <c r="O45" s="3" t="n">
         <v>293.8</v>
@@ -4285,35 +4285,35 @@
       <c r="P45" s="3" t="n">
         <v>1.3</v>
       </c>
-      <c r="Q45" s="13" t="n">
+      <c r="Q45" s="11" t="n">
         <v>172.8</v>
       </c>
-      <c r="R45" s="10" t="n">
+      <c r="R45" s="11" t="n">
         <v>149.1</v>
       </c>
-      <c r="S45" s="3" t="n">
-        <v>121.1</v>
-      </c>
-      <c r="T45" s="3" t="n">
-        <v>1230</v>
-      </c>
-      <c r="U45" s="3" t="n">
-        <v>68.59999999999999</v>
+      <c r="S45" s="11" t="n">
+        <v>5018.5</v>
+      </c>
+      <c r="T45" s="11" t="n">
+        <v>53.6</v>
+      </c>
+      <c r="U45" s="11" t="n">
+        <v>4347.2</v>
       </c>
       <c r="V45" s="13" t="n">
         <v>158.1</v>
       </c>
-      <c r="W45" s="10" t="n">
-        <v>142.8</v>
+      <c r="W45" s="11" t="n">
+        <v>144.9</v>
       </c>
       <c r="X45" s="3" t="n">
         <v>172.2</v>
       </c>
       <c r="Y45" s="3" t="n">
-        <v>503.4</v>
+        <v>583.7</v>
       </c>
       <c r="Z45" s="3" t="n">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -4331,17 +4331,17 @@
       <c r="C46" s="3" t="n">
         <v>237.6</v>
       </c>
-      <c r="D46" s="10" t="n">
+      <c r="D46" s="11" t="n">
         <v>31.7</v>
       </c>
-      <c r="E46" s="10" t="n">
+      <c r="E46" s="11" t="n">
         <v>20.2</v>
       </c>
-      <c r="F46" s="10" t="n">
+      <c r="F46" s="11" t="n">
         <v>26</v>
       </c>
-      <c r="G46" s="3" t="n">
-        <v>21.5</v>
+      <c r="G46" s="11" t="n">
+        <v>11.5</v>
       </c>
       <c r="H46" s="3" t="n">
         <v>19.1</v>
@@ -4352,33 +4352,35 @@
       <c r="J46" s="3" t="n">
         <v>3.1</v>
       </c>
-      <c r="K46" s="3" t="inlineStr"/>
-      <c r="L46" s="13" t="n">
+      <c r="K46" s="3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L46" s="11" t="n">
         <v>21.1</v>
       </c>
-      <c r="M46" s="13" t="n">
-        <v>20</v>
-      </c>
-      <c r="N46" s="3" t="n">
+      <c r="M46" s="11" t="n">
+        <v>21</v>
+      </c>
+      <c r="N46" s="11" t="n">
         <v>24.8</v>
       </c>
-      <c r="O46" s="3" t="n">
-        <v>199</v>
-      </c>
-      <c r="P46" s="3" t="n">
+      <c r="O46" s="11" t="n">
+        <v>99</v>
+      </c>
+      <c r="P46" s="11" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q46" s="13" t="n">
+      <c r="Q46" s="11" t="n">
         <v>28.8</v>
       </c>
-      <c r="R46" s="10" t="n">
+      <c r="R46" s="11" t="n">
         <v>24.1</v>
       </c>
       <c r="S46" s="3" t="n">
         <v>29</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>22.9</v>
+        <v>75</v>
       </c>
       <c r="U46" s="3" t="n">
         <v>11.4</v>
@@ -4386,17 +4388,17 @@
       <c r="V46" s="13" t="n">
         <v>26.3</v>
       </c>
-      <c r="W46" s="10" t="n">
+      <c r="W46" s="11" t="n">
         <v>24.1</v>
       </c>
       <c r="X46" s="3" t="n">
         <v>28.7</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>88.8</v>
+        <v>823.9</v>
       </c>
       <c r="Z46" s="3" t="n">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>

--- a/results/05_transient_transcription_output/203/203_196905_SF.JPG_stage_recalc_multi_day_tot_and_avgs.xlsx
+++ b/results/05_transient_transcription_output/203/203_196905_SF.JPG_stage_recalc_multi_day_tot_and_avgs.xlsx
@@ -26,7 +26,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -55,6 +55,18 @@
       <patternFill patternType="solid">
         <fgColor rgb="0075696F"/>
         <bgColor rgb="0075696F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC0CB"/>
+        <bgColor rgb="00FFC0CB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -125,7 +137,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -155,6 +167,12 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -162,6 +180,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -798,7 +819,7 @@
       <c r="J4" s="3" t="n">
         <v>9.9</v>
       </c>
-      <c r="K4" s="3" t="n">
+      <c r="K4" s="10" t="n">
         <v>0</v>
       </c>
       <c r="L4" s="3" t="n">
@@ -883,7 +904,7 @@
       <c r="J5" s="3" t="n">
         <v>5.5</v>
       </c>
-      <c r="K5" s="3" t="n">
+      <c r="K5" s="10" t="n">
         <v>0</v>
       </c>
       <c r="L5" s="3" t="n">
@@ -968,7 +989,7 @@
       <c r="J6" s="3" t="n">
         <v>7.2</v>
       </c>
-      <c r="K6" s="3" t="n">
+      <c r="K6" s="10" t="n">
         <v>0</v>
       </c>
       <c r="L6" s="3" t="n">
@@ -1053,7 +1074,7 @@
       <c r="J7" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="K7" s="3" t="n">
+      <c r="K7" s="10" t="n">
         <v>0</v>
       </c>
       <c r="L7" s="3" t="n">
@@ -1138,7 +1159,7 @@
       <c r="J8" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="K8" s="3" t="n">
+      <c r="K8" s="10" t="n">
         <v>30.9</v>
       </c>
       <c r="L8" s="3" t="n">
@@ -1223,7 +1244,7 @@
       <c r="J9" s="3" t="n">
         <v>27.5</v>
       </c>
-      <c r="K9" s="3" t="n">
+      <c r="K9" s="10" t="n">
         <v>30.9</v>
       </c>
       <c r="L9" s="3" t="n">
@@ -1814,7 +1835,7 @@
       <c r="J16" s="3" t="n">
         <v>19.4</v>
       </c>
-      <c r="K16" s="3" t="n"/>
+      <c r="K16" s="13" t="n"/>
       <c r="L16" s="3" t="n"/>
       <c r="M16" s="3" t="n">
         <v>109.5</v>
@@ -1978,7 +1999,7 @@
       <c r="J18" s="3" t="n">
         <v>14.3</v>
       </c>
-      <c r="K18" s="3" t="n"/>
+      <c r="K18" s="14" t="n"/>
       <c r="L18" s="3" t="n">
         <v>22.1</v>
       </c>
@@ -2401,7 +2422,7 @@
       <c r="J23" s="3" t="n">
         <v>19.3</v>
       </c>
-      <c r="K23" s="3" t="n">
+      <c r="K23" s="18" t="n">
         <v>7.7</v>
       </c>
       <c r="L23" s="3" t="n">
@@ -2996,7 +3017,7 @@
       <c r="J30" s="3" t="n">
         <v>111</v>
       </c>
-      <c r="K30" s="3" t="n">
+      <c r="K30" s="18" t="n">
         <v>38.8</v>
       </c>
       <c r="L30" s="3" t="n">
@@ -3591,7 +3612,7 @@
       <c r="J37" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="K37" s="3" t="n">
+      <c r="K37" s="18" t="n">
         <v>35.6</v>
       </c>
       <c r="L37" s="3" t="n">
@@ -4271,7 +4292,7 @@
       <c r="J45" s="3" t="n">
         <v>18.8</v>
       </c>
-      <c r="K45" s="3" t="n">
+      <c r="K45" s="18" t="n">
         <v>0</v>
       </c>
       <c r="L45" s="3" t="n">
